--- a/cronograma/CRONOGRAMA_26-27_PROVISIONAL.xlsx
+++ b/cronograma/CRONOGRAMA_26-27_PROVISIONAL.xlsx
@@ -30298,7 +30298,12 @@
       <c r="AG306" s="156" t="n"/>
       <c r="AH306" s="142" t="n"/>
       <c r="AI306" s="500" t="n">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="AK306" s="877" t="inlineStr">
+        <is>
+          <t>Festius: 12/10 Festa Nacional d'Espanya (Nacional)</t>
+        </is>
       </c>
     </row>
     <row r="307" ht="51" customHeight="1" s="757">
@@ -30431,7 +30436,7 @@
       <c r="L308" s="879" t="n"/>
       <c r="M308" s="879" t="n"/>
       <c r="N308" s="756" t="n"/>
-      <c r="O308" s="756" t="n"/>
+      <c r="O308" s="878" t="n"/>
       <c r="P308" s="756" t="n"/>
       <c r="Q308" s="756" t="n"/>
       <c r="R308" s="756" t="n"/>
@@ -30472,7 +30477,7 @@
       <c r="L309" s="879" t="n"/>
       <c r="M309" s="879" t="n"/>
       <c r="N309" s="756" t="n"/>
-      <c r="O309" s="756" t="n"/>
+      <c r="O309" s="878" t="n"/>
       <c r="P309" s="756" t="n"/>
       <c r="Q309" s="756" t="n"/>
       <c r="R309" s="756" t="n"/>
@@ -30513,7 +30518,7 @@
       <c r="L310" s="881" t="n"/>
       <c r="M310" s="881" t="n"/>
       <c r="N310" s="778" t="n"/>
-      <c r="O310" s="778" t="n"/>
+      <c r="O310" s="880" t="n"/>
       <c r="P310" s="778" t="n"/>
       <c r="Q310" s="778" t="n"/>
       <c r="R310" s="778" t="n"/>
@@ -30554,7 +30559,7 @@
       <c r="L311" s="879" t="n"/>
       <c r="M311" s="879" t="n"/>
       <c r="N311" s="756" t="n"/>
-      <c r="O311" s="756" t="n"/>
+      <c r="O311" s="878" t="n"/>
       <c r="P311" s="756" t="n"/>
       <c r="Q311" s="756" t="n"/>
       <c r="R311" s="756" t="n"/>
@@ -30595,7 +30600,7 @@
       <c r="L312" s="879" t="n"/>
       <c r="M312" s="879" t="n"/>
       <c r="N312" s="756" t="n"/>
-      <c r="O312" s="756" t="n"/>
+      <c r="O312" s="878" t="n"/>
       <c r="P312" s="756" t="n"/>
       <c r="Q312" s="756" t="n"/>
       <c r="R312" s="756" t="n"/>
@@ -30635,7 +30640,7 @@
       <c r="L313" s="881" t="n"/>
       <c r="M313" s="881" t="n"/>
       <c r="N313" s="778" t="n"/>
-      <c r="O313" s="778" t="n"/>
+      <c r="O313" s="880" t="n"/>
       <c r="P313" s="778" t="n"/>
       <c r="Q313" s="778" t="n"/>
       <c r="R313" s="778" t="n"/>
@@ -30675,7 +30680,7 @@
       <c r="L314" s="879" t="n"/>
       <c r="M314" s="879" t="n"/>
       <c r="N314" s="755" t="n"/>
-      <c r="O314" s="755" t="n"/>
+      <c r="O314" s="882" t="n"/>
       <c r="P314" s="756" t="n"/>
       <c r="Q314" s="756" t="n"/>
       <c r="R314" s="755" t="n"/>
@@ -30715,7 +30720,7 @@
       <c r="L315" s="879" t="n"/>
       <c r="M315" s="879" t="n"/>
       <c r="N315" s="756" t="n"/>
-      <c r="O315" s="756" t="n"/>
+      <c r="O315" s="878" t="n"/>
       <c r="P315" s="756" t="n"/>
       <c r="Q315" s="756" t="n"/>
       <c r="R315" s="756" t="n"/>
@@ -30755,7 +30760,7 @@
       <c r="L316" s="879" t="n"/>
       <c r="M316" s="879" t="n"/>
       <c r="N316" s="756" t="n"/>
-      <c r="O316" s="756" t="n"/>
+      <c r="O316" s="878" t="n"/>
       <c r="P316" s="756" t="n"/>
       <c r="Q316" s="756" t="n"/>
       <c r="R316" s="756" t="n"/>
@@ -33436,7 +33441,7 @@
     <row r="36">
       <c r="A36" s="916" t="inlineStr">
         <is>
-          <t>• Setembre-desembre 2027: festius i vacances del CALENDARI_LABORAL_2027 (els festius locals 04/09 i 15/09 hi consten com 'a omplir'; el 12/10 no hi apareix com a festiu).</t>
+          <t>• Setembre-desembre 2027: festius i vacances del CALENDARI_LABORAL_2027 (els festius locals 04/09 i 15/09 hi consten com 'a omplir'). S'hi afegeix el 12/10 com a festiu.</t>
         </is>
       </c>
     </row>

--- a/cronograma/CRONOGRAMA_26-27_PROVISIONAL.xlsx
+++ b/cronograma/CRONOGRAMA_26-27_PROVISIONAL.xlsx
@@ -1119,12 +1119,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="2" tint="-0.249977111117893"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -3597,8 +3597,8 @@
     <xf numFmtId="0" fontId="0" fillId="92" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="91" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="92" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="91" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="91" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="92" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="92" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="93" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="93" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="93" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -29775,11 +29775,11 @@
       <c r="AG293" s="156" t="n"/>
       <c r="AH293" s="142" t="n"/>
       <c r="AI293" s="500" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK293" s="877" t="inlineStr">
         <is>
-          <t>Festius: 04/09 Festiu local 1 (a omplir) (Local) · 11/09 Diada Nacional de Catalunya (Autonòmic) · 15/09 Festiu local 2 (a omplir) (Local)</t>
+          <t>Festius: 11/09 Diada Nacional de Catalunya (Autonòmic)</t>
         </is>
       </c>
     </row>
@@ -29904,28 +29904,28 @@
       <c r="E295" s="756" t="n"/>
       <c r="F295" s="756" t="n"/>
       <c r="G295" s="878" t="n"/>
-      <c r="H295" s="879" t="n"/>
+      <c r="H295" s="878" t="n"/>
       <c r="I295" s="756" t="n"/>
       <c r="J295" s="756" t="n"/>
       <c r="K295" s="756" t="n"/>
       <c r="L295" s="756" t="n"/>
       <c r="M295" s="756" t="n"/>
-      <c r="N295" s="878" t="n"/>
-      <c r="O295" s="879" t="n"/>
+      <c r="N295" s="879" t="n"/>
+      <c r="O295" s="878" t="n"/>
       <c r="P295" s="756" t="n"/>
       <c r="Q295" s="756" t="n"/>
-      <c r="R295" s="878" t="n"/>
+      <c r="R295" s="756" t="n"/>
       <c r="S295" s="756" t="n"/>
       <c r="T295" s="756" t="n"/>
-      <c r="U295" s="879" t="n"/>
-      <c r="V295" s="879" t="n"/>
+      <c r="U295" s="878" t="n"/>
+      <c r="V295" s="878" t="n"/>
       <c r="W295" s="756" t="n"/>
       <c r="X295" s="756" t="n"/>
       <c r="Y295" s="756" t="n"/>
       <c r="Z295" s="756" t="n"/>
       <c r="AA295" s="756" t="n"/>
-      <c r="AB295" s="879" t="n"/>
-      <c r="AC295" s="879" t="n"/>
+      <c r="AB295" s="878" t="n"/>
+      <c r="AC295" s="878" t="n"/>
       <c r="AD295" s="756" t="n"/>
       <c r="AE295" s="756" t="n"/>
       <c r="AF295" s="756" t="n"/>
@@ -29945,28 +29945,28 @@
       <c r="E296" s="756" t="n"/>
       <c r="F296" s="756" t="n"/>
       <c r="G296" s="878" t="n"/>
-      <c r="H296" s="879" t="n"/>
+      <c r="H296" s="878" t="n"/>
       <c r="I296" s="756" t="n"/>
       <c r="J296" s="756" t="n"/>
       <c r="K296" s="756" t="n"/>
       <c r="L296" s="756" t="n"/>
       <c r="M296" s="756" t="n"/>
-      <c r="N296" s="878" t="n"/>
-      <c r="O296" s="879" t="n"/>
+      <c r="N296" s="879" t="n"/>
+      <c r="O296" s="878" t="n"/>
       <c r="P296" s="756" t="n"/>
       <c r="Q296" s="756" t="n"/>
-      <c r="R296" s="878" t="n"/>
+      <c r="R296" s="756" t="n"/>
       <c r="S296" s="756" t="n"/>
       <c r="T296" s="756" t="n"/>
-      <c r="U296" s="879" t="n"/>
-      <c r="V296" s="879" t="n"/>
+      <c r="U296" s="878" t="n"/>
+      <c r="V296" s="878" t="n"/>
       <c r="W296" s="756" t="n"/>
       <c r="X296" s="756" t="n"/>
       <c r="Y296" s="756" t="n"/>
       <c r="Z296" s="756" t="n"/>
       <c r="AA296" s="756" t="n"/>
-      <c r="AB296" s="879" t="n"/>
-      <c r="AC296" s="879" t="n"/>
+      <c r="AB296" s="878" t="n"/>
+      <c r="AC296" s="878" t="n"/>
       <c r="AD296" s="756" t="n"/>
       <c r="AE296" s="756" t="n"/>
       <c r="AF296" s="756" t="n"/>
@@ -29986,28 +29986,28 @@
       <c r="E297" s="778" t="n"/>
       <c r="F297" s="778" t="n"/>
       <c r="G297" s="880" t="n"/>
-      <c r="H297" s="881" t="n"/>
+      <c r="H297" s="880" t="n"/>
       <c r="I297" s="778" t="n"/>
       <c r="J297" s="778" t="n"/>
       <c r="K297" s="778" t="n"/>
       <c r="L297" s="778" t="n"/>
       <c r="M297" s="778" t="n"/>
-      <c r="N297" s="880" t="n"/>
-      <c r="O297" s="881" t="n"/>
+      <c r="N297" s="881" t="n"/>
+      <c r="O297" s="880" t="n"/>
       <c r="P297" s="778" t="n"/>
       <c r="Q297" s="778" t="n"/>
-      <c r="R297" s="880" t="n"/>
+      <c r="R297" s="778" t="n"/>
       <c r="S297" s="778" t="n"/>
       <c r="T297" s="778" t="n"/>
-      <c r="U297" s="881" t="n"/>
-      <c r="V297" s="881" t="n"/>
+      <c r="U297" s="880" t="n"/>
+      <c r="V297" s="880" t="n"/>
       <c r="W297" s="778" t="n"/>
       <c r="X297" s="778" t="n"/>
       <c r="Y297" s="778" t="n"/>
       <c r="Z297" s="778" t="n"/>
       <c r="AA297" s="778" t="n"/>
-      <c r="AB297" s="881" t="n"/>
-      <c r="AC297" s="881" t="n"/>
+      <c r="AB297" s="880" t="n"/>
+      <c r="AC297" s="880" t="n"/>
       <c r="AD297" s="778" t="n"/>
       <c r="AE297" s="778" t="n"/>
       <c r="AF297" s="778" t="n"/>
@@ -30027,28 +30027,28 @@
       <c r="E298" s="756" t="n"/>
       <c r="F298" s="756" t="n"/>
       <c r="G298" s="878" t="n"/>
-      <c r="H298" s="879" t="n"/>
+      <c r="H298" s="878" t="n"/>
       <c r="I298" s="756" t="n"/>
       <c r="J298" s="756" t="n"/>
       <c r="K298" s="756" t="n"/>
       <c r="L298" s="756" t="n"/>
       <c r="M298" s="756" t="n"/>
-      <c r="N298" s="878" t="n"/>
-      <c r="O298" s="879" t="n"/>
+      <c r="N298" s="879" t="n"/>
+      <c r="O298" s="878" t="n"/>
       <c r="P298" s="756" t="n"/>
       <c r="Q298" s="756" t="n"/>
-      <c r="R298" s="878" t="n"/>
+      <c r="R298" s="756" t="n"/>
       <c r="S298" s="756" t="n"/>
       <c r="T298" s="756" t="n"/>
-      <c r="U298" s="879" t="n"/>
-      <c r="V298" s="879" t="n"/>
+      <c r="U298" s="878" t="n"/>
+      <c r="V298" s="878" t="n"/>
       <c r="W298" s="756" t="n"/>
       <c r="X298" s="756" t="n"/>
       <c r="Y298" s="756" t="n"/>
       <c r="Z298" s="756" t="n"/>
       <c r="AA298" s="756" t="n"/>
-      <c r="AB298" s="879" t="n"/>
-      <c r="AC298" s="879" t="n"/>
+      <c r="AB298" s="878" t="n"/>
+      <c r="AC298" s="878" t="n"/>
       <c r="AD298" s="756" t="n"/>
       <c r="AE298" s="756" t="n"/>
       <c r="AF298" s="756" t="n"/>
@@ -30068,28 +30068,28 @@
       <c r="E299" s="756" t="n"/>
       <c r="F299" s="756" t="n"/>
       <c r="G299" s="878" t="n"/>
-      <c r="H299" s="879" t="n"/>
+      <c r="H299" s="878" t="n"/>
       <c r="I299" s="756" t="n"/>
       <c r="J299" s="756" t="n"/>
       <c r="K299" s="756" t="n"/>
       <c r="L299" s="756" t="n"/>
       <c r="M299" s="756" t="n"/>
-      <c r="N299" s="878" t="n"/>
-      <c r="O299" s="879" t="n"/>
+      <c r="N299" s="879" t="n"/>
+      <c r="O299" s="878" t="n"/>
       <c r="P299" s="756" t="n"/>
       <c r="Q299" s="756" t="n"/>
-      <c r="R299" s="878" t="n"/>
+      <c r="R299" s="756" t="n"/>
       <c r="S299" s="756" t="n"/>
       <c r="T299" s="756" t="n"/>
-      <c r="U299" s="879" t="n"/>
-      <c r="V299" s="879" t="n"/>
+      <c r="U299" s="878" t="n"/>
+      <c r="V299" s="878" t="n"/>
       <c r="W299" s="756" t="n"/>
       <c r="X299" s="756" t="n"/>
       <c r="Y299" s="756" t="n"/>
       <c r="Z299" s="756" t="n"/>
       <c r="AA299" s="756" t="n"/>
-      <c r="AB299" s="879" t="n"/>
-      <c r="AC299" s="879" t="n"/>
+      <c r="AB299" s="878" t="n"/>
+      <c r="AC299" s="878" t="n"/>
       <c r="AD299" s="756" t="n"/>
       <c r="AE299" s="756" t="n"/>
       <c r="AF299" s="756" t="n"/>
@@ -30108,28 +30108,28 @@
       <c r="E300" s="778" t="n"/>
       <c r="F300" s="778" t="n"/>
       <c r="G300" s="880" t="n"/>
-      <c r="H300" s="881" t="n"/>
+      <c r="H300" s="880" t="n"/>
       <c r="I300" s="778" t="n"/>
       <c r="J300" s="778" t="n"/>
       <c r="K300" s="778" t="n"/>
       <c r="L300" s="778" t="n"/>
       <c r="M300" s="778" t="n"/>
-      <c r="N300" s="880" t="n"/>
-      <c r="O300" s="881" t="n"/>
+      <c r="N300" s="881" t="n"/>
+      <c r="O300" s="880" t="n"/>
       <c r="P300" s="778" t="n"/>
       <c r="Q300" s="778" t="n"/>
-      <c r="R300" s="880" t="n"/>
+      <c r="R300" s="778" t="n"/>
       <c r="S300" s="778" t="n"/>
       <c r="T300" s="778" t="n"/>
-      <c r="U300" s="881" t="n"/>
-      <c r="V300" s="881" t="n"/>
+      <c r="U300" s="880" t="n"/>
+      <c r="V300" s="880" t="n"/>
       <c r="W300" s="778" t="n"/>
       <c r="X300" s="778" t="n"/>
       <c r="Y300" s="778" t="n"/>
       <c r="Z300" s="778" t="n"/>
       <c r="AA300" s="778" t="n"/>
-      <c r="AB300" s="881" t="n"/>
-      <c r="AC300" s="881" t="n"/>
+      <c r="AB300" s="880" t="n"/>
+      <c r="AC300" s="880" t="n"/>
       <c r="AD300" s="778" t="n"/>
       <c r="AE300" s="778" t="n"/>
       <c r="AF300" s="778" t="n"/>
@@ -30148,28 +30148,28 @@
       <c r="E301" s="755" t="n"/>
       <c r="F301" s="756" t="n"/>
       <c r="G301" s="882" t="n"/>
-      <c r="H301" s="879" t="n"/>
+      <c r="H301" s="878" t="n"/>
       <c r="I301" s="755" t="n"/>
       <c r="J301" s="756" t="n"/>
       <c r="K301" s="755" t="n"/>
       <c r="L301" s="756" t="n"/>
       <c r="M301" s="756" t="n"/>
-      <c r="N301" s="882" t="n"/>
-      <c r="O301" s="883" t="n"/>
+      <c r="N301" s="883" t="n"/>
+      <c r="O301" s="882" t="n"/>
       <c r="P301" s="756" t="n"/>
       <c r="Q301" s="756" t="n"/>
-      <c r="R301" s="882" t="n"/>
+      <c r="R301" s="755" t="n"/>
       <c r="S301" s="756" t="n"/>
       <c r="T301" s="756" t="n"/>
-      <c r="U301" s="883" t="n"/>
-      <c r="V301" s="883" t="n"/>
+      <c r="U301" s="882" t="n"/>
+      <c r="V301" s="882" t="n"/>
       <c r="W301" s="756" t="n"/>
       <c r="X301" s="756" t="n"/>
       <c r="Y301" s="755" t="n"/>
       <c r="Z301" s="756" t="n"/>
       <c r="AA301" s="756" t="n"/>
-      <c r="AB301" s="883" t="n"/>
-      <c r="AC301" s="883" t="n"/>
+      <c r="AB301" s="882" t="n"/>
+      <c r="AC301" s="882" t="n"/>
       <c r="AD301" s="756" t="n"/>
       <c r="AE301" s="756" t="n"/>
       <c r="AF301" s="755" t="n"/>
@@ -30188,28 +30188,28 @@
       <c r="E302" s="756" t="n"/>
       <c r="F302" s="756" t="n"/>
       <c r="G302" s="878" t="n"/>
-      <c r="H302" s="879" t="n"/>
+      <c r="H302" s="878" t="n"/>
       <c r="I302" s="756" t="n"/>
       <c r="J302" s="756" t="n"/>
       <c r="K302" s="756" t="n"/>
       <c r="L302" s="756" t="n"/>
       <c r="M302" s="756" t="n"/>
-      <c r="N302" s="878" t="n"/>
-      <c r="O302" s="879" t="n"/>
+      <c r="N302" s="879" t="n"/>
+      <c r="O302" s="878" t="n"/>
       <c r="P302" s="756" t="n"/>
       <c r="Q302" s="756" t="n"/>
-      <c r="R302" s="878" t="n"/>
+      <c r="R302" s="756" t="n"/>
       <c r="S302" s="756" t="n"/>
       <c r="T302" s="756" t="n"/>
-      <c r="U302" s="879" t="n"/>
-      <c r="V302" s="879" t="n"/>
+      <c r="U302" s="878" t="n"/>
+      <c r="V302" s="878" t="n"/>
       <c r="W302" s="756" t="n"/>
       <c r="X302" s="756" t="n"/>
       <c r="Y302" s="756" t="n"/>
       <c r="Z302" s="756" t="n"/>
       <c r="AA302" s="756" t="n"/>
-      <c r="AB302" s="879" t="n"/>
-      <c r="AC302" s="879" t="n"/>
+      <c r="AB302" s="878" t="n"/>
+      <c r="AC302" s="878" t="n"/>
       <c r="AD302" s="756" t="n"/>
       <c r="AE302" s="756" t="n"/>
       <c r="AF302" s="756" t="n"/>
@@ -30228,28 +30228,28 @@
       <c r="E303" s="756" t="n"/>
       <c r="F303" s="756" t="n"/>
       <c r="G303" s="878" t="n"/>
-      <c r="H303" s="879" t="n"/>
+      <c r="H303" s="878" t="n"/>
       <c r="I303" s="756" t="n"/>
       <c r="J303" s="756" t="n"/>
       <c r="K303" s="756" t="n"/>
       <c r="L303" s="756" t="n"/>
       <c r="M303" s="756" t="n"/>
-      <c r="N303" s="878" t="n"/>
-      <c r="O303" s="879" t="n"/>
+      <c r="N303" s="879" t="n"/>
+      <c r="O303" s="878" t="n"/>
       <c r="P303" s="756" t="n"/>
       <c r="Q303" s="756" t="n"/>
-      <c r="R303" s="878" t="n"/>
+      <c r="R303" s="756" t="n"/>
       <c r="S303" s="756" t="n"/>
       <c r="T303" s="756" t="n"/>
-      <c r="U303" s="879" t="n"/>
-      <c r="V303" s="879" t="n"/>
+      <c r="U303" s="878" t="n"/>
+      <c r="V303" s="878" t="n"/>
       <c r="W303" s="756" t="n"/>
       <c r="X303" s="756" t="n"/>
       <c r="Y303" s="756" t="n"/>
       <c r="Z303" s="756" t="n"/>
       <c r="AA303" s="756" t="n"/>
-      <c r="AB303" s="879" t="n"/>
-      <c r="AC303" s="879" t="n"/>
+      <c r="AB303" s="878" t="n"/>
+      <c r="AC303" s="878" t="n"/>
       <c r="AD303" s="756" t="n"/>
       <c r="AE303" s="756" t="n"/>
       <c r="AF303" s="756" t="n"/>
@@ -30426,36 +30426,36 @@
       <c r="B308" s="11" t="n"/>
       <c r="C308" s="11" t="n"/>
       <c r="D308" s="756" t="n"/>
-      <c r="E308" s="879" t="n"/>
-      <c r="F308" s="879" t="n"/>
+      <c r="E308" s="878" t="n"/>
+      <c r="F308" s="878" t="n"/>
       <c r="G308" s="756" t="n"/>
       <c r="H308" s="756" t="n"/>
       <c r="I308" s="756" t="n"/>
       <c r="J308" s="756" t="n"/>
       <c r="K308" s="756" t="n"/>
-      <c r="L308" s="879" t="n"/>
-      <c r="M308" s="879" t="n"/>
+      <c r="L308" s="878" t="n"/>
+      <c r="M308" s="878" t="n"/>
       <c r="N308" s="756" t="n"/>
-      <c r="O308" s="878" t="n"/>
+      <c r="O308" s="879" t="n"/>
       <c r="P308" s="756" t="n"/>
       <c r="Q308" s="756" t="n"/>
       <c r="R308" s="756" t="n"/>
-      <c r="S308" s="879" t="n"/>
-      <c r="T308" s="879" t="n"/>
+      <c r="S308" s="878" t="n"/>
+      <c r="T308" s="878" t="n"/>
       <c r="U308" s="756" t="n"/>
       <c r="V308" s="756" t="n"/>
       <c r="W308" s="756" t="n"/>
       <c r="X308" s="756" t="n"/>
       <c r="Y308" s="756" t="n"/>
-      <c r="Z308" s="879" t="n"/>
-      <c r="AA308" s="879" t="n"/>
+      <c r="Z308" s="878" t="n"/>
+      <c r="AA308" s="878" t="n"/>
       <c r="AB308" s="756" t="n"/>
       <c r="AC308" s="756" t="n"/>
       <c r="AD308" s="756" t="n"/>
       <c r="AE308" s="756" t="n"/>
       <c r="AF308" s="756" t="n"/>
-      <c r="AG308" s="879" t="n"/>
-      <c r="AH308" s="879" t="n"/>
+      <c r="AG308" s="878" t="n"/>
+      <c r="AH308" s="878" t="n"/>
       <c r="AI308" s="4" t="n"/>
     </row>
     <row r="309" ht="15.75" customHeight="1" s="757">
@@ -30467,36 +30467,36 @@
       <c r="B309" s="456" t="n"/>
       <c r="C309" s="456" t="n"/>
       <c r="D309" s="782" t="n"/>
-      <c r="E309" s="879" t="n"/>
-      <c r="F309" s="879" t="n"/>
+      <c r="E309" s="878" t="n"/>
+      <c r="F309" s="878" t="n"/>
       <c r="G309" s="756" t="n"/>
       <c r="H309" s="756" t="n"/>
       <c r="I309" s="756" t="n"/>
       <c r="J309" s="756" t="n"/>
       <c r="K309" s="756" t="n"/>
-      <c r="L309" s="879" t="n"/>
-      <c r="M309" s="879" t="n"/>
+      <c r="L309" s="878" t="n"/>
+      <c r="M309" s="878" t="n"/>
       <c r="N309" s="756" t="n"/>
-      <c r="O309" s="878" t="n"/>
+      <c r="O309" s="879" t="n"/>
       <c r="P309" s="756" t="n"/>
       <c r="Q309" s="756" t="n"/>
       <c r="R309" s="756" t="n"/>
-      <c r="S309" s="879" t="n"/>
-      <c r="T309" s="879" t="n"/>
+      <c r="S309" s="878" t="n"/>
+      <c r="T309" s="878" t="n"/>
       <c r="U309" s="756" t="n"/>
       <c r="V309" s="756" t="n"/>
       <c r="W309" s="756" t="n"/>
       <c r="X309" s="756" t="n"/>
       <c r="Y309" s="756" t="n"/>
-      <c r="Z309" s="879" t="n"/>
-      <c r="AA309" s="879" t="n"/>
+      <c r="Z309" s="878" t="n"/>
+      <c r="AA309" s="878" t="n"/>
       <c r="AB309" s="756" t="n"/>
       <c r="AC309" s="756" t="n"/>
       <c r="AD309" s="756" t="n"/>
       <c r="AE309" s="756" t="n"/>
       <c r="AF309" s="756" t="n"/>
-      <c r="AG309" s="879" t="n"/>
-      <c r="AH309" s="879" t="n"/>
+      <c r="AG309" s="878" t="n"/>
+      <c r="AH309" s="878" t="n"/>
       <c r="AI309" s="4" t="n"/>
     </row>
     <row r="310" ht="19.5" customHeight="1" s="757">
@@ -30508,36 +30508,36 @@
       <c r="B310" s="15" t="n"/>
       <c r="C310" s="15" t="n"/>
       <c r="D310" s="783" t="n"/>
-      <c r="E310" s="881" t="n"/>
-      <c r="F310" s="881" t="n"/>
+      <c r="E310" s="880" t="n"/>
+      <c r="F310" s="880" t="n"/>
       <c r="G310" s="778" t="n"/>
       <c r="H310" s="778" t="n"/>
       <c r="I310" s="778" t="n"/>
       <c r="J310" s="778" t="n"/>
       <c r="K310" s="778" t="n"/>
-      <c r="L310" s="881" t="n"/>
-      <c r="M310" s="881" t="n"/>
+      <c r="L310" s="880" t="n"/>
+      <c r="M310" s="880" t="n"/>
       <c r="N310" s="778" t="n"/>
-      <c r="O310" s="880" t="n"/>
+      <c r="O310" s="881" t="n"/>
       <c r="P310" s="778" t="n"/>
       <c r="Q310" s="778" t="n"/>
       <c r="R310" s="778" t="n"/>
-      <c r="S310" s="881" t="n"/>
-      <c r="T310" s="881" t="n"/>
+      <c r="S310" s="880" t="n"/>
+      <c r="T310" s="880" t="n"/>
       <c r="U310" s="778" t="n"/>
       <c r="V310" s="778" t="n"/>
       <c r="W310" s="778" t="n"/>
       <c r="X310" s="778" t="n"/>
       <c r="Y310" s="778" t="n"/>
-      <c r="Z310" s="881" t="n"/>
-      <c r="AA310" s="881" t="n"/>
+      <c r="Z310" s="880" t="n"/>
+      <c r="AA310" s="880" t="n"/>
       <c r="AB310" s="778" t="n"/>
       <c r="AC310" s="778" t="n"/>
       <c r="AD310" s="778" t="n"/>
       <c r="AE310" s="778" t="n"/>
       <c r="AF310" s="778" t="n"/>
-      <c r="AG310" s="881" t="n"/>
-      <c r="AH310" s="881" t="n"/>
+      <c r="AG310" s="880" t="n"/>
+      <c r="AH310" s="880" t="n"/>
       <c r="AI310" s="4" t="n"/>
     </row>
     <row r="311" ht="16.5" customHeight="1" s="757">
@@ -30549,36 +30549,36 @@
       <c r="B311" s="18" t="n"/>
       <c r="C311" s="18" t="n"/>
       <c r="D311" s="755" t="n"/>
-      <c r="E311" s="879" t="n"/>
-      <c r="F311" s="879" t="n"/>
+      <c r="E311" s="878" t="n"/>
+      <c r="F311" s="878" t="n"/>
       <c r="G311" s="756" t="n"/>
       <c r="H311" s="756" t="n"/>
       <c r="I311" s="756" t="n"/>
       <c r="J311" s="756" t="n"/>
       <c r="K311" s="756" t="n"/>
-      <c r="L311" s="879" t="n"/>
-      <c r="M311" s="879" t="n"/>
+      <c r="L311" s="878" t="n"/>
+      <c r="M311" s="878" t="n"/>
       <c r="N311" s="756" t="n"/>
-      <c r="O311" s="878" t="n"/>
+      <c r="O311" s="879" t="n"/>
       <c r="P311" s="756" t="n"/>
       <c r="Q311" s="756" t="n"/>
       <c r="R311" s="756" t="n"/>
-      <c r="S311" s="879" t="n"/>
-      <c r="T311" s="879" t="n"/>
+      <c r="S311" s="878" t="n"/>
+      <c r="T311" s="878" t="n"/>
       <c r="U311" s="756" t="n"/>
       <c r="V311" s="756" t="n"/>
       <c r="W311" s="756" t="n"/>
       <c r="X311" s="756" t="n"/>
       <c r="Y311" s="756" t="n"/>
-      <c r="Z311" s="879" t="n"/>
-      <c r="AA311" s="879" t="n"/>
+      <c r="Z311" s="878" t="n"/>
+      <c r="AA311" s="878" t="n"/>
       <c r="AB311" s="756" t="n"/>
       <c r="AC311" s="756" t="n"/>
       <c r="AD311" s="756" t="n"/>
       <c r="AE311" s="756" t="n"/>
       <c r="AF311" s="756" t="n"/>
-      <c r="AG311" s="879" t="n"/>
-      <c r="AH311" s="879" t="n"/>
+      <c r="AG311" s="878" t="n"/>
+      <c r="AH311" s="878" t="n"/>
       <c r="AI311" s="4" t="n"/>
     </row>
     <row r="312" ht="15.75" customHeight="1" s="757">
@@ -30590,36 +30590,36 @@
       <c r="B312" s="11" t="n"/>
       <c r="C312" s="11" t="n"/>
       <c r="D312" s="756" t="n"/>
-      <c r="E312" s="879" t="n"/>
-      <c r="F312" s="879" t="n"/>
+      <c r="E312" s="878" t="n"/>
+      <c r="F312" s="878" t="n"/>
       <c r="G312" s="756" t="n"/>
       <c r="H312" s="756" t="n"/>
       <c r="I312" s="756" t="n"/>
       <c r="J312" s="756" t="n"/>
       <c r="K312" s="756" t="n"/>
-      <c r="L312" s="879" t="n"/>
-      <c r="M312" s="879" t="n"/>
+      <c r="L312" s="878" t="n"/>
+      <c r="M312" s="878" t="n"/>
       <c r="N312" s="756" t="n"/>
-      <c r="O312" s="878" t="n"/>
+      <c r="O312" s="879" t="n"/>
       <c r="P312" s="756" t="n"/>
       <c r="Q312" s="756" t="n"/>
       <c r="R312" s="756" t="n"/>
-      <c r="S312" s="879" t="n"/>
-      <c r="T312" s="879" t="n"/>
+      <c r="S312" s="878" t="n"/>
+      <c r="T312" s="878" t="n"/>
       <c r="U312" s="756" t="n"/>
       <c r="V312" s="756" t="n"/>
       <c r="W312" s="756" t="n"/>
       <c r="X312" s="756" t="n"/>
       <c r="Y312" s="756" t="n"/>
-      <c r="Z312" s="879" t="n"/>
-      <c r="AA312" s="879" t="n"/>
+      <c r="Z312" s="878" t="n"/>
+      <c r="AA312" s="878" t="n"/>
       <c r="AB312" s="756" t="n"/>
       <c r="AC312" s="756" t="n"/>
       <c r="AD312" s="756" t="n"/>
       <c r="AE312" s="756" t="n"/>
       <c r="AF312" s="756" t="n"/>
-      <c r="AG312" s="879" t="n"/>
-      <c r="AH312" s="879" t="n"/>
+      <c r="AG312" s="878" t="n"/>
+      <c r="AH312" s="878" t="n"/>
     </row>
     <row r="313" ht="16.5" customHeight="1" s="757">
       <c r="A313" s="14" t="inlineStr">
@@ -30630,36 +30630,36 @@
       <c r="B313" s="15" t="n"/>
       <c r="C313" s="15" t="n"/>
       <c r="D313" s="783" t="n"/>
-      <c r="E313" s="881" t="n"/>
-      <c r="F313" s="881" t="n"/>
+      <c r="E313" s="880" t="n"/>
+      <c r="F313" s="880" t="n"/>
       <c r="G313" s="778" t="n"/>
       <c r="H313" s="778" t="n"/>
       <c r="I313" s="778" t="n"/>
       <c r="J313" s="778" t="n"/>
       <c r="K313" s="778" t="n"/>
-      <c r="L313" s="881" t="n"/>
-      <c r="M313" s="881" t="n"/>
+      <c r="L313" s="880" t="n"/>
+      <c r="M313" s="880" t="n"/>
       <c r="N313" s="778" t="n"/>
-      <c r="O313" s="880" t="n"/>
+      <c r="O313" s="881" t="n"/>
       <c r="P313" s="778" t="n"/>
       <c r="Q313" s="778" t="n"/>
       <c r="R313" s="778" t="n"/>
-      <c r="S313" s="881" t="n"/>
-      <c r="T313" s="881" t="n"/>
+      <c r="S313" s="880" t="n"/>
+      <c r="T313" s="880" t="n"/>
       <c r="U313" s="778" t="n"/>
       <c r="V313" s="778" t="n"/>
       <c r="W313" s="778" t="n"/>
       <c r="X313" s="778" t="n"/>
       <c r="Y313" s="778" t="n"/>
-      <c r="Z313" s="881" t="n"/>
-      <c r="AA313" s="881" t="n"/>
+      <c r="Z313" s="880" t="n"/>
+      <c r="AA313" s="880" t="n"/>
       <c r="AB313" s="778" t="n"/>
       <c r="AC313" s="778" t="n"/>
       <c r="AD313" s="778" t="n"/>
       <c r="AE313" s="778" t="n"/>
       <c r="AF313" s="778" t="n"/>
-      <c r="AG313" s="881" t="n"/>
-      <c r="AH313" s="881" t="n"/>
+      <c r="AG313" s="880" t="n"/>
+      <c r="AH313" s="880" t="n"/>
     </row>
     <row r="314" ht="16.5" customHeight="1" s="757">
       <c r="A314" s="10" t="inlineStr">
@@ -30670,36 +30670,36 @@
       <c r="B314" s="11" t="n"/>
       <c r="C314" s="11" t="n"/>
       <c r="D314" s="755" t="n"/>
-      <c r="E314" s="883" t="n"/>
-      <c r="F314" s="879" t="n"/>
+      <c r="E314" s="882" t="n"/>
+      <c r="F314" s="878" t="n"/>
       <c r="G314" s="755" t="n"/>
       <c r="H314" s="756" t="n"/>
       <c r="I314" s="755" t="n"/>
       <c r="J314" s="756" t="n"/>
       <c r="K314" s="755" t="n"/>
-      <c r="L314" s="879" t="n"/>
-      <c r="M314" s="879" t="n"/>
+      <c r="L314" s="878" t="n"/>
+      <c r="M314" s="878" t="n"/>
       <c r="N314" s="755" t="n"/>
-      <c r="O314" s="882" t="n"/>
+      <c r="O314" s="883" t="n"/>
       <c r="P314" s="756" t="n"/>
       <c r="Q314" s="756" t="n"/>
       <c r="R314" s="755" t="n"/>
-      <c r="S314" s="879" t="n"/>
-      <c r="T314" s="879" t="n"/>
+      <c r="S314" s="878" t="n"/>
+      <c r="T314" s="878" t="n"/>
       <c r="U314" s="755" t="n"/>
       <c r="V314" s="755" t="n"/>
       <c r="W314" s="756" t="n"/>
       <c r="X314" s="756" t="n"/>
       <c r="Y314" s="755" t="n"/>
-      <c r="Z314" s="879" t="n"/>
-      <c r="AA314" s="879" t="n"/>
+      <c r="Z314" s="878" t="n"/>
+      <c r="AA314" s="878" t="n"/>
       <c r="AB314" s="755" t="n"/>
       <c r="AC314" s="755" t="n"/>
       <c r="AD314" s="756" t="n"/>
       <c r="AE314" s="756" t="n"/>
       <c r="AF314" s="755" t="n"/>
-      <c r="AG314" s="879" t="n"/>
-      <c r="AH314" s="879" t="n"/>
+      <c r="AG314" s="878" t="n"/>
+      <c r="AH314" s="878" t="n"/>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="757">
       <c r="A315" s="12" t="inlineStr">
@@ -30710,36 +30710,36 @@
       <c r="B315" s="11" t="n"/>
       <c r="C315" s="11" t="n"/>
       <c r="D315" s="756" t="n"/>
-      <c r="E315" s="879" t="n"/>
-      <c r="F315" s="879" t="n"/>
+      <c r="E315" s="878" t="n"/>
+      <c r="F315" s="878" t="n"/>
       <c r="G315" s="756" t="n"/>
       <c r="H315" s="756" t="n"/>
       <c r="I315" s="756" t="n"/>
       <c r="J315" s="756" t="n"/>
       <c r="K315" s="756" t="n"/>
-      <c r="L315" s="879" t="n"/>
-      <c r="M315" s="879" t="n"/>
+      <c r="L315" s="878" t="n"/>
+      <c r="M315" s="878" t="n"/>
       <c r="N315" s="756" t="n"/>
-      <c r="O315" s="878" t="n"/>
+      <c r="O315" s="879" t="n"/>
       <c r="P315" s="756" t="n"/>
       <c r="Q315" s="756" t="n"/>
       <c r="R315" s="756" t="n"/>
-      <c r="S315" s="879" t="n"/>
-      <c r="T315" s="879" t="n"/>
+      <c r="S315" s="878" t="n"/>
+      <c r="T315" s="878" t="n"/>
       <c r="U315" s="756" t="n"/>
       <c r="V315" s="756" t="n"/>
       <c r="W315" s="756" t="n"/>
       <c r="X315" s="756" t="n"/>
       <c r="Y315" s="756" t="n"/>
-      <c r="Z315" s="879" t="n"/>
-      <c r="AA315" s="879" t="n"/>
+      <c r="Z315" s="878" t="n"/>
+      <c r="AA315" s="878" t="n"/>
       <c r="AB315" s="756" t="n"/>
       <c r="AC315" s="756" t="n"/>
       <c r="AD315" s="756" t="n"/>
       <c r="AE315" s="756" t="n"/>
       <c r="AF315" s="756" t="n"/>
-      <c r="AG315" s="879" t="n"/>
-      <c r="AH315" s="879" t="n"/>
+      <c r="AG315" s="878" t="n"/>
+      <c r="AH315" s="878" t="n"/>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="757">
       <c r="A316" s="12" t="inlineStr">
@@ -30750,36 +30750,36 @@
       <c r="B316" s="11" t="n"/>
       <c r="C316" s="11" t="n"/>
       <c r="D316" s="756" t="n"/>
-      <c r="E316" s="879" t="n"/>
-      <c r="F316" s="879" t="n"/>
+      <c r="E316" s="878" t="n"/>
+      <c r="F316" s="878" t="n"/>
       <c r="G316" s="756" t="n"/>
       <c r="H316" s="756" t="n"/>
       <c r="I316" s="756" t="n"/>
       <c r="J316" s="756" t="n"/>
       <c r="K316" s="756" t="n"/>
-      <c r="L316" s="879" t="n"/>
-      <c r="M316" s="879" t="n"/>
+      <c r="L316" s="878" t="n"/>
+      <c r="M316" s="878" t="n"/>
       <c r="N316" s="756" t="n"/>
-      <c r="O316" s="878" t="n"/>
+      <c r="O316" s="879" t="n"/>
       <c r="P316" s="756" t="n"/>
       <c r="Q316" s="756" t="n"/>
       <c r="R316" s="756" t="n"/>
-      <c r="S316" s="879" t="n"/>
-      <c r="T316" s="879" t="n"/>
+      <c r="S316" s="878" t="n"/>
+      <c r="T316" s="878" t="n"/>
       <c r="U316" s="756" t="n"/>
       <c r="V316" s="756" t="n"/>
       <c r="W316" s="756" t="n"/>
       <c r="X316" s="756" t="n"/>
       <c r="Y316" s="756" t="n"/>
-      <c r="Z316" s="879" t="n"/>
-      <c r="AA316" s="879" t="n"/>
+      <c r="Z316" s="878" t="n"/>
+      <c r="AA316" s="878" t="n"/>
       <c r="AB316" s="756" t="n"/>
       <c r="AC316" s="756" t="n"/>
       <c r="AD316" s="756" t="n"/>
       <c r="AE316" s="756" t="n"/>
       <c r="AF316" s="756" t="n"/>
-      <c r="AG316" s="879" t="n"/>
-      <c r="AH316" s="879" t="n"/>
+      <c r="AG316" s="878" t="n"/>
+      <c r="AH316" s="878" t="n"/>
     </row>
     <row r="317" s="757"/>
     <row r="318" s="757"/>
@@ -30948,34 +30948,34 @@
       </c>
       <c r="B321" s="11" t="n"/>
       <c r="C321" s="11" t="n"/>
-      <c r="D321" s="878" t="n"/>
+      <c r="D321" s="879" t="n"/>
       <c r="E321" s="756" t="n"/>
       <c r="F321" s="756" t="n"/>
       <c r="G321" s="756" t="n"/>
       <c r="H321" s="756" t="n"/>
-      <c r="I321" s="879" t="n"/>
-      <c r="J321" s="879" t="n"/>
+      <c r="I321" s="878" t="n"/>
+      <c r="J321" s="878" t="n"/>
       <c r="K321" s="756" t="n"/>
       <c r="L321" s="756" t="n"/>
       <c r="M321" s="756" t="n"/>
       <c r="N321" s="756" t="n"/>
       <c r="O321" s="756" t="n"/>
-      <c r="P321" s="879" t="n"/>
-      <c r="Q321" s="879" t="n"/>
+      <c r="P321" s="878" t="n"/>
+      <c r="Q321" s="878" t="n"/>
       <c r="R321" s="756" t="n"/>
       <c r="S321" s="756" t="n"/>
       <c r="T321" s="756" t="n"/>
       <c r="U321" s="756" t="n"/>
       <c r="V321" s="756" t="n"/>
-      <c r="W321" s="879" t="n"/>
-      <c r="X321" s="879" t="n"/>
+      <c r="W321" s="878" t="n"/>
+      <c r="X321" s="878" t="n"/>
       <c r="Y321" s="756" t="n"/>
       <c r="Z321" s="756" t="n"/>
       <c r="AA321" s="756" t="n"/>
       <c r="AB321" s="756" t="n"/>
       <c r="AC321" s="756" t="n"/>
-      <c r="AD321" s="879" t="n"/>
-      <c r="AE321" s="879" t="n"/>
+      <c r="AD321" s="878" t="n"/>
+      <c r="AE321" s="878" t="n"/>
       <c r="AF321" s="756" t="n"/>
       <c r="AG321" s="756" t="n"/>
       <c r="AH321" s="756" t="n"/>
@@ -30994,29 +30994,29 @@
       <c r="F322" s="756" t="n"/>
       <c r="G322" s="756" t="n"/>
       <c r="H322" s="756" t="n"/>
-      <c r="I322" s="879" t="n"/>
-      <c r="J322" s="879" t="n"/>
+      <c r="I322" s="878" t="n"/>
+      <c r="J322" s="878" t="n"/>
       <c r="K322" s="756" t="n"/>
       <c r="L322" s="756" t="n"/>
       <c r="M322" s="756" t="n"/>
       <c r="N322" s="756" t="n"/>
       <c r="O322" s="756" t="n"/>
-      <c r="P322" s="879" t="n"/>
-      <c r="Q322" s="879" t="n"/>
+      <c r="P322" s="878" t="n"/>
+      <c r="Q322" s="878" t="n"/>
       <c r="R322" s="756" t="n"/>
       <c r="S322" s="756" t="n"/>
       <c r="T322" s="756" t="n"/>
       <c r="U322" s="756" t="n"/>
       <c r="V322" s="756" t="n"/>
-      <c r="W322" s="879" t="n"/>
-      <c r="X322" s="879" t="n"/>
+      <c r="W322" s="878" t="n"/>
+      <c r="X322" s="878" t="n"/>
       <c r="Y322" s="756" t="n"/>
       <c r="Z322" s="756" t="n"/>
       <c r="AA322" s="756" t="n"/>
       <c r="AB322" s="756" t="n"/>
       <c r="AC322" s="756" t="n"/>
-      <c r="AD322" s="879" t="n"/>
-      <c r="AE322" s="879" t="n"/>
+      <c r="AD322" s="878" t="n"/>
+      <c r="AE322" s="878" t="n"/>
       <c r="AF322" s="756" t="n"/>
       <c r="AG322" s="756" t="n"/>
       <c r="AH322" s="756" t="n"/>
@@ -31035,29 +31035,29 @@
       <c r="F323" s="778" t="n"/>
       <c r="G323" s="778" t="n"/>
       <c r="H323" s="778" t="n"/>
-      <c r="I323" s="881" t="n"/>
-      <c r="J323" s="881" t="n"/>
+      <c r="I323" s="880" t="n"/>
+      <c r="J323" s="880" t="n"/>
       <c r="K323" s="778" t="n"/>
       <c r="L323" s="778" t="n"/>
       <c r="M323" s="778" t="n"/>
       <c r="N323" s="778" t="n"/>
       <c r="O323" s="778" t="n"/>
-      <c r="P323" s="881" t="n"/>
-      <c r="Q323" s="881" t="n"/>
+      <c r="P323" s="880" t="n"/>
+      <c r="Q323" s="880" t="n"/>
       <c r="R323" s="778" t="n"/>
       <c r="S323" s="778" t="n"/>
       <c r="T323" s="778" t="n"/>
       <c r="U323" s="778" t="n"/>
       <c r="V323" s="778" t="n"/>
-      <c r="W323" s="881" t="n"/>
-      <c r="X323" s="881" t="n"/>
+      <c r="W323" s="880" t="n"/>
+      <c r="X323" s="880" t="n"/>
       <c r="Y323" s="778" t="n"/>
       <c r="Z323" s="778" t="n"/>
       <c r="AA323" s="778" t="n"/>
       <c r="AB323" s="778" t="n"/>
       <c r="AC323" s="778" t="n"/>
-      <c r="AD323" s="881" t="n"/>
-      <c r="AE323" s="881" t="n"/>
+      <c r="AD323" s="880" t="n"/>
+      <c r="AE323" s="880" t="n"/>
       <c r="AF323" s="778" t="n"/>
       <c r="AG323" s="778" t="n"/>
       <c r="AH323" s="778" t="n"/>
@@ -31071,34 +31071,34 @@
       </c>
       <c r="B324" s="18" t="n"/>
       <c r="C324" s="18" t="n"/>
-      <c r="D324" s="882" t="n"/>
+      <c r="D324" s="883" t="n"/>
       <c r="E324" s="756" t="n"/>
       <c r="F324" s="756" t="n"/>
       <c r="G324" s="756" t="n"/>
       <c r="H324" s="756" t="n"/>
-      <c r="I324" s="879" t="n"/>
-      <c r="J324" s="879" t="n"/>
+      <c r="I324" s="878" t="n"/>
+      <c r="J324" s="878" t="n"/>
       <c r="K324" s="756" t="n"/>
       <c r="L324" s="756" t="n"/>
       <c r="M324" s="756" t="n"/>
       <c r="N324" s="756" t="n"/>
       <c r="O324" s="756" t="n"/>
-      <c r="P324" s="879" t="n"/>
-      <c r="Q324" s="879" t="n"/>
+      <c r="P324" s="878" t="n"/>
+      <c r="Q324" s="878" t="n"/>
       <c r="R324" s="756" t="n"/>
       <c r="S324" s="756" t="n"/>
       <c r="T324" s="756" t="n"/>
       <c r="U324" s="756" t="n"/>
       <c r="V324" s="756" t="n"/>
-      <c r="W324" s="879" t="n"/>
-      <c r="X324" s="879" t="n"/>
+      <c r="W324" s="878" t="n"/>
+      <c r="X324" s="878" t="n"/>
       <c r="Y324" s="756" t="n"/>
       <c r="Z324" s="756" t="n"/>
       <c r="AA324" s="756" t="n"/>
       <c r="AB324" s="756" t="n"/>
       <c r="AC324" s="756" t="n"/>
-      <c r="AD324" s="879" t="n"/>
-      <c r="AE324" s="879" t="n"/>
+      <c r="AD324" s="878" t="n"/>
+      <c r="AE324" s="878" t="n"/>
       <c r="AF324" s="756" t="n"/>
       <c r="AG324" s="756" t="n"/>
       <c r="AH324" s="756" t="n"/>
@@ -31112,34 +31112,34 @@
       </c>
       <c r="B325" s="11" t="n"/>
       <c r="C325" s="11" t="n"/>
-      <c r="D325" s="878" t="n"/>
+      <c r="D325" s="879" t="n"/>
       <c r="E325" s="756" t="n"/>
       <c r="F325" s="756" t="n"/>
       <c r="G325" s="756" t="n"/>
       <c r="H325" s="756" t="n"/>
-      <c r="I325" s="879" t="n"/>
-      <c r="J325" s="879" t="n"/>
+      <c r="I325" s="878" t="n"/>
+      <c r="J325" s="878" t="n"/>
       <c r="K325" s="756" t="n"/>
       <c r="L325" s="756" t="n"/>
       <c r="M325" s="756" t="n"/>
       <c r="N325" s="756" t="n"/>
       <c r="O325" s="756" t="n"/>
-      <c r="P325" s="879" t="n"/>
-      <c r="Q325" s="879" t="n"/>
+      <c r="P325" s="878" t="n"/>
+      <c r="Q325" s="878" t="n"/>
       <c r="R325" s="756" t="n"/>
       <c r="S325" s="756" t="n"/>
       <c r="T325" s="756" t="n"/>
       <c r="U325" s="756" t="n"/>
       <c r="V325" s="756" t="n"/>
-      <c r="W325" s="879" t="n"/>
-      <c r="X325" s="879" t="n"/>
+      <c r="W325" s="878" t="n"/>
+      <c r="X325" s="878" t="n"/>
       <c r="Y325" s="756" t="n"/>
       <c r="Z325" s="756" t="n"/>
       <c r="AA325" s="756" t="n"/>
       <c r="AB325" s="756" t="n"/>
       <c r="AC325" s="756" t="n"/>
-      <c r="AD325" s="879" t="n"/>
-      <c r="AE325" s="879" t="n"/>
+      <c r="AD325" s="878" t="n"/>
+      <c r="AE325" s="878" t="n"/>
       <c r="AF325" s="756" t="n"/>
       <c r="AG325" s="756" t="n"/>
       <c r="AH325" s="756" t="n"/>
@@ -31157,29 +31157,29 @@
       <c r="F326" s="778" t="n"/>
       <c r="G326" s="778" t="n"/>
       <c r="H326" s="778" t="n"/>
-      <c r="I326" s="881" t="n"/>
-      <c r="J326" s="881" t="n"/>
+      <c r="I326" s="880" t="n"/>
+      <c r="J326" s="880" t="n"/>
       <c r="K326" s="778" t="n"/>
       <c r="L326" s="778" t="n"/>
       <c r="M326" s="778" t="n"/>
       <c r="N326" s="778" t="n"/>
       <c r="O326" s="778" t="n"/>
-      <c r="P326" s="881" t="n"/>
-      <c r="Q326" s="881" t="n"/>
+      <c r="P326" s="880" t="n"/>
+      <c r="Q326" s="880" t="n"/>
       <c r="R326" s="778" t="n"/>
       <c r="S326" s="778" t="n"/>
       <c r="T326" s="778" t="n"/>
       <c r="U326" s="778" t="n"/>
       <c r="V326" s="778" t="n"/>
-      <c r="W326" s="881" t="n"/>
-      <c r="X326" s="881" t="n"/>
+      <c r="W326" s="880" t="n"/>
+      <c r="X326" s="880" t="n"/>
       <c r="Y326" s="778" t="n"/>
       <c r="Z326" s="778" t="n"/>
       <c r="AA326" s="778" t="n"/>
       <c r="AB326" s="778" t="n"/>
       <c r="AC326" s="778" t="n"/>
-      <c r="AD326" s="881" t="n"/>
-      <c r="AE326" s="881" t="n"/>
+      <c r="AD326" s="880" t="n"/>
+      <c r="AE326" s="880" t="n"/>
       <c r="AF326" s="778" t="n"/>
       <c r="AG326" s="778" t="n"/>
       <c r="AH326" s="778" t="n"/>
@@ -31192,34 +31192,34 @@
       </c>
       <c r="B327" s="11" t="n"/>
       <c r="C327" s="11" t="n"/>
-      <c r="D327" s="882" t="n"/>
+      <c r="D327" s="883" t="n"/>
       <c r="E327" s="755" t="n"/>
       <c r="F327" s="756" t="n"/>
       <c r="G327" s="755" t="n"/>
       <c r="H327" s="756" t="n"/>
-      <c r="I327" s="883" t="n"/>
-      <c r="J327" s="879" t="n"/>
+      <c r="I327" s="882" t="n"/>
+      <c r="J327" s="878" t="n"/>
       <c r="K327" s="755" t="n"/>
       <c r="L327" s="756" t="n"/>
       <c r="M327" s="756" t="n"/>
       <c r="N327" s="755" t="n"/>
       <c r="O327" s="755" t="n"/>
-      <c r="P327" s="879" t="n"/>
-      <c r="Q327" s="879" t="n"/>
+      <c r="P327" s="878" t="n"/>
+      <c r="Q327" s="878" t="n"/>
       <c r="R327" s="755" t="n"/>
       <c r="S327" s="756" t="n"/>
       <c r="T327" s="756" t="n"/>
       <c r="U327" s="755" t="n"/>
       <c r="V327" s="755" t="n"/>
-      <c r="W327" s="879" t="n"/>
-      <c r="X327" s="879" t="n"/>
+      <c r="W327" s="878" t="n"/>
+      <c r="X327" s="878" t="n"/>
       <c r="Y327" s="755" t="n"/>
       <c r="Z327" s="756" t="n"/>
       <c r="AA327" s="756" t="n"/>
       <c r="AB327" s="755" t="n"/>
       <c r="AC327" s="755" t="n"/>
-      <c r="AD327" s="879" t="n"/>
-      <c r="AE327" s="879" t="n"/>
+      <c r="AD327" s="878" t="n"/>
+      <c r="AE327" s="878" t="n"/>
       <c r="AF327" s="755" t="n"/>
       <c r="AG327" s="756" t="n"/>
       <c r="AH327" s="756" t="n"/>
@@ -31232,34 +31232,34 @@
       </c>
       <c r="B328" s="11" t="n"/>
       <c r="C328" s="11" t="n"/>
-      <c r="D328" s="878" t="n"/>
+      <c r="D328" s="879" t="n"/>
       <c r="E328" s="756" t="n"/>
       <c r="F328" s="756" t="n"/>
       <c r="G328" s="756" t="n"/>
       <c r="H328" s="756" t="n"/>
-      <c r="I328" s="879" t="n"/>
-      <c r="J328" s="879" t="n"/>
+      <c r="I328" s="878" t="n"/>
+      <c r="J328" s="878" t="n"/>
       <c r="K328" s="756" t="n"/>
       <c r="L328" s="756" t="n"/>
       <c r="M328" s="756" t="n"/>
       <c r="N328" s="756" t="n"/>
       <c r="O328" s="756" t="n"/>
-      <c r="P328" s="879" t="n"/>
-      <c r="Q328" s="879" t="n"/>
+      <c r="P328" s="878" t="n"/>
+      <c r="Q328" s="878" t="n"/>
       <c r="R328" s="756" t="n"/>
       <c r="S328" s="756" t="n"/>
       <c r="T328" s="756" t="n"/>
       <c r="U328" s="756" t="n"/>
       <c r="V328" s="756" t="n"/>
-      <c r="W328" s="879" t="n"/>
-      <c r="X328" s="879" t="n"/>
+      <c r="W328" s="878" t="n"/>
+      <c r="X328" s="878" t="n"/>
       <c r="Y328" s="756" t="n"/>
       <c r="Z328" s="756" t="n"/>
       <c r="AA328" s="756" t="n"/>
       <c r="AB328" s="756" t="n"/>
       <c r="AC328" s="756" t="n"/>
-      <c r="AD328" s="879" t="n"/>
-      <c r="AE328" s="879" t="n"/>
+      <c r="AD328" s="878" t="n"/>
+      <c r="AE328" s="878" t="n"/>
       <c r="AF328" s="756" t="n"/>
       <c r="AG328" s="756" t="n"/>
       <c r="AH328" s="756" t="n"/>
@@ -31272,34 +31272,34 @@
       </c>
       <c r="B329" s="11" t="n"/>
       <c r="C329" s="11" t="n"/>
-      <c r="D329" s="878" t="n"/>
+      <c r="D329" s="879" t="n"/>
       <c r="E329" s="756" t="n"/>
       <c r="F329" s="756" t="n"/>
       <c r="G329" s="756" t="n"/>
       <c r="H329" s="756" t="n"/>
-      <c r="I329" s="879" t="n"/>
-      <c r="J329" s="879" t="n"/>
+      <c r="I329" s="878" t="n"/>
+      <c r="J329" s="878" t="n"/>
       <c r="K329" s="756" t="n"/>
       <c r="L329" s="756" t="n"/>
       <c r="M329" s="756" t="n"/>
       <c r="N329" s="756" t="n"/>
       <c r="O329" s="756" t="n"/>
-      <c r="P329" s="879" t="n"/>
-      <c r="Q329" s="879" t="n"/>
+      <c r="P329" s="878" t="n"/>
+      <c r="Q329" s="878" t="n"/>
       <c r="R329" s="756" t="n"/>
       <c r="S329" s="756" t="n"/>
       <c r="T329" s="756" t="n"/>
       <c r="U329" s="756" t="n"/>
       <c r="V329" s="756" t="n"/>
-      <c r="W329" s="879" t="n"/>
-      <c r="X329" s="879" t="n"/>
+      <c r="W329" s="878" t="n"/>
+      <c r="X329" s="878" t="n"/>
       <c r="Y329" s="756" t="n"/>
       <c r="Z329" s="756" t="n"/>
       <c r="AA329" s="756" t="n"/>
       <c r="AB329" s="756" t="n"/>
       <c r="AC329" s="756" t="n"/>
-      <c r="AD329" s="879" t="n"/>
-      <c r="AE329" s="879" t="n"/>
+      <c r="AD329" s="878" t="n"/>
+      <c r="AE329" s="878" t="n"/>
       <c r="AF329" s="756" t="n"/>
       <c r="AG329" s="756" t="n"/>
       <c r="AH329" s="756" t="n"/>
@@ -31346,11 +31346,11 @@
       <c r="AG332" s="156" t="n"/>
       <c r="AH332" s="142" t="n"/>
       <c r="AI332" s="500" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK332" s="877" t="inlineStr">
         <is>
-          <t>Festius: 06/12 Dia de la Constitució (Nacional) · 08/12 Immaculada Concepció (Nacional) · 25/12 Nadal (Nacional) · Vacances: 23/12–31/12</t>
+          <t>Festius: 06/12 Dia de la Constitució (Nacional) · 07/12 Festiu local (canvi pel 15/09) · 08/12 Immaculada Concepció (Nacional) · 25/12 Nadal (Nacional) · Vacances: 23/12–31/12</t>
         </is>
       </c>
     </row>
@@ -31476,29 +31476,29 @@
       <c r="D334" s="756" t="n"/>
       <c r="E334" s="756" t="n"/>
       <c r="F334" s="756" t="n"/>
-      <c r="G334" s="879" t="n"/>
-      <c r="H334" s="879" t="n"/>
-      <c r="I334" s="878" t="n"/>
-      <c r="J334" s="756" t="n"/>
-      <c r="K334" s="878" t="n"/>
+      <c r="G334" s="878" t="n"/>
+      <c r="H334" s="878" t="n"/>
+      <c r="I334" s="879" t="n"/>
+      <c r="J334" s="879" t="n"/>
+      <c r="K334" s="879" t="n"/>
       <c r="L334" s="756" t="n"/>
       <c r="M334" s="756" t="n"/>
-      <c r="N334" s="879" t="n"/>
-      <c r="O334" s="879" t="n"/>
+      <c r="N334" s="878" t="n"/>
+      <c r="O334" s="878" t="n"/>
       <c r="P334" s="756" t="n"/>
       <c r="Q334" s="756" t="n"/>
       <c r="R334" s="756" t="n"/>
       <c r="S334" s="756" t="n"/>
       <c r="T334" s="756" t="n"/>
-      <c r="U334" s="879" t="n"/>
-      <c r="V334" s="879" t="n"/>
+      <c r="U334" s="878" t="n"/>
+      <c r="V334" s="878" t="n"/>
       <c r="W334" s="756" t="n"/>
       <c r="X334" s="756" t="n"/>
       <c r="Y334" s="756" t="n"/>
       <c r="Z334" s="886" t="n"/>
       <c r="AA334" s="886" t="n"/>
-      <c r="AB334" s="878" t="n"/>
-      <c r="AC334" s="879" t="n"/>
+      <c r="AB334" s="879" t="n"/>
+      <c r="AC334" s="878" t="n"/>
       <c r="AD334" s="886" t="n"/>
       <c r="AE334" s="886" t="n"/>
       <c r="AF334" s="886" t="n"/>
@@ -31517,29 +31517,29 @@
       <c r="D335" s="782" t="n"/>
       <c r="E335" s="756" t="n"/>
       <c r="F335" s="756" t="n"/>
-      <c r="G335" s="879" t="n"/>
-      <c r="H335" s="879" t="n"/>
-      <c r="I335" s="878" t="n"/>
-      <c r="J335" s="756" t="n"/>
-      <c r="K335" s="878" t="n"/>
+      <c r="G335" s="878" t="n"/>
+      <c r="H335" s="878" t="n"/>
+      <c r="I335" s="879" t="n"/>
+      <c r="J335" s="879" t="n"/>
+      <c r="K335" s="879" t="n"/>
       <c r="L335" s="756" t="n"/>
       <c r="M335" s="756" t="n"/>
-      <c r="N335" s="879" t="n"/>
-      <c r="O335" s="879" t="n"/>
+      <c r="N335" s="878" t="n"/>
+      <c r="O335" s="878" t="n"/>
       <c r="P335" s="756" t="n"/>
       <c r="Q335" s="756" t="n"/>
       <c r="R335" s="756" t="n"/>
       <c r="S335" s="756" t="n"/>
       <c r="T335" s="756" t="n"/>
-      <c r="U335" s="879" t="n"/>
-      <c r="V335" s="879" t="n"/>
+      <c r="U335" s="878" t="n"/>
+      <c r="V335" s="878" t="n"/>
       <c r="W335" s="756" t="n"/>
       <c r="X335" s="756" t="n"/>
       <c r="Y335" s="756" t="n"/>
       <c r="Z335" s="886" t="n"/>
       <c r="AA335" s="886" t="n"/>
-      <c r="AB335" s="878" t="n"/>
-      <c r="AC335" s="879" t="n"/>
+      <c r="AB335" s="879" t="n"/>
+      <c r="AC335" s="878" t="n"/>
       <c r="AD335" s="886" t="n"/>
       <c r="AE335" s="886" t="n"/>
       <c r="AF335" s="886" t="n"/>
@@ -31558,29 +31558,29 @@
       <c r="D336" s="783" t="n"/>
       <c r="E336" s="778" t="n"/>
       <c r="F336" s="778" t="n"/>
-      <c r="G336" s="881" t="n"/>
-      <c r="H336" s="881" t="n"/>
-      <c r="I336" s="880" t="n"/>
-      <c r="J336" s="778" t="n"/>
-      <c r="K336" s="880" t="n"/>
+      <c r="G336" s="880" t="n"/>
+      <c r="H336" s="880" t="n"/>
+      <c r="I336" s="881" t="n"/>
+      <c r="J336" s="881" t="n"/>
+      <c r="K336" s="881" t="n"/>
       <c r="L336" s="778" t="n"/>
       <c r="M336" s="778" t="n"/>
-      <c r="N336" s="881" t="n"/>
-      <c r="O336" s="881" t="n"/>
+      <c r="N336" s="880" t="n"/>
+      <c r="O336" s="880" t="n"/>
       <c r="P336" s="778" t="n"/>
       <c r="Q336" s="778" t="n"/>
       <c r="R336" s="778" t="n"/>
       <c r="S336" s="778" t="n"/>
       <c r="T336" s="778" t="n"/>
-      <c r="U336" s="881" t="n"/>
-      <c r="V336" s="881" t="n"/>
+      <c r="U336" s="880" t="n"/>
+      <c r="V336" s="880" t="n"/>
       <c r="W336" s="778" t="n"/>
       <c r="X336" s="778" t="n"/>
       <c r="Y336" s="778" t="n"/>
       <c r="Z336" s="887" t="n"/>
       <c r="AA336" s="887" t="n"/>
-      <c r="AB336" s="880" t="n"/>
-      <c r="AC336" s="881" t="n"/>
+      <c r="AB336" s="881" t="n"/>
+      <c r="AC336" s="880" t="n"/>
       <c r="AD336" s="887" t="n"/>
       <c r="AE336" s="887" t="n"/>
       <c r="AF336" s="887" t="n"/>
@@ -31599,29 +31599,29 @@
       <c r="D337" s="755" t="n"/>
       <c r="E337" s="756" t="n"/>
       <c r="F337" s="756" t="n"/>
-      <c r="G337" s="879" t="n"/>
-      <c r="H337" s="879" t="n"/>
-      <c r="I337" s="878" t="n"/>
-      <c r="J337" s="756" t="n"/>
-      <c r="K337" s="878" t="n"/>
+      <c r="G337" s="878" t="n"/>
+      <c r="H337" s="878" t="n"/>
+      <c r="I337" s="879" t="n"/>
+      <c r="J337" s="879" t="n"/>
+      <c r="K337" s="879" t="n"/>
       <c r="L337" s="756" t="n"/>
       <c r="M337" s="756" t="n"/>
-      <c r="N337" s="879" t="n"/>
-      <c r="O337" s="879" t="n"/>
+      <c r="N337" s="878" t="n"/>
+      <c r="O337" s="878" t="n"/>
       <c r="P337" s="756" t="n"/>
       <c r="Q337" s="756" t="n"/>
       <c r="R337" s="756" t="n"/>
       <c r="S337" s="756" t="n"/>
       <c r="T337" s="756" t="n"/>
-      <c r="U337" s="879" t="n"/>
-      <c r="V337" s="879" t="n"/>
+      <c r="U337" s="878" t="n"/>
+      <c r="V337" s="878" t="n"/>
       <c r="W337" s="756" t="n"/>
       <c r="X337" s="756" t="n"/>
       <c r="Y337" s="756" t="n"/>
       <c r="Z337" s="886" t="n"/>
       <c r="AA337" s="886" t="n"/>
-      <c r="AB337" s="878" t="n"/>
-      <c r="AC337" s="879" t="n"/>
+      <c r="AB337" s="879" t="n"/>
+      <c r="AC337" s="878" t="n"/>
       <c r="AD337" s="886" t="n"/>
       <c r="AE337" s="886" t="n"/>
       <c r="AF337" s="886" t="n"/>
@@ -31640,29 +31640,29 @@
       <c r="D338" s="756" t="n"/>
       <c r="E338" s="756" t="n"/>
       <c r="F338" s="756" t="n"/>
-      <c r="G338" s="879" t="n"/>
-      <c r="H338" s="879" t="n"/>
-      <c r="I338" s="878" t="n"/>
-      <c r="J338" s="756" t="n"/>
-      <c r="K338" s="878" t="n"/>
+      <c r="G338" s="878" t="n"/>
+      <c r="H338" s="878" t="n"/>
+      <c r="I338" s="879" t="n"/>
+      <c r="J338" s="879" t="n"/>
+      <c r="K338" s="879" t="n"/>
       <c r="L338" s="756" t="n"/>
       <c r="M338" s="756" t="n"/>
-      <c r="N338" s="879" t="n"/>
-      <c r="O338" s="879" t="n"/>
+      <c r="N338" s="878" t="n"/>
+      <c r="O338" s="878" t="n"/>
       <c r="P338" s="756" t="n"/>
       <c r="Q338" s="756" t="n"/>
       <c r="R338" s="756" t="n"/>
       <c r="S338" s="756" t="n"/>
       <c r="T338" s="756" t="n"/>
-      <c r="U338" s="879" t="n"/>
-      <c r="V338" s="879" t="n"/>
+      <c r="U338" s="878" t="n"/>
+      <c r="V338" s="878" t="n"/>
       <c r="W338" s="756" t="n"/>
       <c r="X338" s="756" t="n"/>
       <c r="Y338" s="756" t="n"/>
       <c r="Z338" s="886" t="n"/>
       <c r="AA338" s="886" t="n"/>
-      <c r="AB338" s="878" t="n"/>
-      <c r="AC338" s="879" t="n"/>
+      <c r="AB338" s="879" t="n"/>
+      <c r="AC338" s="878" t="n"/>
       <c r="AD338" s="886" t="n"/>
       <c r="AE338" s="886" t="n"/>
       <c r="AF338" s="886" t="n"/>
@@ -31680,29 +31680,29 @@
       <c r="D339" s="783" t="n"/>
       <c r="E339" s="778" t="n"/>
       <c r="F339" s="778" t="n"/>
-      <c r="G339" s="881" t="n"/>
-      <c r="H339" s="881" t="n"/>
-      <c r="I339" s="880" t="n"/>
-      <c r="J339" s="778" t="n"/>
-      <c r="K339" s="880" t="n"/>
+      <c r="G339" s="880" t="n"/>
+      <c r="H339" s="880" t="n"/>
+      <c r="I339" s="881" t="n"/>
+      <c r="J339" s="881" t="n"/>
+      <c r="K339" s="881" t="n"/>
       <c r="L339" s="778" t="n"/>
       <c r="M339" s="778" t="n"/>
-      <c r="N339" s="881" t="n"/>
-      <c r="O339" s="881" t="n"/>
+      <c r="N339" s="880" t="n"/>
+      <c r="O339" s="880" t="n"/>
       <c r="P339" s="778" t="n"/>
       <c r="Q339" s="778" t="n"/>
       <c r="R339" s="778" t="n"/>
       <c r="S339" s="778" t="n"/>
       <c r="T339" s="778" t="n"/>
-      <c r="U339" s="881" t="n"/>
-      <c r="V339" s="881" t="n"/>
+      <c r="U339" s="880" t="n"/>
+      <c r="V339" s="880" t="n"/>
       <c r="W339" s="778" t="n"/>
       <c r="X339" s="778" t="n"/>
       <c r="Y339" s="778" t="n"/>
       <c r="Z339" s="887" t="n"/>
       <c r="AA339" s="887" t="n"/>
-      <c r="AB339" s="880" t="n"/>
-      <c r="AC339" s="881" t="n"/>
+      <c r="AB339" s="881" t="n"/>
+      <c r="AC339" s="880" t="n"/>
       <c r="AD339" s="887" t="n"/>
       <c r="AE339" s="887" t="n"/>
       <c r="AF339" s="887" t="n"/>
@@ -31720,29 +31720,29 @@
       <c r="D340" s="755" t="n"/>
       <c r="E340" s="755" t="n"/>
       <c r="F340" s="756" t="n"/>
-      <c r="G340" s="883" t="n"/>
-      <c r="H340" s="879" t="n"/>
-      <c r="I340" s="882" t="n"/>
-      <c r="J340" s="756" t="n"/>
-      <c r="K340" s="882" t="n"/>
+      <c r="G340" s="882" t="n"/>
+      <c r="H340" s="878" t="n"/>
+      <c r="I340" s="883" t="n"/>
+      <c r="J340" s="879" t="n"/>
+      <c r="K340" s="883" t="n"/>
       <c r="L340" s="756" t="n"/>
       <c r="M340" s="756" t="n"/>
-      <c r="N340" s="883" t="n"/>
-      <c r="O340" s="883" t="n"/>
+      <c r="N340" s="882" t="n"/>
+      <c r="O340" s="882" t="n"/>
       <c r="P340" s="756" t="n"/>
       <c r="Q340" s="756" t="n"/>
       <c r="R340" s="755" t="n"/>
       <c r="S340" s="756" t="n"/>
       <c r="T340" s="756" t="n"/>
-      <c r="U340" s="883" t="n"/>
-      <c r="V340" s="883" t="n"/>
+      <c r="U340" s="882" t="n"/>
+      <c r="V340" s="882" t="n"/>
       <c r="W340" s="756" t="n"/>
       <c r="X340" s="756" t="n"/>
       <c r="Y340" s="755" t="n"/>
       <c r="Z340" s="886" t="n"/>
       <c r="AA340" s="886" t="n"/>
-      <c r="AB340" s="882" t="n"/>
-      <c r="AC340" s="883" t="n"/>
+      <c r="AB340" s="883" t="n"/>
+      <c r="AC340" s="882" t="n"/>
       <c r="AD340" s="886" t="n"/>
       <c r="AE340" s="886" t="n"/>
       <c r="AF340" s="888" t="n"/>
@@ -31760,29 +31760,29 @@
       <c r="D341" s="756" t="n"/>
       <c r="E341" s="756" t="n"/>
       <c r="F341" s="756" t="n"/>
-      <c r="G341" s="879" t="n"/>
-      <c r="H341" s="879" t="n"/>
-      <c r="I341" s="878" t="n"/>
-      <c r="J341" s="756" t="n"/>
-      <c r="K341" s="878" t="n"/>
+      <c r="G341" s="878" t="n"/>
+      <c r="H341" s="878" t="n"/>
+      <c r="I341" s="879" t="n"/>
+      <c r="J341" s="879" t="n"/>
+      <c r="K341" s="879" t="n"/>
       <c r="L341" s="756" t="n"/>
       <c r="M341" s="756" t="n"/>
-      <c r="N341" s="879" t="n"/>
-      <c r="O341" s="879" t="n"/>
+      <c r="N341" s="878" t="n"/>
+      <c r="O341" s="878" t="n"/>
       <c r="P341" s="756" t="n"/>
       <c r="Q341" s="756" t="n"/>
       <c r="R341" s="756" t="n"/>
       <c r="S341" s="756" t="n"/>
       <c r="T341" s="756" t="n"/>
-      <c r="U341" s="879" t="n"/>
-      <c r="V341" s="879" t="n"/>
+      <c r="U341" s="878" t="n"/>
+      <c r="V341" s="878" t="n"/>
       <c r="W341" s="756" t="n"/>
       <c r="X341" s="756" t="n"/>
       <c r="Y341" s="756" t="n"/>
       <c r="Z341" s="886" t="n"/>
       <c r="AA341" s="886" t="n"/>
-      <c r="AB341" s="878" t="n"/>
-      <c r="AC341" s="879" t="n"/>
+      <c r="AB341" s="879" t="n"/>
+      <c r="AC341" s="878" t="n"/>
       <c r="AD341" s="886" t="n"/>
       <c r="AE341" s="886" t="n"/>
       <c r="AF341" s="886" t="n"/>
@@ -31800,29 +31800,29 @@
       <c r="D342" s="756" t="n"/>
       <c r="E342" s="756" t="n"/>
       <c r="F342" s="756" t="n"/>
-      <c r="G342" s="879" t="n"/>
-      <c r="H342" s="879" t="n"/>
-      <c r="I342" s="878" t="n"/>
-      <c r="J342" s="756" t="n"/>
-      <c r="K342" s="878" t="n"/>
+      <c r="G342" s="878" t="n"/>
+      <c r="H342" s="878" t="n"/>
+      <c r="I342" s="879" t="n"/>
+      <c r="J342" s="879" t="n"/>
+      <c r="K342" s="879" t="n"/>
       <c r="L342" s="756" t="n"/>
       <c r="M342" s="756" t="n"/>
-      <c r="N342" s="879" t="n"/>
-      <c r="O342" s="879" t="n"/>
+      <c r="N342" s="878" t="n"/>
+      <c r="O342" s="878" t="n"/>
       <c r="P342" s="756" t="n"/>
       <c r="Q342" s="756" t="n"/>
       <c r="R342" s="756" t="n"/>
       <c r="S342" s="756" t="n"/>
       <c r="T342" s="756" t="n"/>
-      <c r="U342" s="879" t="n"/>
-      <c r="V342" s="879" t="n"/>
+      <c r="U342" s="878" t="n"/>
+      <c r="V342" s="878" t="n"/>
       <c r="W342" s="756" t="n"/>
       <c r="X342" s="756" t="n"/>
       <c r="Y342" s="756" t="n"/>
       <c r="Z342" s="886" t="n"/>
       <c r="AA342" s="886" t="n"/>
-      <c r="AB342" s="878" t="n"/>
-      <c r="AC342" s="879" t="n"/>
+      <c r="AB342" s="879" t="n"/>
+      <c r="AC342" s="878" t="n"/>
       <c r="AD342" s="886" t="n"/>
       <c r="AE342" s="886" t="n"/>
       <c r="AF342" s="886" t="n"/>

--- a/cronograma/CRONOGRAMA_26-27_PROVISIONAL.xlsx
+++ b/cronograma/CRONOGRAMA_26-27_PROVISIONAL.xlsx
@@ -609,7 +609,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="95">
+  <fills count="99">
     <fill>
       <patternFill/>
     </fill>
@@ -1115,6 +1115,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCE5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5A6BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE5CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C4C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -2112,7 +2132,7 @@
     <xf numFmtId="44" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="34" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="919">
+  <cellXfs count="942">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3433,27 +3453,45 @@
     <xf numFmtId="49" fontId="67" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="80" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="73" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="80" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="73" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="80" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="77" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="74" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="77" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="74" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="77" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="83" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="75" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="83" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="75" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="83" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="76" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="73" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="74" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="75" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="76" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="86" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="86" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="86" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="89" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="89" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="89" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="70" fillId="71" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3468,36 +3506,52 @@
     </xf>
     <xf numFmtId="0" fontId="72" fillId="71" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="72" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="85" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="83" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="85" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="83" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="85" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="83" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="76" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="76" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="77" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="77" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="70" fillId="78" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="78" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="72" fillId="77" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="78" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="83" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="72" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="36" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="91" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="73" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="91" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="73" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="89" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="91" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="72" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="84" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="73" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="81" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="84" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="81" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="72" fillId="84" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="78" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="78" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="36" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="79" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3507,35 +3561,91 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="79" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="92" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="92" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="92" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="87" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="87" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="85" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="85" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="85" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="87" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="90" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="90" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="90" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="80" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="80" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="81" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="81" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="80" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="81" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="84" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="88" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="88" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="88" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="92" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="93" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="93" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="93" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="81" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="80" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="81" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="94" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="94" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="94" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="84" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="84" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="84" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="86" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="93" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="71" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="86" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="71" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="86" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="74" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="74" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="75" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="75" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="74" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="75" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="94" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="70" fillId="82" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3543,71 +3653,26 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="82" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="87" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="87" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="87" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="86" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="75" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="88" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="88" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="88" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="87" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="78" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="88" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="89" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="89" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="88" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="89" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="76" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="76" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="76" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="90" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="90" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="89" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="90" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="76" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="71" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="82" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="91" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="92" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="91" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="92" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="91" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="92" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="92" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="92" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="93" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="93" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="93" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="96" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="96" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="96" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="96" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="96" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="94" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="77" fillId="98" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="80" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="73" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3619,61 +3684,73 @@
     <xf numFmtId="166" fontId="78" fillId="0" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="77" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="86" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="89" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="71" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="83" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="71" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="74" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="72" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="75" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="76" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="77" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="91" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="84" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="78" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="79" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="92" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="87" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="85" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="78" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="90" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="72" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="80" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="73" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="93" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="88" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="81" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="86" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="79" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="84" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="74" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="87" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="94" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="82" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="75" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="88" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="89" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="90" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="76" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -23555,15 +23632,21 @@
       </c>
       <c r="AA154" s="24" t="n"/>
       <c r="AB154" s="24" t="n"/>
-      <c r="AC154" s="807" t="n">
+      <c r="AC154" s="808" t="n">
         <v>5</v>
       </c>
-      <c r="AD154" s="807" t="n">
+      <c r="AD154" s="809" t="n">
         <v>5</v>
       </c>
-      <c r="AE154" s="32" t="n"/>
-      <c r="AF154" s="32" t="n"/>
-      <c r="AG154" s="32" t="n"/>
+      <c r="AE154" s="810" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF154" s="811" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG154" s="812" t="n">
+        <v>6</v>
+      </c>
       <c r="AH154" s="24" t="n"/>
       <c r="AI154" s="4" t="n"/>
       <c r="AJ154">
@@ -23576,12 +23659,27 @@
         </is>
       </c>
       <c r="AL154" s="289" t="n"/>
-      <c r="AM154" s="808" t="inlineStr">
-        <is>
-          <t>CTRP0005 Coaching de fortaleses · RAMON · GOOGLE matí 9:00-15:00 · 19/10–27/10 · 40 h</t>
+      <c r="AM154" s="813" t="inlineStr">
+        <is>
+          <t>FCOS02 BASIC PREVENCIO DE RISCOS LABORALS [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 19/10–23/10 · 30 h</t>
         </is>
       </c>
       <c r="AN154" s="637" t="n"/>
+      <c r="AV154" s="814" t="inlineStr">
+        <is>
+          <t>CTRH0011 DRETS I DEURES LABORALS [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-14:00 · 26/10–27/10 · 10 h</t>
+        </is>
+      </c>
+      <c r="BE154" s="815" t="inlineStr">
+        <is>
+          <t>CTRHI0015 IGUALTAT DE GÈNERE EN L'AMBIT LABORAL [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-14:00 · 28/10–29/10 · 10 h</t>
+        </is>
+      </c>
+      <c r="BN154" s="816" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15.75" customHeight="1" s="757">
       <c r="A155" s="10" t="inlineStr">
@@ -23609,22 +23707,40 @@
       <c r="S155" s="756" t="n"/>
       <c r="T155" s="24" t="n"/>
       <c r="U155" s="24" t="n"/>
-      <c r="V155" s="756" t="n"/>
-      <c r="W155" s="756" t="n"/>
-      <c r="X155" s="756" t="n"/>
-      <c r="Y155" s="756" t="n"/>
-      <c r="Z155" s="756" t="n"/>
+      <c r="V155" s="817" t="n">
+        <v>6</v>
+      </c>
+      <c r="W155" s="818" t="n">
+        <v>6</v>
+      </c>
+      <c r="X155" s="818" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y155" s="818" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z155" s="818" t="n">
+        <v>6</v>
+      </c>
       <c r="AA155" s="24" t="n"/>
       <c r="AB155" s="24" t="n"/>
-      <c r="AC155" s="756" t="n"/>
-      <c r="AD155" s="756" t="n"/>
+      <c r="AC155" s="818" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD155" s="818" t="n">
+        <v>5</v>
+      </c>
       <c r="AE155" s="756" t="n"/>
       <c r="AF155" s="756" t="n"/>
       <c r="AG155" s="756" t="n"/>
       <c r="AH155" s="24" t="n"/>
       <c r="AI155" s="4" t="n"/>
       <c r="AK155" s="774" t="n"/>
-      <c r="AL155" s="774" t="n"/>
+      <c r="AL155" s="819" t="inlineStr">
+        <is>
+          <t>CTRP0005 Coaching de fortaleses · RAMON · FIREFOX matí 9:00-15:00 · 19/10–27/10 · 40 h</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="16.5" customHeight="1" s="757" thickBot="1">
       <c r="A156" s="14" t="inlineStr">
@@ -23652,21 +23768,46 @@
       <c r="S156" s="778" t="n"/>
       <c r="T156" s="35" t="n"/>
       <c r="U156" s="35" t="n"/>
-      <c r="V156" s="778" t="n"/>
-      <c r="W156" s="778" t="n"/>
-      <c r="X156" s="778" t="n"/>
-      <c r="Y156" s="778" t="n"/>
-      <c r="Z156" s="778" t="n"/>
+      <c r="V156" s="820" t="n">
+        <v>6</v>
+      </c>
+      <c r="W156" s="821" t="n">
+        <v>6</v>
+      </c>
+      <c r="X156" s="821" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y156" s="821" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z156" s="821" t="n">
+        <v>6</v>
+      </c>
       <c r="AA156" s="35" t="n"/>
       <c r="AB156" s="35" t="n"/>
-      <c r="AC156" s="778" t="n"/>
-      <c r="AD156" s="778" t="n"/>
-      <c r="AE156" s="778" t="n"/>
-      <c r="AF156" s="778" t="n"/>
-      <c r="AG156" s="778" t="n"/>
+      <c r="AC156" s="821" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD156" s="821" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE156" s="821" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF156" s="821" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG156" s="821" t="n">
+        <v>6</v>
+      </c>
       <c r="AH156" s="35" t="n"/>
       <c r="AI156" s="4" t="n"/>
       <c r="AK156" s="775" t="n"/>
+      <c r="AL156" s="822" t="inlineStr">
+        <is>
+          <t>CTRL0040 CTRL0040_2024_Català A1 (Català nivell inicial A1) · PER ASSIGNAR · COPILOT matí 9:00-15:00 · 19/10–06/11 · 90 h</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="16.5" customHeight="1" s="757" thickTop="1">
       <c r="A157" s="17" t="inlineStr">
@@ -23791,24 +23932,38 @@
       <c r="S158" s="756" t="n"/>
       <c r="T158" s="24" t="n"/>
       <c r="U158" s="24" t="n"/>
-      <c r="V158" s="809" t="n">
+      <c r="V158" s="823" t="n">
         <v>6</v>
       </c>
-      <c r="W158" s="810" t="n">
-        <v>5</v>
-      </c>
-      <c r="X158" s="810" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y158" s="756" t="n"/>
-      <c r="Z158" s="756" t="n"/>
+      <c r="W158" s="824" t="n">
+        <v>6</v>
+      </c>
+      <c r="X158" s="824" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y158" s="824" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z158" s="824" t="n">
+        <v>6</v>
+      </c>
       <c r="AA158" s="24" t="n"/>
       <c r="AB158" s="24" t="n"/>
-      <c r="AC158" s="756" t="n"/>
-      <c r="AD158" s="756" t="n"/>
-      <c r="AE158" s="756" t="n"/>
-      <c r="AF158" s="756" t="n"/>
-      <c r="AG158" s="756" t="n"/>
+      <c r="AC158" s="825" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD158" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE158" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF158" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG158" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="AH158" s="24" t="n"/>
       <c r="AJ158" s="428">
         <f>AM145+4</f>
@@ -23819,9 +23974,14 @@
           <t>PNL2 15- 20</t>
         </is>
       </c>
-      <c r="AM158" s="811" t="inlineStr">
-        <is>
-          <t>IMPE0006 Biomagnetisme aplicat a l'estètica · ESTHER · FIREFOX tarda 15:00-21:00 · 19/10–21/10 · 16 h</t>
+      <c r="AM158" s="827" t="inlineStr">
+        <is>
+          <t>FCOS02 BASIC PREVENCIO DE RISCOS LABORALS [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 19/10–23/10 · 30 h</t>
+        </is>
+      </c>
+      <c r="AV158" s="828" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
         </is>
       </c>
     </row>
@@ -23851,42 +24011,28 @@
       <c r="S159" s="778" t="n"/>
       <c r="T159" s="35" t="n"/>
       <c r="U159" s="35" t="n"/>
-      <c r="V159" s="812" t="n">
+      <c r="V159" s="829" t="n">
         <v>6</v>
       </c>
-      <c r="W159" s="813" t="n">
-        <v>6</v>
-      </c>
-      <c r="X159" s="813" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y159" s="813" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z159" s="813" t="n">
-        <v>6</v>
-      </c>
+      <c r="W159" s="830" t="n">
+        <v>5</v>
+      </c>
+      <c r="X159" s="830" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y159" s="778" t="n"/>
+      <c r="Z159" s="778" t="n"/>
       <c r="AA159" s="35" t="n"/>
       <c r="AB159" s="35" t="n"/>
-      <c r="AC159" s="813" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD159" s="813" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE159" s="813" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF159" s="813" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG159" s="813" t="n">
-        <v>6</v>
-      </c>
+      <c r="AC159" s="778" t="n"/>
+      <c r="AD159" s="778" t="n"/>
+      <c r="AE159" s="778" t="n"/>
+      <c r="AF159" s="778" t="n"/>
+      <c r="AG159" s="778" t="n"/>
       <c r="AH159" s="35" t="n"/>
-      <c r="AL159" s="814" t="inlineStr">
-        <is>
-          <t>CTRL0040 CTRL0040_2024_Català A1 (Català nivell inicial A1) · PER ASSIGNAR · COPILOT tarda 15:00-21:00 · 19/10–06/11 · 90 h</t>
+      <c r="AL159" s="831" t="inlineStr">
+        <is>
+          <t>IMPE0006 Biomagnetisme aplicat a l'estètica · ESTHER · COPILOT tarda 15:00-21:00 · 19/10–21/10 · 16 h</t>
         </is>
       </c>
     </row>
@@ -24182,60 +24328,76 @@
       <c r="B165" s="11" t="n"/>
       <c r="C165" s="11" t="n"/>
       <c r="D165" s="24" t="n"/>
-      <c r="E165" s="815" t="n">
+      <c r="E165" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="F165" s="816" t="n">
+      <c r="F165" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="G165" s="816" t="n">
+      <c r="G165" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="H165" s="816" t="n">
+      <c r="H165" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="I165" s="816" t="n">
+      <c r="I165" s="832" t="n">
         <v>6</v>
       </c>
       <c r="J165" s="24" t="n"/>
       <c r="K165" s="24" t="n"/>
-      <c r="L165" s="816" t="n">
-        <v>5</v>
-      </c>
-      <c r="M165" s="816" t="n">
-        <v>5</v>
-      </c>
-      <c r="N165" s="756" t="n"/>
-      <c r="O165" s="756" t="n"/>
-      <c r="P165" s="756" t="n"/>
+      <c r="L165" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="M165" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="N165" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="O165" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="P165" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="Q165" s="24" t="n"/>
       <c r="R165" s="24" t="n"/>
-      <c r="S165" s="756" t="n"/>
-      <c r="T165" s="756" t="n"/>
-      <c r="U165" s="756" t="n"/>
-      <c r="V165" s="756" t="n"/>
-      <c r="W165" s="756" t="n"/>
+      <c r="S165" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="T165" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="U165" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="V165" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="W165" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="X165" s="24" t="n"/>
       <c r="Y165" s="24" t="n"/>
-      <c r="Z165" s="817" t="n">
+      <c r="Z165" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="AA165" s="818" t="n">
+      <c r="AA165" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="AB165" s="818" t="n">
+      <c r="AB165" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="AC165" s="818" t="n">
+      <c r="AC165" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="AD165" s="818" t="n">
+      <c r="AD165" s="832" t="n">
         <v>6</v>
       </c>
       <c r="AE165" s="24" t="n"/>
       <c r="AF165" s="24" t="n"/>
-      <c r="AG165" s="818" t="n">
-        <v>5</v>
+      <c r="AG165" s="832" t="n">
+        <v>6</v>
       </c>
       <c r="AH165" s="756" t="n"/>
       <c r="AI165" s="4" t="n"/>
@@ -24243,14 +24405,9 @@
         <f>AJ154+AI163</f>
         <v/>
       </c>
-      <c r="AL165" s="819" t="inlineStr">
-        <is>
-          <t>FCOI18 Comunicació i col·laboració amb eines digitals (ACTIC Nivell bàsic) · MARIA · GOOGLE matí 9:00-15:00 · 02/11–10/11 · 40 h</t>
-        </is>
-      </c>
-      <c r="AU165" s="820" t="inlineStr">
-        <is>
-          <t>FCOI15 Creació de continguts digitals (ACTIC Nivell bàsic) · MARIA · GOOGLE matí 9:00-15:00 · 23/11–01/12 · 40 h</t>
+      <c r="AL165" s="833" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
         </is>
       </c>
     </row>
@@ -24263,28 +24420,32 @@
       <c r="B166" s="456" t="n"/>
       <c r="C166" s="456" t="n"/>
       <c r="D166" s="119" t="n"/>
-      <c r="E166" s="756" t="n"/>
-      <c r="F166" s="756" t="n"/>
-      <c r="G166" s="756" t="n"/>
-      <c r="H166" s="756" t="n"/>
-      <c r="I166" s="756" t="n"/>
+      <c r="E166" s="834" t="n">
+        <v>6</v>
+      </c>
+      <c r="F166" s="835" t="n">
+        <v>6</v>
+      </c>
+      <c r="G166" s="835" t="n">
+        <v>6</v>
+      </c>
+      <c r="H166" s="835" t="n">
+        <v>6</v>
+      </c>
+      <c r="I166" s="835" t="n">
+        <v>6</v>
+      </c>
       <c r="J166" s="24" t="n"/>
       <c r="K166" s="24" t="n"/>
-      <c r="L166" s="821" t="n">
-        <v>6</v>
-      </c>
-      <c r="M166" s="822" t="n">
-        <v>6</v>
-      </c>
-      <c r="N166" s="822" t="n">
-        <v>6</v>
-      </c>
-      <c r="O166" s="822" t="n">
-        <v>6</v>
-      </c>
-      <c r="P166" s="822" t="n">
-        <v>6</v>
-      </c>
+      <c r="L166" s="835" t="n">
+        <v>5</v>
+      </c>
+      <c r="M166" s="835" t="n">
+        <v>5</v>
+      </c>
+      <c r="N166" s="756" t="n"/>
+      <c r="O166" s="756" t="n"/>
+      <c r="P166" s="756" t="n"/>
       <c r="Q166" s="24" t="n"/>
       <c r="R166" s="24" t="n"/>
       <c r="S166" s="756" t="n"/>
@@ -24294,23 +24455,40 @@
       <c r="W166" s="756" t="n"/>
       <c r="X166" s="24" t="n"/>
       <c r="Y166" s="24" t="n"/>
-      <c r="Z166" s="756" t="n"/>
-      <c r="AA166" s="756" t="n"/>
-      <c r="AB166" s="756" t="n"/>
-      <c r="AC166" s="756" t="n"/>
-      <c r="AD166" s="756" t="n"/>
+      <c r="Z166" s="836" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA166" s="837" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB166" s="837" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC166" s="837" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD166" s="837" t="n">
+        <v>6</v>
+      </c>
       <c r="AE166" s="24" t="n"/>
       <c r="AF166" s="24" t="n"/>
-      <c r="AG166" s="756" t="n"/>
+      <c r="AG166" s="837" t="n">
+        <v>5</v>
+      </c>
       <c r="AH166" s="756" t="n"/>
       <c r="AI166" s="4" t="n"/>
       <c r="AK166" s="774" t="n"/>
-      <c r="AL166" s="823" t="inlineStr">
-        <is>
-          <t>COMM0009 Atenció al client · TANIA/? · FIREFOX matí 9:00-15:00 · 09/11–13/11 · 30 h</t>
+      <c r="AL166" s="838" t="inlineStr">
+        <is>
+          <t>FCOI18 Comunicació i col·laboració amb eines digitals (ACTIC Nivell bàsic) · MARIA · FIREFOX matí 9:00-15:00 · 02/11–10/11 · 40 h</t>
         </is>
       </c>
       <c r="AM166" s="774" t="n"/>
+      <c r="AU166" s="839" t="inlineStr">
+        <is>
+          <t>FCOI15 Creació de continguts digitals (ACTIC Nivell bàsic) · MARIA · FIREFOX matí 9:00-15:00 · 23/11–01/12 · 40 h</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="16.5" customHeight="1" s="757" thickBot="1">
       <c r="A167" s="14" t="inlineStr">
@@ -24321,18 +24499,38 @@
       <c r="B167" s="15" t="n"/>
       <c r="C167" s="15" t="n"/>
       <c r="D167" s="35" t="n"/>
-      <c r="E167" s="778" t="n"/>
-      <c r="F167" s="778" t="n"/>
-      <c r="G167" s="778" t="n"/>
-      <c r="H167" s="778" t="n"/>
-      <c r="I167" s="778" t="n"/>
+      <c r="E167" s="821" t="n">
+        <v>6</v>
+      </c>
+      <c r="F167" s="821" t="n">
+        <v>6</v>
+      </c>
+      <c r="G167" s="821" t="n">
+        <v>6</v>
+      </c>
+      <c r="H167" s="821" t="n">
+        <v>6</v>
+      </c>
+      <c r="I167" s="821" t="n">
+        <v>6</v>
+      </c>
       <c r="J167" s="35" t="n"/>
       <c r="K167" s="35" t="n"/>
-      <c r="L167" s="778" t="n"/>
-      <c r="M167" s="778" t="n"/>
-      <c r="N167" s="778" t="n"/>
-      <c r="O167" s="778" t="n"/>
-      <c r="P167" s="778" t="n"/>
+      <c r="L167" s="840" t="n">
+        <v>6</v>
+      </c>
+      <c r="M167" s="841" t="n">
+        <v>6</v>
+      </c>
+      <c r="N167" s="841" t="n">
+        <v>6</v>
+      </c>
+      <c r="O167" s="841" t="n">
+        <v>6</v>
+      </c>
+      <c r="P167" s="841" t="n">
+        <v>6</v>
+      </c>
       <c r="Q167" s="35" t="n"/>
       <c r="R167" s="35" t="n"/>
       <c r="S167" s="778" t="n"/>
@@ -24353,6 +24551,16 @@
       <c r="AH167" s="778" t="n"/>
       <c r="AI167" s="4" t="n"/>
       <c r="AK167" s="775" t="n"/>
+      <c r="AL167" s="842" t="inlineStr">
+        <is>
+          <t>CTRL0040 CTRL0040_2024_Català A1 (Català nivell inicial A1) · PER ASSIGNAR · COPILOT matí 9:00-15:00 · 19/10–06/11 · 90 h</t>
+        </is>
+      </c>
+      <c r="AU167" s="843" t="inlineStr">
+        <is>
+          <t>COMM0009 Atenció al client · TANIA/? · COPILOT matí 9:00-15:00 · 09/11–13/11 · 30 h</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="16.5" customHeight="1" s="757" thickTop="1">
       <c r="A168" s="17" t="inlineStr">
@@ -24457,47 +24665,81 @@
       <c r="B169" s="11" t="n"/>
       <c r="C169" s="11" t="n"/>
       <c r="D169" s="24" t="n"/>
-      <c r="E169" s="756" t="n"/>
-      <c r="F169" s="756" t="n"/>
-      <c r="G169" s="756" t="n"/>
-      <c r="H169" s="756" t="n"/>
-      <c r="I169" s="756" t="n"/>
+      <c r="E169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="F169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="G169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="H169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="I169" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="J169" s="24" t="n"/>
       <c r="K169" s="24" t="n"/>
-      <c r="L169" s="756" t="n"/>
-      <c r="M169" s="756" t="n"/>
-      <c r="N169" s="756" t="n"/>
-      <c r="O169" s="756" t="n"/>
-      <c r="P169" s="756" t="n"/>
+      <c r="L169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="M169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="N169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="O169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="P169" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="Q169" s="24" t="n"/>
       <c r="R169" s="24" t="n"/>
-      <c r="S169" s="824" t="n">
-        <v>5</v>
-      </c>
-      <c r="T169" s="825" t="n">
-        <v>5</v>
-      </c>
-      <c r="U169" s="825" t="n">
-        <v>5</v>
-      </c>
-      <c r="V169" s="825" t="n">
-        <v>5</v>
-      </c>
-      <c r="W169" s="756" t="n"/>
+      <c r="S169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="T169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="U169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="V169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="W169" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="X169" s="24" t="n"/>
       <c r="Y169" s="24" t="n"/>
-      <c r="Z169" s="756" t="n"/>
-      <c r="AA169" s="756" t="n"/>
-      <c r="AB169" s="756" t="n"/>
-      <c r="AC169" s="756" t="n"/>
-      <c r="AD169" s="756" t="n"/>
+      <c r="Z169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC169" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD169" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="AE169" s="24" t="n"/>
       <c r="AF169" s="24" t="n"/>
-      <c r="AG169" s="756" t="n"/>
+      <c r="AG169" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="AH169" s="756" t="n"/>
-      <c r="AL169" s="826" t="inlineStr">
-        <is>
-          <t>SANP0011 Tècniques de massatge (1a ed.) · ESTHER · FIREFOX tarda 15:00-20:00 · 16/11–19/11 · 20 h</t>
+      <c r="AL169" s="844" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
         </is>
       </c>
     </row>
@@ -24510,21 +24752,11 @@
       <c r="B170" s="15" t="n"/>
       <c r="C170" s="15" t="n"/>
       <c r="D170" s="35" t="n"/>
-      <c r="E170" s="813" t="n">
-        <v>6</v>
-      </c>
-      <c r="F170" s="813" t="n">
-        <v>6</v>
-      </c>
-      <c r="G170" s="813" t="n">
-        <v>6</v>
-      </c>
-      <c r="H170" s="813" t="n">
-        <v>6</v>
-      </c>
-      <c r="I170" s="813" t="n">
-        <v>6</v>
-      </c>
+      <c r="E170" s="778" t="n"/>
+      <c r="F170" s="778" t="n"/>
+      <c r="G170" s="778" t="n"/>
+      <c r="H170" s="778" t="n"/>
+      <c r="I170" s="778" t="n"/>
       <c r="J170" s="35" t="n"/>
       <c r="K170" s="35" t="n"/>
       <c r="L170" s="778" t="n"/>
@@ -24534,10 +24766,18 @@
       <c r="P170" s="778" t="n"/>
       <c r="Q170" s="35" t="n"/>
       <c r="R170" s="35" t="n"/>
-      <c r="S170" s="778" t="n"/>
-      <c r="T170" s="778" t="n"/>
-      <c r="U170" s="778" t="n"/>
-      <c r="V170" s="778" t="n"/>
+      <c r="S170" s="845" t="n">
+        <v>5</v>
+      </c>
+      <c r="T170" s="846" t="n">
+        <v>5</v>
+      </c>
+      <c r="U170" s="846" t="n">
+        <v>5</v>
+      </c>
+      <c r="V170" s="846" t="n">
+        <v>5</v>
+      </c>
       <c r="W170" s="778" t="n"/>
       <c r="X170" s="35" t="n"/>
       <c r="Y170" s="35" t="n"/>
@@ -24550,9 +24790,9 @@
       <c r="AF170" s="35" t="n"/>
       <c r="AG170" s="778" t="n"/>
       <c r="AH170" s="778" t="n"/>
-      <c r="AL170" s="827" t="inlineStr">
-        <is>
-          <t>CTRL0040 CTRL0040_2024_Català A1 (Català nivell inicial A1) · PER ASSIGNAR · COPILOT tarda 15:00-21:00 · 19/10–06/11 · 90 h</t>
+      <c r="AL170" s="847" t="inlineStr">
+        <is>
+          <t>SANP0011 Tècniques de massatge (1a ed.) · ESTHER · COPILOT tarda 15:00-20:00 · 16/11–19/11 · 20 h</t>
         </is>
       </c>
     </row>
@@ -24763,31 +25003,59 @@
       </c>
       <c r="B175" s="11" t="n"/>
       <c r="C175" s="11" t="n"/>
-      <c r="D175" s="818" t="n">
-        <v>5</v>
-      </c>
-      <c r="E175" s="32" t="n"/>
-      <c r="F175" s="32" t="n"/>
-      <c r="G175" s="32" t="n"/>
+      <c r="D175" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="E175" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="F175" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="G175" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="H175" s="24" t="n"/>
       <c r="I175" s="24" t="n"/>
       <c r="J175" s="26" t="n"/>
       <c r="K175" s="26" t="n"/>
-      <c r="L175" s="32" t="n"/>
-      <c r="M175" s="32" t="n"/>
-      <c r="N175" s="32" t="n"/>
+      <c r="L175" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="M175" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="N175" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="O175" s="24" t="n"/>
       <c r="P175" s="24" t="n"/>
-      <c r="Q175" s="32" t="n"/>
-      <c r="R175" s="32" t="n"/>
-      <c r="S175" s="32" t="n"/>
-      <c r="T175" s="32" t="n"/>
-      <c r="U175" s="32" t="n"/>
+      <c r="Q175" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="R175" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="S175" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="T175" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="U175" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="V175" s="24" t="n"/>
       <c r="W175" s="24" t="n"/>
-      <c r="X175" s="32" t="n"/>
-      <c r="Y175" s="32" t="n"/>
-      <c r="Z175" s="32" t="n"/>
+      <c r="X175" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y175" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z175" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="AA175" s="63" t="n"/>
       <c r="AB175" s="26" t="n"/>
       <c r="AC175" s="26" t="n"/>
@@ -24802,9 +25070,9 @@
         <v/>
       </c>
       <c r="AK175" s="627" t="n"/>
-      <c r="AL175" s="828" t="inlineStr">
-        <is>
-          <t>FCOI15 Creació de continguts digitals (ACTIC Nivell bàsic) · MARIA · GOOGLE matí 9:00-15:00 · 23/11–01/12 · 40 h</t>
+      <c r="AL175" s="833" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
         </is>
       </c>
       <c r="AM175" s="774" t="n"/>
@@ -24817,7 +25085,9 @@
       </c>
       <c r="B176" s="456" t="n"/>
       <c r="C176" s="456" t="n"/>
-      <c r="D176" s="782" t="n"/>
+      <c r="D176" s="848" t="n">
+        <v>5</v>
+      </c>
       <c r="E176" s="756" t="n"/>
       <c r="F176" s="756" t="n"/>
       <c r="G176" s="756" t="n"/>
@@ -24850,7 +25120,11 @@
       <c r="AH176" s="63" t="n"/>
       <c r="AI176" s="4" t="n"/>
       <c r="AK176" s="774" t="n"/>
-      <c r="AL176" s="774" t="n"/>
+      <c r="AL176" s="849" t="inlineStr">
+        <is>
+          <t>FCOI15 Creació de continguts digitals (ACTIC Nivell bàsic) · MARIA · FIREFOX matí 9:00-15:00 · 23/11–01/12 · 40 h</t>
+        </is>
+      </c>
       <c r="AM176" s="774" t="n"/>
     </row>
     <row r="177" ht="19.5" customHeight="1" s="757" thickBot="1">
@@ -24967,29 +25241,59 @@
       </c>
       <c r="B179" s="11" t="n"/>
       <c r="C179" s="11" t="n"/>
-      <c r="D179" s="756" t="n"/>
-      <c r="E179" s="756" t="n"/>
-      <c r="F179" s="756" t="n"/>
-      <c r="G179" s="756" t="n"/>
+      <c r="D179" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="E179" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="F179" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="G179" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="H179" s="24" t="n"/>
       <c r="I179" s="24" t="n"/>
       <c r="J179" s="26" t="n"/>
       <c r="K179" s="26" t="n"/>
-      <c r="L179" s="756" t="n"/>
-      <c r="M179" s="756" t="n"/>
-      <c r="N179" s="756" t="n"/>
+      <c r="L179" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="M179" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="N179" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="O179" s="24" t="n"/>
       <c r="P179" s="24" t="n"/>
-      <c r="Q179" s="756" t="n"/>
-      <c r="R179" s="756" t="n"/>
-      <c r="S179" s="756" t="n"/>
-      <c r="T179" s="756" t="n"/>
-      <c r="U179" s="756" t="n"/>
+      <c r="Q179" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="R179" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="S179" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="T179" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="U179" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="V179" s="24" t="n"/>
       <c r="W179" s="24" t="n"/>
-      <c r="X179" s="756" t="n"/>
-      <c r="Y179" s="756" t="n"/>
-      <c r="Z179" s="756" t="n"/>
+      <c r="X179" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y179" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z179" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="AA179" s="63" t="n"/>
       <c r="AB179" s="26" t="n"/>
       <c r="AC179" s="26" t="n"/>
@@ -24998,6 +25302,11 @@
       <c r="AF179" s="63" t="n"/>
       <c r="AG179" s="63" t="n"/>
       <c r="AH179" s="63" t="n"/>
+      <c r="AL179" s="844" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="16.5" customHeight="1" s="757" thickBot="1">
       <c r="A180" s="14" t="inlineStr">
@@ -25083,7 +25392,7 @@
     <row r="183"/>
     <row r="184"/>
     <row r="185" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A185" s="829" t="inlineStr">
+      <c r="A185" s="850" t="inlineStr">
         <is>
           <t>GENER 2027</t>
         </is>
@@ -25247,49 +25556,77 @@
       <c r="D187" s="26" t="n"/>
       <c r="E187" s="24" t="n"/>
       <c r="F187" s="24" t="n"/>
-      <c r="G187" s="32" t="n"/>
-      <c r="H187" s="32" t="n"/>
+      <c r="G187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="H187" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="I187" s="610" t="n"/>
-      <c r="J187" s="32" t="n"/>
-      <c r="K187" s="32" t="n"/>
+      <c r="J187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="K187" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="L187" s="24" t="n"/>
       <c r="M187" s="24" t="n"/>
-      <c r="N187" s="830" t="n">
-        <v>5</v>
-      </c>
-      <c r="O187" s="831" t="n">
-        <v>5</v>
-      </c>
-      <c r="P187" s="831" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q187" s="831" t="n">
-        <v>5</v>
-      </c>
-      <c r="R187" s="831" t="n">
-        <v>5</v>
+      <c r="N187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="O187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="P187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="R187" s="832" t="n">
+        <v>6</v>
       </c>
       <c r="S187" s="24" t="n"/>
       <c r="T187" s="24" t="n"/>
-      <c r="U187" s="32" t="n"/>
-      <c r="V187" s="32" t="n"/>
-      <c r="W187" s="32" t="n"/>
-      <c r="X187" s="32" t="n"/>
-      <c r="Y187" s="32" t="n"/>
+      <c r="U187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="V187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="W187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="X187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y187" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="Z187" s="24" t="n"/>
       <c r="AA187" s="24" t="n"/>
-      <c r="AB187" s="32" t="n"/>
-      <c r="AC187" s="32" t="n"/>
-      <c r="AD187" s="32" t="n"/>
-      <c r="AE187" s="32" t="n"/>
-      <c r="AF187" s="32" t="n"/>
+      <c r="AB187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE187" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF187" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="AG187" s="24" t="n"/>
       <c r="AH187" s="24" t="n"/>
       <c r="AI187" s="4" t="n"/>
       <c r="AK187" s="627" t="n"/>
-      <c r="AL187" s="832" t="inlineStr">
-        <is>
-          <t>IFCT117 Introducció a la intel·ligència artificial (1a ed.) · MARIA · GOOGLE matí 9:00-14:00 · 11/01–15/01 · 25 h</t>
+      <c r="AL187" s="833" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
         </is>
       </c>
     </row>
@@ -25311,11 +25648,21 @@
       <c r="K188" s="756" t="n"/>
       <c r="L188" s="24" t="n"/>
       <c r="M188" s="24" t="n"/>
-      <c r="N188" s="756" t="n"/>
-      <c r="O188" s="756" t="n"/>
-      <c r="P188" s="756" t="n"/>
-      <c r="Q188" s="756" t="n"/>
-      <c r="R188" s="756" t="n"/>
+      <c r="N188" s="851" t="n">
+        <v>5</v>
+      </c>
+      <c r="O188" s="852" t="n">
+        <v>5</v>
+      </c>
+      <c r="P188" s="852" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q188" s="852" t="n">
+        <v>5</v>
+      </c>
+      <c r="R188" s="852" t="n">
+        <v>5</v>
+      </c>
       <c r="S188" s="24" t="n"/>
       <c r="T188" s="24" t="n"/>
       <c r="U188" s="756" t="n"/>
@@ -25333,6 +25680,11 @@
       <c r="AG188" s="24" t="n"/>
       <c r="AH188" s="24" t="n"/>
       <c r="AI188" s="4" t="n"/>
+      <c r="AL188" s="853" t="inlineStr">
+        <is>
+          <t>IFCT117 Introducció a la intel·ligència artificial (1a ed.) · MARIA · FIREFOX matí 9:00-14:00 · 11/01–15/01 · 25 h</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="19.5" customHeight="1" s="757" thickBot="1">
       <c r="A189" s="14" t="inlineStr">
@@ -25352,30 +25704,65 @@
       <c r="K189" s="778" t="n"/>
       <c r="L189" s="35" t="n"/>
       <c r="M189" s="35" t="n"/>
-      <c r="N189" s="778" t="n"/>
-      <c r="O189" s="778" t="n"/>
-      <c r="P189" s="778" t="n"/>
-      <c r="Q189" s="778" t="n"/>
-      <c r="R189" s="778" t="n"/>
+      <c r="N189" s="854" t="n">
+        <v>6</v>
+      </c>
+      <c r="O189" s="855" t="n">
+        <v>6</v>
+      </c>
+      <c r="P189" s="855" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q189" s="855" t="n">
+        <v>6</v>
+      </c>
+      <c r="R189" s="855" t="n">
+        <v>6</v>
+      </c>
       <c r="S189" s="35" t="n"/>
       <c r="T189" s="35" t="n"/>
-      <c r="U189" s="778" t="n"/>
-      <c r="V189" s="778" t="n"/>
-      <c r="W189" s="778" t="n"/>
-      <c r="X189" s="778" t="n"/>
-      <c r="Y189" s="778" t="n"/>
+      <c r="U189" s="855" t="n">
+        <v>6</v>
+      </c>
+      <c r="V189" s="855" t="n">
+        <v>6</v>
+      </c>
+      <c r="W189" s="855" t="n">
+        <v>6</v>
+      </c>
+      <c r="X189" s="855" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y189" s="855" t="n">
+        <v>6</v>
+      </c>
       <c r="Z189" s="35" t="n"/>
       <c r="AA189" s="35" t="n"/>
-      <c r="AB189" s="778" t="n"/>
-      <c r="AC189" s="778" t="n"/>
-      <c r="AD189" s="778" t="n"/>
-      <c r="AE189" s="778" t="n"/>
-      <c r="AF189" s="778" t="n"/>
+      <c r="AB189" s="855" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC189" s="855" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD189" s="855" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE189" s="855" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF189" s="855" t="n">
+        <v>6</v>
+      </c>
       <c r="AG189" s="35" t="n"/>
       <c r="AH189" s="35" t="n"/>
       <c r="AI189" s="4" t="n"/>
       <c r="AJ189" s="428" t="n"/>
       <c r="AK189" s="775" t="n"/>
+      <c r="AL189" s="856" t="inlineStr">
+        <is>
+          <t>IFCD64 Gestió de Projectes d'implementació del CRM · PER ASSIGNAR · COPILOT matí 9:00-15:00 · 11/01–12/02 · 145 h</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="16.5" customHeight="1" s="757" thickTop="1">
       <c r="A190" s="17" t="inlineStr">
@@ -25395,33 +25782,33 @@
       <c r="K190" s="756" t="n"/>
       <c r="L190" s="24" t="n"/>
       <c r="M190" s="24" t="n"/>
-      <c r="N190" s="833" t="n">
+      <c r="N190" s="857" t="n">
         <v>6</v>
       </c>
-      <c r="O190" s="834" t="n">
+      <c r="O190" s="858" t="n">
         <v>6</v>
       </c>
-      <c r="P190" s="834" t="n">
+      <c r="P190" s="858" t="n">
         <v>6</v>
       </c>
-      <c r="Q190" s="834" t="n">
+      <c r="Q190" s="858" t="n">
         <v>6</v>
       </c>
-      <c r="R190" s="834" t="n">
+      <c r="R190" s="858" t="n">
         <v>6</v>
       </c>
       <c r="S190" s="24" t="n"/>
       <c r="T190" s="24" t="n"/>
-      <c r="U190" s="835" t="n">
+      <c r="U190" s="859" t="n">
         <v>5</v>
       </c>
-      <c r="V190" s="836" t="n">
+      <c r="V190" s="860" t="n">
         <v>5</v>
       </c>
-      <c r="W190" s="836" t="n">
+      <c r="W190" s="860" t="n">
         <v>5</v>
       </c>
-      <c r="X190" s="836" t="n">
+      <c r="X190" s="860" t="n">
         <v>5</v>
       </c>
       <c r="Y190" s="756" t="n"/>
@@ -25435,12 +25822,12 @@
       <c r="AG190" s="24" t="n"/>
       <c r="AH190" s="24" t="n"/>
       <c r="AI190" s="4" t="n"/>
-      <c r="AL190" s="837" t="inlineStr">
+      <c r="AL190" s="861" t="inlineStr">
         <is>
           <t>SEAD0227 Tècniques de relaxació · ESTHER · GOOGLE tarda 15:00-20:00 · 18/01–21/01 · 20 h</t>
         </is>
       </c>
-      <c r="AU190" s="838" t="inlineStr">
+      <c r="AU190" s="862" t="inlineStr">
         <is>
           <t>CTRP0006 Mindfulness · RAMON · GOOGLE tarda 15:00-21:00 · 11/01–15/01 · 30 h</t>
         </is>
@@ -25457,53 +25844,75 @@
       <c r="D191" s="26" t="n"/>
       <c r="E191" s="24" t="n"/>
       <c r="F191" s="24" t="n"/>
-      <c r="G191" s="756" t="n"/>
-      <c r="H191" s="756" t="n"/>
+      <c r="G191" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="H191" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="I191" s="610" t="n"/>
-      <c r="J191" s="756" t="n"/>
-      <c r="K191" s="756" t="n"/>
+      <c r="J191" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="K191" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="L191" s="24" t="n"/>
       <c r="M191" s="24" t="n"/>
-      <c r="N191" s="756" t="n"/>
-      <c r="O191" s="756" t="n"/>
-      <c r="P191" s="756" t="n"/>
-      <c r="Q191" s="756" t="n"/>
-      <c r="R191" s="756" t="n"/>
+      <c r="N191" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="O191" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="P191" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q191" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="R191" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="S191" s="24" t="n"/>
       <c r="T191" s="24" t="n"/>
-      <c r="U191" s="839" t="n">
+      <c r="U191" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="V191" s="840" t="n">
+      <c r="V191" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="W191" s="840" t="n">
+      <c r="W191" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="X191" s="840" t="n">
+      <c r="X191" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="Y191" s="840" t="n">
+      <c r="Y191" s="826" t="n">
         <v>6</v>
       </c>
       <c r="Z191" s="24" t="n"/>
       <c r="AA191" s="24" t="n"/>
-      <c r="AB191" s="840" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC191" s="840" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD191" s="840" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE191" s="756" t="n"/>
-      <c r="AF191" s="756" t="n"/>
+      <c r="AB191" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC191" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD191" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE191" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF191" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="AG191" s="24" t="n"/>
       <c r="AH191" s="24" t="n"/>
-      <c r="AL191" s="841" t="inlineStr">
-        <is>
-          <t>CTRL0041 CTRL0041_2024_Català A2.1 (Català bàsic 1 ) · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 18/01–27/01 · 45 h</t>
+      <c r="AL191" s="844" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
         </is>
       </c>
     </row>
@@ -25525,60 +25934,46 @@
       <c r="K192" s="778" t="n"/>
       <c r="L192" s="35" t="n"/>
       <c r="M192" s="35" t="n"/>
-      <c r="N192" s="842" t="n">
-        <v>6</v>
-      </c>
-      <c r="O192" s="843" t="n">
-        <v>6</v>
-      </c>
-      <c r="P192" s="843" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q192" s="843" t="n">
-        <v>6</v>
-      </c>
-      <c r="R192" s="843" t="n">
-        <v>6</v>
-      </c>
+      <c r="N192" s="778" t="n"/>
+      <c r="O192" s="778" t="n"/>
+      <c r="P192" s="778" t="n"/>
+      <c r="Q192" s="778" t="n"/>
+      <c r="R192" s="778" t="n"/>
       <c r="S192" s="35" t="n"/>
       <c r="T192" s="35" t="n"/>
-      <c r="U192" s="843" t="n">
+      <c r="U192" s="863" t="n">
         <v>6</v>
       </c>
-      <c r="V192" s="843" t="n">
+      <c r="V192" s="864" t="n">
         <v>6</v>
       </c>
-      <c r="W192" s="843" t="n">
+      <c r="W192" s="864" t="n">
         <v>6</v>
       </c>
-      <c r="X192" s="843" t="n">
+      <c r="X192" s="864" t="n">
         <v>6</v>
       </c>
-      <c r="Y192" s="843" t="n">
+      <c r="Y192" s="864" t="n">
         <v>6</v>
       </c>
       <c r="Z192" s="35" t="n"/>
       <c r="AA192" s="35" t="n"/>
-      <c r="AB192" s="843" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC192" s="843" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD192" s="843" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE192" s="843" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF192" s="843" t="n">
-        <v>6</v>
-      </c>
+      <c r="AB192" s="864" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC192" s="864" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD192" s="864" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE192" s="778" t="n"/>
+      <c r="AF192" s="778" t="n"/>
       <c r="AG192" s="35" t="n"/>
       <c r="AH192" s="35" t="n"/>
-      <c r="AL192" s="844" t="inlineStr">
-        <is>
-          <t>IFCD64 Gestió de Projectes d'implementació del CRM · PER ASSIGNAR · COPILOT tarda 15:00-21:00 · 11/01–12/02 · 145 h</t>
+      <c r="AL192" s="865" t="inlineStr">
+        <is>
+          <t>CTRL0041 CTRL0041_2024_Català A2.1 (Català bàsic 1 ) · PER ASSIGNAR · COPILOT tarda 15:00-21:00 · 18/01–27/01 · 45 h</t>
         </is>
       </c>
     </row>
@@ -25705,7 +26100,7 @@
     <row r="196"/>
     <row r="197"/>
     <row r="198" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A198" s="829" t="inlineStr">
+      <c r="A198" s="850" t="inlineStr">
         <is>
           <t>FEBRER 2027</t>
         </is>
@@ -25860,54 +26255,70 @@
       </c>
       <c r="B200" s="11" t="n"/>
       <c r="C200" s="11" t="n"/>
-      <c r="D200" s="845" t="n">
+      <c r="D200" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="E200" s="846" t="n">
+      <c r="E200" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="F200" s="846" t="n">
+      <c r="F200" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="G200" s="846" t="n">
+      <c r="G200" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="H200" s="846" t="n">
+      <c r="H200" s="832" t="n">
         <v>6</v>
       </c>
       <c r="I200" s="24" t="n"/>
       <c r="J200" s="24" t="n"/>
-      <c r="K200" s="846" t="n">
-        <v>5</v>
-      </c>
-      <c r="L200" s="846" t="n">
-        <v>5</v>
-      </c>
-      <c r="M200" s="32" t="n"/>
-      <c r="N200" s="32" t="n"/>
-      <c r="O200" s="32" t="n"/>
+      <c r="K200" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="L200" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="M200" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="N200" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="O200" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="P200" s="24" t="n"/>
       <c r="Q200" s="24" t="n"/>
-      <c r="R200" s="32" t="n"/>
-      <c r="S200" s="32" t="n"/>
-      <c r="T200" s="32" t="n"/>
-      <c r="U200" s="32" t="n"/>
-      <c r="V200" s="32" t="n"/>
+      <c r="R200" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="S200" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="T200" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="U200" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="V200" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="W200" s="24" t="n"/>
       <c r="X200" s="24" t="n"/>
-      <c r="Y200" s="847" t="n">
+      <c r="Y200" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="Z200" s="848" t="n">
+      <c r="Z200" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="AA200" s="848" t="n">
+      <c r="AA200" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="AB200" s="848" t="n">
+      <c r="AB200" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="AC200" s="848" t="n">
+      <c r="AC200" s="832" t="n">
         <v>6</v>
       </c>
       <c r="AD200" s="24" t="n"/>
@@ -25917,14 +26328,9 @@
       <c r="AH200" s="756" t="n"/>
       <c r="AI200" s="4" t="n"/>
       <c r="AK200" s="627" t="n"/>
-      <c r="AL200" s="849" t="inlineStr">
-        <is>
-          <t>FCOI19 Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi) (1a ed.) · MARIA · GOOGLE matí 9:00-15:00 · 01/02–09/02 · 40 h</t>
-        </is>
-      </c>
-      <c r="AU200" s="850" t="inlineStr">
-        <is>
-          <t>FCOI16 Creació de continguts digitals i programació (ACTIC Nivell intermedi) (1a ed.) · MARIA · GOOGLE matí 9:00-15:00 · 22/02–02/03 · 40 h</t>
+      <c r="AL200" s="833" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
         </is>
       </c>
     </row>
@@ -25936,46 +26342,56 @@
       </c>
       <c r="B201" s="456" t="n"/>
       <c r="C201" s="456" t="n"/>
-      <c r="D201" s="782" t="n"/>
-      <c r="E201" s="756" t="n"/>
-      <c r="F201" s="756" t="n"/>
-      <c r="G201" s="756" t="n"/>
-      <c r="H201" s="756" t="n"/>
+      <c r="D201" s="866" t="n">
+        <v>6</v>
+      </c>
+      <c r="E201" s="867" t="n">
+        <v>6</v>
+      </c>
+      <c r="F201" s="867" t="n">
+        <v>6</v>
+      </c>
+      <c r="G201" s="867" t="n">
+        <v>6</v>
+      </c>
+      <c r="H201" s="867" t="n">
+        <v>6</v>
+      </c>
       <c r="I201" s="24" t="n"/>
       <c r="J201" s="24" t="n"/>
-      <c r="K201" s="756" t="n"/>
-      <c r="L201" s="756" t="n"/>
+      <c r="K201" s="867" t="n">
+        <v>5</v>
+      </c>
+      <c r="L201" s="867" t="n">
+        <v>5</v>
+      </c>
       <c r="M201" s="756" t="n"/>
       <c r="N201" s="756" t="n"/>
       <c r="O201" s="756" t="n"/>
       <c r="P201" s="24" t="n"/>
       <c r="Q201" s="24" t="n"/>
-      <c r="R201" s="851" t="n">
-        <v>6</v>
-      </c>
-      <c r="S201" s="852" t="n">
-        <v>6</v>
-      </c>
-      <c r="T201" s="852" t="n">
-        <v>6</v>
-      </c>
-      <c r="U201" s="852" t="n">
-        <v>6</v>
-      </c>
-      <c r="V201" s="852" t="n">
-        <v>6</v>
-      </c>
+      <c r="R201" s="756" t="n"/>
+      <c r="S201" s="756" t="n"/>
+      <c r="T201" s="756" t="n"/>
+      <c r="U201" s="756" t="n"/>
+      <c r="V201" s="756" t="n"/>
       <c r="W201" s="24" t="n"/>
       <c r="X201" s="24" t="n"/>
-      <c r="Y201" s="852" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z201" s="852" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA201" s="756" t="n"/>
-      <c r="AB201" s="756" t="n"/>
-      <c r="AC201" s="756" t="n"/>
+      <c r="Y201" s="868" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z201" s="869" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA201" s="869" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB201" s="869" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC201" s="869" t="n">
+        <v>6</v>
+      </c>
       <c r="AD201" s="24" t="n"/>
       <c r="AE201" s="24" t="n"/>
       <c r="AF201" s="756" t="n"/>
@@ -25983,9 +26399,14 @@
       <c r="AH201" s="756" t="n"/>
       <c r="AI201" s="4" t="n"/>
       <c r="AK201" s="774" t="n"/>
-      <c r="AL201" s="853" t="inlineStr">
-        <is>
-          <t>CTRP0037 Coaching de fortaleses. Nivell II · RAMON · FIREFOX matí 9:00-15:00 · 15/02–23/02 · 40 h</t>
+      <c r="AL201" s="870" t="inlineStr">
+        <is>
+          <t>FCOI19 Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi) (1a ed.) · MARIA · FIREFOX matí 9:00-15:00 · 01/02–09/02 · 40 h</t>
+        </is>
+      </c>
+      <c r="AU201" s="871" t="inlineStr">
+        <is>
+          <t>FCOI16 Creació de continguts digitals i programació (ACTIC Nivell intermedi) (1a ed.) · MARIA · FIREFOX matí 9:00-15:00 · 22/02–02/03 · 40 h</t>
         </is>
       </c>
     </row>
@@ -25997,7 +26418,7 @@
       </c>
       <c r="B202" s="15" t="n"/>
       <c r="C202" s="15" t="n"/>
-      <c r="D202" s="854" t="n">
+      <c r="D202" s="855" t="n">
         <v>6</v>
       </c>
       <c r="E202" s="855" t="n">
@@ -26015,54 +26436,48 @@
       <c r="I202" s="35" t="n"/>
       <c r="J202" s="35" t="n"/>
       <c r="K202" s="855" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L202" s="855" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M202" s="855" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N202" s="855" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O202" s="855" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P202" s="35" t="n"/>
       <c r="Q202" s="35" t="n"/>
-      <c r="R202" s="855" t="n">
+      <c r="R202" s="872" t="n">
         <v>6</v>
       </c>
-      <c r="S202" s="855" t="n">
+      <c r="S202" s="873" t="n">
         <v>6</v>
       </c>
-      <c r="T202" s="855" t="n">
+      <c r="T202" s="873" t="n">
         <v>6</v>
       </c>
-      <c r="U202" s="855" t="n">
+      <c r="U202" s="873" t="n">
         <v>6</v>
       </c>
-      <c r="V202" s="855" t="n">
+      <c r="V202" s="873" t="n">
         <v>6</v>
       </c>
       <c r="W202" s="35" t="n"/>
       <c r="X202" s="35" t="n"/>
-      <c r="Y202" s="855" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z202" s="855" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA202" s="855" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB202" s="855" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC202" s="855" t="n">
-        <v>6</v>
-      </c>
+      <c r="Y202" s="873" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z202" s="873" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA202" s="778" t="n"/>
+      <c r="AB202" s="778" t="n"/>
+      <c r="AC202" s="778" t="n"/>
       <c r="AD202" s="35" t="n"/>
       <c r="AE202" s="35" t="n"/>
       <c r="AF202" s="778" t="n"/>
@@ -26071,9 +26486,14 @@
       <c r="AI202" s="4" t="n"/>
       <c r="AJ202" s="428" t="n"/>
       <c r="AK202" s="775" t="n"/>
-      <c r="AL202" s="856" t="inlineStr">
-        <is>
-          <t>IMPE0110 MF0063 MASSATGES ESTÈTIC MANUAL I MECÀNIC · LEIRE · COPILOT matí 9:00-15:00 · 01/02–08/03 · 152 h</t>
+      <c r="AL202" s="874" t="inlineStr">
+        <is>
+          <t>CTRP0037 Coaching de fortaleses. Nivell II · RAMON · COPILOT matí 9:00-15:00 · 15/02–23/02 · 40 h</t>
+        </is>
+      </c>
+      <c r="AU202" s="875" t="inlineStr">
+        <is>
+          <t>IFCD64 Gestió de Projectes d'implementació del CRM · PER ASSIGNAR · COPILOT matí 9:00-15:00 · 11/01–12/02 · 145 h</t>
         </is>
       </c>
     </row>
@@ -26126,37 +26546,82 @@
       </c>
       <c r="B204" s="11" t="n"/>
       <c r="C204" s="11" t="n"/>
-      <c r="D204" s="756" t="n"/>
-      <c r="E204" s="756" t="n"/>
-      <c r="F204" s="756" t="n"/>
-      <c r="G204" s="756" t="n"/>
-      <c r="H204" s="756" t="n"/>
+      <c r="D204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="E204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="F204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="G204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="H204" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="I204" s="24" t="n"/>
       <c r="J204" s="24" t="n"/>
-      <c r="K204" s="756" t="n"/>
-      <c r="L204" s="756" t="n"/>
-      <c r="M204" s="756" t="n"/>
-      <c r="N204" s="756" t="n"/>
-      <c r="O204" s="756" t="n"/>
+      <c r="K204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="L204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="M204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="N204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="O204" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="P204" s="24" t="n"/>
       <c r="Q204" s="24" t="n"/>
-      <c r="R204" s="756" t="n"/>
-      <c r="S204" s="756" t="n"/>
-      <c r="T204" s="756" t="n"/>
-      <c r="U204" s="756" t="n"/>
-      <c r="V204" s="756" t="n"/>
+      <c r="R204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="S204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="T204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="U204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="V204" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="W204" s="24" t="n"/>
       <c r="X204" s="24" t="n"/>
-      <c r="Y204" s="756" t="n"/>
-      <c r="Z204" s="756" t="n"/>
-      <c r="AA204" s="756" t="n"/>
-      <c r="AB204" s="756" t="n"/>
-      <c r="AC204" s="756" t="n"/>
+      <c r="Y204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB204" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC204" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="AD204" s="24" t="n"/>
       <c r="AE204" s="24" t="n"/>
       <c r="AF204" s="756" t="n"/>
       <c r="AG204" s="756" t="n"/>
       <c r="AH204" s="756" t="n"/>
+      <c r="AL204" s="844" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="16.5" customHeight="1" s="757" thickBot="1">
       <c r="A205" s="14" t="inlineStr">
@@ -26166,60 +26631,80 @@
       </c>
       <c r="B205" s="15" t="n"/>
       <c r="C205" s="15" t="n"/>
-      <c r="D205" s="843" t="n">
+      <c r="D205" s="876" t="n">
         <v>6</v>
       </c>
-      <c r="E205" s="843" t="n">
+      <c r="E205" s="877" t="n">
         <v>6</v>
       </c>
-      <c r="F205" s="843" t="n">
+      <c r="F205" s="877" t="n">
         <v>6</v>
       </c>
-      <c r="G205" s="843" t="n">
+      <c r="G205" s="877" t="n">
         <v>6</v>
       </c>
-      <c r="H205" s="843" t="n">
+      <c r="H205" s="877" t="n">
         <v>6</v>
       </c>
       <c r="I205" s="35" t="n"/>
       <c r="J205" s="35" t="n"/>
-      <c r="K205" s="843" t="n">
-        <v>5</v>
-      </c>
-      <c r="L205" s="843" t="n">
-        <v>5</v>
-      </c>
-      <c r="M205" s="843" t="n">
-        <v>5</v>
-      </c>
-      <c r="N205" s="843" t="n">
-        <v>5</v>
-      </c>
-      <c r="O205" s="843" t="n">
-        <v>5</v>
+      <c r="K205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="L205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="M205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="N205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="O205" s="877" t="n">
+        <v>6</v>
       </c>
       <c r="P205" s="35" t="n"/>
       <c r="Q205" s="35" t="n"/>
-      <c r="R205" s="778" t="n"/>
-      <c r="S205" s="778" t="n"/>
-      <c r="T205" s="778" t="n"/>
-      <c r="U205" s="778" t="n"/>
-      <c r="V205" s="778" t="n"/>
+      <c r="R205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="S205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="T205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="U205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="V205" s="877" t="n">
+        <v>6</v>
+      </c>
       <c r="W205" s="35" t="n"/>
       <c r="X205" s="35" t="n"/>
-      <c r="Y205" s="778" t="n"/>
-      <c r="Z205" s="778" t="n"/>
-      <c r="AA205" s="778" t="n"/>
-      <c r="AB205" s="778" t="n"/>
-      <c r="AC205" s="778" t="n"/>
+      <c r="Y205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB205" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC205" s="877" t="n">
+        <v>6</v>
+      </c>
       <c r="AD205" s="35" t="n"/>
       <c r="AE205" s="35" t="n"/>
       <c r="AF205" s="778" t="n"/>
       <c r="AG205" s="778" t="n"/>
       <c r="AH205" s="778" t="n"/>
-      <c r="AL205" s="857" t="inlineStr">
-        <is>
-          <t>IFCD64 Gestió de Projectes d'implementació del CRM · PER ASSIGNAR · COPILOT tarda 15:00-21:00 · 11/01–12/02 · 145 h</t>
+      <c r="AL205" s="878" t="inlineStr">
+        <is>
+          <t>IMPE0110 MF0063 MASSATGES ESTÈTIC MANUAL I MECÀNIC · LEIRE · COPILOT tarda 15:00-21:00 · 01/02–08/03 · 152 h</t>
         </is>
       </c>
     </row>
@@ -26346,7 +26831,7 @@
     <row r="209" ht="15.75" customHeight="1" s="757" thickTop="1"/>
     <row r="210"/>
     <row r="211" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A211" s="829" t="inlineStr">
+      <c r="A211" s="850" t="inlineStr">
         <is>
           <t>MARÇ 2027</t>
         </is>
@@ -26507,65 +26992,84 @@
       </c>
       <c r="B213" s="11" t="n"/>
       <c r="C213" s="11" t="n"/>
-      <c r="D213" s="848" t="n">
-        <v>5</v>
-      </c>
-      <c r="E213" s="848" t="n">
-        <v>5</v>
-      </c>
-      <c r="F213" s="32" t="n"/>
-      <c r="G213" s="32" t="n"/>
-      <c r="H213" s="32" t="n"/>
+      <c r="D213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="E213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="F213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="G213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="H213" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="I213" s="24" t="n"/>
       <c r="J213" s="24" t="n"/>
-      <c r="K213" s="32" t="n"/>
-      <c r="L213" s="32" t="n"/>
-      <c r="M213" s="32" t="n"/>
-      <c r="N213" s="32" t="n"/>
-      <c r="O213" s="32" t="n"/>
+      <c r="K213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="L213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="M213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="N213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="O213" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="P213" s="24" t="n"/>
       <c r="Q213" s="24" t="n"/>
-      <c r="R213" s="845" t="n">
+      <c r="R213" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="S213" s="846" t="n">
+      <c r="S213" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="T213" s="846" t="n">
+      <c r="T213" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="U213" s="846" t="n">
+      <c r="U213" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="V213" s="846" t="n">
+      <c r="V213" s="832" t="n">
         <v>6</v>
       </c>
       <c r="W213" s="24" t="n"/>
       <c r="X213" s="24" t="n"/>
-      <c r="Y213" s="846" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z213" s="846" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA213" s="32" t="n"/>
-      <c r="AB213" s="32" t="n"/>
+      <c r="Y213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB213" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="AC213" s="26" t="n"/>
       <c r="AD213" s="24" t="n"/>
       <c r="AE213" s="24" t="n"/>
       <c r="AF213" s="26" t="n"/>
-      <c r="AG213" s="756" t="n"/>
-      <c r="AH213" s="756" t="n"/>
+      <c r="AG213" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH213" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="AI213" s="4" t="n"/>
       <c r="AK213" s="627" t="n"/>
-      <c r="AL213" s="858" t="inlineStr">
-        <is>
-          <t>FCOI16 Creació de continguts digitals i programació (ACTIC Nivell intermedi) (1a ed.) · MARIA · GOOGLE matí 9:00-15:00 · 22/02–02/03 · 40 h</t>
-        </is>
-      </c>
-      <c r="AU213" s="849" t="inlineStr">
-        <is>
-          <t>FCOI19 Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi) (2a ed.) · MARIA · GOOGLE matí 9:00-15:00 · 15/03–23/03 · 40 h</t>
+      <c r="AL213" s="833" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
         </is>
       </c>
     </row>
@@ -26577,72 +27081,65 @@
       </c>
       <c r="B214" s="456" t="n"/>
       <c r="C214" s="456" t="n"/>
-      <c r="D214" s="782" t="n"/>
-      <c r="E214" s="756" t="n"/>
+      <c r="D214" s="879" t="n">
+        <v>5</v>
+      </c>
+      <c r="E214" s="869" t="n">
+        <v>5</v>
+      </c>
       <c r="F214" s="756" t="n"/>
       <c r="G214" s="756" t="n"/>
       <c r="H214" s="756" t="n"/>
       <c r="I214" s="24" t="n"/>
       <c r="J214" s="24" t="n"/>
       <c r="K214" s="756" t="n"/>
-      <c r="L214" s="859" t="n">
-        <v>6</v>
-      </c>
-      <c r="M214" s="860" t="n">
-        <v>6</v>
-      </c>
-      <c r="N214" s="860" t="n">
-        <v>6</v>
-      </c>
-      <c r="O214" s="860" t="n">
-        <v>6</v>
-      </c>
+      <c r="L214" s="756" t="n"/>
+      <c r="M214" s="756" t="n"/>
+      <c r="N214" s="756" t="n"/>
+      <c r="O214" s="756" t="n"/>
       <c r="P214" s="24" t="n"/>
       <c r="Q214" s="24" t="n"/>
-      <c r="R214" s="860" t="n">
+      <c r="R214" s="880" t="n">
         <v>6</v>
       </c>
-      <c r="S214" s="860" t="n">
+      <c r="S214" s="867" t="n">
         <v>6</v>
       </c>
-      <c r="T214" s="860" t="n">
+      <c r="T214" s="867" t="n">
         <v>6</v>
       </c>
-      <c r="U214" s="860" t="n">
+      <c r="U214" s="867" t="n">
         <v>6</v>
       </c>
-      <c r="V214" s="860" t="n">
+      <c r="V214" s="867" t="n">
         <v>6</v>
       </c>
       <c r="W214" s="24" t="n"/>
       <c r="X214" s="24" t="n"/>
-      <c r="Y214" s="860" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z214" s="860" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA214" s="860" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB214" s="860" t="n">
-        <v>6</v>
-      </c>
+      <c r="Y214" s="867" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z214" s="867" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA214" s="756" t="n"/>
+      <c r="AB214" s="756" t="n"/>
       <c r="AC214" s="26" t="n"/>
       <c r="AD214" s="24" t="n"/>
       <c r="AE214" s="24" t="n"/>
       <c r="AF214" s="26" t="n"/>
-      <c r="AG214" s="860" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH214" s="860" t="n">
-        <v>6</v>
-      </c>
+      <c r="AG214" s="756" t="n"/>
+      <c r="AH214" s="756" t="n"/>
       <c r="AI214" s="4" t="n"/>
       <c r="AK214" s="774" t="n"/>
-      <c r="AL214" s="861" t="inlineStr">
-        <is>
-          <t>IMPE0110 MF0790 DRENATGE LIMFÀTIC ESTÈTIC MANUAL I MECÀNIC · LEIRE · FIREFOX matí 9:00-15:00 · 09/03–06/04 · 114 h</t>
+      <c r="AL214" s="881" t="inlineStr">
+        <is>
+          <t>FCOI16 Creació de continguts digitals i programació (ACTIC Nivell intermedi) (1a ed.) · MARIA · FIREFOX matí 9:00-15:00 · 22/02–02/03 · 40 h</t>
+        </is>
+      </c>
+      <c r="AU214" s="870" t="inlineStr">
+        <is>
+          <t>FCOI19 Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi) (2a ed.) · MARIA · FIREFOX matí 9:00-15:00 · 15/03–23/03 · 40 h</t>
         </is>
       </c>
     </row>
@@ -26654,55 +27151,73 @@
       </c>
       <c r="B215" s="15" t="n"/>
       <c r="C215" s="15" t="n"/>
-      <c r="D215" s="855" t="n">
-        <v>6</v>
-      </c>
-      <c r="E215" s="855" t="n">
-        <v>6</v>
-      </c>
-      <c r="F215" s="855" t="n">
-        <v>5</v>
-      </c>
-      <c r="G215" s="855" t="n">
-        <v>5</v>
-      </c>
-      <c r="H215" s="855" t="n">
-        <v>5</v>
-      </c>
+      <c r="D215" s="783" t="n"/>
+      <c r="E215" s="778" t="n"/>
+      <c r="F215" s="778" t="n"/>
+      <c r="G215" s="778" t="n"/>
+      <c r="H215" s="778" t="n"/>
       <c r="I215" s="35" t="n"/>
       <c r="J215" s="35" t="n"/>
-      <c r="K215" s="855" t="n">
-        <v>5</v>
-      </c>
-      <c r="L215" s="778" t="n"/>
-      <c r="M215" s="778" t="n"/>
-      <c r="N215" s="778" t="n"/>
-      <c r="O215" s="778" t="n"/>
+      <c r="K215" s="778" t="n"/>
+      <c r="L215" s="882" t="n">
+        <v>6</v>
+      </c>
+      <c r="M215" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="N215" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="O215" s="883" t="n">
+        <v>6</v>
+      </c>
       <c r="P215" s="35" t="n"/>
       <c r="Q215" s="35" t="n"/>
-      <c r="R215" s="778" t="n"/>
-      <c r="S215" s="778" t="n"/>
-      <c r="T215" s="778" t="n"/>
-      <c r="U215" s="778" t="n"/>
-      <c r="V215" s="778" t="n"/>
+      <c r="R215" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="S215" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="T215" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="U215" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="V215" s="883" t="n">
+        <v>6</v>
+      </c>
       <c r="W215" s="35" t="n"/>
       <c r="X215" s="35" t="n"/>
-      <c r="Y215" s="778" t="n"/>
-      <c r="Z215" s="778" t="n"/>
-      <c r="AA215" s="778" t="n"/>
-      <c r="AB215" s="778" t="n"/>
+      <c r="Y215" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z215" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA215" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB215" s="883" t="n">
+        <v>6</v>
+      </c>
       <c r="AC215" s="27" t="n"/>
       <c r="AD215" s="35" t="n"/>
       <c r="AE215" s="35" t="n"/>
       <c r="AF215" s="27" t="n"/>
-      <c r="AG215" s="778" t="n"/>
-      <c r="AH215" s="778" t="n"/>
+      <c r="AG215" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH215" s="883" t="n">
+        <v>6</v>
+      </c>
       <c r="AI215" s="4" t="n"/>
       <c r="AJ215" s="428" t="n"/>
       <c r="AK215" s="775" t="n"/>
-      <c r="AL215" s="862" t="inlineStr">
-        <is>
-          <t>IMPE0110 MF0063 MASSATGES ESTÈTIC MANUAL I MECÀNIC · LEIRE · COPILOT matí 9:00-15:00 · 01/02–08/03 · 152 h</t>
+      <c r="AL215" s="884" t="inlineStr">
+        <is>
+          <t>IMPE0110 MF0790 DRENATGE LIMFÀTIC ESTÈTIC MANUAL I MECÀNIC · LEIRE · COPILOT matí 9:00-15:00 · 09/03–06/04 · 114 h</t>
         </is>
       </c>
     </row>
@@ -26714,16 +27229,16 @@
       </c>
       <c r="B216" s="18" t="n"/>
       <c r="C216" s="18" t="n"/>
-      <c r="D216" s="863" t="n">
+      <c r="D216" s="885" t="n">
         <v>5</v>
       </c>
-      <c r="E216" s="825" t="n">
+      <c r="E216" s="886" t="n">
         <v>5</v>
       </c>
-      <c r="F216" s="825" t="n">
+      <c r="F216" s="886" t="n">
         <v>5</v>
       </c>
-      <c r="G216" s="825" t="n">
+      <c r="G216" s="886" t="n">
         <v>5</v>
       </c>
       <c r="H216" s="756" t="n"/>
@@ -26754,7 +27269,7 @@
       <c r="AG216" s="756" t="n"/>
       <c r="AH216" s="756" t="n"/>
       <c r="AI216" s="4" t="n"/>
-      <c r="AL216" s="826" t="inlineStr">
+      <c r="AL216" s="847" t="inlineStr">
         <is>
           <t>SANP0011 Tècniques de massatge (2a ed.) · ESTHER · GOOGLE tarda 15:00-20:00 · 01/03–04/03 · 20 h</t>
         </is>
@@ -26768,37 +27283,84 @@
       </c>
       <c r="B217" s="11" t="n"/>
       <c r="C217" s="11" t="n"/>
-      <c r="D217" s="756" t="n"/>
-      <c r="E217" s="756" t="n"/>
-      <c r="F217" s="756" t="n"/>
-      <c r="G217" s="756" t="n"/>
-      <c r="H217" s="756" t="n"/>
+      <c r="D217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="E217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="F217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="G217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="H217" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="I217" s="24" t="n"/>
       <c r="J217" s="24" t="n"/>
-      <c r="K217" s="756" t="n"/>
-      <c r="L217" s="756" t="n"/>
-      <c r="M217" s="756" t="n"/>
-      <c r="N217" s="756" t="n"/>
-      <c r="O217" s="756" t="n"/>
+      <c r="K217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="L217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="M217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="N217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="O217" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="P217" s="24" t="n"/>
       <c r="Q217" s="24" t="n"/>
-      <c r="R217" s="756" t="n"/>
-      <c r="S217" s="756" t="n"/>
-      <c r="T217" s="756" t="n"/>
-      <c r="U217" s="756" t="n"/>
-      <c r="V217" s="756" t="n"/>
+      <c r="R217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="S217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="T217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="U217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="V217" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="W217" s="24" t="n"/>
       <c r="X217" s="24" t="n"/>
-      <c r="Y217" s="756" t="n"/>
-      <c r="Z217" s="756" t="n"/>
-      <c r="AA217" s="756" t="n"/>
-      <c r="AB217" s="756" t="n"/>
+      <c r="Y217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB217" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="AC217" s="26" t="n"/>
       <c r="AD217" s="24" t="n"/>
       <c r="AE217" s="24" t="n"/>
       <c r="AF217" s="26" t="n"/>
-      <c r="AG217" s="756" t="n"/>
-      <c r="AH217" s="756" t="n"/>
+      <c r="AG217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH217" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL217" s="844" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="16.5" customHeight="1" s="757" thickBot="1">
       <c r="A218" s="14" t="inlineStr">
@@ -26808,14 +27370,26 @@
       </c>
       <c r="B218" s="15" t="n"/>
       <c r="C218" s="15" t="n"/>
-      <c r="D218" s="783" t="n"/>
-      <c r="E218" s="778" t="n"/>
-      <c r="F218" s="778" t="n"/>
-      <c r="G218" s="778" t="n"/>
-      <c r="H218" s="778" t="n"/>
+      <c r="D218" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="E218" s="877" t="n">
+        <v>6</v>
+      </c>
+      <c r="F218" s="877" t="n">
+        <v>5</v>
+      </c>
+      <c r="G218" s="877" t="n">
+        <v>5</v>
+      </c>
+      <c r="H218" s="877" t="n">
+        <v>5</v>
+      </c>
       <c r="I218" s="35" t="n"/>
       <c r="J218" s="35" t="n"/>
-      <c r="K218" s="778" t="n"/>
+      <c r="K218" s="877" t="n">
+        <v>5</v>
+      </c>
       <c r="L218" s="778" t="n"/>
       <c r="M218" s="778" t="n"/>
       <c r="N218" s="778" t="n"/>
@@ -26839,6 +27413,11 @@
       <c r="AF218" s="27" t="n"/>
       <c r="AG218" s="778" t="n"/>
       <c r="AH218" s="778" t="n"/>
+      <c r="AL218" s="887" t="inlineStr">
+        <is>
+          <t>IMPE0110 MF0063 MASSATGES ESTÈTIC MANUAL I MECÀNIC · LEIRE · COPILOT tarda 15:00-21:00 · 01/02–08/03 · 152 h</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="16.5" customHeight="1" s="757" thickTop="1">
       <c r="A219" s="10" t="inlineStr">
@@ -26963,7 +27542,7 @@
     <row r="222" ht="15.75" customHeight="1" s="757" thickTop="1"/>
     <row r="223"/>
     <row r="224" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A224" s="829" t="inlineStr">
+      <c r="A224" s="850" t="inlineStr">
         <is>
           <t>ABRIL 2027</t>
         </is>
@@ -27122,42 +27701,60 @@
       </c>
       <c r="B226" s="11" t="n"/>
       <c r="C226" s="11" t="n"/>
-      <c r="D226" s="32" t="n"/>
-      <c r="E226" s="32" t="n"/>
+      <c r="D226" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="E226" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="F226" s="24" t="n"/>
       <c r="G226" s="24" t="n"/>
-      <c r="H226" s="32" t="n"/>
-      <c r="I226" s="32" t="n"/>
-      <c r="J226" s="32" t="n"/>
-      <c r="K226" s="32" t="n"/>
-      <c r="L226" s="32" t="n"/>
+      <c r="H226" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="I226" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="J226" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="K226" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="L226" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="M226" s="779" t="n"/>
       <c r="N226" s="779" t="n"/>
-      <c r="O226" s="847" t="n">
+      <c r="O226" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="P226" s="848" t="n">
+      <c r="P226" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="Q226" s="848" t="n">
+      <c r="Q226" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="R226" s="848" t="n">
+      <c r="R226" s="832" t="n">
         <v>6</v>
       </c>
-      <c r="S226" s="848" t="n">
+      <c r="S226" s="832" t="n">
         <v>6</v>
       </c>
       <c r="T226" s="779" t="n"/>
       <c r="U226" s="779" t="n"/>
-      <c r="V226" s="848" t="n">
-        <v>5</v>
-      </c>
-      <c r="W226" s="848" t="n">
-        <v>5</v>
-      </c>
-      <c r="X226" s="756" t="n"/>
-      <c r="Y226" s="756" t="n"/>
+      <c r="V226" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="W226" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="X226" s="832" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y226" s="832" t="n">
+        <v>6</v>
+      </c>
       <c r="Z226" s="756" t="n"/>
       <c r="AA226" s="779" t="n"/>
       <c r="AB226" s="779" t="n"/>
@@ -27169,9 +27766,9 @@
       <c r="AH226" s="756" t="n"/>
       <c r="AI226" s="4" t="n"/>
       <c r="AK226" s="627" t="n"/>
-      <c r="AL226" s="850" t="inlineStr">
-        <is>
-          <t>FCOI16 Creació de continguts digitals i programació (ACTIC Nivell intermedi) (2a ed.) · MARIA · GOOGLE matí 9:00-15:00 · 12/04–20/04 · 40 h</t>
+      <c r="AL226" s="833" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
         </is>
       </c>
     </row>
@@ -27183,91 +27780,56 @@
       </c>
       <c r="B227" s="456" t="n"/>
       <c r="C227" s="456" t="n"/>
-      <c r="D227" s="864" t="n">
-        <v>6</v>
-      </c>
-      <c r="E227" s="860" t="n">
-        <v>6</v>
-      </c>
+      <c r="D227" s="782" t="n"/>
+      <c r="E227" s="756" t="n"/>
       <c r="F227" s="24" t="n"/>
       <c r="G227" s="24" t="n"/>
-      <c r="H227" s="860" t="n">
-        <v>6</v>
-      </c>
-      <c r="I227" s="860" t="n">
-        <v>6</v>
-      </c>
-      <c r="J227" s="865" t="n">
-        <v>6</v>
-      </c>
-      <c r="K227" s="866" t="n">
-        <v>6</v>
-      </c>
-      <c r="L227" s="866" t="n">
-        <v>6</v>
-      </c>
+      <c r="H227" s="756" t="n"/>
+      <c r="I227" s="756" t="n"/>
+      <c r="J227" s="756" t="n"/>
+      <c r="K227" s="756" t="n"/>
+      <c r="L227" s="756" t="n"/>
       <c r="M227" s="779" t="n"/>
       <c r="N227" s="779" t="n"/>
-      <c r="O227" s="866" t="n">
+      <c r="O227" s="868" t="n">
         <v>6</v>
       </c>
-      <c r="P227" s="866" t="n">
+      <c r="P227" s="869" t="n">
         <v>6</v>
       </c>
-      <c r="Q227" s="866" t="n">
+      <c r="Q227" s="869" t="n">
         <v>6</v>
       </c>
-      <c r="R227" s="866" t="n">
+      <c r="R227" s="869" t="n">
         <v>6</v>
       </c>
-      <c r="S227" s="866" t="n">
+      <c r="S227" s="869" t="n">
         <v>6</v>
       </c>
       <c r="T227" s="779" t="n"/>
       <c r="U227" s="779" t="n"/>
-      <c r="V227" s="866" t="n">
-        <v>6</v>
-      </c>
-      <c r="W227" s="866" t="n">
-        <v>6</v>
-      </c>
-      <c r="X227" s="866" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y227" s="866" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z227" s="866" t="n">
-        <v>6</v>
-      </c>
+      <c r="V227" s="869" t="n">
+        <v>5</v>
+      </c>
+      <c r="W227" s="869" t="n">
+        <v>5</v>
+      </c>
+      <c r="X227" s="756" t="n"/>
+      <c r="Y227" s="756" t="n"/>
+      <c r="Z227" s="756" t="n"/>
       <c r="AA227" s="779" t="n"/>
       <c r="AB227" s="779" t="n"/>
-      <c r="AC227" s="866" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD227" s="866" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE227" s="866" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF227" s="866" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG227" s="866" t="n">
-        <v>6</v>
-      </c>
+      <c r="AC227" s="756" t="n"/>
+      <c r="AD227" s="756" t="n"/>
+      <c r="AE227" s="756" t="n"/>
+      <c r="AF227" s="756" t="n"/>
+      <c r="AG227" s="756" t="n"/>
       <c r="AH227" s="756" t="n"/>
       <c r="AI227" s="4" t="n"/>
       <c r="AK227" s="774" t="n"/>
-      <c r="AL227" s="867" t="inlineStr">
-        <is>
-          <t>IMPE0110 MF0790 DRENATGE LIMFÀTIC ESTÈTIC MANUAL I MECÀNIC · LEIRE · FIREFOX matí 9:00-15:00 · 09/03–06/04 · 114 h</t>
-        </is>
-      </c>
-      <c r="AU227" s="868" t="inlineStr">
-        <is>
-          <t>IMPE110 MF0791 MASSATGES ESTÈTICS AMB TÈCNIQUES PER PRESSIÓ · LEIRE · FIREFOX matí 9:00-15:00 · 07/04–03/05 · 114 h</t>
+      <c r="AL227" s="871" t="inlineStr">
+        <is>
+          <t>FCOI16 Creació de continguts digitals i programació (ACTIC Nivell intermedi) (2a ed.) · MARIA · FIREFOX matí 9:00-15:00 · 12/04–20/04 · 40 h</t>
         </is>
       </c>
     </row>
@@ -27279,40 +27841,94 @@
       </c>
       <c r="B228" s="15" t="n"/>
       <c r="C228" s="15" t="n"/>
-      <c r="D228" s="783" t="n"/>
-      <c r="E228" s="778" t="n"/>
+      <c r="D228" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="E228" s="883" t="n">
+        <v>6</v>
+      </c>
       <c r="F228" s="35" t="n"/>
       <c r="G228" s="35" t="n"/>
-      <c r="H228" s="778" t="n"/>
-      <c r="I228" s="778" t="n"/>
-      <c r="J228" s="778" t="n"/>
-      <c r="K228" s="778" t="n"/>
-      <c r="L228" s="778" t="n"/>
+      <c r="H228" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="I228" s="883" t="n">
+        <v>6</v>
+      </c>
+      <c r="J228" s="888" t="n">
+        <v>6</v>
+      </c>
+      <c r="K228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="L228" s="889" t="n">
+        <v>6</v>
+      </c>
       <c r="M228" s="780" t="n"/>
       <c r="N228" s="780" t="n"/>
-      <c r="O228" s="778" t="n"/>
-      <c r="P228" s="778" t="n"/>
-      <c r="Q228" s="778" t="n"/>
-      <c r="R228" s="778" t="n"/>
-      <c r="S228" s="778" t="n"/>
+      <c r="O228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="P228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="R228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="S228" s="889" t="n">
+        <v>6</v>
+      </c>
       <c r="T228" s="780" t="n"/>
       <c r="U228" s="780" t="n"/>
-      <c r="V228" s="778" t="n"/>
-      <c r="W228" s="778" t="n"/>
-      <c r="X228" s="778" t="n"/>
-      <c r="Y228" s="778" t="n"/>
-      <c r="Z228" s="778" t="n"/>
+      <c r="V228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="W228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="X228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z228" s="889" t="n">
+        <v>6</v>
+      </c>
       <c r="AA228" s="780" t="n"/>
       <c r="AB228" s="780" t="n"/>
-      <c r="AC228" s="778" t="n"/>
-      <c r="AD228" s="778" t="n"/>
-      <c r="AE228" s="778" t="n"/>
-      <c r="AF228" s="778" t="n"/>
-      <c r="AG228" s="778" t="n"/>
+      <c r="AC228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF228" s="889" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG228" s="889" t="n">
+        <v>6</v>
+      </c>
       <c r="AH228" s="778" t="n"/>
       <c r="AI228" s="4" t="n"/>
       <c r="AJ228" s="428" t="n"/>
       <c r="AK228" s="775" t="n"/>
+      <c r="AL228" s="890" t="inlineStr">
+        <is>
+          <t>IMPE0110 MF0790 DRENATGE LIMFÀTIC ESTÈTIC MANUAL I MECÀNIC · LEIRE · COPILOT matí 9:00-15:00 · 09/03–06/04 · 114 h</t>
+        </is>
+      </c>
+      <c r="AU228" s="827" t="inlineStr">
+        <is>
+          <t>IMPE110 MF0791 MASSATGES ESTÈTICS AMB TÈCNIQUES PER PRESSIÓ · LEIRE · COPILOT matí 9:00-15:00 · 07/04–03/05 · 114 h</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="16.5" customHeight="1" s="757" thickTop="1">
       <c r="A229" s="17" t="inlineStr">
@@ -27363,22 +27979,46 @@
       </c>
       <c r="B230" s="11" t="n"/>
       <c r="C230" s="11" t="n"/>
-      <c r="D230" s="756" t="n"/>
-      <c r="E230" s="756" t="n"/>
+      <c r="D230" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="E230" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="F230" s="24" t="n"/>
       <c r="G230" s="24" t="n"/>
-      <c r="H230" s="756" t="n"/>
-      <c r="I230" s="756" t="n"/>
-      <c r="J230" s="756" t="n"/>
-      <c r="K230" s="756" t="n"/>
-      <c r="L230" s="756" t="n"/>
+      <c r="H230" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="I230" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="J230" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="K230" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="L230" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="M230" s="779" t="n"/>
       <c r="N230" s="779" t="n"/>
-      <c r="O230" s="756" t="n"/>
-      <c r="P230" s="756" t="n"/>
-      <c r="Q230" s="756" t="n"/>
-      <c r="R230" s="756" t="n"/>
-      <c r="S230" s="756" t="n"/>
+      <c r="O230" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="P230" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q230" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="R230" s="826" t="n">
+        <v>6</v>
+      </c>
+      <c r="S230" s="826" t="n">
+        <v>6</v>
+      </c>
       <c r="T230" s="779" t="n"/>
       <c r="U230" s="779" t="n"/>
       <c r="V230" s="756" t="n"/>
@@ -27394,6 +28034,11 @@
       <c r="AF230" s="756" t="n"/>
       <c r="AG230" s="756" t="n"/>
       <c r="AH230" s="756" t="n"/>
+      <c r="AL230" s="844" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="16.5" customHeight="1" s="757" thickBot="1">
       <c r="A231" s="14" t="inlineStr">
@@ -27559,7 +28204,7 @@
     <row r="236"/>
     <row r="237"/>
     <row r="238" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A238" s="829" t="inlineStr">
+      <c r="A238" s="850" t="inlineStr">
         <is>
           <t>MAIG 2027</t>
         </is>
@@ -27722,19 +28367,19 @@
       <c r="C240" s="11" t="n"/>
       <c r="D240" s="26" t="n"/>
       <c r="E240" s="779" t="n"/>
-      <c r="F240" s="830" t="n">
+      <c r="F240" s="851" t="n">
         <v>5</v>
       </c>
-      <c r="G240" s="831" t="n">
+      <c r="G240" s="852" t="n">
         <v>5</v>
       </c>
-      <c r="H240" s="831" t="n">
+      <c r="H240" s="852" t="n">
         <v>5</v>
       </c>
-      <c r="I240" s="831" t="n">
+      <c r="I240" s="852" t="n">
         <v>5</v>
       </c>
-      <c r="J240" s="831" t="n">
+      <c r="J240" s="852" t="n">
         <v>5</v>
       </c>
       <c r="K240" s="779" t="n"/>
@@ -27753,34 +28398,34 @@
       <c r="X240" s="756" t="n"/>
       <c r="Y240" s="779" t="n"/>
       <c r="Z240" s="779" t="n"/>
-      <c r="AA240" s="869" t="n">
+      <c r="AA240" s="891" t="n">
         <v>6</v>
       </c>
-      <c r="AB240" s="870" t="n">
+      <c r="AB240" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="AC240" s="870" t="n">
+      <c r="AC240" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="AD240" s="870" t="n">
+      <c r="AD240" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="AE240" s="870" t="n">
+      <c r="AE240" s="892" t="n">
         <v>6</v>
       </c>
       <c r="AF240" s="779" t="n"/>
       <c r="AG240" s="779" t="n"/>
-      <c r="AH240" s="870" t="n">
+      <c r="AH240" s="892" t="n">
         <v>5</v>
       </c>
       <c r="AI240" s="4" t="n"/>
       <c r="AK240" s="627" t="n"/>
-      <c r="AL240" s="832" t="inlineStr">
+      <c r="AL240" s="853" t="inlineStr">
         <is>
           <t>IFCT117 Introducció a la intel·ligència artificial (2a ed.) · MARIA · GOOGLE matí 9:00-14:00 · 03/05–07/05 · 25 h</t>
         </is>
       </c>
-      <c r="AU240" s="871" t="inlineStr">
+      <c r="AU240" s="893" t="inlineStr">
         <is>
           <t>FCOI20 Comunicació i col·laboració amb eines digitals (ACTIC Nivell avançat) · MARIA · GOOGLE matí 9:00-15:00 · 24/05–01/06 · 40 h</t>
         </is>
@@ -27796,50 +28441,48 @@
       <c r="C241" s="456" t="n"/>
       <c r="D241" s="218" t="n"/>
       <c r="E241" s="779" t="n"/>
-      <c r="F241" s="866" t="n">
+      <c r="F241" s="756" t="n"/>
+      <c r="G241" s="825" t="n">
         <v>6</v>
       </c>
-      <c r="G241" s="872" t="n">
+      <c r="H241" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="H241" s="873" t="n">
+      <c r="I241" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="I241" s="873" t="n">
-        <v>6</v>
-      </c>
-      <c r="J241" s="873" t="n">
+      <c r="J241" s="826" t="n">
         <v>6</v>
       </c>
       <c r="K241" s="779" t="n"/>
       <c r="L241" s="779" t="n"/>
-      <c r="M241" s="873" t="n">
+      <c r="M241" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="N241" s="873" t="n">
+      <c r="N241" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="O241" s="873" t="n">
+      <c r="O241" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="P241" s="873" t="n">
+      <c r="P241" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="Q241" s="873" t="n">
+      <c r="Q241" s="826" t="n">
         <v>6</v>
       </c>
       <c r="R241" s="779" t="n"/>
       <c r="S241" s="779" t="n"/>
-      <c r="T241" s="873" t="n">
+      <c r="T241" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="U241" s="873" t="n">
+      <c r="U241" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="V241" s="873" t="n">
+      <c r="V241" s="826" t="n">
         <v>5</v>
       </c>
-      <c r="W241" s="873" t="n">
+      <c r="W241" s="826" t="n">
         <v>5</v>
       </c>
       <c r="X241" s="756" t="n"/>
@@ -27855,12 +28498,7 @@
       <c r="AH241" s="756" t="n"/>
       <c r="AI241" s="4" t="n"/>
       <c r="AK241" s="774" t="n"/>
-      <c r="AL241" s="874" t="inlineStr">
-        <is>
-          <t>IMPE110 MF0791 MASSATGES ESTÈTICS AMB TÈCNIQUES PER PRESSIÓ · LEIRE · FIREFOX matí 9:00-15:00 · 07/04–03/05 · 114 h</t>
-        </is>
-      </c>
-      <c r="AU241" s="875" t="inlineStr">
+      <c r="AL241" s="828" t="inlineStr">
         <is>
           <t>IMPE0110 MF0792 TÈCNIQUES SENSORIALS ESTÈTIQUES · LEIRE · FIREFOX matí 9:00-15:00 · 04/05–20/05 · 76 h</t>
         </is>
@@ -27876,7 +28514,9 @@
       <c r="C242" s="15" t="n"/>
       <c r="D242" s="596" t="n"/>
       <c r="E242" s="780" t="n"/>
-      <c r="F242" s="778" t="n"/>
+      <c r="F242" s="889" t="n">
+        <v>6</v>
+      </c>
       <c r="G242" s="778" t="n"/>
       <c r="H242" s="778" t="n"/>
       <c r="I242" s="778" t="n"/>
@@ -27908,6 +28548,11 @@
       <c r="AI242" s="4" t="n"/>
       <c r="AJ242" s="428" t="n"/>
       <c r="AK242" s="775" t="n"/>
+      <c r="AL242" s="894" t="inlineStr">
+        <is>
+          <t>IMPE110 MF0791 MASSATGES ESTÈTICS AMB TÈCNIQUES PER PRESSIÓ · LEIRE · COPILOT matí 9:00-15:00 · 07/04–03/05 · 114 h</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="16.5" customHeight="1" s="757" thickTop="1">
       <c r="A243" s="17" t="inlineStr">
@@ -28153,7 +28798,7 @@
     <row r="249"/>
     <row r="250"/>
     <row r="251" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A251" s="829" t="inlineStr">
+      <c r="A251" s="850" t="inlineStr">
         <is>
           <t>JUNY 2027</t>
         </is>
@@ -28312,7 +28957,7 @@
       </c>
       <c r="B253" s="11" t="n"/>
       <c r="C253" s="11" t="n"/>
-      <c r="D253" s="870" t="n">
+      <c r="D253" s="892" t="n">
         <v>5</v>
       </c>
       <c r="E253" s="756" t="n"/>
@@ -28347,7 +28992,7 @@
       <c r="AH253" s="756" t="n"/>
       <c r="AI253" s="4" t="n"/>
       <c r="AK253" s="627" t="n"/>
-      <c r="AL253" s="876" t="inlineStr">
+      <c r="AL253" s="895" t="inlineStr">
         <is>
           <t>FCOI20 Comunicació i col·laboració amb eines digitals (ACTIC Nivell avançat) · MARIA · GOOGLE matí 9:00-15:00 · 24/05–01/06 · 40 h</t>
         </is>
@@ -28684,7 +29329,7 @@
     <row r="263"/>
     <row r="264"/>
     <row r="265" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A265" s="829" t="inlineStr">
+      <c r="A265" s="850" t="inlineStr">
         <is>
           <t>JULIOL 2027</t>
         </is>
@@ -29211,7 +29856,7 @@
     <row r="277" s="757"/>
     <row r="278"/>
     <row r="279" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A279" s="829" t="inlineStr">
+      <c r="A279" s="850" t="inlineStr">
         <is>
           <t>AGOST 2027</t>
         </is>
@@ -29777,7 +30422,7 @@
       <c r="AI293" s="500" t="n">
         <v>22</v>
       </c>
-      <c r="AK293" s="877" t="inlineStr">
+      <c r="AK293" s="896" t="inlineStr">
         <is>
           <t>Festius: 11/09 Diada Nacional de Catalunya (Autonòmic)</t>
         </is>
@@ -29903,29 +30548,29 @@
       <c r="D295" s="756" t="n"/>
       <c r="E295" s="756" t="n"/>
       <c r="F295" s="756" t="n"/>
-      <c r="G295" s="878" t="n"/>
-      <c r="H295" s="878" t="n"/>
+      <c r="G295" s="897" t="n"/>
+      <c r="H295" s="897" t="n"/>
       <c r="I295" s="756" t="n"/>
       <c r="J295" s="756" t="n"/>
       <c r="K295" s="756" t="n"/>
       <c r="L295" s="756" t="n"/>
       <c r="M295" s="756" t="n"/>
-      <c r="N295" s="879" t="n"/>
-      <c r="O295" s="878" t="n"/>
+      <c r="N295" s="898" t="n"/>
+      <c r="O295" s="897" t="n"/>
       <c r="P295" s="756" t="n"/>
       <c r="Q295" s="756" t="n"/>
       <c r="R295" s="756" t="n"/>
       <c r="S295" s="756" t="n"/>
       <c r="T295" s="756" t="n"/>
-      <c r="U295" s="878" t="n"/>
-      <c r="V295" s="878" t="n"/>
+      <c r="U295" s="897" t="n"/>
+      <c r="V295" s="897" t="n"/>
       <c r="W295" s="756" t="n"/>
       <c r="X295" s="756" t="n"/>
       <c r="Y295" s="756" t="n"/>
       <c r="Z295" s="756" t="n"/>
       <c r="AA295" s="756" t="n"/>
-      <c r="AB295" s="878" t="n"/>
-      <c r="AC295" s="878" t="n"/>
+      <c r="AB295" s="897" t="n"/>
+      <c r="AC295" s="897" t="n"/>
       <c r="AD295" s="756" t="n"/>
       <c r="AE295" s="756" t="n"/>
       <c r="AF295" s="756" t="n"/>
@@ -29944,29 +30589,29 @@
       <c r="D296" s="782" t="n"/>
       <c r="E296" s="756" t="n"/>
       <c r="F296" s="756" t="n"/>
-      <c r="G296" s="878" t="n"/>
-      <c r="H296" s="878" t="n"/>
+      <c r="G296" s="897" t="n"/>
+      <c r="H296" s="897" t="n"/>
       <c r="I296" s="756" t="n"/>
       <c r="J296" s="756" t="n"/>
       <c r="K296" s="756" t="n"/>
       <c r="L296" s="756" t="n"/>
       <c r="M296" s="756" t="n"/>
-      <c r="N296" s="879" t="n"/>
-      <c r="O296" s="878" t="n"/>
+      <c r="N296" s="898" t="n"/>
+      <c r="O296" s="897" t="n"/>
       <c r="P296" s="756" t="n"/>
       <c r="Q296" s="756" t="n"/>
       <c r="R296" s="756" t="n"/>
       <c r="S296" s="756" t="n"/>
       <c r="T296" s="756" t="n"/>
-      <c r="U296" s="878" t="n"/>
-      <c r="V296" s="878" t="n"/>
+      <c r="U296" s="897" t="n"/>
+      <c r="V296" s="897" t="n"/>
       <c r="W296" s="756" t="n"/>
       <c r="X296" s="756" t="n"/>
       <c r="Y296" s="756" t="n"/>
       <c r="Z296" s="756" t="n"/>
       <c r="AA296" s="756" t="n"/>
-      <c r="AB296" s="878" t="n"/>
-      <c r="AC296" s="878" t="n"/>
+      <c r="AB296" s="897" t="n"/>
+      <c r="AC296" s="897" t="n"/>
       <c r="AD296" s="756" t="n"/>
       <c r="AE296" s="756" t="n"/>
       <c r="AF296" s="756" t="n"/>
@@ -29985,29 +30630,29 @@
       <c r="D297" s="783" t="n"/>
       <c r="E297" s="778" t="n"/>
       <c r="F297" s="778" t="n"/>
-      <c r="G297" s="880" t="n"/>
-      <c r="H297" s="880" t="n"/>
+      <c r="G297" s="899" t="n"/>
+      <c r="H297" s="899" t="n"/>
       <c r="I297" s="778" t="n"/>
       <c r="J297" s="778" t="n"/>
       <c r="K297" s="778" t="n"/>
       <c r="L297" s="778" t="n"/>
       <c r="M297" s="778" t="n"/>
-      <c r="N297" s="881" t="n"/>
-      <c r="O297" s="880" t="n"/>
+      <c r="N297" s="900" t="n"/>
+      <c r="O297" s="899" t="n"/>
       <c r="P297" s="778" t="n"/>
       <c r="Q297" s="778" t="n"/>
       <c r="R297" s="778" t="n"/>
       <c r="S297" s="778" t="n"/>
       <c r="T297" s="778" t="n"/>
-      <c r="U297" s="880" t="n"/>
-      <c r="V297" s="880" t="n"/>
+      <c r="U297" s="899" t="n"/>
+      <c r="V297" s="899" t="n"/>
       <c r="W297" s="778" t="n"/>
       <c r="X297" s="778" t="n"/>
       <c r="Y297" s="778" t="n"/>
       <c r="Z297" s="778" t="n"/>
       <c r="AA297" s="778" t="n"/>
-      <c r="AB297" s="880" t="n"/>
-      <c r="AC297" s="880" t="n"/>
+      <c r="AB297" s="899" t="n"/>
+      <c r="AC297" s="899" t="n"/>
       <c r="AD297" s="778" t="n"/>
       <c r="AE297" s="778" t="n"/>
       <c r="AF297" s="778" t="n"/>
@@ -30026,29 +30671,29 @@
       <c r="D298" s="755" t="n"/>
       <c r="E298" s="756" t="n"/>
       <c r="F298" s="756" t="n"/>
-      <c r="G298" s="878" t="n"/>
-      <c r="H298" s="878" t="n"/>
+      <c r="G298" s="897" t="n"/>
+      <c r="H298" s="897" t="n"/>
       <c r="I298" s="756" t="n"/>
       <c r="J298" s="756" t="n"/>
       <c r="K298" s="756" t="n"/>
       <c r="L298" s="756" t="n"/>
       <c r="M298" s="756" t="n"/>
-      <c r="N298" s="879" t="n"/>
-      <c r="O298" s="878" t="n"/>
+      <c r="N298" s="898" t="n"/>
+      <c r="O298" s="897" t="n"/>
       <c r="P298" s="756" t="n"/>
       <c r="Q298" s="756" t="n"/>
       <c r="R298" s="756" t="n"/>
       <c r="S298" s="756" t="n"/>
       <c r="T298" s="756" t="n"/>
-      <c r="U298" s="878" t="n"/>
-      <c r="V298" s="878" t="n"/>
+      <c r="U298" s="897" t="n"/>
+      <c r="V298" s="897" t="n"/>
       <c r="W298" s="756" t="n"/>
       <c r="X298" s="756" t="n"/>
       <c r="Y298" s="756" t="n"/>
       <c r="Z298" s="756" t="n"/>
       <c r="AA298" s="756" t="n"/>
-      <c r="AB298" s="878" t="n"/>
-      <c r="AC298" s="878" t="n"/>
+      <c r="AB298" s="897" t="n"/>
+      <c r="AC298" s="897" t="n"/>
       <c r="AD298" s="756" t="n"/>
       <c r="AE298" s="756" t="n"/>
       <c r="AF298" s="756" t="n"/>
@@ -30067,29 +30712,29 @@
       <c r="D299" s="756" t="n"/>
       <c r="E299" s="756" t="n"/>
       <c r="F299" s="756" t="n"/>
-      <c r="G299" s="878" t="n"/>
-      <c r="H299" s="878" t="n"/>
+      <c r="G299" s="897" t="n"/>
+      <c r="H299" s="897" t="n"/>
       <c r="I299" s="756" t="n"/>
       <c r="J299" s="756" t="n"/>
       <c r="K299" s="756" t="n"/>
       <c r="L299" s="756" t="n"/>
       <c r="M299" s="756" t="n"/>
-      <c r="N299" s="879" t="n"/>
-      <c r="O299" s="878" t="n"/>
+      <c r="N299" s="898" t="n"/>
+      <c r="O299" s="897" t="n"/>
       <c r="P299" s="756" t="n"/>
       <c r="Q299" s="756" t="n"/>
       <c r="R299" s="756" t="n"/>
       <c r="S299" s="756" t="n"/>
       <c r="T299" s="756" t="n"/>
-      <c r="U299" s="878" t="n"/>
-      <c r="V299" s="878" t="n"/>
+      <c r="U299" s="897" t="n"/>
+      <c r="V299" s="897" t="n"/>
       <c r="W299" s="756" t="n"/>
       <c r="X299" s="756" t="n"/>
       <c r="Y299" s="756" t="n"/>
       <c r="Z299" s="756" t="n"/>
       <c r="AA299" s="756" t="n"/>
-      <c r="AB299" s="878" t="n"/>
-      <c r="AC299" s="878" t="n"/>
+      <c r="AB299" s="897" t="n"/>
+      <c r="AC299" s="897" t="n"/>
       <c r="AD299" s="756" t="n"/>
       <c r="AE299" s="756" t="n"/>
       <c r="AF299" s="756" t="n"/>
@@ -30107,29 +30752,29 @@
       <c r="D300" s="783" t="n"/>
       <c r="E300" s="778" t="n"/>
       <c r="F300" s="778" t="n"/>
-      <c r="G300" s="880" t="n"/>
-      <c r="H300" s="880" t="n"/>
+      <c r="G300" s="899" t="n"/>
+      <c r="H300" s="899" t="n"/>
       <c r="I300" s="778" t="n"/>
       <c r="J300" s="778" t="n"/>
       <c r="K300" s="778" t="n"/>
       <c r="L300" s="778" t="n"/>
       <c r="M300" s="778" t="n"/>
-      <c r="N300" s="881" t="n"/>
-      <c r="O300" s="880" t="n"/>
+      <c r="N300" s="900" t="n"/>
+      <c r="O300" s="899" t="n"/>
       <c r="P300" s="778" t="n"/>
       <c r="Q300" s="778" t="n"/>
       <c r="R300" s="778" t="n"/>
       <c r="S300" s="778" t="n"/>
       <c r="T300" s="778" t="n"/>
-      <c r="U300" s="880" t="n"/>
-      <c r="V300" s="880" t="n"/>
+      <c r="U300" s="899" t="n"/>
+      <c r="V300" s="899" t="n"/>
       <c r="W300" s="778" t="n"/>
       <c r="X300" s="778" t="n"/>
       <c r="Y300" s="778" t="n"/>
       <c r="Z300" s="778" t="n"/>
       <c r="AA300" s="778" t="n"/>
-      <c r="AB300" s="880" t="n"/>
-      <c r="AC300" s="880" t="n"/>
+      <c r="AB300" s="899" t="n"/>
+      <c r="AC300" s="899" t="n"/>
       <c r="AD300" s="778" t="n"/>
       <c r="AE300" s="778" t="n"/>
       <c r="AF300" s="778" t="n"/>
@@ -30147,29 +30792,29 @@
       <c r="D301" s="755" t="n"/>
       <c r="E301" s="755" t="n"/>
       <c r="F301" s="756" t="n"/>
-      <c r="G301" s="882" t="n"/>
-      <c r="H301" s="878" t="n"/>
+      <c r="G301" s="901" t="n"/>
+      <c r="H301" s="897" t="n"/>
       <c r="I301" s="755" t="n"/>
       <c r="J301" s="756" t="n"/>
       <c r="K301" s="755" t="n"/>
       <c r="L301" s="756" t="n"/>
       <c r="M301" s="756" t="n"/>
-      <c r="N301" s="883" t="n"/>
-      <c r="O301" s="882" t="n"/>
+      <c r="N301" s="902" t="n"/>
+      <c r="O301" s="901" t="n"/>
       <c r="P301" s="756" t="n"/>
       <c r="Q301" s="756" t="n"/>
       <c r="R301" s="755" t="n"/>
       <c r="S301" s="756" t="n"/>
       <c r="T301" s="756" t="n"/>
-      <c r="U301" s="882" t="n"/>
-      <c r="V301" s="882" t="n"/>
+      <c r="U301" s="901" t="n"/>
+      <c r="V301" s="901" t="n"/>
       <c r="W301" s="756" t="n"/>
       <c r="X301" s="756" t="n"/>
       <c r="Y301" s="755" t="n"/>
       <c r="Z301" s="756" t="n"/>
       <c r="AA301" s="756" t="n"/>
-      <c r="AB301" s="882" t="n"/>
-      <c r="AC301" s="882" t="n"/>
+      <c r="AB301" s="901" t="n"/>
+      <c r="AC301" s="901" t="n"/>
       <c r="AD301" s="756" t="n"/>
       <c r="AE301" s="756" t="n"/>
       <c r="AF301" s="755" t="n"/>
@@ -30187,29 +30832,29 @@
       <c r="D302" s="756" t="n"/>
       <c r="E302" s="756" t="n"/>
       <c r="F302" s="756" t="n"/>
-      <c r="G302" s="878" t="n"/>
-      <c r="H302" s="878" t="n"/>
+      <c r="G302" s="897" t="n"/>
+      <c r="H302" s="897" t="n"/>
       <c r="I302" s="756" t="n"/>
       <c r="J302" s="756" t="n"/>
       <c r="K302" s="756" t="n"/>
       <c r="L302" s="756" t="n"/>
       <c r="M302" s="756" t="n"/>
-      <c r="N302" s="879" t="n"/>
-      <c r="O302" s="878" t="n"/>
+      <c r="N302" s="898" t="n"/>
+      <c r="O302" s="897" t="n"/>
       <c r="P302" s="756" t="n"/>
       <c r="Q302" s="756" t="n"/>
       <c r="R302" s="756" t="n"/>
       <c r="S302" s="756" t="n"/>
       <c r="T302" s="756" t="n"/>
-      <c r="U302" s="878" t="n"/>
-      <c r="V302" s="878" t="n"/>
+      <c r="U302" s="897" t="n"/>
+      <c r="V302" s="897" t="n"/>
       <c r="W302" s="756" t="n"/>
       <c r="X302" s="756" t="n"/>
       <c r="Y302" s="756" t="n"/>
       <c r="Z302" s="756" t="n"/>
       <c r="AA302" s="756" t="n"/>
-      <c r="AB302" s="878" t="n"/>
-      <c r="AC302" s="878" t="n"/>
+      <c r="AB302" s="897" t="n"/>
+      <c r="AC302" s="897" t="n"/>
       <c r="AD302" s="756" t="n"/>
       <c r="AE302" s="756" t="n"/>
       <c r="AF302" s="756" t="n"/>
@@ -30227,29 +30872,29 @@
       <c r="D303" s="756" t="n"/>
       <c r="E303" s="756" t="n"/>
       <c r="F303" s="756" t="n"/>
-      <c r="G303" s="878" t="n"/>
-      <c r="H303" s="878" t="n"/>
+      <c r="G303" s="897" t="n"/>
+      <c r="H303" s="897" t="n"/>
       <c r="I303" s="756" t="n"/>
       <c r="J303" s="756" t="n"/>
       <c r="K303" s="756" t="n"/>
       <c r="L303" s="756" t="n"/>
       <c r="M303" s="756" t="n"/>
-      <c r="N303" s="879" t="n"/>
-      <c r="O303" s="878" t="n"/>
+      <c r="N303" s="898" t="n"/>
+      <c r="O303" s="897" t="n"/>
       <c r="P303" s="756" t="n"/>
       <c r="Q303" s="756" t="n"/>
       <c r="R303" s="756" t="n"/>
       <c r="S303" s="756" t="n"/>
       <c r="T303" s="756" t="n"/>
-      <c r="U303" s="878" t="n"/>
-      <c r="V303" s="878" t="n"/>
+      <c r="U303" s="897" t="n"/>
+      <c r="V303" s="897" t="n"/>
       <c r="W303" s="756" t="n"/>
       <c r="X303" s="756" t="n"/>
       <c r="Y303" s="756" t="n"/>
       <c r="Z303" s="756" t="n"/>
       <c r="AA303" s="756" t="n"/>
-      <c r="AB303" s="878" t="n"/>
-      <c r="AC303" s="878" t="n"/>
+      <c r="AB303" s="897" t="n"/>
+      <c r="AC303" s="897" t="n"/>
       <c r="AD303" s="756" t="n"/>
       <c r="AE303" s="756" t="n"/>
       <c r="AF303" s="756" t="n"/>
@@ -30300,7 +30945,7 @@
       <c r="AI306" s="500" t="n">
         <v>20</v>
       </c>
-      <c r="AK306" s="877" t="inlineStr">
+      <c r="AK306" s="896" t="inlineStr">
         <is>
           <t>Festius: 12/10 Festa Nacional d'Espanya (Nacional)</t>
         </is>
@@ -30426,36 +31071,36 @@
       <c r="B308" s="11" t="n"/>
       <c r="C308" s="11" t="n"/>
       <c r="D308" s="756" t="n"/>
-      <c r="E308" s="878" t="n"/>
-      <c r="F308" s="878" t="n"/>
+      <c r="E308" s="897" t="n"/>
+      <c r="F308" s="897" t="n"/>
       <c r="G308" s="756" t="n"/>
       <c r="H308" s="756" t="n"/>
       <c r="I308" s="756" t="n"/>
       <c r="J308" s="756" t="n"/>
       <c r="K308" s="756" t="n"/>
-      <c r="L308" s="878" t="n"/>
-      <c r="M308" s="878" t="n"/>
+      <c r="L308" s="897" t="n"/>
+      <c r="M308" s="897" t="n"/>
       <c r="N308" s="756" t="n"/>
-      <c r="O308" s="879" t="n"/>
+      <c r="O308" s="898" t="n"/>
       <c r="P308" s="756" t="n"/>
       <c r="Q308" s="756" t="n"/>
       <c r="R308" s="756" t="n"/>
-      <c r="S308" s="878" t="n"/>
-      <c r="T308" s="878" t="n"/>
+      <c r="S308" s="897" t="n"/>
+      <c r="T308" s="897" t="n"/>
       <c r="U308" s="756" t="n"/>
       <c r="V308" s="756" t="n"/>
       <c r="W308" s="756" t="n"/>
       <c r="X308" s="756" t="n"/>
       <c r="Y308" s="756" t="n"/>
-      <c r="Z308" s="878" t="n"/>
-      <c r="AA308" s="878" t="n"/>
+      <c r="Z308" s="897" t="n"/>
+      <c r="AA308" s="897" t="n"/>
       <c r="AB308" s="756" t="n"/>
       <c r="AC308" s="756" t="n"/>
       <c r="AD308" s="756" t="n"/>
       <c r="AE308" s="756" t="n"/>
       <c r="AF308" s="756" t="n"/>
-      <c r="AG308" s="878" t="n"/>
-      <c r="AH308" s="878" t="n"/>
+      <c r="AG308" s="897" t="n"/>
+      <c r="AH308" s="897" t="n"/>
       <c r="AI308" s="4" t="n"/>
     </row>
     <row r="309" ht="15.75" customHeight="1" s="757">
@@ -30467,36 +31112,36 @@
       <c r="B309" s="456" t="n"/>
       <c r="C309" s="456" t="n"/>
       <c r="D309" s="782" t="n"/>
-      <c r="E309" s="878" t="n"/>
-      <c r="F309" s="878" t="n"/>
+      <c r="E309" s="897" t="n"/>
+      <c r="F309" s="897" t="n"/>
       <c r="G309" s="756" t="n"/>
       <c r="H309" s="756" t="n"/>
       <c r="I309" s="756" t="n"/>
       <c r="J309" s="756" t="n"/>
       <c r="K309" s="756" t="n"/>
-      <c r="L309" s="878" t="n"/>
-      <c r="M309" s="878" t="n"/>
+      <c r="L309" s="897" t="n"/>
+      <c r="M309" s="897" t="n"/>
       <c r="N309" s="756" t="n"/>
-      <c r="O309" s="879" t="n"/>
+      <c r="O309" s="898" t="n"/>
       <c r="P309" s="756" t="n"/>
       <c r="Q309" s="756" t="n"/>
       <c r="R309" s="756" t="n"/>
-      <c r="S309" s="878" t="n"/>
-      <c r="T309" s="878" t="n"/>
+      <c r="S309" s="897" t="n"/>
+      <c r="T309" s="897" t="n"/>
       <c r="U309" s="756" t="n"/>
       <c r="V309" s="756" t="n"/>
       <c r="W309" s="756" t="n"/>
       <c r="X309" s="756" t="n"/>
       <c r="Y309" s="756" t="n"/>
-      <c r="Z309" s="878" t="n"/>
-      <c r="AA309" s="878" t="n"/>
+      <c r="Z309" s="897" t="n"/>
+      <c r="AA309" s="897" t="n"/>
       <c r="AB309" s="756" t="n"/>
       <c r="AC309" s="756" t="n"/>
       <c r="AD309" s="756" t="n"/>
       <c r="AE309" s="756" t="n"/>
       <c r="AF309" s="756" t="n"/>
-      <c r="AG309" s="878" t="n"/>
-      <c r="AH309" s="878" t="n"/>
+      <c r="AG309" s="897" t="n"/>
+      <c r="AH309" s="897" t="n"/>
       <c r="AI309" s="4" t="n"/>
     </row>
     <row r="310" ht="19.5" customHeight="1" s="757">
@@ -30508,36 +31153,36 @@
       <c r="B310" s="15" t="n"/>
       <c r="C310" s="15" t="n"/>
       <c r="D310" s="783" t="n"/>
-      <c r="E310" s="880" t="n"/>
-      <c r="F310" s="880" t="n"/>
+      <c r="E310" s="899" t="n"/>
+      <c r="F310" s="899" t="n"/>
       <c r="G310" s="778" t="n"/>
       <c r="H310" s="778" t="n"/>
       <c r="I310" s="778" t="n"/>
       <c r="J310" s="778" t="n"/>
       <c r="K310" s="778" t="n"/>
-      <c r="L310" s="880" t="n"/>
-      <c r="M310" s="880" t="n"/>
+      <c r="L310" s="899" t="n"/>
+      <c r="M310" s="899" t="n"/>
       <c r="N310" s="778" t="n"/>
-      <c r="O310" s="881" t="n"/>
+      <c r="O310" s="900" t="n"/>
       <c r="P310" s="778" t="n"/>
       <c r="Q310" s="778" t="n"/>
       <c r="R310" s="778" t="n"/>
-      <c r="S310" s="880" t="n"/>
-      <c r="T310" s="880" t="n"/>
+      <c r="S310" s="899" t="n"/>
+      <c r="T310" s="899" t="n"/>
       <c r="U310" s="778" t="n"/>
       <c r="V310" s="778" t="n"/>
       <c r="W310" s="778" t="n"/>
       <c r="X310" s="778" t="n"/>
       <c r="Y310" s="778" t="n"/>
-      <c r="Z310" s="880" t="n"/>
-      <c r="AA310" s="880" t="n"/>
+      <c r="Z310" s="899" t="n"/>
+      <c r="AA310" s="899" t="n"/>
       <c r="AB310" s="778" t="n"/>
       <c r="AC310" s="778" t="n"/>
       <c r="AD310" s="778" t="n"/>
       <c r="AE310" s="778" t="n"/>
       <c r="AF310" s="778" t="n"/>
-      <c r="AG310" s="880" t="n"/>
-      <c r="AH310" s="880" t="n"/>
+      <c r="AG310" s="899" t="n"/>
+      <c r="AH310" s="899" t="n"/>
       <c r="AI310" s="4" t="n"/>
     </row>
     <row r="311" ht="16.5" customHeight="1" s="757">
@@ -30549,36 +31194,36 @@
       <c r="B311" s="18" t="n"/>
       <c r="C311" s="18" t="n"/>
       <c r="D311" s="755" t="n"/>
-      <c r="E311" s="878" t="n"/>
-      <c r="F311" s="878" t="n"/>
+      <c r="E311" s="897" t="n"/>
+      <c r="F311" s="897" t="n"/>
       <c r="G311" s="756" t="n"/>
       <c r="H311" s="756" t="n"/>
       <c r="I311" s="756" t="n"/>
       <c r="J311" s="756" t="n"/>
       <c r="K311" s="756" t="n"/>
-      <c r="L311" s="878" t="n"/>
-      <c r="M311" s="878" t="n"/>
+      <c r="L311" s="897" t="n"/>
+      <c r="M311" s="897" t="n"/>
       <c r="N311" s="756" t="n"/>
-      <c r="O311" s="879" t="n"/>
+      <c r="O311" s="898" t="n"/>
       <c r="P311" s="756" t="n"/>
       <c r="Q311" s="756" t="n"/>
       <c r="R311" s="756" t="n"/>
-      <c r="S311" s="878" t="n"/>
-      <c r="T311" s="878" t="n"/>
+      <c r="S311" s="897" t="n"/>
+      <c r="T311" s="897" t="n"/>
       <c r="U311" s="756" t="n"/>
       <c r="V311" s="756" t="n"/>
       <c r="W311" s="756" t="n"/>
       <c r="X311" s="756" t="n"/>
       <c r="Y311" s="756" t="n"/>
-      <c r="Z311" s="878" t="n"/>
-      <c r="AA311" s="878" t="n"/>
+      <c r="Z311" s="897" t="n"/>
+      <c r="AA311" s="897" t="n"/>
       <c r="AB311" s="756" t="n"/>
       <c r="AC311" s="756" t="n"/>
       <c r="AD311" s="756" t="n"/>
       <c r="AE311" s="756" t="n"/>
       <c r="AF311" s="756" t="n"/>
-      <c r="AG311" s="878" t="n"/>
-      <c r="AH311" s="878" t="n"/>
+      <c r="AG311" s="897" t="n"/>
+      <c r="AH311" s="897" t="n"/>
       <c r="AI311" s="4" t="n"/>
     </row>
     <row r="312" ht="15.75" customHeight="1" s="757">
@@ -30590,36 +31235,36 @@
       <c r="B312" s="11" t="n"/>
       <c r="C312" s="11" t="n"/>
       <c r="D312" s="756" t="n"/>
-      <c r="E312" s="878" t="n"/>
-      <c r="F312" s="878" t="n"/>
+      <c r="E312" s="897" t="n"/>
+      <c r="F312" s="897" t="n"/>
       <c r="G312" s="756" t="n"/>
       <c r="H312" s="756" t="n"/>
       <c r="I312" s="756" t="n"/>
       <c r="J312" s="756" t="n"/>
       <c r="K312" s="756" t="n"/>
-      <c r="L312" s="878" t="n"/>
-      <c r="M312" s="878" t="n"/>
+      <c r="L312" s="897" t="n"/>
+      <c r="M312" s="897" t="n"/>
       <c r="N312" s="756" t="n"/>
-      <c r="O312" s="879" t="n"/>
+      <c r="O312" s="898" t="n"/>
       <c r="P312" s="756" t="n"/>
       <c r="Q312" s="756" t="n"/>
       <c r="R312" s="756" t="n"/>
-      <c r="S312" s="878" t="n"/>
-      <c r="T312" s="878" t="n"/>
+      <c r="S312" s="897" t="n"/>
+      <c r="T312" s="897" t="n"/>
       <c r="U312" s="756" t="n"/>
       <c r="V312" s="756" t="n"/>
       <c r="W312" s="756" t="n"/>
       <c r="X312" s="756" t="n"/>
       <c r="Y312" s="756" t="n"/>
-      <c r="Z312" s="878" t="n"/>
-      <c r="AA312" s="878" t="n"/>
+      <c r="Z312" s="897" t="n"/>
+      <c r="AA312" s="897" t="n"/>
       <c r="AB312" s="756" t="n"/>
       <c r="AC312" s="756" t="n"/>
       <c r="AD312" s="756" t="n"/>
       <c r="AE312" s="756" t="n"/>
       <c r="AF312" s="756" t="n"/>
-      <c r="AG312" s="878" t="n"/>
-      <c r="AH312" s="878" t="n"/>
+      <c r="AG312" s="897" t="n"/>
+      <c r="AH312" s="897" t="n"/>
     </row>
     <row r="313" ht="16.5" customHeight="1" s="757">
       <c r="A313" s="14" t="inlineStr">
@@ -30630,36 +31275,36 @@
       <c r="B313" s="15" t="n"/>
       <c r="C313" s="15" t="n"/>
       <c r="D313" s="783" t="n"/>
-      <c r="E313" s="880" t="n"/>
-      <c r="F313" s="880" t="n"/>
+      <c r="E313" s="899" t="n"/>
+      <c r="F313" s="899" t="n"/>
       <c r="G313" s="778" t="n"/>
       <c r="H313" s="778" t="n"/>
       <c r="I313" s="778" t="n"/>
       <c r="J313" s="778" t="n"/>
       <c r="K313" s="778" t="n"/>
-      <c r="L313" s="880" t="n"/>
-      <c r="M313" s="880" t="n"/>
+      <c r="L313" s="899" t="n"/>
+      <c r="M313" s="899" t="n"/>
       <c r="N313" s="778" t="n"/>
-      <c r="O313" s="881" t="n"/>
+      <c r="O313" s="900" t="n"/>
       <c r="P313" s="778" t="n"/>
       <c r="Q313" s="778" t="n"/>
       <c r="R313" s="778" t="n"/>
-      <c r="S313" s="880" t="n"/>
-      <c r="T313" s="880" t="n"/>
+      <c r="S313" s="899" t="n"/>
+      <c r="T313" s="899" t="n"/>
       <c r="U313" s="778" t="n"/>
       <c r="V313" s="778" t="n"/>
       <c r="W313" s="778" t="n"/>
       <c r="X313" s="778" t="n"/>
       <c r="Y313" s="778" t="n"/>
-      <c r="Z313" s="880" t="n"/>
-      <c r="AA313" s="880" t="n"/>
+      <c r="Z313" s="899" t="n"/>
+      <c r="AA313" s="899" t="n"/>
       <c r="AB313" s="778" t="n"/>
       <c r="AC313" s="778" t="n"/>
       <c r="AD313" s="778" t="n"/>
       <c r="AE313" s="778" t="n"/>
       <c r="AF313" s="778" t="n"/>
-      <c r="AG313" s="880" t="n"/>
-      <c r="AH313" s="880" t="n"/>
+      <c r="AG313" s="899" t="n"/>
+      <c r="AH313" s="899" t="n"/>
     </row>
     <row r="314" ht="16.5" customHeight="1" s="757">
       <c r="A314" s="10" t="inlineStr">
@@ -30670,36 +31315,36 @@
       <c r="B314" s="11" t="n"/>
       <c r="C314" s="11" t="n"/>
       <c r="D314" s="755" t="n"/>
-      <c r="E314" s="882" t="n"/>
-      <c r="F314" s="878" t="n"/>
+      <c r="E314" s="901" t="n"/>
+      <c r="F314" s="897" t="n"/>
       <c r="G314" s="755" t="n"/>
       <c r="H314" s="756" t="n"/>
       <c r="I314" s="755" t="n"/>
       <c r="J314" s="756" t="n"/>
       <c r="K314" s="755" t="n"/>
-      <c r="L314" s="878" t="n"/>
-      <c r="M314" s="878" t="n"/>
+      <c r="L314" s="897" t="n"/>
+      <c r="M314" s="897" t="n"/>
       <c r="N314" s="755" t="n"/>
-      <c r="O314" s="883" t="n"/>
+      <c r="O314" s="902" t="n"/>
       <c r="P314" s="756" t="n"/>
       <c r="Q314" s="756" t="n"/>
       <c r="R314" s="755" t="n"/>
-      <c r="S314" s="878" t="n"/>
-      <c r="T314" s="878" t="n"/>
+      <c r="S314" s="897" t="n"/>
+      <c r="T314" s="897" t="n"/>
       <c r="U314" s="755" t="n"/>
       <c r="V314" s="755" t="n"/>
       <c r="W314" s="756" t="n"/>
       <c r="X314" s="756" t="n"/>
       <c r="Y314" s="755" t="n"/>
-      <c r="Z314" s="878" t="n"/>
-      <c r="AA314" s="878" t="n"/>
+      <c r="Z314" s="897" t="n"/>
+      <c r="AA314" s="897" t="n"/>
       <c r="AB314" s="755" t="n"/>
       <c r="AC314" s="755" t="n"/>
       <c r="AD314" s="756" t="n"/>
       <c r="AE314" s="756" t="n"/>
       <c r="AF314" s="755" t="n"/>
-      <c r="AG314" s="878" t="n"/>
-      <c r="AH314" s="878" t="n"/>
+      <c r="AG314" s="897" t="n"/>
+      <c r="AH314" s="897" t="n"/>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="757">
       <c r="A315" s="12" t="inlineStr">
@@ -30710,36 +31355,36 @@
       <c r="B315" s="11" t="n"/>
       <c r="C315" s="11" t="n"/>
       <c r="D315" s="756" t="n"/>
-      <c r="E315" s="878" t="n"/>
-      <c r="F315" s="878" t="n"/>
+      <c r="E315" s="897" t="n"/>
+      <c r="F315" s="897" t="n"/>
       <c r="G315" s="756" t="n"/>
       <c r="H315" s="756" t="n"/>
       <c r="I315" s="756" t="n"/>
       <c r="J315" s="756" t="n"/>
       <c r="K315" s="756" t="n"/>
-      <c r="L315" s="878" t="n"/>
-      <c r="M315" s="878" t="n"/>
+      <c r="L315" s="897" t="n"/>
+      <c r="M315" s="897" t="n"/>
       <c r="N315" s="756" t="n"/>
-      <c r="O315" s="879" t="n"/>
+      <c r="O315" s="898" t="n"/>
       <c r="P315" s="756" t="n"/>
       <c r="Q315" s="756" t="n"/>
       <c r="R315" s="756" t="n"/>
-      <c r="S315" s="878" t="n"/>
-      <c r="T315" s="878" t="n"/>
+      <c r="S315" s="897" t="n"/>
+      <c r="T315" s="897" t="n"/>
       <c r="U315" s="756" t="n"/>
       <c r="V315" s="756" t="n"/>
       <c r="W315" s="756" t="n"/>
       <c r="X315" s="756" t="n"/>
       <c r="Y315" s="756" t="n"/>
-      <c r="Z315" s="878" t="n"/>
-      <c r="AA315" s="878" t="n"/>
+      <c r="Z315" s="897" t="n"/>
+      <c r="AA315" s="897" t="n"/>
       <c r="AB315" s="756" t="n"/>
       <c r="AC315" s="756" t="n"/>
       <c r="AD315" s="756" t="n"/>
       <c r="AE315" s="756" t="n"/>
       <c r="AF315" s="756" t="n"/>
-      <c r="AG315" s="878" t="n"/>
-      <c r="AH315" s="878" t="n"/>
+      <c r="AG315" s="897" t="n"/>
+      <c r="AH315" s="897" t="n"/>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="757">
       <c r="A316" s="12" t="inlineStr">
@@ -30750,36 +31395,36 @@
       <c r="B316" s="11" t="n"/>
       <c r="C316" s="11" t="n"/>
       <c r="D316" s="756" t="n"/>
-      <c r="E316" s="878" t="n"/>
-      <c r="F316" s="878" t="n"/>
+      <c r="E316" s="897" t="n"/>
+      <c r="F316" s="897" t="n"/>
       <c r="G316" s="756" t="n"/>
       <c r="H316" s="756" t="n"/>
       <c r="I316" s="756" t="n"/>
       <c r="J316" s="756" t="n"/>
       <c r="K316" s="756" t="n"/>
-      <c r="L316" s="878" t="n"/>
-      <c r="M316" s="878" t="n"/>
+      <c r="L316" s="897" t="n"/>
+      <c r="M316" s="897" t="n"/>
       <c r="N316" s="756" t="n"/>
-      <c r="O316" s="879" t="n"/>
+      <c r="O316" s="898" t="n"/>
       <c r="P316" s="756" t="n"/>
       <c r="Q316" s="756" t="n"/>
       <c r="R316" s="756" t="n"/>
-      <c r="S316" s="878" t="n"/>
-      <c r="T316" s="878" t="n"/>
+      <c r="S316" s="897" t="n"/>
+      <c r="T316" s="897" t="n"/>
       <c r="U316" s="756" t="n"/>
       <c r="V316" s="756" t="n"/>
       <c r="W316" s="756" t="n"/>
       <c r="X316" s="756" t="n"/>
       <c r="Y316" s="756" t="n"/>
-      <c r="Z316" s="878" t="n"/>
-      <c r="AA316" s="878" t="n"/>
+      <c r="Z316" s="897" t="n"/>
+      <c r="AA316" s="897" t="n"/>
       <c r="AB316" s="756" t="n"/>
       <c r="AC316" s="756" t="n"/>
       <c r="AD316" s="756" t="n"/>
       <c r="AE316" s="756" t="n"/>
       <c r="AF316" s="756" t="n"/>
-      <c r="AG316" s="878" t="n"/>
-      <c r="AH316" s="878" t="n"/>
+      <c r="AG316" s="897" t="n"/>
+      <c r="AH316" s="897" t="n"/>
     </row>
     <row r="317" s="757"/>
     <row r="318" s="757"/>
@@ -30825,7 +31470,7 @@
       <c r="AI319" s="500" t="n">
         <v>21</v>
       </c>
-      <c r="AK319" s="877" t="inlineStr">
+      <c r="AK319" s="896" t="inlineStr">
         <is>
           <t>Festius: 01/11 Tots Sants (Nacional)</t>
         </is>
@@ -30948,34 +31593,34 @@
       </c>
       <c r="B321" s="11" t="n"/>
       <c r="C321" s="11" t="n"/>
-      <c r="D321" s="879" t="n"/>
+      <c r="D321" s="898" t="n"/>
       <c r="E321" s="756" t="n"/>
       <c r="F321" s="756" t="n"/>
       <c r="G321" s="756" t="n"/>
       <c r="H321" s="756" t="n"/>
-      <c r="I321" s="878" t="n"/>
-      <c r="J321" s="878" t="n"/>
+      <c r="I321" s="897" t="n"/>
+      <c r="J321" s="897" t="n"/>
       <c r="K321" s="756" t="n"/>
       <c r="L321" s="756" t="n"/>
       <c r="M321" s="756" t="n"/>
       <c r="N321" s="756" t="n"/>
       <c r="O321" s="756" t="n"/>
-      <c r="P321" s="878" t="n"/>
-      <c r="Q321" s="878" t="n"/>
+      <c r="P321" s="897" t="n"/>
+      <c r="Q321" s="897" t="n"/>
       <c r="R321" s="756" t="n"/>
       <c r="S321" s="756" t="n"/>
       <c r="T321" s="756" t="n"/>
       <c r="U321" s="756" t="n"/>
       <c r="V321" s="756" t="n"/>
-      <c r="W321" s="878" t="n"/>
-      <c r="X321" s="878" t="n"/>
+      <c r="W321" s="897" t="n"/>
+      <c r="X321" s="897" t="n"/>
       <c r="Y321" s="756" t="n"/>
       <c r="Z321" s="756" t="n"/>
       <c r="AA321" s="756" t="n"/>
       <c r="AB321" s="756" t="n"/>
       <c r="AC321" s="756" t="n"/>
-      <c r="AD321" s="878" t="n"/>
-      <c r="AE321" s="878" t="n"/>
+      <c r="AD321" s="897" t="n"/>
+      <c r="AE321" s="897" t="n"/>
       <c r="AF321" s="756" t="n"/>
       <c r="AG321" s="756" t="n"/>
       <c r="AH321" s="756" t="n"/>
@@ -30989,34 +31634,34 @@
       </c>
       <c r="B322" s="456" t="n"/>
       <c r="C322" s="456" t="n"/>
-      <c r="D322" s="884" t="n"/>
+      <c r="D322" s="903" t="n"/>
       <c r="E322" s="756" t="n"/>
       <c r="F322" s="756" t="n"/>
       <c r="G322" s="756" t="n"/>
       <c r="H322" s="756" t="n"/>
-      <c r="I322" s="878" t="n"/>
-      <c r="J322" s="878" t="n"/>
+      <c r="I322" s="897" t="n"/>
+      <c r="J322" s="897" t="n"/>
       <c r="K322" s="756" t="n"/>
       <c r="L322" s="756" t="n"/>
       <c r="M322" s="756" t="n"/>
       <c r="N322" s="756" t="n"/>
       <c r="O322" s="756" t="n"/>
-      <c r="P322" s="878" t="n"/>
-      <c r="Q322" s="878" t="n"/>
+      <c r="P322" s="897" t="n"/>
+      <c r="Q322" s="897" t="n"/>
       <c r="R322" s="756" t="n"/>
       <c r="S322" s="756" t="n"/>
       <c r="T322" s="756" t="n"/>
       <c r="U322" s="756" t="n"/>
       <c r="V322" s="756" t="n"/>
-      <c r="W322" s="878" t="n"/>
-      <c r="X322" s="878" t="n"/>
+      <c r="W322" s="897" t="n"/>
+      <c r="X322" s="897" t="n"/>
       <c r="Y322" s="756" t="n"/>
       <c r="Z322" s="756" t="n"/>
       <c r="AA322" s="756" t="n"/>
       <c r="AB322" s="756" t="n"/>
       <c r="AC322" s="756" t="n"/>
-      <c r="AD322" s="878" t="n"/>
-      <c r="AE322" s="878" t="n"/>
+      <c r="AD322" s="897" t="n"/>
+      <c r="AE322" s="897" t="n"/>
       <c r="AF322" s="756" t="n"/>
       <c r="AG322" s="756" t="n"/>
       <c r="AH322" s="756" t="n"/>
@@ -31030,34 +31675,34 @@
       </c>
       <c r="B323" s="15" t="n"/>
       <c r="C323" s="15" t="n"/>
-      <c r="D323" s="885" t="n"/>
+      <c r="D323" s="904" t="n"/>
       <c r="E323" s="778" t="n"/>
       <c r="F323" s="778" t="n"/>
       <c r="G323" s="778" t="n"/>
       <c r="H323" s="778" t="n"/>
-      <c r="I323" s="880" t="n"/>
-      <c r="J323" s="880" t="n"/>
+      <c r="I323" s="899" t="n"/>
+      <c r="J323" s="899" t="n"/>
       <c r="K323" s="778" t="n"/>
       <c r="L323" s="778" t="n"/>
       <c r="M323" s="778" t="n"/>
       <c r="N323" s="778" t="n"/>
       <c r="O323" s="778" t="n"/>
-      <c r="P323" s="880" t="n"/>
-      <c r="Q323" s="880" t="n"/>
+      <c r="P323" s="899" t="n"/>
+      <c r="Q323" s="899" t="n"/>
       <c r="R323" s="778" t="n"/>
       <c r="S323" s="778" t="n"/>
       <c r="T323" s="778" t="n"/>
       <c r="U323" s="778" t="n"/>
       <c r="V323" s="778" t="n"/>
-      <c r="W323" s="880" t="n"/>
-      <c r="X323" s="880" t="n"/>
+      <c r="W323" s="899" t="n"/>
+      <c r="X323" s="899" t="n"/>
       <c r="Y323" s="778" t="n"/>
       <c r="Z323" s="778" t="n"/>
       <c r="AA323" s="778" t="n"/>
       <c r="AB323" s="778" t="n"/>
       <c r="AC323" s="778" t="n"/>
-      <c r="AD323" s="880" t="n"/>
-      <c r="AE323" s="880" t="n"/>
+      <c r="AD323" s="899" t="n"/>
+      <c r="AE323" s="899" t="n"/>
       <c r="AF323" s="778" t="n"/>
       <c r="AG323" s="778" t="n"/>
       <c r="AH323" s="778" t="n"/>
@@ -31071,34 +31716,34 @@
       </c>
       <c r="B324" s="18" t="n"/>
       <c r="C324" s="18" t="n"/>
-      <c r="D324" s="883" t="n"/>
+      <c r="D324" s="902" t="n"/>
       <c r="E324" s="756" t="n"/>
       <c r="F324" s="756" t="n"/>
       <c r="G324" s="756" t="n"/>
       <c r="H324" s="756" t="n"/>
-      <c r="I324" s="878" t="n"/>
-      <c r="J324" s="878" t="n"/>
+      <c r="I324" s="897" t="n"/>
+      <c r="J324" s="897" t="n"/>
       <c r="K324" s="756" t="n"/>
       <c r="L324" s="756" t="n"/>
       <c r="M324" s="756" t="n"/>
       <c r="N324" s="756" t="n"/>
       <c r="O324" s="756" t="n"/>
-      <c r="P324" s="878" t="n"/>
-      <c r="Q324" s="878" t="n"/>
+      <c r="P324" s="897" t="n"/>
+      <c r="Q324" s="897" t="n"/>
       <c r="R324" s="756" t="n"/>
       <c r="S324" s="756" t="n"/>
       <c r="T324" s="756" t="n"/>
       <c r="U324" s="756" t="n"/>
       <c r="V324" s="756" t="n"/>
-      <c r="W324" s="878" t="n"/>
-      <c r="X324" s="878" t="n"/>
+      <c r="W324" s="897" t="n"/>
+      <c r="X324" s="897" t="n"/>
       <c r="Y324" s="756" t="n"/>
       <c r="Z324" s="756" t="n"/>
       <c r="AA324" s="756" t="n"/>
       <c r="AB324" s="756" t="n"/>
       <c r="AC324" s="756" t="n"/>
-      <c r="AD324" s="878" t="n"/>
-      <c r="AE324" s="878" t="n"/>
+      <c r="AD324" s="897" t="n"/>
+      <c r="AE324" s="897" t="n"/>
       <c r="AF324" s="756" t="n"/>
       <c r="AG324" s="756" t="n"/>
       <c r="AH324" s="756" t="n"/>
@@ -31112,34 +31757,34 @@
       </c>
       <c r="B325" s="11" t="n"/>
       <c r="C325" s="11" t="n"/>
-      <c r="D325" s="879" t="n"/>
+      <c r="D325" s="898" t="n"/>
       <c r="E325" s="756" t="n"/>
       <c r="F325" s="756" t="n"/>
       <c r="G325" s="756" t="n"/>
       <c r="H325" s="756" t="n"/>
-      <c r="I325" s="878" t="n"/>
-      <c r="J325" s="878" t="n"/>
+      <c r="I325" s="897" t="n"/>
+      <c r="J325" s="897" t="n"/>
       <c r="K325" s="756" t="n"/>
       <c r="L325" s="756" t="n"/>
       <c r="M325" s="756" t="n"/>
       <c r="N325" s="756" t="n"/>
       <c r="O325" s="756" t="n"/>
-      <c r="P325" s="878" t="n"/>
-      <c r="Q325" s="878" t="n"/>
+      <c r="P325" s="897" t="n"/>
+      <c r="Q325" s="897" t="n"/>
       <c r="R325" s="756" t="n"/>
       <c r="S325" s="756" t="n"/>
       <c r="T325" s="756" t="n"/>
       <c r="U325" s="756" t="n"/>
       <c r="V325" s="756" t="n"/>
-      <c r="W325" s="878" t="n"/>
-      <c r="X325" s="878" t="n"/>
+      <c r="W325" s="897" t="n"/>
+      <c r="X325" s="897" t="n"/>
       <c r="Y325" s="756" t="n"/>
       <c r="Z325" s="756" t="n"/>
       <c r="AA325" s="756" t="n"/>
       <c r="AB325" s="756" t="n"/>
       <c r="AC325" s="756" t="n"/>
-      <c r="AD325" s="878" t="n"/>
-      <c r="AE325" s="878" t="n"/>
+      <c r="AD325" s="897" t="n"/>
+      <c r="AE325" s="897" t="n"/>
       <c r="AF325" s="756" t="n"/>
       <c r="AG325" s="756" t="n"/>
       <c r="AH325" s="756" t="n"/>
@@ -31152,34 +31797,34 @@
       </c>
       <c r="B326" s="15" t="n"/>
       <c r="C326" s="15" t="n"/>
-      <c r="D326" s="885" t="n"/>
+      <c r="D326" s="904" t="n"/>
       <c r="E326" s="778" t="n"/>
       <c r="F326" s="778" t="n"/>
       <c r="G326" s="778" t="n"/>
       <c r="H326" s="778" t="n"/>
-      <c r="I326" s="880" t="n"/>
-      <c r="J326" s="880" t="n"/>
+      <c r="I326" s="899" t="n"/>
+      <c r="J326" s="899" t="n"/>
       <c r="K326" s="778" t="n"/>
       <c r="L326" s="778" t="n"/>
       <c r="M326" s="778" t="n"/>
       <c r="N326" s="778" t="n"/>
       <c r="O326" s="778" t="n"/>
-      <c r="P326" s="880" t="n"/>
-      <c r="Q326" s="880" t="n"/>
+      <c r="P326" s="899" t="n"/>
+      <c r="Q326" s="899" t="n"/>
       <c r="R326" s="778" t="n"/>
       <c r="S326" s="778" t="n"/>
       <c r="T326" s="778" t="n"/>
       <c r="U326" s="778" t="n"/>
       <c r="V326" s="778" t="n"/>
-      <c r="W326" s="880" t="n"/>
-      <c r="X326" s="880" t="n"/>
+      <c r="W326" s="899" t="n"/>
+      <c r="X326" s="899" t="n"/>
       <c r="Y326" s="778" t="n"/>
       <c r="Z326" s="778" t="n"/>
       <c r="AA326" s="778" t="n"/>
       <c r="AB326" s="778" t="n"/>
       <c r="AC326" s="778" t="n"/>
-      <c r="AD326" s="880" t="n"/>
-      <c r="AE326" s="880" t="n"/>
+      <c r="AD326" s="899" t="n"/>
+      <c r="AE326" s="899" t="n"/>
       <c r="AF326" s="778" t="n"/>
       <c r="AG326" s="778" t="n"/>
       <c r="AH326" s="778" t="n"/>
@@ -31192,34 +31837,34 @@
       </c>
       <c r="B327" s="11" t="n"/>
       <c r="C327" s="11" t="n"/>
-      <c r="D327" s="883" t="n"/>
+      <c r="D327" s="902" t="n"/>
       <c r="E327" s="755" t="n"/>
       <c r="F327" s="756" t="n"/>
       <c r="G327" s="755" t="n"/>
       <c r="H327" s="756" t="n"/>
-      <c r="I327" s="882" t="n"/>
-      <c r="J327" s="878" t="n"/>
+      <c r="I327" s="901" t="n"/>
+      <c r="J327" s="897" t="n"/>
       <c r="K327" s="755" t="n"/>
       <c r="L327" s="756" t="n"/>
       <c r="M327" s="756" t="n"/>
       <c r="N327" s="755" t="n"/>
       <c r="O327" s="755" t="n"/>
-      <c r="P327" s="878" t="n"/>
-      <c r="Q327" s="878" t="n"/>
+      <c r="P327" s="897" t="n"/>
+      <c r="Q327" s="897" t="n"/>
       <c r="R327" s="755" t="n"/>
       <c r="S327" s="756" t="n"/>
       <c r="T327" s="756" t="n"/>
       <c r="U327" s="755" t="n"/>
       <c r="V327" s="755" t="n"/>
-      <c r="W327" s="878" t="n"/>
-      <c r="X327" s="878" t="n"/>
+      <c r="W327" s="897" t="n"/>
+      <c r="X327" s="897" t="n"/>
       <c r="Y327" s="755" t="n"/>
       <c r="Z327" s="756" t="n"/>
       <c r="AA327" s="756" t="n"/>
       <c r="AB327" s="755" t="n"/>
       <c r="AC327" s="755" t="n"/>
-      <c r="AD327" s="878" t="n"/>
-      <c r="AE327" s="878" t="n"/>
+      <c r="AD327" s="897" t="n"/>
+      <c r="AE327" s="897" t="n"/>
       <c r="AF327" s="755" t="n"/>
       <c r="AG327" s="756" t="n"/>
       <c r="AH327" s="756" t="n"/>
@@ -31232,34 +31877,34 @@
       </c>
       <c r="B328" s="11" t="n"/>
       <c r="C328" s="11" t="n"/>
-      <c r="D328" s="879" t="n"/>
+      <c r="D328" s="898" t="n"/>
       <c r="E328" s="756" t="n"/>
       <c r="F328" s="756" t="n"/>
       <c r="G328" s="756" t="n"/>
       <c r="H328" s="756" t="n"/>
-      <c r="I328" s="878" t="n"/>
-      <c r="J328" s="878" t="n"/>
+      <c r="I328" s="897" t="n"/>
+      <c r="J328" s="897" t="n"/>
       <c r="K328" s="756" t="n"/>
       <c r="L328" s="756" t="n"/>
       <c r="M328" s="756" t="n"/>
       <c r="N328" s="756" t="n"/>
       <c r="O328" s="756" t="n"/>
-      <c r="P328" s="878" t="n"/>
-      <c r="Q328" s="878" t="n"/>
+      <c r="P328" s="897" t="n"/>
+      <c r="Q328" s="897" t="n"/>
       <c r="R328" s="756" t="n"/>
       <c r="S328" s="756" t="n"/>
       <c r="T328" s="756" t="n"/>
       <c r="U328" s="756" t="n"/>
       <c r="V328" s="756" t="n"/>
-      <c r="W328" s="878" t="n"/>
-      <c r="X328" s="878" t="n"/>
+      <c r="W328" s="897" t="n"/>
+      <c r="X328" s="897" t="n"/>
       <c r="Y328" s="756" t="n"/>
       <c r="Z328" s="756" t="n"/>
       <c r="AA328" s="756" t="n"/>
       <c r="AB328" s="756" t="n"/>
       <c r="AC328" s="756" t="n"/>
-      <c r="AD328" s="878" t="n"/>
-      <c r="AE328" s="878" t="n"/>
+      <c r="AD328" s="897" t="n"/>
+      <c r="AE328" s="897" t="n"/>
       <c r="AF328" s="756" t="n"/>
       <c r="AG328" s="756" t="n"/>
       <c r="AH328" s="756" t="n"/>
@@ -31272,34 +31917,34 @@
       </c>
       <c r="B329" s="11" t="n"/>
       <c r="C329" s="11" t="n"/>
-      <c r="D329" s="879" t="n"/>
+      <c r="D329" s="898" t="n"/>
       <c r="E329" s="756" t="n"/>
       <c r="F329" s="756" t="n"/>
       <c r="G329" s="756" t="n"/>
       <c r="H329" s="756" t="n"/>
-      <c r="I329" s="878" t="n"/>
-      <c r="J329" s="878" t="n"/>
+      <c r="I329" s="897" t="n"/>
+      <c r="J329" s="897" t="n"/>
       <c r="K329" s="756" t="n"/>
       <c r="L329" s="756" t="n"/>
       <c r="M329" s="756" t="n"/>
       <c r="N329" s="756" t="n"/>
       <c r="O329" s="756" t="n"/>
-      <c r="P329" s="878" t="n"/>
-      <c r="Q329" s="878" t="n"/>
+      <c r="P329" s="897" t="n"/>
+      <c r="Q329" s="897" t="n"/>
       <c r="R329" s="756" t="n"/>
       <c r="S329" s="756" t="n"/>
       <c r="T329" s="756" t="n"/>
       <c r="U329" s="756" t="n"/>
       <c r="V329" s="756" t="n"/>
-      <c r="W329" s="878" t="n"/>
-      <c r="X329" s="878" t="n"/>
+      <c r="W329" s="897" t="n"/>
+      <c r="X329" s="897" t="n"/>
       <c r="Y329" s="756" t="n"/>
       <c r="Z329" s="756" t="n"/>
       <c r="AA329" s="756" t="n"/>
       <c r="AB329" s="756" t="n"/>
       <c r="AC329" s="756" t="n"/>
-      <c r="AD329" s="878" t="n"/>
-      <c r="AE329" s="878" t="n"/>
+      <c r="AD329" s="897" t="n"/>
+      <c r="AE329" s="897" t="n"/>
       <c r="AF329" s="756" t="n"/>
       <c r="AG329" s="756" t="n"/>
       <c r="AH329" s="756" t="n"/>
@@ -31348,7 +31993,7 @@
       <c r="AI332" s="500" t="n">
         <v>13</v>
       </c>
-      <c r="AK332" s="877" t="inlineStr">
+      <c r="AK332" s="896" t="inlineStr">
         <is>
           <t>Festius: 06/12 Dia de la Constitució (Nacional) · 07/12 Festiu local (canvi pel 15/09) · 08/12 Immaculada Concepció (Nacional) · 25/12 Nadal (Nacional) · Vacances: 23/12–31/12</t>
         </is>
@@ -31476,34 +32121,34 @@
       <c r="D334" s="756" t="n"/>
       <c r="E334" s="756" t="n"/>
       <c r="F334" s="756" t="n"/>
-      <c r="G334" s="878" t="n"/>
-      <c r="H334" s="878" t="n"/>
-      <c r="I334" s="879" t="n"/>
-      <c r="J334" s="879" t="n"/>
-      <c r="K334" s="879" t="n"/>
+      <c r="G334" s="897" t="n"/>
+      <c r="H334" s="897" t="n"/>
+      <c r="I334" s="898" t="n"/>
+      <c r="J334" s="898" t="n"/>
+      <c r="K334" s="898" t="n"/>
       <c r="L334" s="756" t="n"/>
       <c r="M334" s="756" t="n"/>
-      <c r="N334" s="878" t="n"/>
-      <c r="O334" s="878" t="n"/>
+      <c r="N334" s="897" t="n"/>
+      <c r="O334" s="897" t="n"/>
       <c r="P334" s="756" t="n"/>
       <c r="Q334" s="756" t="n"/>
       <c r="R334" s="756" t="n"/>
       <c r="S334" s="756" t="n"/>
       <c r="T334" s="756" t="n"/>
-      <c r="U334" s="878" t="n"/>
-      <c r="V334" s="878" t="n"/>
+      <c r="U334" s="897" t="n"/>
+      <c r="V334" s="897" t="n"/>
       <c r="W334" s="756" t="n"/>
       <c r="X334" s="756" t="n"/>
       <c r="Y334" s="756" t="n"/>
-      <c r="Z334" s="886" t="n"/>
-      <c r="AA334" s="886" t="n"/>
-      <c r="AB334" s="879" t="n"/>
-      <c r="AC334" s="878" t="n"/>
-      <c r="AD334" s="886" t="n"/>
-      <c r="AE334" s="886" t="n"/>
-      <c r="AF334" s="886" t="n"/>
-      <c r="AG334" s="886" t="n"/>
-      <c r="AH334" s="886" t="n"/>
+      <c r="Z334" s="905" t="n"/>
+      <c r="AA334" s="905" t="n"/>
+      <c r="AB334" s="898" t="n"/>
+      <c r="AC334" s="897" t="n"/>
+      <c r="AD334" s="905" t="n"/>
+      <c r="AE334" s="905" t="n"/>
+      <c r="AF334" s="905" t="n"/>
+      <c r="AG334" s="905" t="n"/>
+      <c r="AH334" s="905" t="n"/>
       <c r="AI334" s="4" t="n"/>
     </row>
     <row r="335" ht="15.75" customHeight="1" s="757">
@@ -31517,34 +32162,34 @@
       <c r="D335" s="782" t="n"/>
       <c r="E335" s="756" t="n"/>
       <c r="F335" s="756" t="n"/>
-      <c r="G335" s="878" t="n"/>
-      <c r="H335" s="878" t="n"/>
-      <c r="I335" s="879" t="n"/>
-      <c r="J335" s="879" t="n"/>
-      <c r="K335" s="879" t="n"/>
+      <c r="G335" s="897" t="n"/>
+      <c r="H335" s="897" t="n"/>
+      <c r="I335" s="898" t="n"/>
+      <c r="J335" s="898" t="n"/>
+      <c r="K335" s="898" t="n"/>
       <c r="L335" s="756" t="n"/>
       <c r="M335" s="756" t="n"/>
-      <c r="N335" s="878" t="n"/>
-      <c r="O335" s="878" t="n"/>
+      <c r="N335" s="897" t="n"/>
+      <c r="O335" s="897" t="n"/>
       <c r="P335" s="756" t="n"/>
       <c r="Q335" s="756" t="n"/>
       <c r="R335" s="756" t="n"/>
       <c r="S335" s="756" t="n"/>
       <c r="T335" s="756" t="n"/>
-      <c r="U335" s="878" t="n"/>
-      <c r="V335" s="878" t="n"/>
+      <c r="U335" s="897" t="n"/>
+      <c r="V335" s="897" t="n"/>
       <c r="W335" s="756" t="n"/>
       <c r="X335" s="756" t="n"/>
       <c r="Y335" s="756" t="n"/>
-      <c r="Z335" s="886" t="n"/>
-      <c r="AA335" s="886" t="n"/>
-      <c r="AB335" s="879" t="n"/>
-      <c r="AC335" s="878" t="n"/>
-      <c r="AD335" s="886" t="n"/>
-      <c r="AE335" s="886" t="n"/>
-      <c r="AF335" s="886" t="n"/>
-      <c r="AG335" s="886" t="n"/>
-      <c r="AH335" s="886" t="n"/>
+      <c r="Z335" s="905" t="n"/>
+      <c r="AA335" s="905" t="n"/>
+      <c r="AB335" s="898" t="n"/>
+      <c r="AC335" s="897" t="n"/>
+      <c r="AD335" s="905" t="n"/>
+      <c r="AE335" s="905" t="n"/>
+      <c r="AF335" s="905" t="n"/>
+      <c r="AG335" s="905" t="n"/>
+      <c r="AH335" s="905" t="n"/>
       <c r="AI335" s="4" t="n"/>
     </row>
     <row r="336" ht="19.5" customHeight="1" s="757">
@@ -31558,34 +32203,34 @@
       <c r="D336" s="783" t="n"/>
       <c r="E336" s="778" t="n"/>
       <c r="F336" s="778" t="n"/>
-      <c r="G336" s="880" t="n"/>
-      <c r="H336" s="880" t="n"/>
-      <c r="I336" s="881" t="n"/>
-      <c r="J336" s="881" t="n"/>
-      <c r="K336" s="881" t="n"/>
+      <c r="G336" s="899" t="n"/>
+      <c r="H336" s="899" t="n"/>
+      <c r="I336" s="900" t="n"/>
+      <c r="J336" s="900" t="n"/>
+      <c r="K336" s="900" t="n"/>
       <c r="L336" s="778" t="n"/>
       <c r="M336" s="778" t="n"/>
-      <c r="N336" s="880" t="n"/>
-      <c r="O336" s="880" t="n"/>
+      <c r="N336" s="899" t="n"/>
+      <c r="O336" s="899" t="n"/>
       <c r="P336" s="778" t="n"/>
       <c r="Q336" s="778" t="n"/>
       <c r="R336" s="778" t="n"/>
       <c r="S336" s="778" t="n"/>
       <c r="T336" s="778" t="n"/>
-      <c r="U336" s="880" t="n"/>
-      <c r="V336" s="880" t="n"/>
+      <c r="U336" s="899" t="n"/>
+      <c r="V336" s="899" t="n"/>
       <c r="W336" s="778" t="n"/>
       <c r="X336" s="778" t="n"/>
       <c r="Y336" s="778" t="n"/>
-      <c r="Z336" s="887" t="n"/>
-      <c r="AA336" s="887" t="n"/>
-      <c r="AB336" s="881" t="n"/>
-      <c r="AC336" s="880" t="n"/>
-      <c r="AD336" s="887" t="n"/>
-      <c r="AE336" s="887" t="n"/>
-      <c r="AF336" s="887" t="n"/>
-      <c r="AG336" s="887" t="n"/>
-      <c r="AH336" s="887" t="n"/>
+      <c r="Z336" s="906" t="n"/>
+      <c r="AA336" s="906" t="n"/>
+      <c r="AB336" s="900" t="n"/>
+      <c r="AC336" s="899" t="n"/>
+      <c r="AD336" s="906" t="n"/>
+      <c r="AE336" s="906" t="n"/>
+      <c r="AF336" s="906" t="n"/>
+      <c r="AG336" s="906" t="n"/>
+      <c r="AH336" s="906" t="n"/>
       <c r="AI336" s="4" t="n"/>
     </row>
     <row r="337" ht="16.5" customHeight="1" s="757">
@@ -31599,34 +32244,34 @@
       <c r="D337" s="755" t="n"/>
       <c r="E337" s="756" t="n"/>
       <c r="F337" s="756" t="n"/>
-      <c r="G337" s="878" t="n"/>
-      <c r="H337" s="878" t="n"/>
-      <c r="I337" s="879" t="n"/>
-      <c r="J337" s="879" t="n"/>
-      <c r="K337" s="879" t="n"/>
+      <c r="G337" s="897" t="n"/>
+      <c r="H337" s="897" t="n"/>
+      <c r="I337" s="898" t="n"/>
+      <c r="J337" s="898" t="n"/>
+      <c r="K337" s="898" t="n"/>
       <c r="L337" s="756" t="n"/>
       <c r="M337" s="756" t="n"/>
-      <c r="N337" s="878" t="n"/>
-      <c r="O337" s="878" t="n"/>
+      <c r="N337" s="897" t="n"/>
+      <c r="O337" s="897" t="n"/>
       <c r="P337" s="756" t="n"/>
       <c r="Q337" s="756" t="n"/>
       <c r="R337" s="756" t="n"/>
       <c r="S337" s="756" t="n"/>
       <c r="T337" s="756" t="n"/>
-      <c r="U337" s="878" t="n"/>
-      <c r="V337" s="878" t="n"/>
+      <c r="U337" s="897" t="n"/>
+      <c r="V337" s="897" t="n"/>
       <c r="W337" s="756" t="n"/>
       <c r="X337" s="756" t="n"/>
       <c r="Y337" s="756" t="n"/>
-      <c r="Z337" s="886" t="n"/>
-      <c r="AA337" s="886" t="n"/>
-      <c r="AB337" s="879" t="n"/>
-      <c r="AC337" s="878" t="n"/>
-      <c r="AD337" s="886" t="n"/>
-      <c r="AE337" s="886" t="n"/>
-      <c r="AF337" s="886" t="n"/>
-      <c r="AG337" s="886" t="n"/>
-      <c r="AH337" s="886" t="n"/>
+      <c r="Z337" s="905" t="n"/>
+      <c r="AA337" s="905" t="n"/>
+      <c r="AB337" s="898" t="n"/>
+      <c r="AC337" s="897" t="n"/>
+      <c r="AD337" s="905" t="n"/>
+      <c r="AE337" s="905" t="n"/>
+      <c r="AF337" s="905" t="n"/>
+      <c r="AG337" s="905" t="n"/>
+      <c r="AH337" s="905" t="n"/>
       <c r="AI337" s="4" t="n"/>
     </row>
     <row r="338" ht="15.75" customHeight="1" s="757">
@@ -31640,34 +32285,34 @@
       <c r="D338" s="756" t="n"/>
       <c r="E338" s="756" t="n"/>
       <c r="F338" s="756" t="n"/>
-      <c r="G338" s="878" t="n"/>
-      <c r="H338" s="878" t="n"/>
-      <c r="I338" s="879" t="n"/>
-      <c r="J338" s="879" t="n"/>
-      <c r="K338" s="879" t="n"/>
+      <c r="G338" s="897" t="n"/>
+      <c r="H338" s="897" t="n"/>
+      <c r="I338" s="898" t="n"/>
+      <c r="J338" s="898" t="n"/>
+      <c r="K338" s="898" t="n"/>
       <c r="L338" s="756" t="n"/>
       <c r="M338" s="756" t="n"/>
-      <c r="N338" s="878" t="n"/>
-      <c r="O338" s="878" t="n"/>
+      <c r="N338" s="897" t="n"/>
+      <c r="O338" s="897" t="n"/>
       <c r="P338" s="756" t="n"/>
       <c r="Q338" s="756" t="n"/>
       <c r="R338" s="756" t="n"/>
       <c r="S338" s="756" t="n"/>
       <c r="T338" s="756" t="n"/>
-      <c r="U338" s="878" t="n"/>
-      <c r="V338" s="878" t="n"/>
+      <c r="U338" s="897" t="n"/>
+      <c r="V338" s="897" t="n"/>
       <c r="W338" s="756" t="n"/>
       <c r="X338" s="756" t="n"/>
       <c r="Y338" s="756" t="n"/>
-      <c r="Z338" s="886" t="n"/>
-      <c r="AA338" s="886" t="n"/>
-      <c r="AB338" s="879" t="n"/>
-      <c r="AC338" s="878" t="n"/>
-      <c r="AD338" s="886" t="n"/>
-      <c r="AE338" s="886" t="n"/>
-      <c r="AF338" s="886" t="n"/>
-      <c r="AG338" s="886" t="n"/>
-      <c r="AH338" s="886" t="n"/>
+      <c r="Z338" s="905" t="n"/>
+      <c r="AA338" s="905" t="n"/>
+      <c r="AB338" s="898" t="n"/>
+      <c r="AC338" s="897" t="n"/>
+      <c r="AD338" s="905" t="n"/>
+      <c r="AE338" s="905" t="n"/>
+      <c r="AF338" s="905" t="n"/>
+      <c r="AG338" s="905" t="n"/>
+      <c r="AH338" s="905" t="n"/>
     </row>
     <row r="339" ht="16.5" customHeight="1" s="757">
       <c r="A339" s="14" t="inlineStr">
@@ -31680,34 +32325,34 @@
       <c r="D339" s="783" t="n"/>
       <c r="E339" s="778" t="n"/>
       <c r="F339" s="778" t="n"/>
-      <c r="G339" s="880" t="n"/>
-      <c r="H339" s="880" t="n"/>
-      <c r="I339" s="881" t="n"/>
-      <c r="J339" s="881" t="n"/>
-      <c r="K339" s="881" t="n"/>
+      <c r="G339" s="899" t="n"/>
+      <c r="H339" s="899" t="n"/>
+      <c r="I339" s="900" t="n"/>
+      <c r="J339" s="900" t="n"/>
+      <c r="K339" s="900" t="n"/>
       <c r="L339" s="778" t="n"/>
       <c r="M339" s="778" t="n"/>
-      <c r="N339" s="880" t="n"/>
-      <c r="O339" s="880" t="n"/>
+      <c r="N339" s="899" t="n"/>
+      <c r="O339" s="899" t="n"/>
       <c r="P339" s="778" t="n"/>
       <c r="Q339" s="778" t="n"/>
       <c r="R339" s="778" t="n"/>
       <c r="S339" s="778" t="n"/>
       <c r="T339" s="778" t="n"/>
-      <c r="U339" s="880" t="n"/>
-      <c r="V339" s="880" t="n"/>
+      <c r="U339" s="899" t="n"/>
+      <c r="V339" s="899" t="n"/>
       <c r="W339" s="778" t="n"/>
       <c r="X339" s="778" t="n"/>
       <c r="Y339" s="778" t="n"/>
-      <c r="Z339" s="887" t="n"/>
-      <c r="AA339" s="887" t="n"/>
-      <c r="AB339" s="881" t="n"/>
-      <c r="AC339" s="880" t="n"/>
-      <c r="AD339" s="887" t="n"/>
-      <c r="AE339" s="887" t="n"/>
-      <c r="AF339" s="887" t="n"/>
-      <c r="AG339" s="887" t="n"/>
-      <c r="AH339" s="887" t="n"/>
+      <c r="Z339" s="906" t="n"/>
+      <c r="AA339" s="906" t="n"/>
+      <c r="AB339" s="900" t="n"/>
+      <c r="AC339" s="899" t="n"/>
+      <c r="AD339" s="906" t="n"/>
+      <c r="AE339" s="906" t="n"/>
+      <c r="AF339" s="906" t="n"/>
+      <c r="AG339" s="906" t="n"/>
+      <c r="AH339" s="906" t="n"/>
     </row>
     <row r="340" ht="16.5" customHeight="1" s="757">
       <c r="A340" s="10" t="inlineStr">
@@ -31720,34 +32365,34 @@
       <c r="D340" s="755" t="n"/>
       <c r="E340" s="755" t="n"/>
       <c r="F340" s="756" t="n"/>
-      <c r="G340" s="882" t="n"/>
-      <c r="H340" s="878" t="n"/>
-      <c r="I340" s="883" t="n"/>
-      <c r="J340" s="879" t="n"/>
-      <c r="K340" s="883" t="n"/>
+      <c r="G340" s="901" t="n"/>
+      <c r="H340" s="897" t="n"/>
+      <c r="I340" s="902" t="n"/>
+      <c r="J340" s="898" t="n"/>
+      <c r="K340" s="902" t="n"/>
       <c r="L340" s="756" t="n"/>
       <c r="M340" s="756" t="n"/>
-      <c r="N340" s="882" t="n"/>
-      <c r="O340" s="882" t="n"/>
+      <c r="N340" s="901" t="n"/>
+      <c r="O340" s="901" t="n"/>
       <c r="P340" s="756" t="n"/>
       <c r="Q340" s="756" t="n"/>
       <c r="R340" s="755" t="n"/>
       <c r="S340" s="756" t="n"/>
       <c r="T340" s="756" t="n"/>
-      <c r="U340" s="882" t="n"/>
-      <c r="V340" s="882" t="n"/>
+      <c r="U340" s="901" t="n"/>
+      <c r="V340" s="901" t="n"/>
       <c r="W340" s="756" t="n"/>
       <c r="X340" s="756" t="n"/>
       <c r="Y340" s="755" t="n"/>
-      <c r="Z340" s="886" t="n"/>
-      <c r="AA340" s="886" t="n"/>
-      <c r="AB340" s="883" t="n"/>
-      <c r="AC340" s="882" t="n"/>
-      <c r="AD340" s="886" t="n"/>
-      <c r="AE340" s="886" t="n"/>
-      <c r="AF340" s="888" t="n"/>
-      <c r="AG340" s="886" t="n"/>
-      <c r="AH340" s="886" t="n"/>
+      <c r="Z340" s="905" t="n"/>
+      <c r="AA340" s="905" t="n"/>
+      <c r="AB340" s="902" t="n"/>
+      <c r="AC340" s="901" t="n"/>
+      <c r="AD340" s="905" t="n"/>
+      <c r="AE340" s="905" t="n"/>
+      <c r="AF340" s="907" t="n"/>
+      <c r="AG340" s="905" t="n"/>
+      <c r="AH340" s="905" t="n"/>
     </row>
     <row r="341" ht="15.75" customHeight="1" s="757">
       <c r="A341" s="12" t="inlineStr">
@@ -31760,34 +32405,34 @@
       <c r="D341" s="756" t="n"/>
       <c r="E341" s="756" t="n"/>
       <c r="F341" s="756" t="n"/>
-      <c r="G341" s="878" t="n"/>
-      <c r="H341" s="878" t="n"/>
-      <c r="I341" s="879" t="n"/>
-      <c r="J341" s="879" t="n"/>
-      <c r="K341" s="879" t="n"/>
+      <c r="G341" s="897" t="n"/>
+      <c r="H341" s="897" t="n"/>
+      <c r="I341" s="898" t="n"/>
+      <c r="J341" s="898" t="n"/>
+      <c r="K341" s="898" t="n"/>
       <c r="L341" s="756" t="n"/>
       <c r="M341" s="756" t="n"/>
-      <c r="N341" s="878" t="n"/>
-      <c r="O341" s="878" t="n"/>
+      <c r="N341" s="897" t="n"/>
+      <c r="O341" s="897" t="n"/>
       <c r="P341" s="756" t="n"/>
       <c r="Q341" s="756" t="n"/>
       <c r="R341" s="756" t="n"/>
       <c r="S341" s="756" t="n"/>
       <c r="T341" s="756" t="n"/>
-      <c r="U341" s="878" t="n"/>
-      <c r="V341" s="878" t="n"/>
+      <c r="U341" s="897" t="n"/>
+      <c r="V341" s="897" t="n"/>
       <c r="W341" s="756" t="n"/>
       <c r="X341" s="756" t="n"/>
       <c r="Y341" s="756" t="n"/>
-      <c r="Z341" s="886" t="n"/>
-      <c r="AA341" s="886" t="n"/>
-      <c r="AB341" s="879" t="n"/>
-      <c r="AC341" s="878" t="n"/>
-      <c r="AD341" s="886" t="n"/>
-      <c r="AE341" s="886" t="n"/>
-      <c r="AF341" s="886" t="n"/>
-      <c r="AG341" s="886" t="n"/>
-      <c r="AH341" s="886" t="n"/>
+      <c r="Z341" s="905" t="n"/>
+      <c r="AA341" s="905" t="n"/>
+      <c r="AB341" s="898" t="n"/>
+      <c r="AC341" s="897" t="n"/>
+      <c r="AD341" s="905" t="n"/>
+      <c r="AE341" s="905" t="n"/>
+      <c r="AF341" s="905" t="n"/>
+      <c r="AG341" s="905" t="n"/>
+      <c r="AH341" s="905" t="n"/>
     </row>
     <row r="342" ht="15.75" customHeight="1" s="757">
       <c r="A342" s="12" t="inlineStr">
@@ -31800,34 +32445,34 @@
       <c r="D342" s="756" t="n"/>
       <c r="E342" s="756" t="n"/>
       <c r="F342" s="756" t="n"/>
-      <c r="G342" s="878" t="n"/>
-      <c r="H342" s="878" t="n"/>
-      <c r="I342" s="879" t="n"/>
-      <c r="J342" s="879" t="n"/>
-      <c r="K342" s="879" t="n"/>
+      <c r="G342" s="897" t="n"/>
+      <c r="H342" s="897" t="n"/>
+      <c r="I342" s="898" t="n"/>
+      <c r="J342" s="898" t="n"/>
+      <c r="K342" s="898" t="n"/>
       <c r="L342" s="756" t="n"/>
       <c r="M342" s="756" t="n"/>
-      <c r="N342" s="878" t="n"/>
-      <c r="O342" s="878" t="n"/>
+      <c r="N342" s="897" t="n"/>
+      <c r="O342" s="897" t="n"/>
       <c r="P342" s="756" t="n"/>
       <c r="Q342" s="756" t="n"/>
       <c r="R342" s="756" t="n"/>
       <c r="S342" s="756" t="n"/>
       <c r="T342" s="756" t="n"/>
-      <c r="U342" s="878" t="n"/>
-      <c r="V342" s="878" t="n"/>
+      <c r="U342" s="897" t="n"/>
+      <c r="V342" s="897" t="n"/>
       <c r="W342" s="756" t="n"/>
       <c r="X342" s="756" t="n"/>
       <c r="Y342" s="756" t="n"/>
-      <c r="Z342" s="886" t="n"/>
-      <c r="AA342" s="886" t="n"/>
-      <c r="AB342" s="879" t="n"/>
-      <c r="AC342" s="878" t="n"/>
-      <c r="AD342" s="886" t="n"/>
-      <c r="AE342" s="886" t="n"/>
-      <c r="AF342" s="886" t="n"/>
-      <c r="AG342" s="886" t="n"/>
-      <c r="AH342" s="886" t="n"/>
+      <c r="Z342" s="905" t="n"/>
+      <c r="AA342" s="905" t="n"/>
+      <c r="AB342" s="898" t="n"/>
+      <c r="AC342" s="897" t="n"/>
+      <c r="AD342" s="905" t="n"/>
+      <c r="AE342" s="905" t="n"/>
+      <c r="AF342" s="905" t="n"/>
+      <c r="AG342" s="905" t="n"/>
+      <c r="AH342" s="905" t="n"/>
     </row>
     <row r="343" s="757"/>
     <row r="344" s="757"/>
@@ -31921,7 +32566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="757" min="1" max="1"/>
@@ -31940,1506 +32585,1848 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="889" t="inlineStr">
+      <c r="A1" s="908" t="inlineStr">
         <is>
           <t>CRONOGRAMA 26-27 PROVISIONAL — PLANIFICACIÓ DE FORMACIONS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="890" t="inlineStr">
+      <c r="A2" s="909" t="inlineStr">
         <is>
           <t>Font: FORMACIONS_26-27_PROVISIONAL.xlsx (hores i docents) · Calendari: full 'CRONO 25-26' i CALENDARI_LABORAL_2027.xlsx · Criteri: 5-6 h/dia en dies laborables consecutius.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="891" t="inlineStr">
+      <c r="A4" s="910" t="inlineStr">
         <is>
           <t>CODI</t>
         </is>
       </c>
-      <c r="B4" s="891" t="inlineStr">
+      <c r="B4" s="910" t="inlineStr">
         <is>
           <t>NOM FORMACIÓ</t>
         </is>
       </c>
-      <c r="C4" s="891" t="inlineStr">
+      <c r="C4" s="910" t="inlineStr">
         <is>
           <t>EDICIÓ</t>
         </is>
       </c>
-      <c r="D4" s="891" t="inlineStr">
+      <c r="D4" s="910" t="inlineStr">
         <is>
           <t>DOCENT</t>
         </is>
       </c>
-      <c r="E4" s="891" t="inlineStr">
+      <c r="E4" s="910" t="inlineStr">
         <is>
           <t>AULA</t>
         </is>
       </c>
-      <c r="F4" s="891" t="inlineStr">
+      <c r="F4" s="910" t="inlineStr">
         <is>
           <t>TORN</t>
         </is>
       </c>
-      <c r="G4" s="891" t="inlineStr">
+      <c r="G4" s="910" t="inlineStr">
         <is>
           <t>HORARI</t>
         </is>
       </c>
-      <c r="H4" s="891" t="inlineStr">
+      <c r="H4" s="910" t="inlineStr">
         <is>
           <t>DATA INICI</t>
         </is>
       </c>
-      <c r="I4" s="891" t="inlineStr">
+      <c r="I4" s="910" t="inlineStr">
         <is>
           <t>DATA FINAL</t>
         </is>
       </c>
-      <c r="J4" s="891" t="inlineStr">
+      <c r="J4" s="910" t="inlineStr">
         <is>
           <t>DIES</t>
         </is>
       </c>
-      <c r="K4" s="891" t="inlineStr">
+      <c r="K4" s="910" t="inlineStr">
         <is>
           <t>HORES PREVISTES</t>
         </is>
       </c>
-      <c r="L4" s="891" t="inlineStr">
+      <c r="L4" s="910" t="inlineStr">
         <is>
           <t>HORES PROGRAMADES</t>
         </is>
       </c>
-      <c r="M4" s="891" t="inlineStr">
+      <c r="M4" s="910" t="inlineStr">
         <is>
           <t>DISTRIBUCIÓ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="892" t="inlineStr">
+      <c r="A5" s="911" t="inlineStr">
+        <is>
+          <t>FCOS02</t>
+        </is>
+      </c>
+      <c r="B5" s="912" t="inlineStr">
+        <is>
+          <t>BASIC PREVENCIO DE RISCOS LABORALS [FORMA I CONTRACTE - ATURATS]</t>
+        </is>
+      </c>
+      <c r="C5" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D5" s="913" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E5" s="913" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F5" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G5" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00</t>
+        </is>
+      </c>
+      <c r="H5" s="914" t="n">
+        <v>46314</v>
+      </c>
+      <c r="I5" s="914" t="n">
+        <v>46318</v>
+      </c>
+      <c r="J5" s="913" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="913" t="n">
+        <v>30</v>
+      </c>
+      <c r="L5" s="913" t="n">
+        <v>30</v>
+      </c>
+      <c r="M5" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="915" t="inlineStr">
         <is>
           <t>FC01_CTRP0005_202370</t>
         </is>
       </c>
-      <c r="B5" s="893" t="inlineStr">
+      <c r="B6" s="912" t="inlineStr">
         <is>
           <t>Coaching de fortaleses</t>
         </is>
       </c>
-      <c r="C5" s="894" t="inlineStr">
+      <c r="C6" s="913" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D5" s="894" t="inlineStr">
+      <c r="D6" s="913" t="inlineStr">
         <is>
           <t>RAMON</t>
         </is>
       </c>
-      <c r="E5" s="894" t="inlineStr">
+      <c r="E6" s="913" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F6" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G6" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H6" s="914" t="n">
+        <v>46314</v>
+      </c>
+      <c r="I6" s="914" t="n">
+        <v>46322</v>
+      </c>
+      <c r="J6" s="913" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="L6" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="916" t="inlineStr">
+        <is>
+          <t>FC01_CTRL0040_202470</t>
+        </is>
+      </c>
+      <c r="B7" s="912" t="inlineStr">
+        <is>
+          <t>CTRL0040_2024_Català A1 (Català nivell inicial A1)</t>
+        </is>
+      </c>
+      <c r="C7" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D7" s="913" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E7" s="913" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F7" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G7" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00</t>
+        </is>
+      </c>
+      <c r="H7" s="914" t="n">
+        <v>46314</v>
+      </c>
+      <c r="I7" s="914" t="n">
+        <v>46332</v>
+      </c>
+      <c r="J7" s="913" t="n">
+        <v>15</v>
+      </c>
+      <c r="K7" s="913" t="n">
+        <v>90</v>
+      </c>
+      <c r="L7" s="913" t="n">
+        <v>90</v>
+      </c>
+      <c r="M7" s="912" t="inlineStr">
+        <is>
+          <t>15 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="917" t="inlineStr">
+        <is>
+          <t>FCOS02</t>
+        </is>
+      </c>
+      <c r="B8" s="912" t="inlineStr">
+        <is>
+          <t>BASIC PREVENCIO DE RISCOS LABORALS [CFCC - TREBALLADORS]</t>
+        </is>
+      </c>
+      <c r="C8" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D8" s="913" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E8" s="913" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F8" s="913" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G8" s="912" t="inlineStr">
+        <is>
+          <t>15:00-21:00</t>
+        </is>
+      </c>
+      <c r="H8" s="914" t="n">
+        <v>46314</v>
+      </c>
+      <c r="I8" s="914" t="n">
+        <v>46318</v>
+      </c>
+      <c r="J8" s="913" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="913" t="n">
+        <v>30</v>
+      </c>
+      <c r="L8" s="913" t="n">
+        <v>30</v>
+      </c>
+      <c r="M8" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="918" t="inlineStr">
+        <is>
+          <t>FC01_IMPE0006_202449</t>
+        </is>
+      </c>
+      <c r="B9" s="912" t="inlineStr">
+        <is>
+          <t>Biomagnetisme aplicat a l'estètica</t>
+        </is>
+      </c>
+      <c r="C9" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D9" s="913" t="inlineStr">
+        <is>
+          <t>ESTHER</t>
+        </is>
+      </c>
+      <c r="E9" s="913" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F9" s="913" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G9" s="912" t="inlineStr">
+        <is>
+          <t>15:00-21:00 (15:00-20:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H9" s="914" t="n">
+        <v>46314</v>
+      </c>
+      <c r="I9" s="914" t="n">
+        <v>46316</v>
+      </c>
+      <c r="J9" s="913" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="913" t="n">
+        <v>16</v>
+      </c>
+      <c r="L9" s="913" t="n">
+        <v>16</v>
+      </c>
+      <c r="M9" s="912" t="inlineStr">
+        <is>
+          <t>1 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="919" t="inlineStr">
+        <is>
+          <t>CTRH0011</t>
+        </is>
+      </c>
+      <c r="B10" s="912" t="inlineStr">
+        <is>
+          <t>DRETS I DEURES LABORALS [FORMA I CONTRACTE - ATURATS]</t>
+        </is>
+      </c>
+      <c r="C10" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D10" s="913" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E10" s="913" t="inlineStr">
         <is>
           <t>GOOGLE</t>
         </is>
       </c>
-      <c r="F5" s="894" t="inlineStr">
+      <c r="F10" s="913" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G5" s="893" t="inlineStr">
+      <c r="G10" s="912" t="inlineStr">
+        <is>
+          <t>9:00-14:00</t>
+        </is>
+      </c>
+      <c r="H10" s="914" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I10" s="914" t="n">
+        <v>46322</v>
+      </c>
+      <c r="J10" s="913" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="913" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="913" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" s="912" t="inlineStr">
+        <is>
+          <t>2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="920" t="inlineStr">
+        <is>
+          <t>ADGG0208</t>
+        </is>
+      </c>
+      <c r="B11" s="912" t="inlineStr">
+        <is>
+          <t>ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS]</t>
+        </is>
+      </c>
+      <c r="C11" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D11" s="913" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E11" s="913" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F11" s="913" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G11" s="912" t="inlineStr">
+        <is>
+          <t>15:00-21:00</t>
+        </is>
+      </c>
+      <c r="H11" s="914" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I11" s="914" t="n">
+        <v>46493</v>
+      </c>
+      <c r="J11" s="913" t="n">
+        <v>113</v>
+      </c>
+      <c r="K11" s="913" t="n">
+        <v>678</v>
+      </c>
+      <c r="L11" s="913" t="n">
+        <v>678</v>
+      </c>
+      <c r="M11" s="912" t="inlineStr">
+        <is>
+          <t>113 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="921" t="inlineStr">
+        <is>
+          <t>CTRHI0015</t>
+        </is>
+      </c>
+      <c r="B12" s="912" t="inlineStr">
+        <is>
+          <t>IGUALTAT DE GÈNERE EN L'AMBIT LABORAL [FORMA I CONTRACTE - ATURATS]</t>
+        </is>
+      </c>
+      <c r="C12" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D12" s="913" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E12" s="913" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F12" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G12" s="912" t="inlineStr">
+        <is>
+          <t>9:00-14:00</t>
+        </is>
+      </c>
+      <c r="H12" s="914" t="n">
+        <v>46323</v>
+      </c>
+      <c r="I12" s="914" t="n">
+        <v>46324</v>
+      </c>
+      <c r="J12" s="913" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="913" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" s="913" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" s="912" t="inlineStr">
+        <is>
+          <t>2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="922" t="inlineStr">
+        <is>
+          <t>ADGG0208</t>
+        </is>
+      </c>
+      <c r="B13" s="912" t="inlineStr">
+        <is>
+          <t>ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS]</t>
+        </is>
+      </c>
+      <c r="C13" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D13" s="913" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E13" s="913" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F13" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G13" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00</t>
+        </is>
+      </c>
+      <c r="H13" s="914" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I13" s="914" t="n">
+        <v>46499</v>
+      </c>
+      <c r="J13" s="913" t="n">
+        <v>113</v>
+      </c>
+      <c r="K13" s="913" t="n">
+        <v>678</v>
+      </c>
+      <c r="L13" s="913" t="n">
+        <v>678</v>
+      </c>
+      <c r="M13" s="912" t="inlineStr">
+        <is>
+          <t>113 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="923" t="inlineStr">
+        <is>
+          <t>FC01_FCOI18_202271</t>
+        </is>
+      </c>
+      <c r="B14" s="912" t="inlineStr">
+        <is>
+          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell bàsic)</t>
+        </is>
+      </c>
+      <c r="C14" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D14" s="913" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E14" s="913" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F14" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G14" s="912" t="inlineStr">
         <is>
           <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
         </is>
       </c>
-      <c r="H5" s="895" t="n">
-        <v>46314</v>
-      </c>
-      <c r="I5" s="895" t="n">
-        <v>46322</v>
-      </c>
-      <c r="J5" s="894" t="n">
+      <c r="H14" s="914" t="n">
+        <v>46328</v>
+      </c>
+      <c r="I14" s="914" t="n">
+        <v>46336</v>
+      </c>
+      <c r="J14" s="913" t="n">
         <v>7</v>
       </c>
-      <c r="K5" s="894" t="n">
+      <c r="K14" s="913" t="n">
         <v>40</v>
       </c>
-      <c r="L5" s="894" t="n">
+      <c r="L14" s="913" t="n">
         <v>40</v>
       </c>
-      <c r="M5" s="893" t="inlineStr">
+      <c r="M14" s="912" t="inlineStr">
         <is>
           <t>5 dies × 6 h + 2 dies × 5 h</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="896" t="inlineStr">
-        <is>
-          <t>FC01_IMPE0006_202449</t>
-        </is>
-      </c>
-      <c r="B6" s="893" t="inlineStr">
-        <is>
-          <t>Biomagnetisme aplicat a l'estètica</t>
-        </is>
-      </c>
-      <c r="C6" s="894" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="924" t="inlineStr">
+        <is>
+          <t>FC01_COMM0009_202370</t>
+        </is>
+      </c>
+      <c r="B15" s="912" t="inlineStr">
+        <is>
+          <t>Atenció al client</t>
+        </is>
+      </c>
+      <c r="C15" s="913" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D6" s="894" t="inlineStr">
+      <c r="D15" s="913" t="inlineStr">
+        <is>
+          <t>TANIA/?</t>
+        </is>
+      </c>
+      <c r="E15" s="913" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F15" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G15" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00</t>
+        </is>
+      </c>
+      <c r="H15" s="914" t="n">
+        <v>46335</v>
+      </c>
+      <c r="I15" s="914" t="n">
+        <v>46339</v>
+      </c>
+      <c r="J15" s="913" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="913" t="n">
+        <v>30</v>
+      </c>
+      <c r="L15" s="913" t="n">
+        <v>30</v>
+      </c>
+      <c r="M15" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="925" t="inlineStr">
+        <is>
+          <t>FC01_SANP0011_202349</t>
+        </is>
+      </c>
+      <c r="B16" s="912" t="inlineStr">
+        <is>
+          <t>Tècniques de massatge</t>
+        </is>
+      </c>
+      <c r="C16" s="913" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="D16" s="913" t="inlineStr">
         <is>
           <t>ESTHER</t>
         </is>
       </c>
-      <c r="E6" s="894" t="inlineStr">
+      <c r="E16" s="913" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F16" s="913" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G16" s="912" t="inlineStr">
+        <is>
+          <t>15:00-20:00</t>
+        </is>
+      </c>
+      <c r="H16" s="914" t="n">
+        <v>46342</v>
+      </c>
+      <c r="I16" s="914" t="n">
+        <v>46345</v>
+      </c>
+      <c r="J16" s="913" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" s="913" t="n">
+        <v>20</v>
+      </c>
+      <c r="L16" s="913" t="n">
+        <v>20</v>
+      </c>
+      <c r="M16" s="912" t="inlineStr">
+        <is>
+          <t>4 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="926" t="inlineStr">
+        <is>
+          <t>FC01_FCOI15_202271</t>
+        </is>
+      </c>
+      <c r="B17" s="912" t="inlineStr">
+        <is>
+          <t>Creació de continguts digitals (ACTIC Nivell bàsic)</t>
+        </is>
+      </c>
+      <c r="C17" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D17" s="913" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E17" s="913" t="inlineStr">
         <is>
           <t>FIREFOX</t>
         </is>
       </c>
-      <c r="F6" s="894" t="inlineStr">
+      <c r="F17" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G17" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H17" s="914" t="n">
+        <v>46349</v>
+      </c>
+      <c r="I17" s="914" t="n">
+        <v>46357</v>
+      </c>
+      <c r="J17" s="913" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="L17" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="M17" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="927" t="inlineStr">
+        <is>
+          <t>FC01_IFCT117_202470</t>
+        </is>
+      </c>
+      <c r="B18" s="912" t="inlineStr">
+        <is>
+          <t>Introducció a la intel·ligència artificial</t>
+        </is>
+      </c>
+      <c r="C18" s="913" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="D18" s="913" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E18" s="913" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F18" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G18" s="912" t="inlineStr">
+        <is>
+          <t>9:00-14:00</t>
+        </is>
+      </c>
+      <c r="H18" s="914" t="n">
+        <v>46398</v>
+      </c>
+      <c r="I18" s="914" t="n">
+        <v>46402</v>
+      </c>
+      <c r="J18" s="913" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="913" t="n">
+        <v>25</v>
+      </c>
+      <c r="L18" s="913" t="n">
+        <v>25</v>
+      </c>
+      <c r="M18" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="928" t="inlineStr">
+        <is>
+          <t>FC01_IFCD64_202164</t>
+        </is>
+      </c>
+      <c r="B19" s="912" t="inlineStr">
+        <is>
+          <t>Gestió de Projectes d'implementació del CRM</t>
+        </is>
+      </c>
+      <c r="C19" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D19" s="913" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E19" s="913" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F19" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G19" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H19" s="914" t="n">
+        <v>46398</v>
+      </c>
+      <c r="I19" s="914" t="n">
+        <v>46430</v>
+      </c>
+      <c r="J19" s="913" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" s="913" t="n">
+        <v>145</v>
+      </c>
+      <c r="L19" s="913" t="n">
+        <v>145</v>
+      </c>
+      <c r="M19" s="912" t="inlineStr">
+        <is>
+          <t>20 dies × 6 h + 5 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="929" t="inlineStr">
+        <is>
+          <t>FC01_CTRP0006_202370</t>
+        </is>
+      </c>
+      <c r="B20" s="912" t="inlineStr">
+        <is>
+          <t>Mindfulness</t>
+        </is>
+      </c>
+      <c r="C20" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D20" s="913" t="inlineStr">
+        <is>
+          <t>RAMON</t>
+        </is>
+      </c>
+      <c r="E20" s="913" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F20" s="913" t="inlineStr">
         <is>
           <t>TARDA</t>
         </is>
       </c>
-      <c r="G6" s="893" t="inlineStr">
+      <c r="G20" s="912" t="inlineStr">
+        <is>
+          <t>15:00-21:00</t>
+        </is>
+      </c>
+      <c r="H20" s="914" t="n">
+        <v>46398</v>
+      </c>
+      <c r="I20" s="914" t="n">
+        <v>46402</v>
+      </c>
+      <c r="J20" s="913" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" s="913" t="n">
+        <v>30</v>
+      </c>
+      <c r="L20" s="913" t="n">
+        <v>30</v>
+      </c>
+      <c r="M20" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="930" t="inlineStr">
+        <is>
+          <t>FC01_SEAD0227_202370</t>
+        </is>
+      </c>
+      <c r="B21" s="912" t="inlineStr">
+        <is>
+          <t>Tècniques de relaxació</t>
+        </is>
+      </c>
+      <c r="C21" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D21" s="913" t="inlineStr">
+        <is>
+          <t>ESTHER</t>
+        </is>
+      </c>
+      <c r="E21" s="913" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F21" s="913" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G21" s="912" t="inlineStr">
+        <is>
+          <t>15:00-20:00</t>
+        </is>
+      </c>
+      <c r="H21" s="914" t="n">
+        <v>46405</v>
+      </c>
+      <c r="I21" s="914" t="n">
+        <v>46408</v>
+      </c>
+      <c r="J21" s="913" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="913" t="n">
+        <v>20</v>
+      </c>
+      <c r="L21" s="913" t="n">
+        <v>20</v>
+      </c>
+      <c r="M21" s="912" t="inlineStr">
+        <is>
+          <t>4 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="931" t="inlineStr">
+        <is>
+          <t>FC01_CTRL0041_202470</t>
+        </is>
+      </c>
+      <c r="B22" s="912" t="inlineStr">
+        <is>
+          <t>CTRL0041_2024_Català A2.1 (Català bàsic 1 )</t>
+        </is>
+      </c>
+      <c r="C22" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D22" s="913" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E22" s="913" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F22" s="913" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G22" s="912" t="inlineStr">
         <is>
           <t>15:00-21:00 (15:00-20:00 els dies de 5 h)</t>
         </is>
       </c>
-      <c r="H6" s="895" t="n">
-        <v>46314</v>
-      </c>
-      <c r="I6" s="895" t="n">
-        <v>46316</v>
-      </c>
-      <c r="J6" s="894" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" s="894" t="n">
-        <v>16</v>
-      </c>
-      <c r="L6" s="894" t="n">
-        <v>16</v>
-      </c>
-      <c r="M6" s="893" t="inlineStr">
-        <is>
-          <t>1 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="897" t="inlineStr">
-        <is>
-          <t>FC01_CTRL0040_202470</t>
-        </is>
-      </c>
-      <c r="B7" s="893" t="inlineStr">
-        <is>
-          <t>CTRL0040_2024_Català A1 (Català nivell inicial A1)</t>
-        </is>
-      </c>
-      <c r="C7" s="894" t="inlineStr">
+      <c r="H22" s="914" t="n">
+        <v>46405</v>
+      </c>
+      <c r="I22" s="914" t="n">
+        <v>46414</v>
+      </c>
+      <c r="J22" s="913" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" s="913" t="n">
+        <v>45</v>
+      </c>
+      <c r="L22" s="913" t="n">
+        <v>45</v>
+      </c>
+      <c r="M22" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 3 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="932" t="inlineStr">
+        <is>
+          <t>FC01_FCOI19_202271</t>
+        </is>
+      </c>
+      <c r="B23" s="912" t="inlineStr">
+        <is>
+          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi)</t>
+        </is>
+      </c>
+      <c r="C23" s="913" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="D23" s="913" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E23" s="913" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F23" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G23" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H23" s="914" t="n">
+        <v>46419</v>
+      </c>
+      <c r="I23" s="914" t="n">
+        <v>46427</v>
+      </c>
+      <c r="J23" s="913" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="L23" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="M23" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="933" t="inlineStr">
+        <is>
+          <t>B_IMPE0110_MF0063</t>
+        </is>
+      </c>
+      <c r="B24" s="912" t="inlineStr">
+        <is>
+          <t>MASSATGES ESTÈTIC MANUAL I MECÀNIC</t>
+        </is>
+      </c>
+      <c r="C24" s="913" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D7" s="894" t="inlineStr">
-        <is>
-          <t>PER ASSIGNAR</t>
-        </is>
-      </c>
-      <c r="E7" s="894" t="inlineStr">
+      <c r="D24" s="913" t="inlineStr">
+        <is>
+          <t>LEIRE</t>
+        </is>
+      </c>
+      <c r="E24" s="913" t="inlineStr">
         <is>
           <t>COPILOT</t>
         </is>
       </c>
-      <c r="F7" s="894" t="inlineStr">
+      <c r="F24" s="913" t="inlineStr">
         <is>
           <t>TARDA</t>
         </is>
       </c>
-      <c r="G7" s="893" t="inlineStr">
-        <is>
-          <t>15:00-21:00</t>
-        </is>
-      </c>
-      <c r="H7" s="895" t="n">
-        <v>46314</v>
-      </c>
-      <c r="I7" s="895" t="n">
-        <v>46332</v>
-      </c>
-      <c r="J7" s="894" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" s="894" t="n">
-        <v>90</v>
-      </c>
-      <c r="L7" s="894" t="n">
-        <v>90</v>
-      </c>
-      <c r="M7" s="893" t="inlineStr">
-        <is>
-          <t>15 dies × 6 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="898" t="inlineStr">
-        <is>
-          <t>FC01_FCOI18_202271</t>
-        </is>
-      </c>
-      <c r="B8" s="893" t="inlineStr">
-        <is>
-          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell bàsic)</t>
-        </is>
-      </c>
-      <c r="C8" s="894" t="inlineStr">
+      <c r="G24" s="912" t="inlineStr">
+        <is>
+          <t>15:00-21:00 (15:00-20:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H24" s="914" t="n">
+        <v>46419</v>
+      </c>
+      <c r="I24" s="914" t="n">
+        <v>46454</v>
+      </c>
+      <c r="J24" s="913" t="n">
+        <v>26</v>
+      </c>
+      <c r="K24" s="913" t="n">
+        <v>152</v>
+      </c>
+      <c r="L24" s="913" t="n">
+        <v>152</v>
+      </c>
+      <c r="M24" s="912" t="inlineStr">
+        <is>
+          <t>22 dies × 6 h + 4 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="934" t="inlineStr">
+        <is>
+          <t>FC01_CTRP0037_202670</t>
+        </is>
+      </c>
+      <c r="B25" s="912" t="inlineStr">
+        <is>
+          <t>Coaching de fortaleses. Nivell II</t>
+        </is>
+      </c>
+      <c r="C25" s="913" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D8" s="894" t="inlineStr">
+      <c r="D25" s="913" t="inlineStr">
+        <is>
+          <t>RAMON</t>
+        </is>
+      </c>
+      <c r="E25" s="913" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F25" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G25" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H25" s="914" t="n">
+        <v>46433</v>
+      </c>
+      <c r="I25" s="914" t="n">
+        <v>46441</v>
+      </c>
+      <c r="J25" s="913" t="n">
+        <v>7</v>
+      </c>
+      <c r="K25" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="L25" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="M25" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="935" t="inlineStr">
+        <is>
+          <t>FC01_FCOI16_202271</t>
+        </is>
+      </c>
+      <c r="B26" s="912" t="inlineStr">
+        <is>
+          <t>Creació de continguts digitals i programació (ACTIC Nivell intermedi)</t>
+        </is>
+      </c>
+      <c r="C26" s="913" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="D26" s="913" t="inlineStr">
         <is>
           <t>MARIA</t>
         </is>
       </c>
-      <c r="E8" s="894" t="inlineStr">
+      <c r="E26" s="913" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F26" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G26" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H26" s="914" t="n">
+        <v>46440</v>
+      </c>
+      <c r="I26" s="914" t="n">
+        <v>46448</v>
+      </c>
+      <c r="J26" s="913" t="n">
+        <v>7</v>
+      </c>
+      <c r="K26" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="L26" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="M26" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="925" t="inlineStr">
+        <is>
+          <t>FC01_SANP0011_202349</t>
+        </is>
+      </c>
+      <c r="B27" s="912" t="inlineStr">
+        <is>
+          <t>Tècniques de massatge</t>
+        </is>
+      </c>
+      <c r="C27" s="913" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D27" s="913" t="inlineStr">
+        <is>
+          <t>ESTHER</t>
+        </is>
+      </c>
+      <c r="E27" s="913" t="inlineStr">
         <is>
           <t>GOOGLE</t>
         </is>
       </c>
-      <c r="F8" s="894" t="inlineStr">
+      <c r="F27" s="913" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G27" s="912" t="inlineStr">
+        <is>
+          <t>15:00-20:00</t>
+        </is>
+      </c>
+      <c r="H27" s="914" t="n">
+        <v>46447</v>
+      </c>
+      <c r="I27" s="914" t="n">
+        <v>46450</v>
+      </c>
+      <c r="J27" s="913" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" s="913" t="n">
+        <v>20</v>
+      </c>
+      <c r="L27" s="913" t="n">
+        <v>20</v>
+      </c>
+      <c r="M27" s="912" t="inlineStr">
+        <is>
+          <t>4 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="936" t="inlineStr">
+        <is>
+          <t>B_IMPE0110_MF0790</t>
+        </is>
+      </c>
+      <c r="B28" s="912" t="inlineStr">
+        <is>
+          <t>DRENATGE LIMFÀTIC ESTÈTIC MANUAL I MECÀNIC</t>
+        </is>
+      </c>
+      <c r="C28" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D28" s="913" t="inlineStr">
+        <is>
+          <t>LEIRE</t>
+        </is>
+      </c>
+      <c r="E28" s="913" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F28" s="913" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G8" s="893" t="inlineStr">
+      <c r="G28" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00</t>
+        </is>
+      </c>
+      <c r="H28" s="914" t="n">
+        <v>46455</v>
+      </c>
+      <c r="I28" s="914" t="n">
+        <v>46483</v>
+      </c>
+      <c r="J28" s="913" t="n">
+        <v>19</v>
+      </c>
+      <c r="K28" s="913" t="n">
+        <v>114</v>
+      </c>
+      <c r="L28" s="913" t="n">
+        <v>114</v>
+      </c>
+      <c r="M28" s="912" t="inlineStr">
+        <is>
+          <t>19 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="932" t="inlineStr">
+        <is>
+          <t>FC01_FCOI19_202271</t>
+        </is>
+      </c>
+      <c r="B29" s="912" t="inlineStr">
+        <is>
+          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi)</t>
+        </is>
+      </c>
+      <c r="C29" s="913" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D29" s="913" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E29" s="913" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F29" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G29" s="912" t="inlineStr">
         <is>
           <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
         </is>
       </c>
-      <c r="H8" s="895" t="n">
-        <v>46328</v>
-      </c>
-      <c r="I8" s="895" t="n">
-        <v>46336</v>
-      </c>
-      <c r="J8" s="894" t="n">
+      <c r="H29" s="914" t="n">
+        <v>46461</v>
+      </c>
+      <c r="I29" s="914" t="n">
+        <v>46469</v>
+      </c>
+      <c r="J29" s="913" t="n">
         <v>7</v>
       </c>
-      <c r="K8" s="894" t="n">
+      <c r="K29" s="913" t="n">
         <v>40</v>
       </c>
-      <c r="L8" s="894" t="n">
+      <c r="L29" s="913" t="n">
         <v>40</v>
       </c>
-      <c r="M8" s="893" t="inlineStr">
+      <c r="M29" s="912" t="inlineStr">
         <is>
           <t>5 dies × 6 h + 2 dies × 5 h</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="899" t="inlineStr">
-        <is>
-          <t>FC01_COMM0009_202370</t>
-        </is>
-      </c>
-      <c r="B9" s="893" t="inlineStr">
-        <is>
-          <t>Atenció al client</t>
-        </is>
-      </c>
-      <c r="C9" s="894" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="917" t="inlineStr">
+        <is>
+          <t>B_IMPE110_MF0791</t>
+        </is>
+      </c>
+      <c r="B30" s="912" t="inlineStr">
+        <is>
+          <t>MASSATGES ESTÈTICS AMB TÈCNIQUES PER PRESSIÓ</t>
+        </is>
+      </c>
+      <c r="C30" s="913" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D9" s="894" t="inlineStr">
-        <is>
-          <t>TANIA/?</t>
-        </is>
-      </c>
-      <c r="E9" s="894" t="inlineStr">
+      <c r="D30" s="913" t="inlineStr">
+        <is>
+          <t>LEIRE</t>
+        </is>
+      </c>
+      <c r="E30" s="913" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F30" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G30" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00</t>
+        </is>
+      </c>
+      <c r="H30" s="914" t="n">
+        <v>46484</v>
+      </c>
+      <c r="I30" s="914" t="n">
+        <v>46510</v>
+      </c>
+      <c r="J30" s="913" t="n">
+        <v>19</v>
+      </c>
+      <c r="K30" s="913" t="n">
+        <v>114</v>
+      </c>
+      <c r="L30" s="913" t="n">
+        <v>114</v>
+      </c>
+      <c r="M30" s="912" t="inlineStr">
+        <is>
+          <t>19 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="935" t="inlineStr">
+        <is>
+          <t>FC01_FCOI16_202271</t>
+        </is>
+      </c>
+      <c r="B31" s="912" t="inlineStr">
+        <is>
+          <t>Creació de continguts digitals i programació (ACTIC Nivell intermedi)</t>
+        </is>
+      </c>
+      <c r="C31" s="913" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D31" s="913" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E31" s="913" t="inlineStr">
         <is>
           <t>FIREFOX</t>
         </is>
       </c>
-      <c r="F9" s="894" t="inlineStr">
+      <c r="F31" s="913" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G9" s="893" t="inlineStr">
-        <is>
-          <t>9:00-15:00</t>
-        </is>
-      </c>
-      <c r="H9" s="895" t="n">
-        <v>46335</v>
-      </c>
-      <c r="I9" s="895" t="n">
-        <v>46339</v>
-      </c>
-      <c r="J9" s="894" t="n">
+      <c r="G31" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H31" s="914" t="n">
+        <v>46489</v>
+      </c>
+      <c r="I31" s="914" t="n">
+        <v>46497</v>
+      </c>
+      <c r="J31" s="913" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="L31" s="913" t="n">
+        <v>40</v>
+      </c>
+      <c r="M31" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="927" t="inlineStr">
+        <is>
+          <t>FC01_IFCT117_202470</t>
+        </is>
+      </c>
+      <c r="B32" s="912" t="inlineStr">
+        <is>
+          <t>Introducció a la intel·ligència artificial</t>
+        </is>
+      </c>
+      <c r="C32" s="913" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D32" s="913" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E32" s="913" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F32" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G32" s="912" t="inlineStr">
+        <is>
+          <t>9:00-14:00</t>
+        </is>
+      </c>
+      <c r="H32" s="914" t="n">
+        <v>46510</v>
+      </c>
+      <c r="I32" s="914" t="n">
+        <v>46514</v>
+      </c>
+      <c r="J32" s="913" t="n">
         <v>5</v>
       </c>
-      <c r="K9" s="894" t="n">
-        <v>30</v>
-      </c>
-      <c r="L9" s="894" t="n">
-        <v>30</v>
-      </c>
-      <c r="M9" s="893" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="900" t="inlineStr">
-        <is>
-          <t>FC01_SANP0011_202349</t>
-        </is>
-      </c>
-      <c r="B10" s="893" t="inlineStr">
-        <is>
-          <t>Tècniques de massatge</t>
-        </is>
-      </c>
-      <c r="C10" s="894" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="D10" s="894" t="inlineStr">
-        <is>
-          <t>ESTHER</t>
-        </is>
-      </c>
-      <c r="E10" s="894" t="inlineStr">
+      <c r="K32" s="913" t="n">
+        <v>25</v>
+      </c>
+      <c r="L32" s="913" t="n">
+        <v>25</v>
+      </c>
+      <c r="M32" s="912" t="inlineStr">
+        <is>
+          <t>5 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="920" t="inlineStr">
+        <is>
+          <t>B_IMPE0110_MF0792</t>
+        </is>
+      </c>
+      <c r="B33" s="912" t="inlineStr">
+        <is>
+          <t>TÈCNIQUES SENSORIALS ESTÈTIQUES</t>
+        </is>
+      </c>
+      <c r="C33" s="913" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D33" s="913" t="inlineStr">
+        <is>
+          <t>LEIRE</t>
+        </is>
+      </c>
+      <c r="E33" s="913" t="inlineStr">
         <is>
           <t>FIREFOX</t>
         </is>
       </c>
-      <c r="F10" s="894" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G10" s="893" t="inlineStr">
-        <is>
-          <t>15:00-20:00</t>
-        </is>
-      </c>
-      <c r="H10" s="895" t="n">
-        <v>46342</v>
-      </c>
-      <c r="I10" s="895" t="n">
-        <v>46345</v>
-      </c>
-      <c r="J10" s="894" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" s="894" t="n">
-        <v>20</v>
-      </c>
-      <c r="L10" s="894" t="n">
-        <v>20</v>
-      </c>
-      <c r="M10" s="893" t="inlineStr">
-        <is>
-          <t>4 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="901" t="inlineStr">
-        <is>
-          <t>FC01_FCOI15_202271</t>
-        </is>
-      </c>
-      <c r="B11" s="893" t="inlineStr">
-        <is>
-          <t>Creació de continguts digitals (ACTIC Nivell bàsic)</t>
-        </is>
-      </c>
-      <c r="C11" s="894" t="inlineStr">
+      <c r="F33" s="913" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G33" s="912" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H33" s="914" t="n">
+        <v>46511</v>
+      </c>
+      <c r="I33" s="914" t="n">
+        <v>46527</v>
+      </c>
+      <c r="J33" s="913" t="n">
+        <v>13</v>
+      </c>
+      <c r="K33" s="913" t="n">
+        <v>76</v>
+      </c>
+      <c r="L33" s="913" t="n">
+        <v>76</v>
+      </c>
+      <c r="M33" s="912" t="inlineStr">
+        <is>
+          <t>11 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="937" t="inlineStr">
+        <is>
+          <t>FC01_FCOI20_202271</t>
+        </is>
+      </c>
+      <c r="B34" s="912" t="inlineStr">
+        <is>
+          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell avançat)</t>
+        </is>
+      </c>
+      <c r="C34" s="913" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D11" s="894" t="inlineStr">
+      <c r="D34" s="913" t="inlineStr">
         <is>
           <t>MARIA</t>
         </is>
       </c>
-      <c r="E11" s="894" t="inlineStr">
+      <c r="E34" s="913" t="inlineStr">
         <is>
           <t>GOOGLE</t>
         </is>
       </c>
-      <c r="F11" s="894" t="inlineStr">
+      <c r="F34" s="913" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G11" s="893" t="inlineStr">
+      <c r="G34" s="912" t="inlineStr">
         <is>
           <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
         </is>
       </c>
-      <c r="H11" s="895" t="n">
-        <v>46349</v>
-      </c>
-      <c r="I11" s="895" t="n">
-        <v>46357</v>
-      </c>
-      <c r="J11" s="894" t="n">
+      <c r="H34" s="914" t="n">
+        <v>46531</v>
+      </c>
+      <c r="I34" s="914" t="n">
+        <v>46539</v>
+      </c>
+      <c r="J34" s="913" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="894" t="n">
+      <c r="K34" s="913" t="n">
         <v>40</v>
       </c>
-      <c r="L11" s="894" t="n">
+      <c r="L34" s="913" t="n">
         <v>40</v>
       </c>
-      <c r="M11" s="893" t="inlineStr">
+      <c r="M34" s="912" t="inlineStr">
         <is>
           <t>5 dies × 6 h + 2 dies × 5 h</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="902" t="inlineStr">
-        <is>
-          <t>FC01_IFCT117_202470</t>
-        </is>
-      </c>
-      <c r="B12" s="893" t="inlineStr">
-        <is>
-          <t>Introducció a la intel·ligència artificial</t>
-        </is>
-      </c>
-      <c r="C12" s="894" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="D12" s="894" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E12" s="894" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F12" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G12" s="893" t="inlineStr">
-        <is>
-          <t>9:00-14:00</t>
-        </is>
-      </c>
-      <c r="H12" s="895" t="n">
-        <v>46398</v>
-      </c>
-      <c r="I12" s="895" t="n">
-        <v>46402</v>
-      </c>
-      <c r="J12" s="894" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" s="894" t="n">
-        <v>25</v>
-      </c>
-      <c r="L12" s="894" t="n">
-        <v>25</v>
-      </c>
-      <c r="M12" s="893" t="inlineStr">
-        <is>
-          <t>5 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="903" t="inlineStr">
-        <is>
-          <t>FC01_CTRP0006_202370</t>
-        </is>
-      </c>
-      <c r="B13" s="893" t="inlineStr">
-        <is>
-          <t>Mindfulness</t>
-        </is>
-      </c>
-      <c r="C13" s="894" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D13" s="894" t="inlineStr">
-        <is>
-          <t>RAMON</t>
-        </is>
-      </c>
-      <c r="E13" s="894" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F13" s="894" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G13" s="893" t="inlineStr">
-        <is>
-          <t>15:00-21:00</t>
-        </is>
-      </c>
-      <c r="H13" s="895" t="n">
-        <v>46398</v>
-      </c>
-      <c r="I13" s="895" t="n">
-        <v>46402</v>
-      </c>
-      <c r="J13" s="894" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" s="894" t="n">
-        <v>30</v>
-      </c>
-      <c r="L13" s="894" t="n">
-        <v>30</v>
-      </c>
-      <c r="M13" s="893" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="904" t="inlineStr">
-        <is>
-          <t>FC01_IFCD64_202164</t>
-        </is>
-      </c>
-      <c r="B14" s="893" t="inlineStr">
-        <is>
-          <t>Gestió de Projectes d'implementació del CRM</t>
-        </is>
-      </c>
-      <c r="C14" s="894" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D14" s="894" t="inlineStr">
-        <is>
-          <t>PER ASSIGNAR</t>
-        </is>
-      </c>
-      <c r="E14" s="894" t="inlineStr">
-        <is>
-          <t>COPILOT</t>
-        </is>
-      </c>
-      <c r="F14" s="894" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G14" s="893" t="inlineStr">
-        <is>
-          <t>15:00-21:00 (15:00-20:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H14" s="895" t="n">
-        <v>46398</v>
-      </c>
-      <c r="I14" s="895" t="n">
-        <v>46430</v>
-      </c>
-      <c r="J14" s="894" t="n">
-        <v>25</v>
-      </c>
-      <c r="K14" s="894" t="n">
-        <v>145</v>
-      </c>
-      <c r="L14" s="894" t="n">
-        <v>145</v>
-      </c>
-      <c r="M14" s="893" t="inlineStr">
-        <is>
-          <t>20 dies × 6 h + 5 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="905" t="inlineStr">
-        <is>
-          <t>FC01_SEAD0227_202370</t>
-        </is>
-      </c>
-      <c r="B15" s="893" t="inlineStr">
-        <is>
-          <t>Tècniques de relaxació</t>
-        </is>
-      </c>
-      <c r="C15" s="894" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D15" s="894" t="inlineStr">
-        <is>
-          <t>ESTHER</t>
-        </is>
-      </c>
-      <c r="E15" s="894" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F15" s="894" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G15" s="893" t="inlineStr">
-        <is>
-          <t>15:00-20:00</t>
-        </is>
-      </c>
-      <c r="H15" s="895" t="n">
-        <v>46405</v>
-      </c>
-      <c r="I15" s="895" t="n">
-        <v>46408</v>
-      </c>
-      <c r="J15" s="894" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="894" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" s="894" t="n">
-        <v>20</v>
-      </c>
-      <c r="M15" s="893" t="inlineStr">
-        <is>
-          <t>4 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="906" t="inlineStr">
-        <is>
-          <t>FC01_CTRL0041_202470</t>
-        </is>
-      </c>
-      <c r="B16" s="893" t="inlineStr">
-        <is>
-          <t>CTRL0041_2024_Català A2.1 (Català bàsic 1 )</t>
-        </is>
-      </c>
-      <c r="C16" s="894" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D16" s="894" t="inlineStr">
-        <is>
-          <t>PER ASSIGNAR</t>
-        </is>
-      </c>
-      <c r="E16" s="894" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F16" s="894" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G16" s="893" t="inlineStr">
-        <is>
-          <t>15:00-21:00 (15:00-20:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H16" s="895" t="n">
-        <v>46405</v>
-      </c>
-      <c r="I16" s="895" t="n">
-        <v>46414</v>
-      </c>
-      <c r="J16" s="894" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" s="894" t="n">
-        <v>45</v>
-      </c>
-      <c r="L16" s="894" t="n">
-        <v>45</v>
-      </c>
-      <c r="M16" s="893" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 3 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="907" t="inlineStr">
-        <is>
-          <t>FC01_FCOI19_202271</t>
-        </is>
-      </c>
-      <c r="B17" s="893" t="inlineStr">
-        <is>
-          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi)</t>
-        </is>
-      </c>
-      <c r="C17" s="894" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="D17" s="894" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E17" s="894" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F17" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G17" s="893" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H17" s="895" t="n">
-        <v>46419</v>
-      </c>
-      <c r="I17" s="895" t="n">
-        <v>46427</v>
-      </c>
-      <c r="J17" s="894" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="L17" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="M17" s="893" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="908" t="inlineStr">
-        <is>
-          <t>B_IMPE0110_MF0063</t>
-        </is>
-      </c>
-      <c r="B18" s="893" t="inlineStr">
-        <is>
-          <t>MASSATGES ESTÈTIC MANUAL I MECÀNIC</t>
-        </is>
-      </c>
-      <c r="C18" s="894" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D18" s="894" t="inlineStr">
-        <is>
-          <t>LEIRE</t>
-        </is>
-      </c>
-      <c r="E18" s="894" t="inlineStr">
-        <is>
-          <t>COPILOT</t>
-        </is>
-      </c>
-      <c r="F18" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G18" s="893" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H18" s="895" t="n">
-        <v>46419</v>
-      </c>
-      <c r="I18" s="895" t="n">
-        <v>46454</v>
-      </c>
-      <c r="J18" s="894" t="n">
-        <v>26</v>
-      </c>
-      <c r="K18" s="894" t="n">
-        <v>152</v>
-      </c>
-      <c r="L18" s="894" t="n">
-        <v>152</v>
-      </c>
-      <c r="M18" s="893" t="inlineStr">
-        <is>
-          <t>22 dies × 6 h + 4 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="909" t="inlineStr">
-        <is>
-          <t>FC01_CTRP0037_202670</t>
-        </is>
-      </c>
-      <c r="B19" s="893" t="inlineStr">
-        <is>
-          <t>Coaching de fortaleses. Nivell II</t>
-        </is>
-      </c>
-      <c r="C19" s="894" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D19" s="894" t="inlineStr">
-        <is>
-          <t>RAMON</t>
-        </is>
-      </c>
-      <c r="E19" s="894" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F19" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G19" s="893" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H19" s="895" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I19" s="895" t="n">
-        <v>46441</v>
-      </c>
-      <c r="J19" s="894" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="L19" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="M19" s="893" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="910" t="inlineStr">
-        <is>
-          <t>FC01_FCOI16_202271</t>
-        </is>
-      </c>
-      <c r="B20" s="893" t="inlineStr">
-        <is>
-          <t>Creació de continguts digitals i programació (ACTIC Nivell intermedi)</t>
-        </is>
-      </c>
-      <c r="C20" s="894" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="D20" s="894" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E20" s="894" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F20" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G20" s="893" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H20" s="895" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I20" s="895" t="n">
-        <v>46448</v>
-      </c>
-      <c r="J20" s="894" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="L20" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="M20" s="893" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="900" t="inlineStr">
-        <is>
-          <t>FC01_SANP0011_202349</t>
-        </is>
-      </c>
-      <c r="B21" s="893" t="inlineStr">
-        <is>
-          <t>Tècniques de massatge</t>
-        </is>
-      </c>
-      <c r="C21" s="894" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="D21" s="894" t="inlineStr">
-        <is>
-          <t>ESTHER</t>
-        </is>
-      </c>
-      <c r="E21" s="894" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F21" s="894" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G21" s="893" t="inlineStr">
-        <is>
-          <t>15:00-20:00</t>
-        </is>
-      </c>
-      <c r="H21" s="895" t="n">
-        <v>46447</v>
-      </c>
-      <c r="I21" s="895" t="n">
-        <v>46450</v>
-      </c>
-      <c r="J21" s="894" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" s="894" t="n">
-        <v>20</v>
-      </c>
-      <c r="L21" s="894" t="n">
-        <v>20</v>
-      </c>
-      <c r="M21" s="893" t="inlineStr">
-        <is>
-          <t>4 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="911" t="inlineStr">
-        <is>
-          <t>B_IMPE0110_MF0790</t>
-        </is>
-      </c>
-      <c r="B22" s="893" t="inlineStr">
-        <is>
-          <t>DRENATGE LIMFÀTIC ESTÈTIC MANUAL I MECÀNIC</t>
-        </is>
-      </c>
-      <c r="C22" s="894" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D22" s="894" t="inlineStr">
-        <is>
-          <t>LEIRE</t>
-        </is>
-      </c>
-      <c r="E22" s="894" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F22" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G22" s="893" t="inlineStr">
-        <is>
-          <t>9:00-15:00</t>
-        </is>
-      </c>
-      <c r="H22" s="895" t="n">
-        <v>46455</v>
-      </c>
-      <c r="I22" s="895" t="n">
-        <v>46483</v>
-      </c>
-      <c r="J22" s="894" t="n">
-        <v>19</v>
-      </c>
-      <c r="K22" s="894" t="n">
-        <v>114</v>
-      </c>
-      <c r="L22" s="894" t="n">
-        <v>114</v>
-      </c>
-      <c r="M22" s="893" t="inlineStr">
-        <is>
-          <t>19 dies × 6 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="907" t="inlineStr">
-        <is>
-          <t>FC01_FCOI19_202271</t>
-        </is>
-      </c>
-      <c r="B23" s="893" t="inlineStr">
-        <is>
-          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi)</t>
-        </is>
-      </c>
-      <c r="C23" s="894" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="D23" s="894" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E23" s="894" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F23" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G23" s="893" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H23" s="895" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I23" s="895" t="n">
-        <v>46469</v>
-      </c>
-      <c r="J23" s="894" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="L23" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="M23" s="893" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="912" t="inlineStr">
-        <is>
-          <t>B_IMPE110_MF0791</t>
-        </is>
-      </c>
-      <c r="B24" s="893" t="inlineStr">
-        <is>
-          <t>MASSATGES ESTÈTICS AMB TÈCNIQUES PER PRESSIÓ</t>
-        </is>
-      </c>
-      <c r="C24" s="894" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D24" s="894" t="inlineStr">
-        <is>
-          <t>LEIRE</t>
-        </is>
-      </c>
-      <c r="E24" s="894" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F24" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G24" s="893" t="inlineStr">
-        <is>
-          <t>9:00-15:00</t>
-        </is>
-      </c>
-      <c r="H24" s="895" t="n">
-        <v>46484</v>
-      </c>
-      <c r="I24" s="895" t="n">
-        <v>46510</v>
-      </c>
-      <c r="J24" s="894" t="n">
-        <v>19</v>
-      </c>
-      <c r="K24" s="894" t="n">
-        <v>114</v>
-      </c>
-      <c r="L24" s="894" t="n">
-        <v>114</v>
-      </c>
-      <c r="M24" s="893" t="inlineStr">
-        <is>
-          <t>19 dies × 6 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="910" t="inlineStr">
-        <is>
-          <t>FC01_FCOI16_202271</t>
-        </is>
-      </c>
-      <c r="B25" s="893" t="inlineStr">
-        <is>
-          <t>Creació de continguts digitals i programació (ACTIC Nivell intermedi)</t>
-        </is>
-      </c>
-      <c r="C25" s="894" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="D25" s="894" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E25" s="894" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F25" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G25" s="893" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H25" s="895" t="n">
-        <v>46489</v>
-      </c>
-      <c r="I25" s="895" t="n">
-        <v>46497</v>
-      </c>
-      <c r="J25" s="894" t="n">
-        <v>7</v>
-      </c>
-      <c r="K25" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="L25" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="M25" s="893" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="902" t="inlineStr">
-        <is>
-          <t>FC01_IFCT117_202470</t>
-        </is>
-      </c>
-      <c r="B26" s="893" t="inlineStr">
-        <is>
-          <t>Introducció a la intel·ligència artificial</t>
-        </is>
-      </c>
-      <c r="C26" s="894" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="D26" s="894" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E26" s="894" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F26" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G26" s="893" t="inlineStr">
-        <is>
-          <t>9:00-14:00</t>
-        </is>
-      </c>
-      <c r="H26" s="895" t="n">
-        <v>46510</v>
-      </c>
-      <c r="I26" s="895" t="n">
-        <v>46514</v>
-      </c>
-      <c r="J26" s="894" t="n">
-        <v>5</v>
-      </c>
-      <c r="K26" s="894" t="n">
-        <v>25</v>
-      </c>
-      <c r="L26" s="894" t="n">
-        <v>25</v>
-      </c>
-      <c r="M26" s="893" t="inlineStr">
-        <is>
-          <t>5 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="913" t="inlineStr">
-        <is>
-          <t>B_IMPE0110_MF0792</t>
-        </is>
-      </c>
-      <c r="B27" s="893" t="inlineStr">
-        <is>
-          <t>TÈCNIQUES SENSORIALS ESTÈTIQUES</t>
-        </is>
-      </c>
-      <c r="C27" s="894" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D27" s="894" t="inlineStr">
-        <is>
-          <t>LEIRE</t>
-        </is>
-      </c>
-      <c r="E27" s="894" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F27" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G27" s="893" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H27" s="895" t="n">
-        <v>46511</v>
-      </c>
-      <c r="I27" s="895" t="n">
-        <v>46527</v>
-      </c>
-      <c r="J27" s="894" t="n">
-        <v>13</v>
-      </c>
-      <c r="K27" s="894" t="n">
-        <v>76</v>
-      </c>
-      <c r="L27" s="894" t="n">
-        <v>76</v>
-      </c>
-      <c r="M27" s="893" t="inlineStr">
-        <is>
-          <t>11 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="914" t="inlineStr">
-        <is>
-          <t>FC01_FCOI20_202271</t>
-        </is>
-      </c>
-      <c r="B28" s="893" t="inlineStr">
-        <is>
-          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell avançat)</t>
-        </is>
-      </c>
-      <c r="C28" s="894" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D28" s="894" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E28" s="894" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F28" s="894" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G28" s="893" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H28" s="895" t="n">
-        <v>46531</v>
-      </c>
-      <c r="I28" s="895" t="n">
-        <v>46539</v>
-      </c>
-      <c r="J28" s="894" t="n">
-        <v>7</v>
-      </c>
-      <c r="K28" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="L28" s="894" t="n">
-        <v>40</v>
-      </c>
-      <c r="M28" s="893" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="J29" s="915" t="inlineStr">
+    <row r="35">
+      <c r="J35" s="938" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="K29" s="915">
-        <f>SUM(K5:K28)</f>
+      <c r="K35" s="938">
+        <f>SUM(K5:K34)</f>
         <v/>
       </c>
-      <c r="L29" s="915">
-        <f>SUM(L5:L28)</f>
+      <c r="L35" s="938">
+        <f>SUM(L5:L34)</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="916" t="inlineStr">
-        <is>
-          <t>• Formacions sense hores al fitxer d'origen (ADGG0208, FCOS02, CTRH0011, CTRHI0015, FCOI25 i blocs Forma i Contracte) no s'han programat: cal indicar-ne les hores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="916" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="939" t="inlineStr">
+        <is>
+          <t>• Hores d'ADGG0208 (678), FCOS02 (30), CTRH0011 (10) i CTRHI0015 (10) facilitades per l'usuari. FCOI25 i els codis de les files 31-43 no tenen hores i no s'han programat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="939" t="inlineStr">
         <is>
           <t>• MARIA: només matins (disponibilitat 'Matins lliure // Tardes: 1 formació per mes'). S'han evitat els dies en què ja fa 'IA MARIA' a GOOGLE MATINS (set.-oct. 2026).</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="916" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="939" t="inlineStr">
         <is>
           <t>• Un docent no té mai dues formacions el mateix dia. Els nivells (bàsic → intermedi → avançat, Coaching I → II, Català A1 → A2.1 i mòduls IMPE0110) es programen en ordre.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="916" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="939" t="inlineStr">
         <is>
           <t>• No s'ha tocat cap cel·la ja ocupada del cronograma ni les aules de TARRAGONA / ON LINE.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="916" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="939" t="inlineStr">
         <is>
           <t>• Setembre-desembre 2027: festius i vacances del CALENDARI_LABORAL_2027 (els festius locals 04/09 i 15/09 hi consten com 'a omplir'). S'hi afegeix el 12/10 com a festiu.</t>
         </is>
@@ -34959,13 +35946,13 @@
           <t>004-FCOV05 1A ED (5H)</t>
         </is>
       </c>
-      <c r="AP22" s="917" t="inlineStr">
+      <c r="AP22" s="940" t="inlineStr">
         <is>
           <t>019+020 FCO</t>
         </is>
       </c>
-      <c r="AQ22" s="917" t="n"/>
-      <c r="AR22" s="918" t="n"/>
+      <c r="AQ22" s="940" t="n"/>
+      <c r="AR22" s="941" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="757">
       <c r="A23" s="10" t="inlineStr">
@@ -40950,13 +41937,13 @@
           <t>004-FCOV05 1A ED (5H)</t>
         </is>
       </c>
-      <c r="AP22" s="917" t="inlineStr">
+      <c r="AP22" s="940" t="inlineStr">
         <is>
           <t>019+020 FCO</t>
         </is>
       </c>
-      <c r="AQ22" s="917" t="n"/>
-      <c r="AR22" s="918" t="n"/>
+      <c r="AQ22" s="940" t="n"/>
+      <c r="AR22" s="941" t="n"/>
       <c r="AS22" s="745" t="inlineStr">
         <is>
           <t>015- FCOI11ACTIC MITJ- FOAP(5 H)</t>

--- a/cronograma/CRONOGRAMA_26-27_PROVISIONAL.xlsx
+++ b/cronograma/CRONOGRAMA_26-27_PROVISIONAL.xlsx
@@ -2132,7 +2132,7 @@
     <xf numFmtId="44" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="34" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="942">
+  <cellXfs count="944">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3478,20 +3478,20 @@
     <xf numFmtId="0" fontId="72" fillId="74" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="75" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="76" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="86" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="87" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="86" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="87" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="86" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="89" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="72" fillId="87" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="90" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="89" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="90" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="89" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="90" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="70" fillId="71" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3506,40 +3506,6 @@
     </xf>
     <xf numFmtId="0" fontId="72" fillId="71" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="72" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="83" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="83" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="83" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="76" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="76" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="77" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="77" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="78" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="78" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="77" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="78" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="91" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="91" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="89" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="91" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="72" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="70" fillId="84" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3547,11 +3513,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="84" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="78" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="76" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="78" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="36" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="77" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="77" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="76" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="77" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="78" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="78" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="79" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3560,6 +3536,7 @@
     <xf numFmtId="0" fontId="71" fillId="79" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="72" fillId="78" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="79" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="70" fillId="92" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3567,50 +3544,31 @@
     <xf numFmtId="0" fontId="71" fillId="92" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="73" fillId="90" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="92" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="87" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="72" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="85" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="87" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="85" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="85" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="85" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="85" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="87" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="90" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="77" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="79" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="90" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="79" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="36" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="90" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="80" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="80" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="80" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="81" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="81" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="72" fillId="80" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="81" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="88" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="88" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="88" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="92" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="70" fillId="93" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3618,13 +3576,49 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="93" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="81" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="88" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="80" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="88" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="81" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="86" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="86" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="86" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="88" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="91" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="91" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="91" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="81" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="81" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="82" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="82" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="81" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="82" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="89" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="89" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="89" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="93" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="70" fillId="94" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3632,29 +3626,41 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="94" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="84" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="82" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="84" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="81" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="93" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="82" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="70" fillId="71" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="71" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="94" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="70" fillId="82" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="85" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="82" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="71" fillId="85" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="82" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="94" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="72" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="72" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="73" fillId="71" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="82" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="83" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="83" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="83" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="83" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="95" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="96" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3684,16 +3690,16 @@
     <xf numFmtId="166" fontId="78" fillId="0" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="86" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="87" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="89" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="90" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="71" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="83" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="84" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="74" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3708,31 +3714,19 @@
     <xf numFmtId="0" fontId="78" fillId="76" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="77" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="91" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="84" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="78" fillId="78" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="79" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="92" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="87" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="77" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="85" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="90" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="78" fillId="79" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="80" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3744,13 +3738,25 @@
     <xf numFmtId="0" fontId="78" fillId="88" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="78" fillId="86" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="91" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="78" fillId="81" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="94" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="78" fillId="89" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="78" fillId="82" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="83" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -23677,7 +23683,7 @@
       </c>
       <c r="BN154" s="816" t="inlineStr">
         <is>
-          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
+          <t>FCOI25 ACTIC. Seguretat i civisme en l'entorn digital – nivell intermedi [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–09/11 · 40 h</t>
         </is>
       </c>
     </row>
@@ -24341,62 +24347,62 @@
         <v>6</v>
       </c>
       <c r="I165" s="832" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J165" s="24" t="n"/>
       <c r="K165" s="24" t="n"/>
       <c r="L165" s="832" t="n">
+        <v>5</v>
+      </c>
+      <c r="M165" s="833" t="n">
         <v>6</v>
       </c>
-      <c r="M165" s="832" t="n">
+      <c r="N165" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="N165" s="832" t="n">
+      <c r="O165" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="O165" s="832" t="n">
-        <v>6</v>
-      </c>
-      <c r="P165" s="832" t="n">
+      <c r="P165" s="834" t="n">
         <v>6</v>
       </c>
       <c r="Q165" s="24" t="n"/>
       <c r="R165" s="24" t="n"/>
-      <c r="S165" s="832" t="n">
+      <c r="S165" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="T165" s="832" t="n">
+      <c r="T165" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="U165" s="832" t="n">
+      <c r="U165" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="V165" s="832" t="n">
+      <c r="V165" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="W165" s="832" t="n">
+      <c r="W165" s="834" t="n">
         <v>6</v>
       </c>
       <c r="X165" s="24" t="n"/>
       <c r="Y165" s="24" t="n"/>
-      <c r="Z165" s="832" t="n">
+      <c r="Z165" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AA165" s="832" t="n">
+      <c r="AA165" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AB165" s="832" t="n">
+      <c r="AB165" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AC165" s="832" t="n">
+      <c r="AC165" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AD165" s="832" t="n">
+      <c r="AD165" s="834" t="n">
         <v>6</v>
       </c>
       <c r="AE165" s="24" t="n"/>
       <c r="AF165" s="24" t="n"/>
-      <c r="AG165" s="832" t="n">
+      <c r="AG165" s="834" t="n">
         <v>6</v>
       </c>
       <c r="AH165" s="756" t="n"/>
@@ -24405,9 +24411,14 @@
         <f>AJ154+AI163</f>
         <v/>
       </c>
-      <c r="AL165" s="833" t="inlineStr">
-        <is>
-          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
+      <c r="AL165" s="835" t="inlineStr">
+        <is>
+          <t>FCOI25 ACTIC. Seguretat i civisme en l'entorn digital – nivell intermedi [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–09/11 · 40 h</t>
+        </is>
+      </c>
+      <c r="AU165" s="836" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 10/11–03/05 · 678 h</t>
         </is>
       </c>
     </row>
@@ -24420,27 +24431,27 @@
       <c r="B166" s="456" t="n"/>
       <c r="C166" s="456" t="n"/>
       <c r="D166" s="119" t="n"/>
-      <c r="E166" s="834" t="n">
+      <c r="E166" s="837" t="n">
         <v>6</v>
       </c>
-      <c r="F166" s="835" t="n">
+      <c r="F166" s="838" t="n">
         <v>6</v>
       </c>
-      <c r="G166" s="835" t="n">
+      <c r="G166" s="838" t="n">
         <v>6</v>
       </c>
-      <c r="H166" s="835" t="n">
+      <c r="H166" s="838" t="n">
         <v>6</v>
       </c>
-      <c r="I166" s="835" t="n">
+      <c r="I166" s="838" t="n">
         <v>6</v>
       </c>
       <c r="J166" s="24" t="n"/>
       <c r="K166" s="24" t="n"/>
-      <c r="L166" s="835" t="n">
+      <c r="L166" s="838" t="n">
         <v>5</v>
       </c>
-      <c r="M166" s="835" t="n">
+      <c r="M166" s="838" t="n">
         <v>5</v>
       </c>
       <c r="N166" s="756" t="n"/>
@@ -24455,36 +24466,36 @@
       <c r="W166" s="756" t="n"/>
       <c r="X166" s="24" t="n"/>
       <c r="Y166" s="24" t="n"/>
-      <c r="Z166" s="836" t="n">
+      <c r="Z166" s="839" t="n">
         <v>6</v>
       </c>
-      <c r="AA166" s="837" t="n">
+      <c r="AA166" s="840" t="n">
         <v>6</v>
       </c>
-      <c r="AB166" s="837" t="n">
+      <c r="AB166" s="840" t="n">
         <v>6</v>
       </c>
-      <c r="AC166" s="837" t="n">
+      <c r="AC166" s="840" t="n">
         <v>6</v>
       </c>
-      <c r="AD166" s="837" t="n">
+      <c r="AD166" s="840" t="n">
         <v>6</v>
       </c>
       <c r="AE166" s="24" t="n"/>
       <c r="AF166" s="24" t="n"/>
-      <c r="AG166" s="837" t="n">
+      <c r="AG166" s="840" t="n">
         <v>5</v>
       </c>
       <c r="AH166" s="756" t="n"/>
       <c r="AI166" s="4" t="n"/>
       <c r="AK166" s="774" t="n"/>
-      <c r="AL166" s="838" t="inlineStr">
+      <c r="AL166" s="841" t="inlineStr">
         <is>
           <t>FCOI18 Comunicació i col·laboració amb eines digitals (ACTIC Nivell bàsic) · MARIA · FIREFOX matí 9:00-15:00 · 02/11–10/11 · 40 h</t>
         </is>
       </c>
       <c r="AM166" s="774" t="n"/>
-      <c r="AU166" s="839" t="inlineStr">
+      <c r="AU166" s="842" t="inlineStr">
         <is>
           <t>FCOI15 Creació de continguts digitals (ACTIC Nivell bàsic) · MARIA · FIREFOX matí 9:00-15:00 · 23/11–01/12 · 40 h</t>
         </is>
@@ -24516,19 +24527,19 @@
       </c>
       <c r="J167" s="35" t="n"/>
       <c r="K167" s="35" t="n"/>
-      <c r="L167" s="840" t="n">
+      <c r="L167" s="843" t="n">
         <v>6</v>
       </c>
-      <c r="M167" s="841" t="n">
+      <c r="M167" s="844" t="n">
         <v>6</v>
       </c>
-      <c r="N167" s="841" t="n">
+      <c r="N167" s="844" t="n">
         <v>6</v>
       </c>
-      <c r="O167" s="841" t="n">
+      <c r="O167" s="844" t="n">
         <v>6</v>
       </c>
-      <c r="P167" s="841" t="n">
+      <c r="P167" s="844" t="n">
         <v>6</v>
       </c>
       <c r="Q167" s="35" t="n"/>
@@ -24551,12 +24562,12 @@
       <c r="AH167" s="778" t="n"/>
       <c r="AI167" s="4" t="n"/>
       <c r="AK167" s="775" t="n"/>
-      <c r="AL167" s="842" t="inlineStr">
+      <c r="AL167" s="845" t="inlineStr">
         <is>
           <t>CTRL0040 CTRL0040_2024_Català A1 (Català nivell inicial A1) · PER ASSIGNAR · COPILOT matí 9:00-15:00 · 19/10–06/11 · 90 h</t>
         </is>
       </c>
-      <c r="AU167" s="843" t="inlineStr">
+      <c r="AU167" s="846" t="inlineStr">
         <is>
           <t>COMM0009 Atenció al client · TANIA/? · COPILOT matí 9:00-15:00 · 09/11–13/11 · 30 h</t>
         </is>
@@ -24737,7 +24748,7 @@
         <v>6</v>
       </c>
       <c r="AH169" s="756" t="n"/>
-      <c r="AL169" s="844" t="inlineStr">
+      <c r="AL169" s="847" t="inlineStr">
         <is>
           <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
         </is>
@@ -24766,16 +24777,16 @@
       <c r="P170" s="778" t="n"/>
       <c r="Q170" s="35" t="n"/>
       <c r="R170" s="35" t="n"/>
-      <c r="S170" s="845" t="n">
+      <c r="S170" s="848" t="n">
         <v>5</v>
       </c>
-      <c r="T170" s="846" t="n">
+      <c r="T170" s="849" t="n">
         <v>5</v>
       </c>
-      <c r="U170" s="846" t="n">
+      <c r="U170" s="849" t="n">
         <v>5</v>
       </c>
-      <c r="V170" s="846" t="n">
+      <c r="V170" s="849" t="n">
         <v>5</v>
       </c>
       <c r="W170" s="778" t="n"/>
@@ -24790,7 +24801,7 @@
       <c r="AF170" s="35" t="n"/>
       <c r="AG170" s="778" t="n"/>
       <c r="AH170" s="778" t="n"/>
-      <c r="AL170" s="847" t="inlineStr">
+      <c r="AL170" s="850" t="inlineStr">
         <is>
           <t>SANP0011 Tècniques de massatge (1a ed.) · ESTHER · COPILOT tarda 15:00-20:00 · 16/11–19/11 · 20 h</t>
         </is>
@@ -25003,57 +25014,57 @@
       </c>
       <c r="B175" s="11" t="n"/>
       <c r="C175" s="11" t="n"/>
-      <c r="D175" s="832" t="n">
+      <c r="D175" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="E175" s="832" t="n">
+      <c r="E175" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="F175" s="832" t="n">
+      <c r="F175" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="G175" s="832" t="n">
+      <c r="G175" s="834" t="n">
         <v>6</v>
       </c>
       <c r="H175" s="24" t="n"/>
       <c r="I175" s="24" t="n"/>
       <c r="J175" s="26" t="n"/>
       <c r="K175" s="26" t="n"/>
-      <c r="L175" s="832" t="n">
+      <c r="L175" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="M175" s="832" t="n">
+      <c r="M175" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="N175" s="832" t="n">
+      <c r="N175" s="834" t="n">
         <v>6</v>
       </c>
       <c r="O175" s="24" t="n"/>
       <c r="P175" s="24" t="n"/>
-      <c r="Q175" s="832" t="n">
+      <c r="Q175" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="R175" s="832" t="n">
+      <c r="R175" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="S175" s="832" t="n">
+      <c r="S175" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="T175" s="832" t="n">
+      <c r="T175" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="U175" s="832" t="n">
+      <c r="U175" s="834" t="n">
         <v>6</v>
       </c>
       <c r="V175" s="24" t="n"/>
       <c r="W175" s="24" t="n"/>
-      <c r="X175" s="832" t="n">
+      <c r="X175" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="Y175" s="832" t="n">
+      <c r="Y175" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="Z175" s="832" t="n">
+      <c r="Z175" s="834" t="n">
         <v>6</v>
       </c>
       <c r="AA175" s="63" t="n"/>
@@ -25070,9 +25081,9 @@
         <v/>
       </c>
       <c r="AK175" s="627" t="n"/>
-      <c r="AL175" s="833" t="inlineStr">
-        <is>
-          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
+      <c r="AL175" s="851" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 10/11–03/05 · 678 h</t>
         </is>
       </c>
       <c r="AM175" s="774" t="n"/>
@@ -25085,7 +25096,7 @@
       </c>
       <c r="B176" s="456" t="n"/>
       <c r="C176" s="456" t="n"/>
-      <c r="D176" s="848" t="n">
+      <c r="D176" s="852" t="n">
         <v>5</v>
       </c>
       <c r="E176" s="756" t="n"/>
@@ -25120,7 +25131,7 @@
       <c r="AH176" s="63" t="n"/>
       <c r="AI176" s="4" t="n"/>
       <c r="AK176" s="774" t="n"/>
-      <c r="AL176" s="849" t="inlineStr">
+      <c r="AL176" s="853" t="inlineStr">
         <is>
           <t>FCOI15 Creació de continguts digitals (ACTIC Nivell bàsic) · MARIA · FIREFOX matí 9:00-15:00 · 23/11–01/12 · 40 h</t>
         </is>
@@ -25302,7 +25313,7 @@
       <c r="AF179" s="63" t="n"/>
       <c r="AG179" s="63" t="n"/>
       <c r="AH179" s="63" t="n"/>
-      <c r="AL179" s="844" t="inlineStr">
+      <c r="AL179" s="847" t="inlineStr">
         <is>
           <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
         </is>
@@ -25392,7 +25403,7 @@
     <row r="183"/>
     <row r="184"/>
     <row r="185" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A185" s="850" t="inlineStr">
+      <c r="A185" s="854" t="inlineStr">
         <is>
           <t>GENER 2027</t>
         </is>
@@ -25556,77 +25567,77 @@
       <c r="D187" s="26" t="n"/>
       <c r="E187" s="24" t="n"/>
       <c r="F187" s="24" t="n"/>
-      <c r="G187" s="832" t="n">
+      <c r="G187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="H187" s="832" t="n">
+      <c r="H187" s="834" t="n">
         <v>6</v>
       </c>
       <c r="I187" s="610" t="n"/>
-      <c r="J187" s="832" t="n">
+      <c r="J187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="K187" s="832" t="n">
+      <c r="K187" s="834" t="n">
         <v>6</v>
       </c>
       <c r="L187" s="24" t="n"/>
       <c r="M187" s="24" t="n"/>
-      <c r="N187" s="832" t="n">
+      <c r="N187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="O187" s="832" t="n">
+      <c r="O187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="P187" s="832" t="n">
+      <c r="P187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="Q187" s="832" t="n">
+      <c r="Q187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="R187" s="832" t="n">
+      <c r="R187" s="834" t="n">
         <v>6</v>
       </c>
       <c r="S187" s="24" t="n"/>
       <c r="T187" s="24" t="n"/>
-      <c r="U187" s="832" t="n">
+      <c r="U187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="V187" s="832" t="n">
+      <c r="V187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="W187" s="832" t="n">
+      <c r="W187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="X187" s="832" t="n">
+      <c r="X187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="Y187" s="832" t="n">
+      <c r="Y187" s="834" t="n">
         <v>6</v>
       </c>
       <c r="Z187" s="24" t="n"/>
       <c r="AA187" s="24" t="n"/>
-      <c r="AB187" s="832" t="n">
+      <c r="AB187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AC187" s="832" t="n">
+      <c r="AC187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AD187" s="832" t="n">
+      <c r="AD187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AE187" s="832" t="n">
+      <c r="AE187" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AF187" s="832" t="n">
+      <c r="AF187" s="834" t="n">
         <v>6</v>
       </c>
       <c r="AG187" s="24" t="n"/>
       <c r="AH187" s="24" t="n"/>
       <c r="AI187" s="4" t="n"/>
       <c r="AK187" s="627" t="n"/>
-      <c r="AL187" s="833" t="inlineStr">
-        <is>
-          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
+      <c r="AL187" s="851" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 10/11–03/05 · 678 h</t>
         </is>
       </c>
     </row>
@@ -25648,19 +25659,19 @@
       <c r="K188" s="756" t="n"/>
       <c r="L188" s="24" t="n"/>
       <c r="M188" s="24" t="n"/>
-      <c r="N188" s="851" t="n">
+      <c r="N188" s="855" t="n">
         <v>5</v>
       </c>
-      <c r="O188" s="852" t="n">
+      <c r="O188" s="856" t="n">
         <v>5</v>
       </c>
-      <c r="P188" s="852" t="n">
+      <c r="P188" s="856" t="n">
         <v>5</v>
       </c>
-      <c r="Q188" s="852" t="n">
+      <c r="Q188" s="856" t="n">
         <v>5</v>
       </c>
-      <c r="R188" s="852" t="n">
+      <c r="R188" s="856" t="n">
         <v>5</v>
       </c>
       <c r="S188" s="24" t="n"/>
@@ -25680,7 +25691,7 @@
       <c r="AG188" s="24" t="n"/>
       <c r="AH188" s="24" t="n"/>
       <c r="AI188" s="4" t="n"/>
-      <c r="AL188" s="853" t="inlineStr">
+      <c r="AL188" s="857" t="inlineStr">
         <is>
           <t>IFCT117 Introducció a la intel·ligència artificial (1a ed.) · MARIA · FIREFOX matí 9:00-14:00 · 11/01–15/01 · 25 h</t>
         </is>
@@ -25704,53 +25715,53 @@
       <c r="K189" s="778" t="n"/>
       <c r="L189" s="35" t="n"/>
       <c r="M189" s="35" t="n"/>
-      <c r="N189" s="854" t="n">
+      <c r="N189" s="858" t="n">
         <v>6</v>
       </c>
-      <c r="O189" s="855" t="n">
+      <c r="O189" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="P189" s="855" t="n">
+      <c r="P189" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="Q189" s="855" t="n">
+      <c r="Q189" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="R189" s="855" t="n">
+      <c r="R189" s="859" t="n">
         <v>6</v>
       </c>
       <c r="S189" s="35" t="n"/>
       <c r="T189" s="35" t="n"/>
-      <c r="U189" s="855" t="n">
+      <c r="U189" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="V189" s="855" t="n">
+      <c r="V189" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="W189" s="855" t="n">
+      <c r="W189" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="X189" s="855" t="n">
+      <c r="X189" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="Y189" s="855" t="n">
+      <c r="Y189" s="859" t="n">
         <v>6</v>
       </c>
       <c r="Z189" s="35" t="n"/>
       <c r="AA189" s="35" t="n"/>
-      <c r="AB189" s="855" t="n">
+      <c r="AB189" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="AC189" s="855" t="n">
+      <c r="AC189" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="AD189" s="855" t="n">
+      <c r="AD189" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="AE189" s="855" t="n">
+      <c r="AE189" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="AF189" s="855" t="n">
+      <c r="AF189" s="859" t="n">
         <v>6</v>
       </c>
       <c r="AG189" s="35" t="n"/>
@@ -25758,7 +25769,7 @@
       <c r="AI189" s="4" t="n"/>
       <c r="AJ189" s="428" t="n"/>
       <c r="AK189" s="775" t="n"/>
-      <c r="AL189" s="856" t="inlineStr">
+      <c r="AL189" s="860" t="inlineStr">
         <is>
           <t>IFCD64 Gestió de Projectes d'implementació del CRM · PER ASSIGNAR · COPILOT matí 9:00-15:00 · 11/01–12/02 · 145 h</t>
         </is>
@@ -25782,33 +25793,33 @@
       <c r="K190" s="756" t="n"/>
       <c r="L190" s="24" t="n"/>
       <c r="M190" s="24" t="n"/>
-      <c r="N190" s="857" t="n">
+      <c r="N190" s="861" t="n">
         <v>6</v>
       </c>
-      <c r="O190" s="858" t="n">
+      <c r="O190" s="862" t="n">
         <v>6</v>
       </c>
-      <c r="P190" s="858" t="n">
+      <c r="P190" s="862" t="n">
         <v>6</v>
       </c>
-      <c r="Q190" s="858" t="n">
+      <c r="Q190" s="862" t="n">
         <v>6</v>
       </c>
-      <c r="R190" s="858" t="n">
+      <c r="R190" s="862" t="n">
         <v>6</v>
       </c>
       <c r="S190" s="24" t="n"/>
       <c r="T190" s="24" t="n"/>
-      <c r="U190" s="859" t="n">
+      <c r="U190" s="863" t="n">
         <v>5</v>
       </c>
-      <c r="V190" s="860" t="n">
+      <c r="V190" s="864" t="n">
         <v>5</v>
       </c>
-      <c r="W190" s="860" t="n">
+      <c r="W190" s="864" t="n">
         <v>5</v>
       </c>
-      <c r="X190" s="860" t="n">
+      <c r="X190" s="864" t="n">
         <v>5</v>
       </c>
       <c r="Y190" s="756" t="n"/>
@@ -25822,12 +25833,12 @@
       <c r="AG190" s="24" t="n"/>
       <c r="AH190" s="24" t="n"/>
       <c r="AI190" s="4" t="n"/>
-      <c r="AL190" s="861" t="inlineStr">
+      <c r="AL190" s="865" t="inlineStr">
         <is>
           <t>SEAD0227 Tècniques de relaxació · ESTHER · GOOGLE tarda 15:00-20:00 · 18/01–21/01 · 20 h</t>
         </is>
       </c>
-      <c r="AU190" s="862" t="inlineStr">
+      <c r="AU190" s="866" t="inlineStr">
         <is>
           <t>CTRP0006 Mindfulness · RAMON · GOOGLE tarda 15:00-21:00 · 11/01–15/01 · 30 h</t>
         </is>
@@ -25910,7 +25921,7 @@
       </c>
       <c r="AG191" s="24" t="n"/>
       <c r="AH191" s="24" t="n"/>
-      <c r="AL191" s="844" t="inlineStr">
+      <c r="AL191" s="847" t="inlineStr">
         <is>
           <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
         </is>
@@ -25941,37 +25952,37 @@
       <c r="R192" s="778" t="n"/>
       <c r="S192" s="35" t="n"/>
       <c r="T192" s="35" t="n"/>
-      <c r="U192" s="863" t="n">
+      <c r="U192" s="867" t="n">
         <v>6</v>
       </c>
-      <c r="V192" s="864" t="n">
+      <c r="V192" s="868" t="n">
         <v>6</v>
       </c>
-      <c r="W192" s="864" t="n">
+      <c r="W192" s="868" t="n">
         <v>6</v>
       </c>
-      <c r="X192" s="864" t="n">
+      <c r="X192" s="868" t="n">
         <v>6</v>
       </c>
-      <c r="Y192" s="864" t="n">
+      <c r="Y192" s="868" t="n">
         <v>6</v>
       </c>
       <c r="Z192" s="35" t="n"/>
       <c r="AA192" s="35" t="n"/>
-      <c r="AB192" s="864" t="n">
+      <c r="AB192" s="868" t="n">
         <v>5</v>
       </c>
-      <c r="AC192" s="864" t="n">
+      <c r="AC192" s="868" t="n">
         <v>5</v>
       </c>
-      <c r="AD192" s="864" t="n">
+      <c r="AD192" s="868" t="n">
         <v>5</v>
       </c>
       <c r="AE192" s="778" t="n"/>
       <c r="AF192" s="778" t="n"/>
       <c r="AG192" s="35" t="n"/>
       <c r="AH192" s="35" t="n"/>
-      <c r="AL192" s="865" t="inlineStr">
+      <c r="AL192" s="869" t="inlineStr">
         <is>
           <t>CTRL0041 CTRL0041_2024_Català A2.1 (Català bàsic 1 ) · PER ASSIGNAR · COPILOT tarda 15:00-21:00 · 18/01–27/01 · 45 h</t>
         </is>
@@ -26100,7 +26111,7 @@
     <row r="196"/>
     <row r="197"/>
     <row r="198" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A198" s="850" t="inlineStr">
+      <c r="A198" s="854" t="inlineStr">
         <is>
           <t>FEBRER 2027</t>
         </is>
@@ -26255,70 +26266,70 @@
       </c>
       <c r="B200" s="11" t="n"/>
       <c r="C200" s="11" t="n"/>
-      <c r="D200" s="832" t="n">
+      <c r="D200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="E200" s="832" t="n">
+      <c r="E200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="F200" s="832" t="n">
+      <c r="F200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="G200" s="832" t="n">
+      <c r="G200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="H200" s="832" t="n">
+      <c r="H200" s="834" t="n">
         <v>6</v>
       </c>
       <c r="I200" s="24" t="n"/>
       <c r="J200" s="24" t="n"/>
-      <c r="K200" s="832" t="n">
+      <c r="K200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="L200" s="832" t="n">
+      <c r="L200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="M200" s="832" t="n">
+      <c r="M200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="N200" s="832" t="n">
+      <c r="N200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="O200" s="832" t="n">
+      <c r="O200" s="834" t="n">
         <v>6</v>
       </c>
       <c r="P200" s="24" t="n"/>
       <c r="Q200" s="24" t="n"/>
-      <c r="R200" s="832" t="n">
+      <c r="R200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="S200" s="832" t="n">
+      <c r="S200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="T200" s="832" t="n">
+      <c r="T200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="U200" s="832" t="n">
+      <c r="U200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="V200" s="832" t="n">
+      <c r="V200" s="834" t="n">
         <v>6</v>
       </c>
       <c r="W200" s="24" t="n"/>
       <c r="X200" s="24" t="n"/>
-      <c r="Y200" s="832" t="n">
+      <c r="Y200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="Z200" s="832" t="n">
+      <c r="Z200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AA200" s="832" t="n">
+      <c r="AA200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AB200" s="832" t="n">
+      <c r="AB200" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AC200" s="832" t="n">
+      <c r="AC200" s="834" t="n">
         <v>6</v>
       </c>
       <c r="AD200" s="24" t="n"/>
@@ -26328,9 +26339,9 @@
       <c r="AH200" s="756" t="n"/>
       <c r="AI200" s="4" t="n"/>
       <c r="AK200" s="627" t="n"/>
-      <c r="AL200" s="833" t="inlineStr">
-        <is>
-          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
+      <c r="AL200" s="851" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 10/11–03/05 · 678 h</t>
         </is>
       </c>
     </row>
@@ -26342,27 +26353,27 @@
       </c>
       <c r="B201" s="456" t="n"/>
       <c r="C201" s="456" t="n"/>
-      <c r="D201" s="866" t="n">
+      <c r="D201" s="870" t="n">
         <v>6</v>
       </c>
-      <c r="E201" s="867" t="n">
+      <c r="E201" s="871" t="n">
         <v>6</v>
       </c>
-      <c r="F201" s="867" t="n">
+      <c r="F201" s="871" t="n">
         <v>6</v>
       </c>
-      <c r="G201" s="867" t="n">
+      <c r="G201" s="871" t="n">
         <v>6</v>
       </c>
-      <c r="H201" s="867" t="n">
+      <c r="H201" s="871" t="n">
         <v>6</v>
       </c>
       <c r="I201" s="24" t="n"/>
       <c r="J201" s="24" t="n"/>
-      <c r="K201" s="867" t="n">
+      <c r="K201" s="871" t="n">
         <v>5</v>
       </c>
-      <c r="L201" s="867" t="n">
+      <c r="L201" s="871" t="n">
         <v>5</v>
       </c>
       <c r="M201" s="756" t="n"/>
@@ -26377,19 +26388,19 @@
       <c r="V201" s="756" t="n"/>
       <c r="W201" s="24" t="n"/>
       <c r="X201" s="24" t="n"/>
-      <c r="Y201" s="868" t="n">
+      <c r="Y201" s="872" t="n">
         <v>6</v>
       </c>
-      <c r="Z201" s="869" t="n">
+      <c r="Z201" s="873" t="n">
         <v>6</v>
       </c>
-      <c r="AA201" s="869" t="n">
+      <c r="AA201" s="873" t="n">
         <v>6</v>
       </c>
-      <c r="AB201" s="869" t="n">
+      <c r="AB201" s="873" t="n">
         <v>6</v>
       </c>
-      <c r="AC201" s="869" t="n">
+      <c r="AC201" s="873" t="n">
         <v>6</v>
       </c>
       <c r="AD201" s="24" t="n"/>
@@ -26399,12 +26410,12 @@
       <c r="AH201" s="756" t="n"/>
       <c r="AI201" s="4" t="n"/>
       <c r="AK201" s="774" t="n"/>
-      <c r="AL201" s="870" t="inlineStr">
+      <c r="AL201" s="874" t="inlineStr">
         <is>
           <t>FCOI19 Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi) (1a ed.) · MARIA · FIREFOX matí 9:00-15:00 · 01/02–09/02 · 40 h</t>
         </is>
       </c>
-      <c r="AU201" s="871" t="inlineStr">
+      <c r="AU201" s="875" t="inlineStr">
         <is>
           <t>FCOI16 Creació de continguts digitals i programació (ACTIC Nivell intermedi) (1a ed.) · MARIA · FIREFOX matí 9:00-15:00 · 22/02–02/03 · 40 h</t>
         </is>
@@ -26418,61 +26429,61 @@
       </c>
       <c r="B202" s="15" t="n"/>
       <c r="C202" s="15" t="n"/>
-      <c r="D202" s="855" t="n">
+      <c r="D202" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="E202" s="855" t="n">
+      <c r="E202" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="F202" s="855" t="n">
+      <c r="F202" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="G202" s="855" t="n">
+      <c r="G202" s="859" t="n">
         <v>6</v>
       </c>
-      <c r="H202" s="855" t="n">
+      <c r="H202" s="859" t="n">
         <v>6</v>
       </c>
       <c r="I202" s="35" t="n"/>
       <c r="J202" s="35" t="n"/>
-      <c r="K202" s="855" t="n">
+      <c r="K202" s="859" t="n">
         <v>5</v>
       </c>
-      <c r="L202" s="855" t="n">
+      <c r="L202" s="859" t="n">
         <v>5</v>
       </c>
-      <c r="M202" s="855" t="n">
+      <c r="M202" s="859" t="n">
         <v>5</v>
       </c>
-      <c r="N202" s="855" t="n">
+      <c r="N202" s="859" t="n">
         <v>5</v>
       </c>
-      <c r="O202" s="855" t="n">
+      <c r="O202" s="859" t="n">
         <v>5</v>
       </c>
       <c r="P202" s="35" t="n"/>
       <c r="Q202" s="35" t="n"/>
-      <c r="R202" s="872" t="n">
+      <c r="R202" s="876" t="n">
         <v>6</v>
       </c>
-      <c r="S202" s="873" t="n">
+      <c r="S202" s="877" t="n">
         <v>6</v>
       </c>
-      <c r="T202" s="873" t="n">
+      <c r="T202" s="877" t="n">
         <v>6</v>
       </c>
-      <c r="U202" s="873" t="n">
+      <c r="U202" s="877" t="n">
         <v>6</v>
       </c>
-      <c r="V202" s="873" t="n">
+      <c r="V202" s="877" t="n">
         <v>6</v>
       </c>
       <c r="W202" s="35" t="n"/>
       <c r="X202" s="35" t="n"/>
-      <c r="Y202" s="873" t="n">
+      <c r="Y202" s="877" t="n">
         <v>5</v>
       </c>
-      <c r="Z202" s="873" t="n">
+      <c r="Z202" s="877" t="n">
         <v>5</v>
       </c>
       <c r="AA202" s="778" t="n"/>
@@ -26486,12 +26497,12 @@
       <c r="AI202" s="4" t="n"/>
       <c r="AJ202" s="428" t="n"/>
       <c r="AK202" s="775" t="n"/>
-      <c r="AL202" s="874" t="inlineStr">
+      <c r="AL202" s="878" t="inlineStr">
         <is>
           <t>CTRP0037 Coaching de fortaleses. Nivell II · RAMON · COPILOT matí 9:00-15:00 · 15/02–23/02 · 40 h</t>
         </is>
       </c>
-      <c r="AU202" s="875" t="inlineStr">
+      <c r="AU202" s="879" t="inlineStr">
         <is>
           <t>IFCD64 Gestió de Projectes d'implementació del CRM · PER ASSIGNAR · COPILOT matí 9:00-15:00 · 11/01–12/02 · 145 h</t>
         </is>
@@ -26617,7 +26628,7 @@
       <c r="AF204" s="756" t="n"/>
       <c r="AG204" s="756" t="n"/>
       <c r="AH204" s="756" t="n"/>
-      <c r="AL204" s="844" t="inlineStr">
+      <c r="AL204" s="847" t="inlineStr">
         <is>
           <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
         </is>
@@ -26631,70 +26642,70 @@
       </c>
       <c r="B205" s="15" t="n"/>
       <c r="C205" s="15" t="n"/>
-      <c r="D205" s="876" t="n">
+      <c r="D205" s="880" t="n">
         <v>6</v>
       </c>
-      <c r="E205" s="877" t="n">
+      <c r="E205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="F205" s="877" t="n">
+      <c r="F205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="G205" s="877" t="n">
+      <c r="G205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="H205" s="877" t="n">
+      <c r="H205" s="881" t="n">
         <v>6</v>
       </c>
       <c r="I205" s="35" t="n"/>
       <c r="J205" s="35" t="n"/>
-      <c r="K205" s="877" t="n">
+      <c r="K205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="L205" s="877" t="n">
+      <c r="L205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="M205" s="877" t="n">
+      <c r="M205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="N205" s="877" t="n">
+      <c r="N205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="O205" s="877" t="n">
+      <c r="O205" s="881" t="n">
         <v>6</v>
       </c>
       <c r="P205" s="35" t="n"/>
       <c r="Q205" s="35" t="n"/>
-      <c r="R205" s="877" t="n">
+      <c r="R205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="S205" s="877" t="n">
+      <c r="S205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="T205" s="877" t="n">
+      <c r="T205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="U205" s="877" t="n">
+      <c r="U205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="V205" s="877" t="n">
+      <c r="V205" s="881" t="n">
         <v>6</v>
       </c>
       <c r="W205" s="35" t="n"/>
       <c r="X205" s="35" t="n"/>
-      <c r="Y205" s="877" t="n">
+      <c r="Y205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="Z205" s="877" t="n">
+      <c r="Z205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="AA205" s="877" t="n">
+      <c r="AA205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="AB205" s="877" t="n">
+      <c r="AB205" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="AC205" s="877" t="n">
+      <c r="AC205" s="881" t="n">
         <v>6</v>
       </c>
       <c r="AD205" s="35" t="n"/>
@@ -26702,7 +26713,7 @@
       <c r="AF205" s="778" t="n"/>
       <c r="AG205" s="778" t="n"/>
       <c r="AH205" s="778" t="n"/>
-      <c r="AL205" s="878" t="inlineStr">
+      <c r="AL205" s="882" t="inlineStr">
         <is>
           <t>IMPE0110 MF0063 MASSATGES ESTÈTIC MANUAL I MECÀNIC · LEIRE · COPILOT tarda 15:00-21:00 · 01/02–08/03 · 152 h</t>
         </is>
@@ -26831,7 +26842,7 @@
     <row r="209" ht="15.75" customHeight="1" s="757" thickTop="1"/>
     <row r="210"/>
     <row r="211" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A211" s="850" t="inlineStr">
+      <c r="A211" s="854" t="inlineStr">
         <is>
           <t>MARÇ 2027</t>
         </is>
@@ -26992,84 +27003,84 @@
       </c>
       <c r="B213" s="11" t="n"/>
       <c r="C213" s="11" t="n"/>
-      <c r="D213" s="832" t="n">
+      <c r="D213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="E213" s="832" t="n">
+      <c r="E213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="F213" s="832" t="n">
+      <c r="F213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="G213" s="832" t="n">
+      <c r="G213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="H213" s="832" t="n">
+      <c r="H213" s="834" t="n">
         <v>6</v>
       </c>
       <c r="I213" s="24" t="n"/>
       <c r="J213" s="24" t="n"/>
-      <c r="K213" s="832" t="n">
+      <c r="K213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="L213" s="832" t="n">
+      <c r="L213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="M213" s="832" t="n">
+      <c r="M213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="N213" s="832" t="n">
+      <c r="N213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="O213" s="832" t="n">
+      <c r="O213" s="834" t="n">
         <v>6</v>
       </c>
       <c r="P213" s="24" t="n"/>
       <c r="Q213" s="24" t="n"/>
-      <c r="R213" s="832" t="n">
+      <c r="R213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="S213" s="832" t="n">
+      <c r="S213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="T213" s="832" t="n">
+      <c r="T213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="U213" s="832" t="n">
+      <c r="U213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="V213" s="832" t="n">
+      <c r="V213" s="834" t="n">
         <v>6</v>
       </c>
       <c r="W213" s="24" t="n"/>
       <c r="X213" s="24" t="n"/>
-      <c r="Y213" s="832" t="n">
+      <c r="Y213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="Z213" s="832" t="n">
+      <c r="Z213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AA213" s="832" t="n">
+      <c r="AA213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AB213" s="832" t="n">
+      <c r="AB213" s="834" t="n">
         <v>6</v>
       </c>
       <c r="AC213" s="26" t="n"/>
       <c r="AD213" s="24" t="n"/>
       <c r="AE213" s="24" t="n"/>
       <c r="AF213" s="26" t="n"/>
-      <c r="AG213" s="832" t="n">
+      <c r="AG213" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="AH213" s="832" t="n">
+      <c r="AH213" s="834" t="n">
         <v>6</v>
       </c>
       <c r="AI213" s="4" t="n"/>
       <c r="AK213" s="627" t="n"/>
-      <c r="AL213" s="833" t="inlineStr">
-        <is>
-          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
+      <c r="AL213" s="851" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 10/11–03/05 · 678 h</t>
         </is>
       </c>
     </row>
@@ -27081,10 +27092,10 @@
       </c>
       <c r="B214" s="456" t="n"/>
       <c r="C214" s="456" t="n"/>
-      <c r="D214" s="879" t="n">
+      <c r="D214" s="883" t="n">
         <v>5</v>
       </c>
-      <c r="E214" s="869" t="n">
+      <c r="E214" s="873" t="n">
         <v>5</v>
       </c>
       <c r="F214" s="756" t="n"/>
@@ -27099,27 +27110,27 @@
       <c r="O214" s="756" t="n"/>
       <c r="P214" s="24" t="n"/>
       <c r="Q214" s="24" t="n"/>
-      <c r="R214" s="880" t="n">
+      <c r="R214" s="884" t="n">
         <v>6</v>
       </c>
-      <c r="S214" s="867" t="n">
+      <c r="S214" s="871" t="n">
         <v>6</v>
       </c>
-      <c r="T214" s="867" t="n">
+      <c r="T214" s="871" t="n">
         <v>6</v>
       </c>
-      <c r="U214" s="867" t="n">
+      <c r="U214" s="871" t="n">
         <v>6</v>
       </c>
-      <c r="V214" s="867" t="n">
+      <c r="V214" s="871" t="n">
         <v>6</v>
       </c>
       <c r="W214" s="24" t="n"/>
       <c r="X214" s="24" t="n"/>
-      <c r="Y214" s="867" t="n">
+      <c r="Y214" s="871" t="n">
         <v>5</v>
       </c>
-      <c r="Z214" s="867" t="n">
+      <c r="Z214" s="871" t="n">
         <v>5</v>
       </c>
       <c r="AA214" s="756" t="n"/>
@@ -27132,12 +27143,12 @@
       <c r="AH214" s="756" t="n"/>
       <c r="AI214" s="4" t="n"/>
       <c r="AK214" s="774" t="n"/>
-      <c r="AL214" s="881" t="inlineStr">
+      <c r="AL214" s="885" t="inlineStr">
         <is>
           <t>FCOI16 Creació de continguts digitals i programació (ACTIC Nivell intermedi) (1a ed.) · MARIA · FIREFOX matí 9:00-15:00 · 22/02–02/03 · 40 h</t>
         </is>
       </c>
-      <c r="AU214" s="870" t="inlineStr">
+      <c r="AU214" s="874" t="inlineStr">
         <is>
           <t>FCOI19 Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi) (2a ed.) · MARIA · FIREFOX matí 9:00-15:00 · 15/03–23/03 · 40 h</t>
         </is>
@@ -27159,63 +27170,63 @@
       <c r="I215" s="35" t="n"/>
       <c r="J215" s="35" t="n"/>
       <c r="K215" s="778" t="n"/>
-      <c r="L215" s="882" t="n">
+      <c r="L215" s="886" t="n">
         <v>6</v>
       </c>
-      <c r="M215" s="883" t="n">
+      <c r="M215" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="N215" s="883" t="n">
+      <c r="N215" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="O215" s="883" t="n">
+      <c r="O215" s="887" t="n">
         <v>6</v>
       </c>
       <c r="P215" s="35" t="n"/>
       <c r="Q215" s="35" t="n"/>
-      <c r="R215" s="883" t="n">
+      <c r="R215" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="S215" s="883" t="n">
+      <c r="S215" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="T215" s="883" t="n">
+      <c r="T215" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="U215" s="883" t="n">
+      <c r="U215" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="V215" s="883" t="n">
+      <c r="V215" s="887" t="n">
         <v>6</v>
       </c>
       <c r="W215" s="35" t="n"/>
       <c r="X215" s="35" t="n"/>
-      <c r="Y215" s="883" t="n">
+      <c r="Y215" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="Z215" s="883" t="n">
+      <c r="Z215" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="AA215" s="883" t="n">
+      <c r="AA215" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="AB215" s="883" t="n">
+      <c r="AB215" s="887" t="n">
         <v>6</v>
       </c>
       <c r="AC215" s="27" t="n"/>
       <c r="AD215" s="35" t="n"/>
       <c r="AE215" s="35" t="n"/>
       <c r="AF215" s="27" t="n"/>
-      <c r="AG215" s="883" t="n">
+      <c r="AG215" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="AH215" s="883" t="n">
+      <c r="AH215" s="887" t="n">
         <v>6</v>
       </c>
       <c r="AI215" s="4" t="n"/>
       <c r="AJ215" s="428" t="n"/>
       <c r="AK215" s="775" t="n"/>
-      <c r="AL215" s="884" t="inlineStr">
+      <c r="AL215" s="827" t="inlineStr">
         <is>
           <t>IMPE0110 MF0790 DRENATGE LIMFÀTIC ESTÈTIC MANUAL I MECÀNIC · LEIRE · COPILOT matí 9:00-15:00 · 09/03–06/04 · 114 h</t>
         </is>
@@ -27229,16 +27240,16 @@
       </c>
       <c r="B216" s="18" t="n"/>
       <c r="C216" s="18" t="n"/>
-      <c r="D216" s="885" t="n">
+      <c r="D216" s="888" t="n">
         <v>5</v>
       </c>
-      <c r="E216" s="886" t="n">
+      <c r="E216" s="889" t="n">
         <v>5</v>
       </c>
-      <c r="F216" s="886" t="n">
+      <c r="F216" s="889" t="n">
         <v>5</v>
       </c>
-      <c r="G216" s="886" t="n">
+      <c r="G216" s="889" t="n">
         <v>5</v>
       </c>
       <c r="H216" s="756" t="n"/>
@@ -27269,7 +27280,7 @@
       <c r="AG216" s="756" t="n"/>
       <c r="AH216" s="756" t="n"/>
       <c r="AI216" s="4" t="n"/>
-      <c r="AL216" s="847" t="inlineStr">
+      <c r="AL216" s="850" t="inlineStr">
         <is>
           <t>SANP0011 Tècniques de massatge (2a ed.) · ESTHER · GOOGLE tarda 15:00-20:00 · 01/03–04/03 · 20 h</t>
         </is>
@@ -27356,7 +27367,7 @@
       <c r="AH217" s="826" t="n">
         <v>6</v>
       </c>
-      <c r="AL217" s="844" t="inlineStr">
+      <c r="AL217" s="847" t="inlineStr">
         <is>
           <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
         </is>
@@ -27370,24 +27381,24 @@
       </c>
       <c r="B218" s="15" t="n"/>
       <c r="C218" s="15" t="n"/>
-      <c r="D218" s="877" t="n">
+      <c r="D218" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="E218" s="877" t="n">
+      <c r="E218" s="881" t="n">
         <v>6</v>
       </c>
-      <c r="F218" s="877" t="n">
+      <c r="F218" s="881" t="n">
         <v>5</v>
       </c>
-      <c r="G218" s="877" t="n">
+      <c r="G218" s="881" t="n">
         <v>5</v>
       </c>
-      <c r="H218" s="877" t="n">
+      <c r="H218" s="881" t="n">
         <v>5</v>
       </c>
       <c r="I218" s="35" t="n"/>
       <c r="J218" s="35" t="n"/>
-      <c r="K218" s="877" t="n">
+      <c r="K218" s="881" t="n">
         <v>5</v>
       </c>
       <c r="L218" s="778" t="n"/>
@@ -27413,7 +27424,7 @@
       <c r="AF218" s="27" t="n"/>
       <c r="AG218" s="778" t="n"/>
       <c r="AH218" s="778" t="n"/>
-      <c r="AL218" s="887" t="inlineStr">
+      <c r="AL218" s="890" t="inlineStr">
         <is>
           <t>IMPE0110 MF0063 MASSATGES ESTÈTIC MANUAL I MECÀNIC · LEIRE · COPILOT tarda 15:00-21:00 · 01/02–08/03 · 152 h</t>
         </is>
@@ -27542,7 +27553,7 @@
     <row r="222" ht="15.75" customHeight="1" s="757" thickTop="1"/>
     <row r="223"/>
     <row r="224" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A224" s="850" t="inlineStr">
+      <c r="A224" s="854" t="inlineStr">
         <is>
           <t>ABRIL 2027</t>
         </is>
@@ -27701,74 +27712,86 @@
       </c>
       <c r="B226" s="11" t="n"/>
       <c r="C226" s="11" t="n"/>
-      <c r="D226" s="832" t="n">
+      <c r="D226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="E226" s="832" t="n">
+      <c r="E226" s="834" t="n">
         <v>6</v>
       </c>
       <c r="F226" s="24" t="n"/>
       <c r="G226" s="24" t="n"/>
-      <c r="H226" s="832" t="n">
+      <c r="H226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="I226" s="832" t="n">
+      <c r="I226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="J226" s="832" t="n">
+      <c r="J226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="K226" s="832" t="n">
+      <c r="K226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="L226" s="832" t="n">
+      <c r="L226" s="834" t="n">
         <v>6</v>
       </c>
       <c r="M226" s="779" t="n"/>
       <c r="N226" s="779" t="n"/>
-      <c r="O226" s="832" t="n">
+      <c r="O226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="P226" s="832" t="n">
+      <c r="P226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="Q226" s="832" t="n">
+      <c r="Q226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="R226" s="832" t="n">
+      <c r="R226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="S226" s="832" t="n">
+      <c r="S226" s="834" t="n">
         <v>6</v>
       </c>
       <c r="T226" s="779" t="n"/>
       <c r="U226" s="779" t="n"/>
-      <c r="V226" s="832" t="n">
+      <c r="V226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="W226" s="832" t="n">
+      <c r="W226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="X226" s="832" t="n">
+      <c r="X226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="Y226" s="832" t="n">
+      <c r="Y226" s="834" t="n">
         <v>6</v>
       </c>
-      <c r="Z226" s="756" t="n"/>
+      <c r="Z226" s="834" t="n">
+        <v>6</v>
+      </c>
       <c r="AA226" s="779" t="n"/>
       <c r="AB226" s="779" t="n"/>
-      <c r="AC226" s="756" t="n"/>
-      <c r="AD226" s="756" t="n"/>
-      <c r="AE226" s="756" t="n"/>
-      <c r="AF226" s="756" t="n"/>
-      <c r="AG226" s="756" t="n"/>
+      <c r="AC226" s="834" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD226" s="834" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE226" s="834" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF226" s="834" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG226" s="834" t="n">
+        <v>6</v>
+      </c>
       <c r="AH226" s="756" t="n"/>
       <c r="AI226" s="4" t="n"/>
       <c r="AK226" s="627" t="n"/>
-      <c r="AL226" s="833" t="inlineStr">
-        <is>
-          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 30/10–22/04 · 678 h</t>
+      <c r="AL226" s="851" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 10/11–03/05 · 678 h</t>
         </is>
       </c>
     </row>
@@ -27791,27 +27814,27 @@
       <c r="L227" s="756" t="n"/>
       <c r="M227" s="779" t="n"/>
       <c r="N227" s="779" t="n"/>
-      <c r="O227" s="868" t="n">
+      <c r="O227" s="872" t="n">
         <v>6</v>
       </c>
-      <c r="P227" s="869" t="n">
+      <c r="P227" s="873" t="n">
         <v>6</v>
       </c>
-      <c r="Q227" s="869" t="n">
+      <c r="Q227" s="873" t="n">
         <v>6</v>
       </c>
-      <c r="R227" s="869" t="n">
+      <c r="R227" s="873" t="n">
         <v>6</v>
       </c>
-      <c r="S227" s="869" t="n">
+      <c r="S227" s="873" t="n">
         <v>6</v>
       </c>
       <c r="T227" s="779" t="n"/>
       <c r="U227" s="779" t="n"/>
-      <c r="V227" s="869" t="n">
+      <c r="V227" s="873" t="n">
         <v>5</v>
       </c>
-      <c r="W227" s="869" t="n">
+      <c r="W227" s="873" t="n">
         <v>5</v>
       </c>
       <c r="X227" s="756" t="n"/>
@@ -27827,7 +27850,7 @@
       <c r="AH227" s="756" t="n"/>
       <c r="AI227" s="4" t="n"/>
       <c r="AK227" s="774" t="n"/>
-      <c r="AL227" s="871" t="inlineStr">
+      <c r="AL227" s="875" t="inlineStr">
         <is>
           <t>FCOI16 Creació de continguts digitals i programació (ACTIC Nivell intermedi) (2a ed.) · MARIA · FIREFOX matí 9:00-15:00 · 12/04–20/04 · 40 h</t>
         </is>
@@ -27841,90 +27864,90 @@
       </c>
       <c r="B228" s="15" t="n"/>
       <c r="C228" s="15" t="n"/>
-      <c r="D228" s="883" t="n">
+      <c r="D228" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="E228" s="883" t="n">
+      <c r="E228" s="887" t="n">
         <v>6</v>
       </c>
       <c r="F228" s="35" t="n"/>
       <c r="G228" s="35" t="n"/>
-      <c r="H228" s="883" t="n">
+      <c r="H228" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="I228" s="883" t="n">
+      <c r="I228" s="887" t="n">
         <v>6</v>
       </c>
-      <c r="J228" s="888" t="n">
+      <c r="J228" s="891" t="n">
         <v>6</v>
       </c>
-      <c r="K228" s="889" t="n">
+      <c r="K228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="L228" s="889" t="n">
+      <c r="L228" s="892" t="n">
         <v>6</v>
       </c>
       <c r="M228" s="780" t="n"/>
       <c r="N228" s="780" t="n"/>
-      <c r="O228" s="889" t="n">
+      <c r="O228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="P228" s="889" t="n">
+      <c r="P228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="Q228" s="889" t="n">
+      <c r="Q228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="R228" s="889" t="n">
+      <c r="R228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="S228" s="889" t="n">
+      <c r="S228" s="892" t="n">
         <v>6</v>
       </c>
       <c r="T228" s="780" t="n"/>
       <c r="U228" s="780" t="n"/>
-      <c r="V228" s="889" t="n">
+      <c r="V228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="W228" s="889" t="n">
+      <c r="W228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="X228" s="889" t="n">
+      <c r="X228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="Y228" s="889" t="n">
+      <c r="Y228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="Z228" s="889" t="n">
+      <c r="Z228" s="892" t="n">
         <v>6</v>
       </c>
       <c r="AA228" s="780" t="n"/>
       <c r="AB228" s="780" t="n"/>
-      <c r="AC228" s="889" t="n">
+      <c r="AC228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="AD228" s="889" t="n">
+      <c r="AD228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="AE228" s="889" t="n">
+      <c r="AE228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="AF228" s="889" t="n">
+      <c r="AF228" s="892" t="n">
         <v>6</v>
       </c>
-      <c r="AG228" s="889" t="n">
+      <c r="AG228" s="892" t="n">
         <v>6</v>
       </c>
       <c r="AH228" s="778" t="n"/>
       <c r="AI228" s="4" t="n"/>
       <c r="AJ228" s="428" t="n"/>
       <c r="AK228" s="775" t="n"/>
-      <c r="AL228" s="890" t="inlineStr">
+      <c r="AL228" s="893" t="inlineStr">
         <is>
           <t>IMPE0110 MF0790 DRENATGE LIMFÀTIC ESTÈTIC MANUAL I MECÀNIC · LEIRE · COPILOT matí 9:00-15:00 · 09/03–06/04 · 114 h</t>
         </is>
       </c>
-      <c r="AU228" s="827" t="inlineStr">
+      <c r="AU228" s="828" t="inlineStr">
         <is>
           <t>IMPE110 MF0791 MASSATGES ESTÈTICS AMB TÈCNIQUES PER PRESSIÓ · LEIRE · COPILOT matí 9:00-15:00 · 07/04–03/05 · 114 h</t>
         </is>
@@ -28034,7 +28057,7 @@
       <c r="AF230" s="756" t="n"/>
       <c r="AG230" s="756" t="n"/>
       <c r="AH230" s="756" t="n"/>
-      <c r="AL230" s="844" t="inlineStr">
+      <c r="AL230" s="847" t="inlineStr">
         <is>
           <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS] · PER ASSIGNAR · FIREFOX tarda 15:00-21:00 · 26/10–16/04 · 678 h</t>
         </is>
@@ -28204,7 +28227,7 @@
     <row r="236"/>
     <row r="237"/>
     <row r="238" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A238" s="850" t="inlineStr">
+      <c r="A238" s="854" t="inlineStr">
         <is>
           <t>MAIG 2027</t>
         </is>
@@ -28367,67 +28390,90 @@
       <c r="C240" s="11" t="n"/>
       <c r="D240" s="26" t="n"/>
       <c r="E240" s="779" t="n"/>
-      <c r="F240" s="851" t="n">
-        <v>5</v>
-      </c>
-      <c r="G240" s="852" t="n">
-        <v>5</v>
-      </c>
-      <c r="H240" s="852" t="n">
-        <v>5</v>
-      </c>
-      <c r="I240" s="852" t="n">
-        <v>5</v>
-      </c>
-      <c r="J240" s="852" t="n">
-        <v>5</v>
+      <c r="F240" s="834" t="n">
+        <v>6</v>
+      </c>
+      <c r="G240" s="806" t="n">
+        <v>6</v>
+      </c>
+      <c r="H240" s="807" t="n">
+        <v>6</v>
+      </c>
+      <c r="I240" s="807" t="n">
+        <v>6</v>
+      </c>
+      <c r="J240" s="807" t="n">
+        <v>6</v>
       </c>
       <c r="K240" s="779" t="n"/>
       <c r="L240" s="779" t="n"/>
-      <c r="M240" s="756" t="n"/>
-      <c r="N240" s="756" t="n"/>
-      <c r="O240" s="756" t="n"/>
-      <c r="P240" s="756" t="n"/>
-      <c r="Q240" s="756" t="n"/>
+      <c r="M240" s="807" t="n">
+        <v>6</v>
+      </c>
+      <c r="N240" s="807" t="n">
+        <v>6</v>
+      </c>
+      <c r="O240" s="807" t="n">
+        <v>6</v>
+      </c>
+      <c r="P240" s="807" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q240" s="807" t="n">
+        <v>6</v>
+      </c>
       <c r="R240" s="779" t="n"/>
       <c r="S240" s="779" t="n"/>
-      <c r="T240" s="756" t="n"/>
-      <c r="U240" s="756" t="n"/>
-      <c r="V240" s="756" t="n"/>
-      <c r="W240" s="756" t="n"/>
+      <c r="T240" s="807" t="n">
+        <v>6</v>
+      </c>
+      <c r="U240" s="807" t="n">
+        <v>6</v>
+      </c>
+      <c r="V240" s="807" t="n">
+        <v>5</v>
+      </c>
+      <c r="W240" s="807" t="n">
+        <v>5</v>
+      </c>
       <c r="X240" s="756" t="n"/>
       <c r="Y240" s="779" t="n"/>
       <c r="Z240" s="779" t="n"/>
-      <c r="AA240" s="891" t="n">
+      <c r="AA240" s="894" t="n">
         <v>6</v>
       </c>
-      <c r="AB240" s="892" t="n">
+      <c r="AB240" s="895" t="n">
         <v>6</v>
       </c>
-      <c r="AC240" s="892" t="n">
+      <c r="AC240" s="895" t="n">
         <v>6</v>
       </c>
-      <c r="AD240" s="892" t="n">
+      <c r="AD240" s="895" t="n">
         <v>6</v>
       </c>
-      <c r="AE240" s="892" t="n">
+      <c r="AE240" s="895" t="n">
         <v>6</v>
       </c>
       <c r="AF240" s="779" t="n"/>
       <c r="AG240" s="779" t="n"/>
-      <c r="AH240" s="892" t="n">
+      <c r="AH240" s="895" t="n">
         <v>5</v>
       </c>
       <c r="AI240" s="4" t="n"/>
       <c r="AK240" s="627" t="n"/>
-      <c r="AL240" s="853" t="inlineStr">
-        <is>
-          <t>IFCT117 Introducció a la intel·ligència artificial (2a ed.) · MARIA · GOOGLE matí 9:00-14:00 · 03/05–07/05 · 25 h</t>
-        </is>
-      </c>
-      <c r="AU240" s="893" t="inlineStr">
+      <c r="AL240" s="851" t="inlineStr">
+        <is>
+          <t>ADGG0208 ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS] · PER ASSIGNAR · GOOGLE matí 9:00-15:00 · 10/11–03/05 · 678 h</t>
+        </is>
+      </c>
+      <c r="AU240" s="896" t="inlineStr">
         <is>
           <t>FCOI20 Comunicació i col·laboració amb eines digitals (ACTIC Nivell avançat) · MARIA · GOOGLE matí 9:00-15:00 · 24/05–01/06 · 40 h</t>
+        </is>
+      </c>
+      <c r="BD240" s="813" t="inlineStr">
+        <is>
+          <t>IMPE0110 MF0792 TÈCNIQUES SENSORIALS ESTÈTIQUES · LEIRE · GOOGLE matí 9:00-15:00 · 04/05–20/05 · 76 h</t>
         </is>
       </c>
     </row>
@@ -28441,50 +28487,34 @@
       <c r="C241" s="456" t="n"/>
       <c r="D241" s="218" t="n"/>
       <c r="E241" s="779" t="n"/>
-      <c r="F241" s="756" t="n"/>
-      <c r="G241" s="825" t="n">
-        <v>6</v>
-      </c>
-      <c r="H241" s="826" t="n">
-        <v>6</v>
-      </c>
-      <c r="I241" s="826" t="n">
-        <v>6</v>
-      </c>
-      <c r="J241" s="826" t="n">
-        <v>6</v>
+      <c r="F241" s="855" t="n">
+        <v>5</v>
+      </c>
+      <c r="G241" s="856" t="n">
+        <v>5</v>
+      </c>
+      <c r="H241" s="856" t="n">
+        <v>5</v>
+      </c>
+      <c r="I241" s="856" t="n">
+        <v>5</v>
+      </c>
+      <c r="J241" s="856" t="n">
+        <v>5</v>
       </c>
       <c r="K241" s="779" t="n"/>
       <c r="L241" s="779" t="n"/>
-      <c r="M241" s="826" t="n">
-        <v>6</v>
-      </c>
-      <c r="N241" s="826" t="n">
-        <v>6</v>
-      </c>
-      <c r="O241" s="826" t="n">
-        <v>6</v>
-      </c>
-      <c r="P241" s="826" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q241" s="826" t="n">
-        <v>6</v>
-      </c>
+      <c r="M241" s="756" t="n"/>
+      <c r="N241" s="756" t="n"/>
+      <c r="O241" s="756" t="n"/>
+      <c r="P241" s="756" t="n"/>
+      <c r="Q241" s="756" t="n"/>
       <c r="R241" s="779" t="n"/>
       <c r="S241" s="779" t="n"/>
-      <c r="T241" s="826" t="n">
-        <v>6</v>
-      </c>
-      <c r="U241" s="826" t="n">
-        <v>6</v>
-      </c>
-      <c r="V241" s="826" t="n">
-        <v>5</v>
-      </c>
-      <c r="W241" s="826" t="n">
-        <v>5</v>
-      </c>
+      <c r="T241" s="756" t="n"/>
+      <c r="U241" s="756" t="n"/>
+      <c r="V241" s="756" t="n"/>
+      <c r="W241" s="756" t="n"/>
       <c r="X241" s="756" t="n"/>
       <c r="Y241" s="779" t="n"/>
       <c r="Z241" s="779" t="n"/>
@@ -28498,9 +28528,9 @@
       <c r="AH241" s="756" t="n"/>
       <c r="AI241" s="4" t="n"/>
       <c r="AK241" s="774" t="n"/>
-      <c r="AL241" s="828" t="inlineStr">
-        <is>
-          <t>IMPE0110 MF0792 TÈCNIQUES SENSORIALS ESTÈTIQUES · LEIRE · FIREFOX matí 9:00-15:00 · 04/05–20/05 · 76 h</t>
+      <c r="AL241" s="857" t="inlineStr">
+        <is>
+          <t>IFCT117 Introducció a la intel·ligència artificial (2a ed.) · MARIA · FIREFOX matí 9:00-14:00 · 03/05–07/05 · 25 h</t>
         </is>
       </c>
     </row>
@@ -28514,7 +28544,7 @@
       <c r="C242" s="15" t="n"/>
       <c r="D242" s="596" t="n"/>
       <c r="E242" s="780" t="n"/>
-      <c r="F242" s="889" t="n">
+      <c r="F242" s="892" t="n">
         <v>6</v>
       </c>
       <c r="G242" s="778" t="n"/>
@@ -28548,7 +28578,7 @@
       <c r="AI242" s="4" t="n"/>
       <c r="AJ242" s="428" t="n"/>
       <c r="AK242" s="775" t="n"/>
-      <c r="AL242" s="894" t="inlineStr">
+      <c r="AL242" s="847" t="inlineStr">
         <is>
           <t>IMPE110 MF0791 MASSATGES ESTÈTICS AMB TÈCNIQUES PER PRESSIÓ · LEIRE · COPILOT matí 9:00-15:00 · 07/04–03/05 · 114 h</t>
         </is>
@@ -28798,7 +28828,7 @@
     <row r="249"/>
     <row r="250"/>
     <row r="251" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A251" s="850" t="inlineStr">
+      <c r="A251" s="854" t="inlineStr">
         <is>
           <t>JUNY 2027</t>
         </is>
@@ -28957,7 +28987,7 @@
       </c>
       <c r="B253" s="11" t="n"/>
       <c r="C253" s="11" t="n"/>
-      <c r="D253" s="892" t="n">
+      <c r="D253" s="895" t="n">
         <v>5</v>
       </c>
       <c r="E253" s="756" t="n"/>
@@ -28992,7 +29022,7 @@
       <c r="AH253" s="756" t="n"/>
       <c r="AI253" s="4" t="n"/>
       <c r="AK253" s="627" t="n"/>
-      <c r="AL253" s="895" t="inlineStr">
+      <c r="AL253" s="897" t="inlineStr">
         <is>
           <t>FCOI20 Comunicació i col·laboració amb eines digitals (ACTIC Nivell avançat) · MARIA · GOOGLE matí 9:00-15:00 · 24/05–01/06 · 40 h</t>
         </is>
@@ -29329,7 +29359,7 @@
     <row r="263"/>
     <row r="264"/>
     <row r="265" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A265" s="850" t="inlineStr">
+      <c r="A265" s="854" t="inlineStr">
         <is>
           <t>JULIOL 2027</t>
         </is>
@@ -29856,7 +29886,7 @@
     <row r="277" s="757"/>
     <row r="278"/>
     <row r="279" ht="21.75" customHeight="1" s="757" thickBot="1">
-      <c r="A279" s="850" t="inlineStr">
+      <c r="A279" s="854" t="inlineStr">
         <is>
           <t>AGOST 2027</t>
         </is>
@@ -30422,7 +30452,7 @@
       <c r="AI293" s="500" t="n">
         <v>22</v>
       </c>
-      <c r="AK293" s="896" t="inlineStr">
+      <c r="AK293" s="898" t="inlineStr">
         <is>
           <t>Festius: 11/09 Diada Nacional de Catalunya (Autonòmic)</t>
         </is>
@@ -30548,29 +30578,29 @@
       <c r="D295" s="756" t="n"/>
       <c r="E295" s="756" t="n"/>
       <c r="F295" s="756" t="n"/>
-      <c r="G295" s="897" t="n"/>
-      <c r="H295" s="897" t="n"/>
+      <c r="G295" s="899" t="n"/>
+      <c r="H295" s="899" t="n"/>
       <c r="I295" s="756" t="n"/>
       <c r="J295" s="756" t="n"/>
       <c r="K295" s="756" t="n"/>
       <c r="L295" s="756" t="n"/>
       <c r="M295" s="756" t="n"/>
-      <c r="N295" s="898" t="n"/>
-      <c r="O295" s="897" t="n"/>
+      <c r="N295" s="900" t="n"/>
+      <c r="O295" s="899" t="n"/>
       <c r="P295" s="756" t="n"/>
       <c r="Q295" s="756" t="n"/>
       <c r="R295" s="756" t="n"/>
       <c r="S295" s="756" t="n"/>
       <c r="T295" s="756" t="n"/>
-      <c r="U295" s="897" t="n"/>
-      <c r="V295" s="897" t="n"/>
+      <c r="U295" s="899" t="n"/>
+      <c r="V295" s="899" t="n"/>
       <c r="W295" s="756" t="n"/>
       <c r="X295" s="756" t="n"/>
       <c r="Y295" s="756" t="n"/>
       <c r="Z295" s="756" t="n"/>
       <c r="AA295" s="756" t="n"/>
-      <c r="AB295" s="897" t="n"/>
-      <c r="AC295" s="897" t="n"/>
+      <c r="AB295" s="899" t="n"/>
+      <c r="AC295" s="899" t="n"/>
       <c r="AD295" s="756" t="n"/>
       <c r="AE295" s="756" t="n"/>
       <c r="AF295" s="756" t="n"/>
@@ -30589,29 +30619,29 @@
       <c r="D296" s="782" t="n"/>
       <c r="E296" s="756" t="n"/>
       <c r="F296" s="756" t="n"/>
-      <c r="G296" s="897" t="n"/>
-      <c r="H296" s="897" t="n"/>
+      <c r="G296" s="899" t="n"/>
+      <c r="H296" s="899" t="n"/>
       <c r="I296" s="756" t="n"/>
       <c r="J296" s="756" t="n"/>
       <c r="K296" s="756" t="n"/>
       <c r="L296" s="756" t="n"/>
       <c r="M296" s="756" t="n"/>
-      <c r="N296" s="898" t="n"/>
-      <c r="O296" s="897" t="n"/>
+      <c r="N296" s="900" t="n"/>
+      <c r="O296" s="899" t="n"/>
       <c r="P296" s="756" t="n"/>
       <c r="Q296" s="756" t="n"/>
       <c r="R296" s="756" t="n"/>
       <c r="S296" s="756" t="n"/>
       <c r="T296" s="756" t="n"/>
-      <c r="U296" s="897" t="n"/>
-      <c r="V296" s="897" t="n"/>
+      <c r="U296" s="899" t="n"/>
+      <c r="V296" s="899" t="n"/>
       <c r="W296" s="756" t="n"/>
       <c r="X296" s="756" t="n"/>
       <c r="Y296" s="756" t="n"/>
       <c r="Z296" s="756" t="n"/>
       <c r="AA296" s="756" t="n"/>
-      <c r="AB296" s="897" t="n"/>
-      <c r="AC296" s="897" t="n"/>
+      <c r="AB296" s="899" t="n"/>
+      <c r="AC296" s="899" t="n"/>
       <c r="AD296" s="756" t="n"/>
       <c r="AE296" s="756" t="n"/>
       <c r="AF296" s="756" t="n"/>
@@ -30630,29 +30660,29 @@
       <c r="D297" s="783" t="n"/>
       <c r="E297" s="778" t="n"/>
       <c r="F297" s="778" t="n"/>
-      <c r="G297" s="899" t="n"/>
-      <c r="H297" s="899" t="n"/>
+      <c r="G297" s="901" t="n"/>
+      <c r="H297" s="901" t="n"/>
       <c r="I297" s="778" t="n"/>
       <c r="J297" s="778" t="n"/>
       <c r="K297" s="778" t="n"/>
       <c r="L297" s="778" t="n"/>
       <c r="M297" s="778" t="n"/>
-      <c r="N297" s="900" t="n"/>
-      <c r="O297" s="899" t="n"/>
+      <c r="N297" s="902" t="n"/>
+      <c r="O297" s="901" t="n"/>
       <c r="P297" s="778" t="n"/>
       <c r="Q297" s="778" t="n"/>
       <c r="R297" s="778" t="n"/>
       <c r="S297" s="778" t="n"/>
       <c r="T297" s="778" t="n"/>
-      <c r="U297" s="899" t="n"/>
-      <c r="V297" s="899" t="n"/>
+      <c r="U297" s="901" t="n"/>
+      <c r="V297" s="901" t="n"/>
       <c r="W297" s="778" t="n"/>
       <c r="X297" s="778" t="n"/>
       <c r="Y297" s="778" t="n"/>
       <c r="Z297" s="778" t="n"/>
       <c r="AA297" s="778" t="n"/>
-      <c r="AB297" s="899" t="n"/>
-      <c r="AC297" s="899" t="n"/>
+      <c r="AB297" s="901" t="n"/>
+      <c r="AC297" s="901" t="n"/>
       <c r="AD297" s="778" t="n"/>
       <c r="AE297" s="778" t="n"/>
       <c r="AF297" s="778" t="n"/>
@@ -30671,29 +30701,29 @@
       <c r="D298" s="755" t="n"/>
       <c r="E298" s="756" t="n"/>
       <c r="F298" s="756" t="n"/>
-      <c r="G298" s="897" t="n"/>
-      <c r="H298" s="897" t="n"/>
+      <c r="G298" s="899" t="n"/>
+      <c r="H298" s="899" t="n"/>
       <c r="I298" s="756" t="n"/>
       <c r="J298" s="756" t="n"/>
       <c r="K298" s="756" t="n"/>
       <c r="L298" s="756" t="n"/>
       <c r="M298" s="756" t="n"/>
-      <c r="N298" s="898" t="n"/>
-      <c r="O298" s="897" t="n"/>
+      <c r="N298" s="900" t="n"/>
+      <c r="O298" s="899" t="n"/>
       <c r="P298" s="756" t="n"/>
       <c r="Q298" s="756" t="n"/>
       <c r="R298" s="756" t="n"/>
       <c r="S298" s="756" t="n"/>
       <c r="T298" s="756" t="n"/>
-      <c r="U298" s="897" t="n"/>
-      <c r="V298" s="897" t="n"/>
+      <c r="U298" s="899" t="n"/>
+      <c r="V298" s="899" t="n"/>
       <c r="W298" s="756" t="n"/>
       <c r="X298" s="756" t="n"/>
       <c r="Y298" s="756" t="n"/>
       <c r="Z298" s="756" t="n"/>
       <c r="AA298" s="756" t="n"/>
-      <c r="AB298" s="897" t="n"/>
-      <c r="AC298" s="897" t="n"/>
+      <c r="AB298" s="899" t="n"/>
+      <c r="AC298" s="899" t="n"/>
       <c r="AD298" s="756" t="n"/>
       <c r="AE298" s="756" t="n"/>
       <c r="AF298" s="756" t="n"/>
@@ -30712,29 +30742,29 @@
       <c r="D299" s="756" t="n"/>
       <c r="E299" s="756" t="n"/>
       <c r="F299" s="756" t="n"/>
-      <c r="G299" s="897" t="n"/>
-      <c r="H299" s="897" t="n"/>
+      <c r="G299" s="899" t="n"/>
+      <c r="H299" s="899" t="n"/>
       <c r="I299" s="756" t="n"/>
       <c r="J299" s="756" t="n"/>
       <c r="K299" s="756" t="n"/>
       <c r="L299" s="756" t="n"/>
       <c r="M299" s="756" t="n"/>
-      <c r="N299" s="898" t="n"/>
-      <c r="O299" s="897" t="n"/>
+      <c r="N299" s="900" t="n"/>
+      <c r="O299" s="899" t="n"/>
       <c r="P299" s="756" t="n"/>
       <c r="Q299" s="756" t="n"/>
       <c r="R299" s="756" t="n"/>
       <c r="S299" s="756" t="n"/>
       <c r="T299" s="756" t="n"/>
-      <c r="U299" s="897" t="n"/>
-      <c r="V299" s="897" t="n"/>
+      <c r="U299" s="899" t="n"/>
+      <c r="V299" s="899" t="n"/>
       <c r="W299" s="756" t="n"/>
       <c r="X299" s="756" t="n"/>
       <c r="Y299" s="756" t="n"/>
       <c r="Z299" s="756" t="n"/>
       <c r="AA299" s="756" t="n"/>
-      <c r="AB299" s="897" t="n"/>
-      <c r="AC299" s="897" t="n"/>
+      <c r="AB299" s="899" t="n"/>
+      <c r="AC299" s="899" t="n"/>
       <c r="AD299" s="756" t="n"/>
       <c r="AE299" s="756" t="n"/>
       <c r="AF299" s="756" t="n"/>
@@ -30752,29 +30782,29 @@
       <c r="D300" s="783" t="n"/>
       <c r="E300" s="778" t="n"/>
       <c r="F300" s="778" t="n"/>
-      <c r="G300" s="899" t="n"/>
-      <c r="H300" s="899" t="n"/>
+      <c r="G300" s="901" t="n"/>
+      <c r="H300" s="901" t="n"/>
       <c r="I300" s="778" t="n"/>
       <c r="J300" s="778" t="n"/>
       <c r="K300" s="778" t="n"/>
       <c r="L300" s="778" t="n"/>
       <c r="M300" s="778" t="n"/>
-      <c r="N300" s="900" t="n"/>
-      <c r="O300" s="899" t="n"/>
+      <c r="N300" s="902" t="n"/>
+      <c r="O300" s="901" t="n"/>
       <c r="P300" s="778" t="n"/>
       <c r="Q300" s="778" t="n"/>
       <c r="R300" s="778" t="n"/>
       <c r="S300" s="778" t="n"/>
       <c r="T300" s="778" t="n"/>
-      <c r="U300" s="899" t="n"/>
-      <c r="V300" s="899" t="n"/>
+      <c r="U300" s="901" t="n"/>
+      <c r="V300" s="901" t="n"/>
       <c r="W300" s="778" t="n"/>
       <c r="X300" s="778" t="n"/>
       <c r="Y300" s="778" t="n"/>
       <c r="Z300" s="778" t="n"/>
       <c r="AA300" s="778" t="n"/>
-      <c r="AB300" s="899" t="n"/>
-      <c r="AC300" s="899" t="n"/>
+      <c r="AB300" s="901" t="n"/>
+      <c r="AC300" s="901" t="n"/>
       <c r="AD300" s="778" t="n"/>
       <c r="AE300" s="778" t="n"/>
       <c r="AF300" s="778" t="n"/>
@@ -30792,29 +30822,29 @@
       <c r="D301" s="755" t="n"/>
       <c r="E301" s="755" t="n"/>
       <c r="F301" s="756" t="n"/>
-      <c r="G301" s="901" t="n"/>
-      <c r="H301" s="897" t="n"/>
+      <c r="G301" s="903" t="n"/>
+      <c r="H301" s="899" t="n"/>
       <c r="I301" s="755" t="n"/>
       <c r="J301" s="756" t="n"/>
       <c r="K301" s="755" t="n"/>
       <c r="L301" s="756" t="n"/>
       <c r="M301" s="756" t="n"/>
-      <c r="N301" s="902" t="n"/>
-      <c r="O301" s="901" t="n"/>
+      <c r="N301" s="904" t="n"/>
+      <c r="O301" s="903" t="n"/>
       <c r="P301" s="756" t="n"/>
       <c r="Q301" s="756" t="n"/>
       <c r="R301" s="755" t="n"/>
       <c r="S301" s="756" t="n"/>
       <c r="T301" s="756" t="n"/>
-      <c r="U301" s="901" t="n"/>
-      <c r="V301" s="901" t="n"/>
+      <c r="U301" s="903" t="n"/>
+      <c r="V301" s="903" t="n"/>
       <c r="W301" s="756" t="n"/>
       <c r="X301" s="756" t="n"/>
       <c r="Y301" s="755" t="n"/>
       <c r="Z301" s="756" t="n"/>
       <c r="AA301" s="756" t="n"/>
-      <c r="AB301" s="901" t="n"/>
-      <c r="AC301" s="901" t="n"/>
+      <c r="AB301" s="903" t="n"/>
+      <c r="AC301" s="903" t="n"/>
       <c r="AD301" s="756" t="n"/>
       <c r="AE301" s="756" t="n"/>
       <c r="AF301" s="755" t="n"/>
@@ -30832,29 +30862,29 @@
       <c r="D302" s="756" t="n"/>
       <c r="E302" s="756" t="n"/>
       <c r="F302" s="756" t="n"/>
-      <c r="G302" s="897" t="n"/>
-      <c r="H302" s="897" t="n"/>
+      <c r="G302" s="899" t="n"/>
+      <c r="H302" s="899" t="n"/>
       <c r="I302" s="756" t="n"/>
       <c r="J302" s="756" t="n"/>
       <c r="K302" s="756" t="n"/>
       <c r="L302" s="756" t="n"/>
       <c r="M302" s="756" t="n"/>
-      <c r="N302" s="898" t="n"/>
-      <c r="O302" s="897" t="n"/>
+      <c r="N302" s="900" t="n"/>
+      <c r="O302" s="899" t="n"/>
       <c r="P302" s="756" t="n"/>
       <c r="Q302" s="756" t="n"/>
       <c r="R302" s="756" t="n"/>
       <c r="S302" s="756" t="n"/>
       <c r="T302" s="756" t="n"/>
-      <c r="U302" s="897" t="n"/>
-      <c r="V302" s="897" t="n"/>
+      <c r="U302" s="899" t="n"/>
+      <c r="V302" s="899" t="n"/>
       <c r="W302" s="756" t="n"/>
       <c r="X302" s="756" t="n"/>
       <c r="Y302" s="756" t="n"/>
       <c r="Z302" s="756" t="n"/>
       <c r="AA302" s="756" t="n"/>
-      <c r="AB302" s="897" t="n"/>
-      <c r="AC302" s="897" t="n"/>
+      <c r="AB302" s="899" t="n"/>
+      <c r="AC302" s="899" t="n"/>
       <c r="AD302" s="756" t="n"/>
       <c r="AE302" s="756" t="n"/>
       <c r="AF302" s="756" t="n"/>
@@ -30872,29 +30902,29 @@
       <c r="D303" s="756" t="n"/>
       <c r="E303" s="756" t="n"/>
       <c r="F303" s="756" t="n"/>
-      <c r="G303" s="897" t="n"/>
-      <c r="H303" s="897" t="n"/>
+      <c r="G303" s="899" t="n"/>
+      <c r="H303" s="899" t="n"/>
       <c r="I303" s="756" t="n"/>
       <c r="J303" s="756" t="n"/>
       <c r="K303" s="756" t="n"/>
       <c r="L303" s="756" t="n"/>
       <c r="M303" s="756" t="n"/>
-      <c r="N303" s="898" t="n"/>
-      <c r="O303" s="897" t="n"/>
+      <c r="N303" s="900" t="n"/>
+      <c r="O303" s="899" t="n"/>
       <c r="P303" s="756" t="n"/>
       <c r="Q303" s="756" t="n"/>
       <c r="R303" s="756" t="n"/>
       <c r="S303" s="756" t="n"/>
       <c r="T303" s="756" t="n"/>
-      <c r="U303" s="897" t="n"/>
-      <c r="V303" s="897" t="n"/>
+      <c r="U303" s="899" t="n"/>
+      <c r="V303" s="899" t="n"/>
       <c r="W303" s="756" t="n"/>
       <c r="X303" s="756" t="n"/>
       <c r="Y303" s="756" t="n"/>
       <c r="Z303" s="756" t="n"/>
       <c r="AA303" s="756" t="n"/>
-      <c r="AB303" s="897" t="n"/>
-      <c r="AC303" s="897" t="n"/>
+      <c r="AB303" s="899" t="n"/>
+      <c r="AC303" s="899" t="n"/>
       <c r="AD303" s="756" t="n"/>
       <c r="AE303" s="756" t="n"/>
       <c r="AF303" s="756" t="n"/>
@@ -30945,7 +30975,7 @@
       <c r="AI306" s="500" t="n">
         <v>20</v>
       </c>
-      <c r="AK306" s="896" t="inlineStr">
+      <c r="AK306" s="898" t="inlineStr">
         <is>
           <t>Festius: 12/10 Festa Nacional d'Espanya (Nacional)</t>
         </is>
@@ -31071,36 +31101,36 @@
       <c r="B308" s="11" t="n"/>
       <c r="C308" s="11" t="n"/>
       <c r="D308" s="756" t="n"/>
-      <c r="E308" s="897" t="n"/>
-      <c r="F308" s="897" t="n"/>
+      <c r="E308" s="899" t="n"/>
+      <c r="F308" s="899" t="n"/>
       <c r="G308" s="756" t="n"/>
       <c r="H308" s="756" t="n"/>
       <c r="I308" s="756" t="n"/>
       <c r="J308" s="756" t="n"/>
       <c r="K308" s="756" t="n"/>
-      <c r="L308" s="897" t="n"/>
-      <c r="M308" s="897" t="n"/>
+      <c r="L308" s="899" t="n"/>
+      <c r="M308" s="899" t="n"/>
       <c r="N308" s="756" t="n"/>
-      <c r="O308" s="898" t="n"/>
+      <c r="O308" s="900" t="n"/>
       <c r="P308" s="756" t="n"/>
       <c r="Q308" s="756" t="n"/>
       <c r="R308" s="756" t="n"/>
-      <c r="S308" s="897" t="n"/>
-      <c r="T308" s="897" t="n"/>
+      <c r="S308" s="899" t="n"/>
+      <c r="T308" s="899" t="n"/>
       <c r="U308" s="756" t="n"/>
       <c r="V308" s="756" t="n"/>
       <c r="W308" s="756" t="n"/>
       <c r="X308" s="756" t="n"/>
       <c r="Y308" s="756" t="n"/>
-      <c r="Z308" s="897" t="n"/>
-      <c r="AA308" s="897" t="n"/>
+      <c r="Z308" s="899" t="n"/>
+      <c r="AA308" s="899" t="n"/>
       <c r="AB308" s="756" t="n"/>
       <c r="AC308" s="756" t="n"/>
       <c r="AD308" s="756" t="n"/>
       <c r="AE308" s="756" t="n"/>
       <c r="AF308" s="756" t="n"/>
-      <c r="AG308" s="897" t="n"/>
-      <c r="AH308" s="897" t="n"/>
+      <c r="AG308" s="899" t="n"/>
+      <c r="AH308" s="899" t="n"/>
       <c r="AI308" s="4" t="n"/>
     </row>
     <row r="309" ht="15.75" customHeight="1" s="757">
@@ -31112,36 +31142,36 @@
       <c r="B309" s="456" t="n"/>
       <c r="C309" s="456" t="n"/>
       <c r="D309" s="782" t="n"/>
-      <c r="E309" s="897" t="n"/>
-      <c r="F309" s="897" t="n"/>
+      <c r="E309" s="899" t="n"/>
+      <c r="F309" s="899" t="n"/>
       <c r="G309" s="756" t="n"/>
       <c r="H309" s="756" t="n"/>
       <c r="I309" s="756" t="n"/>
       <c r="J309" s="756" t="n"/>
       <c r="K309" s="756" t="n"/>
-      <c r="L309" s="897" t="n"/>
-      <c r="M309" s="897" t="n"/>
+      <c r="L309" s="899" t="n"/>
+      <c r="M309" s="899" t="n"/>
       <c r="N309" s="756" t="n"/>
-      <c r="O309" s="898" t="n"/>
+      <c r="O309" s="900" t="n"/>
       <c r="P309" s="756" t="n"/>
       <c r="Q309" s="756" t="n"/>
       <c r="R309" s="756" t="n"/>
-      <c r="S309" s="897" t="n"/>
-      <c r="T309" s="897" t="n"/>
+      <c r="S309" s="899" t="n"/>
+      <c r="T309" s="899" t="n"/>
       <c r="U309" s="756" t="n"/>
       <c r="V309" s="756" t="n"/>
       <c r="W309" s="756" t="n"/>
       <c r="X309" s="756" t="n"/>
       <c r="Y309" s="756" t="n"/>
-      <c r="Z309" s="897" t="n"/>
-      <c r="AA309" s="897" t="n"/>
+      <c r="Z309" s="899" t="n"/>
+      <c r="AA309" s="899" t="n"/>
       <c r="AB309" s="756" t="n"/>
       <c r="AC309" s="756" t="n"/>
       <c r="AD309" s="756" t="n"/>
       <c r="AE309" s="756" t="n"/>
       <c r="AF309" s="756" t="n"/>
-      <c r="AG309" s="897" t="n"/>
-      <c r="AH309" s="897" t="n"/>
+      <c r="AG309" s="899" t="n"/>
+      <c r="AH309" s="899" t="n"/>
       <c r="AI309" s="4" t="n"/>
     </row>
     <row r="310" ht="19.5" customHeight="1" s="757">
@@ -31153,36 +31183,36 @@
       <c r="B310" s="15" t="n"/>
       <c r="C310" s="15" t="n"/>
       <c r="D310" s="783" t="n"/>
-      <c r="E310" s="899" t="n"/>
-      <c r="F310" s="899" t="n"/>
+      <c r="E310" s="901" t="n"/>
+      <c r="F310" s="901" t="n"/>
       <c r="G310" s="778" t="n"/>
       <c r="H310" s="778" t="n"/>
       <c r="I310" s="778" t="n"/>
       <c r="J310" s="778" t="n"/>
       <c r="K310" s="778" t="n"/>
-      <c r="L310" s="899" t="n"/>
-      <c r="M310" s="899" t="n"/>
+      <c r="L310" s="901" t="n"/>
+      <c r="M310" s="901" t="n"/>
       <c r="N310" s="778" t="n"/>
-      <c r="O310" s="900" t="n"/>
+      <c r="O310" s="902" t="n"/>
       <c r="P310" s="778" t="n"/>
       <c r="Q310" s="778" t="n"/>
       <c r="R310" s="778" t="n"/>
-      <c r="S310" s="899" t="n"/>
-      <c r="T310" s="899" t="n"/>
+      <c r="S310" s="901" t="n"/>
+      <c r="T310" s="901" t="n"/>
       <c r="U310" s="778" t="n"/>
       <c r="V310" s="778" t="n"/>
       <c r="W310" s="778" t="n"/>
       <c r="X310" s="778" t="n"/>
       <c r="Y310" s="778" t="n"/>
-      <c r="Z310" s="899" t="n"/>
-      <c r="AA310" s="899" t="n"/>
+      <c r="Z310" s="901" t="n"/>
+      <c r="AA310" s="901" t="n"/>
       <c r="AB310" s="778" t="n"/>
       <c r="AC310" s="778" t="n"/>
       <c r="AD310" s="778" t="n"/>
       <c r="AE310" s="778" t="n"/>
       <c r="AF310" s="778" t="n"/>
-      <c r="AG310" s="899" t="n"/>
-      <c r="AH310" s="899" t="n"/>
+      <c r="AG310" s="901" t="n"/>
+      <c r="AH310" s="901" t="n"/>
       <c r="AI310" s="4" t="n"/>
     </row>
     <row r="311" ht="16.5" customHeight="1" s="757">
@@ -31194,36 +31224,36 @@
       <c r="B311" s="18" t="n"/>
       <c r="C311" s="18" t="n"/>
       <c r="D311" s="755" t="n"/>
-      <c r="E311" s="897" t="n"/>
-      <c r="F311" s="897" t="n"/>
+      <c r="E311" s="899" t="n"/>
+      <c r="F311" s="899" t="n"/>
       <c r="G311" s="756" t="n"/>
       <c r="H311" s="756" t="n"/>
       <c r="I311" s="756" t="n"/>
       <c r="J311" s="756" t="n"/>
       <c r="K311" s="756" t="n"/>
-      <c r="L311" s="897" t="n"/>
-      <c r="M311" s="897" t="n"/>
+      <c r="L311" s="899" t="n"/>
+      <c r="M311" s="899" t="n"/>
       <c r="N311" s="756" t="n"/>
-      <c r="O311" s="898" t="n"/>
+      <c r="O311" s="900" t="n"/>
       <c r="P311" s="756" t="n"/>
       <c r="Q311" s="756" t="n"/>
       <c r="R311" s="756" t="n"/>
-      <c r="S311" s="897" t="n"/>
-      <c r="T311" s="897" t="n"/>
+      <c r="S311" s="899" t="n"/>
+      <c r="T311" s="899" t="n"/>
       <c r="U311" s="756" t="n"/>
       <c r="V311" s="756" t="n"/>
       <c r="W311" s="756" t="n"/>
       <c r="X311" s="756" t="n"/>
       <c r="Y311" s="756" t="n"/>
-      <c r="Z311" s="897" t="n"/>
-      <c r="AA311" s="897" t="n"/>
+      <c r="Z311" s="899" t="n"/>
+      <c r="AA311" s="899" t="n"/>
       <c r="AB311" s="756" t="n"/>
       <c r="AC311" s="756" t="n"/>
       <c r="AD311" s="756" t="n"/>
       <c r="AE311" s="756" t="n"/>
       <c r="AF311" s="756" t="n"/>
-      <c r="AG311" s="897" t="n"/>
-      <c r="AH311" s="897" t="n"/>
+      <c r="AG311" s="899" t="n"/>
+      <c r="AH311" s="899" t="n"/>
       <c r="AI311" s="4" t="n"/>
     </row>
     <row r="312" ht="15.75" customHeight="1" s="757">
@@ -31235,36 +31265,36 @@
       <c r="B312" s="11" t="n"/>
       <c r="C312" s="11" t="n"/>
       <c r="D312" s="756" t="n"/>
-      <c r="E312" s="897" t="n"/>
-      <c r="F312" s="897" t="n"/>
+      <c r="E312" s="899" t="n"/>
+      <c r="F312" s="899" t="n"/>
       <c r="G312" s="756" t="n"/>
       <c r="H312" s="756" t="n"/>
       <c r="I312" s="756" t="n"/>
       <c r="J312" s="756" t="n"/>
       <c r="K312" s="756" t="n"/>
-      <c r="L312" s="897" t="n"/>
-      <c r="M312" s="897" t="n"/>
+      <c r="L312" s="899" t="n"/>
+      <c r="M312" s="899" t="n"/>
       <c r="N312" s="756" t="n"/>
-      <c r="O312" s="898" t="n"/>
+      <c r="O312" s="900" t="n"/>
       <c r="P312" s="756" t="n"/>
       <c r="Q312" s="756" t="n"/>
       <c r="R312" s="756" t="n"/>
-      <c r="S312" s="897" t="n"/>
-      <c r="T312" s="897" t="n"/>
+      <c r="S312" s="899" t="n"/>
+      <c r="T312" s="899" t="n"/>
       <c r="U312" s="756" t="n"/>
       <c r="V312" s="756" t="n"/>
       <c r="W312" s="756" t="n"/>
       <c r="X312" s="756" t="n"/>
       <c r="Y312" s="756" t="n"/>
-      <c r="Z312" s="897" t="n"/>
-      <c r="AA312" s="897" t="n"/>
+      <c r="Z312" s="899" t="n"/>
+      <c r="AA312" s="899" t="n"/>
       <c r="AB312" s="756" t="n"/>
       <c r="AC312" s="756" t="n"/>
       <c r="AD312" s="756" t="n"/>
       <c r="AE312" s="756" t="n"/>
       <c r="AF312" s="756" t="n"/>
-      <c r="AG312" s="897" t="n"/>
-      <c r="AH312" s="897" t="n"/>
+      <c r="AG312" s="899" t="n"/>
+      <c r="AH312" s="899" t="n"/>
     </row>
     <row r="313" ht="16.5" customHeight="1" s="757">
       <c r="A313" s="14" t="inlineStr">
@@ -31275,36 +31305,36 @@
       <c r="B313" s="15" t="n"/>
       <c r="C313" s="15" t="n"/>
       <c r="D313" s="783" t="n"/>
-      <c r="E313" s="899" t="n"/>
-      <c r="F313" s="899" t="n"/>
+      <c r="E313" s="901" t="n"/>
+      <c r="F313" s="901" t="n"/>
       <c r="G313" s="778" t="n"/>
       <c r="H313" s="778" t="n"/>
       <c r="I313" s="778" t="n"/>
       <c r="J313" s="778" t="n"/>
       <c r="K313" s="778" t="n"/>
-      <c r="L313" s="899" t="n"/>
-      <c r="M313" s="899" t="n"/>
+      <c r="L313" s="901" t="n"/>
+      <c r="M313" s="901" t="n"/>
       <c r="N313" s="778" t="n"/>
-      <c r="O313" s="900" t="n"/>
+      <c r="O313" s="902" t="n"/>
       <c r="P313" s="778" t="n"/>
       <c r="Q313" s="778" t="n"/>
       <c r="R313" s="778" t="n"/>
-      <c r="S313" s="899" t="n"/>
-      <c r="T313" s="899" t="n"/>
+      <c r="S313" s="901" t="n"/>
+      <c r="T313" s="901" t="n"/>
       <c r="U313" s="778" t="n"/>
       <c r="V313" s="778" t="n"/>
       <c r="W313" s="778" t="n"/>
       <c r="X313" s="778" t="n"/>
       <c r="Y313" s="778" t="n"/>
-      <c r="Z313" s="899" t="n"/>
-      <c r="AA313" s="899" t="n"/>
+      <c r="Z313" s="901" t="n"/>
+      <c r="AA313" s="901" t="n"/>
       <c r="AB313" s="778" t="n"/>
       <c r="AC313" s="778" t="n"/>
       <c r="AD313" s="778" t="n"/>
       <c r="AE313" s="778" t="n"/>
       <c r="AF313" s="778" t="n"/>
-      <c r="AG313" s="899" t="n"/>
-      <c r="AH313" s="899" t="n"/>
+      <c r="AG313" s="901" t="n"/>
+      <c r="AH313" s="901" t="n"/>
     </row>
     <row r="314" ht="16.5" customHeight="1" s="757">
       <c r="A314" s="10" t="inlineStr">
@@ -31315,36 +31345,36 @@
       <c r="B314" s="11" t="n"/>
       <c r="C314" s="11" t="n"/>
       <c r="D314" s="755" t="n"/>
-      <c r="E314" s="901" t="n"/>
-      <c r="F314" s="897" t="n"/>
+      <c r="E314" s="903" t="n"/>
+      <c r="F314" s="899" t="n"/>
       <c r="G314" s="755" t="n"/>
       <c r="H314" s="756" t="n"/>
       <c r="I314" s="755" t="n"/>
       <c r="J314" s="756" t="n"/>
       <c r="K314" s="755" t="n"/>
-      <c r="L314" s="897" t="n"/>
-      <c r="M314" s="897" t="n"/>
+      <c r="L314" s="899" t="n"/>
+      <c r="M314" s="899" t="n"/>
       <c r="N314" s="755" t="n"/>
-      <c r="O314" s="902" t="n"/>
+      <c r="O314" s="904" t="n"/>
       <c r="P314" s="756" t="n"/>
       <c r="Q314" s="756" t="n"/>
       <c r="R314" s="755" t="n"/>
-      <c r="S314" s="897" t="n"/>
-      <c r="T314" s="897" t="n"/>
+      <c r="S314" s="899" t="n"/>
+      <c r="T314" s="899" t="n"/>
       <c r="U314" s="755" t="n"/>
       <c r="V314" s="755" t="n"/>
       <c r="W314" s="756" t="n"/>
       <c r="X314" s="756" t="n"/>
       <c r="Y314" s="755" t="n"/>
-      <c r="Z314" s="897" t="n"/>
-      <c r="AA314" s="897" t="n"/>
+      <c r="Z314" s="899" t="n"/>
+      <c r="AA314" s="899" t="n"/>
       <c r="AB314" s="755" t="n"/>
       <c r="AC314" s="755" t="n"/>
       <c r="AD314" s="756" t="n"/>
       <c r="AE314" s="756" t="n"/>
       <c r="AF314" s="755" t="n"/>
-      <c r="AG314" s="897" t="n"/>
-      <c r="AH314" s="897" t="n"/>
+      <c r="AG314" s="899" t="n"/>
+      <c r="AH314" s="899" t="n"/>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="757">
       <c r="A315" s="12" t="inlineStr">
@@ -31355,36 +31385,36 @@
       <c r="B315" s="11" t="n"/>
       <c r="C315" s="11" t="n"/>
       <c r="D315" s="756" t="n"/>
-      <c r="E315" s="897" t="n"/>
-      <c r="F315" s="897" t="n"/>
+      <c r="E315" s="899" t="n"/>
+      <c r="F315" s="899" t="n"/>
       <c r="G315" s="756" t="n"/>
       <c r="H315" s="756" t="n"/>
       <c r="I315" s="756" t="n"/>
       <c r="J315" s="756" t="n"/>
       <c r="K315" s="756" t="n"/>
-      <c r="L315" s="897" t="n"/>
-      <c r="M315" s="897" t="n"/>
+      <c r="L315" s="899" t="n"/>
+      <c r="M315" s="899" t="n"/>
       <c r="N315" s="756" t="n"/>
-      <c r="O315" s="898" t="n"/>
+      <c r="O315" s="900" t="n"/>
       <c r="P315" s="756" t="n"/>
       <c r="Q315" s="756" t="n"/>
       <c r="R315" s="756" t="n"/>
-      <c r="S315" s="897" t="n"/>
-      <c r="T315" s="897" t="n"/>
+      <c r="S315" s="899" t="n"/>
+      <c r="T315" s="899" t="n"/>
       <c r="U315" s="756" t="n"/>
       <c r="V315" s="756" t="n"/>
       <c r="W315" s="756" t="n"/>
       <c r="X315" s="756" t="n"/>
       <c r="Y315" s="756" t="n"/>
-      <c r="Z315" s="897" t="n"/>
-      <c r="AA315" s="897" t="n"/>
+      <c r="Z315" s="899" t="n"/>
+      <c r="AA315" s="899" t="n"/>
       <c r="AB315" s="756" t="n"/>
       <c r="AC315" s="756" t="n"/>
       <c r="AD315" s="756" t="n"/>
       <c r="AE315" s="756" t="n"/>
       <c r="AF315" s="756" t="n"/>
-      <c r="AG315" s="897" t="n"/>
-      <c r="AH315" s="897" t="n"/>
+      <c r="AG315" s="899" t="n"/>
+      <c r="AH315" s="899" t="n"/>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="757">
       <c r="A316" s="12" t="inlineStr">
@@ -31395,36 +31425,36 @@
       <c r="B316" s="11" t="n"/>
       <c r="C316" s="11" t="n"/>
       <c r="D316" s="756" t="n"/>
-      <c r="E316" s="897" t="n"/>
-      <c r="F316" s="897" t="n"/>
+      <c r="E316" s="899" t="n"/>
+      <c r="F316" s="899" t="n"/>
       <c r="G316" s="756" t="n"/>
       <c r="H316" s="756" t="n"/>
       <c r="I316" s="756" t="n"/>
       <c r="J316" s="756" t="n"/>
       <c r="K316" s="756" t="n"/>
-      <c r="L316" s="897" t="n"/>
-      <c r="M316" s="897" t="n"/>
+      <c r="L316" s="899" t="n"/>
+      <c r="M316" s="899" t="n"/>
       <c r="N316" s="756" t="n"/>
-      <c r="O316" s="898" t="n"/>
+      <c r="O316" s="900" t="n"/>
       <c r="P316" s="756" t="n"/>
       <c r="Q316" s="756" t="n"/>
       <c r="R316" s="756" t="n"/>
-      <c r="S316" s="897" t="n"/>
-      <c r="T316" s="897" t="n"/>
+      <c r="S316" s="899" t="n"/>
+      <c r="T316" s="899" t="n"/>
       <c r="U316" s="756" t="n"/>
       <c r="V316" s="756" t="n"/>
       <c r="W316" s="756" t="n"/>
       <c r="X316" s="756" t="n"/>
       <c r="Y316" s="756" t="n"/>
-      <c r="Z316" s="897" t="n"/>
-      <c r="AA316" s="897" t="n"/>
+      <c r="Z316" s="899" t="n"/>
+      <c r="AA316" s="899" t="n"/>
       <c r="AB316" s="756" t="n"/>
       <c r="AC316" s="756" t="n"/>
       <c r="AD316" s="756" t="n"/>
       <c r="AE316" s="756" t="n"/>
       <c r="AF316" s="756" t="n"/>
-      <c r="AG316" s="897" t="n"/>
-      <c r="AH316" s="897" t="n"/>
+      <c r="AG316" s="899" t="n"/>
+      <c r="AH316" s="899" t="n"/>
     </row>
     <row r="317" s="757"/>
     <row r="318" s="757"/>
@@ -31470,7 +31500,7 @@
       <c r="AI319" s="500" t="n">
         <v>21</v>
       </c>
-      <c r="AK319" s="896" t="inlineStr">
+      <c r="AK319" s="898" t="inlineStr">
         <is>
           <t>Festius: 01/11 Tots Sants (Nacional)</t>
         </is>
@@ -31593,34 +31623,34 @@
       </c>
       <c r="B321" s="11" t="n"/>
       <c r="C321" s="11" t="n"/>
-      <c r="D321" s="898" t="n"/>
+      <c r="D321" s="900" t="n"/>
       <c r="E321" s="756" t="n"/>
       <c r="F321" s="756" t="n"/>
       <c r="G321" s="756" t="n"/>
       <c r="H321" s="756" t="n"/>
-      <c r="I321" s="897" t="n"/>
-      <c r="J321" s="897" t="n"/>
+      <c r="I321" s="899" t="n"/>
+      <c r="J321" s="899" t="n"/>
       <c r="K321" s="756" t="n"/>
       <c r="L321" s="756" t="n"/>
       <c r="M321" s="756" t="n"/>
       <c r="N321" s="756" t="n"/>
       <c r="O321" s="756" t="n"/>
-      <c r="P321" s="897" t="n"/>
-      <c r="Q321" s="897" t="n"/>
+      <c r="P321" s="899" t="n"/>
+      <c r="Q321" s="899" t="n"/>
       <c r="R321" s="756" t="n"/>
       <c r="S321" s="756" t="n"/>
       <c r="T321" s="756" t="n"/>
       <c r="U321" s="756" t="n"/>
       <c r="V321" s="756" t="n"/>
-      <c r="W321" s="897" t="n"/>
-      <c r="X321" s="897" t="n"/>
+      <c r="W321" s="899" t="n"/>
+      <c r="X321" s="899" t="n"/>
       <c r="Y321" s="756" t="n"/>
       <c r="Z321" s="756" t="n"/>
       <c r="AA321" s="756" t="n"/>
       <c r="AB321" s="756" t="n"/>
       <c r="AC321" s="756" t="n"/>
-      <c r="AD321" s="897" t="n"/>
-      <c r="AE321" s="897" t="n"/>
+      <c r="AD321" s="899" t="n"/>
+      <c r="AE321" s="899" t="n"/>
       <c r="AF321" s="756" t="n"/>
       <c r="AG321" s="756" t="n"/>
       <c r="AH321" s="756" t="n"/>
@@ -31634,34 +31664,34 @@
       </c>
       <c r="B322" s="456" t="n"/>
       <c r="C322" s="456" t="n"/>
-      <c r="D322" s="903" t="n"/>
+      <c r="D322" s="905" t="n"/>
       <c r="E322" s="756" t="n"/>
       <c r="F322" s="756" t="n"/>
       <c r="G322" s="756" t="n"/>
       <c r="H322" s="756" t="n"/>
-      <c r="I322" s="897" t="n"/>
-      <c r="J322" s="897" t="n"/>
+      <c r="I322" s="899" t="n"/>
+      <c r="J322" s="899" t="n"/>
       <c r="K322" s="756" t="n"/>
       <c r="L322" s="756" t="n"/>
       <c r="M322" s="756" t="n"/>
       <c r="N322" s="756" t="n"/>
       <c r="O322" s="756" t="n"/>
-      <c r="P322" s="897" t="n"/>
-      <c r="Q322" s="897" t="n"/>
+      <c r="P322" s="899" t="n"/>
+      <c r="Q322" s="899" t="n"/>
       <c r="R322" s="756" t="n"/>
       <c r="S322" s="756" t="n"/>
       <c r="T322" s="756" t="n"/>
       <c r="U322" s="756" t="n"/>
       <c r="V322" s="756" t="n"/>
-      <c r="W322" s="897" t="n"/>
-      <c r="X322" s="897" t="n"/>
+      <c r="W322" s="899" t="n"/>
+      <c r="X322" s="899" t="n"/>
       <c r="Y322" s="756" t="n"/>
       <c r="Z322" s="756" t="n"/>
       <c r="AA322" s="756" t="n"/>
       <c r="AB322" s="756" t="n"/>
       <c r="AC322" s="756" t="n"/>
-      <c r="AD322" s="897" t="n"/>
-      <c r="AE322" s="897" t="n"/>
+      <c r="AD322" s="899" t="n"/>
+      <c r="AE322" s="899" t="n"/>
       <c r="AF322" s="756" t="n"/>
       <c r="AG322" s="756" t="n"/>
       <c r="AH322" s="756" t="n"/>
@@ -31675,34 +31705,34 @@
       </c>
       <c r="B323" s="15" t="n"/>
       <c r="C323" s="15" t="n"/>
-      <c r="D323" s="904" t="n"/>
+      <c r="D323" s="906" t="n"/>
       <c r="E323" s="778" t="n"/>
       <c r="F323" s="778" t="n"/>
       <c r="G323" s="778" t="n"/>
       <c r="H323" s="778" t="n"/>
-      <c r="I323" s="899" t="n"/>
-      <c r="J323" s="899" t="n"/>
+      <c r="I323" s="901" t="n"/>
+      <c r="J323" s="901" t="n"/>
       <c r="K323" s="778" t="n"/>
       <c r="L323" s="778" t="n"/>
       <c r="M323" s="778" t="n"/>
       <c r="N323" s="778" t="n"/>
       <c r="O323" s="778" t="n"/>
-      <c r="P323" s="899" t="n"/>
-      <c r="Q323" s="899" t="n"/>
+      <c r="P323" s="901" t="n"/>
+      <c r="Q323" s="901" t="n"/>
       <c r="R323" s="778" t="n"/>
       <c r="S323" s="778" t="n"/>
       <c r="T323" s="778" t="n"/>
       <c r="U323" s="778" t="n"/>
       <c r="V323" s="778" t="n"/>
-      <c r="W323" s="899" t="n"/>
-      <c r="X323" s="899" t="n"/>
+      <c r="W323" s="901" t="n"/>
+      <c r="X323" s="901" t="n"/>
       <c r="Y323" s="778" t="n"/>
       <c r="Z323" s="778" t="n"/>
       <c r="AA323" s="778" t="n"/>
       <c r="AB323" s="778" t="n"/>
       <c r="AC323" s="778" t="n"/>
-      <c r="AD323" s="899" t="n"/>
-      <c r="AE323" s="899" t="n"/>
+      <c r="AD323" s="901" t="n"/>
+      <c r="AE323" s="901" t="n"/>
       <c r="AF323" s="778" t="n"/>
       <c r="AG323" s="778" t="n"/>
       <c r="AH323" s="778" t="n"/>
@@ -31716,34 +31746,34 @@
       </c>
       <c r="B324" s="18" t="n"/>
       <c r="C324" s="18" t="n"/>
-      <c r="D324" s="902" t="n"/>
+      <c r="D324" s="904" t="n"/>
       <c r="E324" s="756" t="n"/>
       <c r="F324" s="756" t="n"/>
       <c r="G324" s="756" t="n"/>
       <c r="H324" s="756" t="n"/>
-      <c r="I324" s="897" t="n"/>
-      <c r="J324" s="897" t="n"/>
+      <c r="I324" s="899" t="n"/>
+      <c r="J324" s="899" t="n"/>
       <c r="K324" s="756" t="n"/>
       <c r="L324" s="756" t="n"/>
       <c r="M324" s="756" t="n"/>
       <c r="N324" s="756" t="n"/>
       <c r="O324" s="756" t="n"/>
-      <c r="P324" s="897" t="n"/>
-      <c r="Q324" s="897" t="n"/>
+      <c r="P324" s="899" t="n"/>
+      <c r="Q324" s="899" t="n"/>
       <c r="R324" s="756" t="n"/>
       <c r="S324" s="756" t="n"/>
       <c r="T324" s="756" t="n"/>
       <c r="U324" s="756" t="n"/>
       <c r="V324" s="756" t="n"/>
-      <c r="W324" s="897" t="n"/>
-      <c r="X324" s="897" t="n"/>
+      <c r="W324" s="899" t="n"/>
+      <c r="X324" s="899" t="n"/>
       <c r="Y324" s="756" t="n"/>
       <c r="Z324" s="756" t="n"/>
       <c r="AA324" s="756" t="n"/>
       <c r="AB324" s="756" t="n"/>
       <c r="AC324" s="756" t="n"/>
-      <c r="AD324" s="897" t="n"/>
-      <c r="AE324" s="897" t="n"/>
+      <c r="AD324" s="899" t="n"/>
+      <c r="AE324" s="899" t="n"/>
       <c r="AF324" s="756" t="n"/>
       <c r="AG324" s="756" t="n"/>
       <c r="AH324" s="756" t="n"/>
@@ -31757,34 +31787,34 @@
       </c>
       <c r="B325" s="11" t="n"/>
       <c r="C325" s="11" t="n"/>
-      <c r="D325" s="898" t="n"/>
+      <c r="D325" s="900" t="n"/>
       <c r="E325" s="756" t="n"/>
       <c r="F325" s="756" t="n"/>
       <c r="G325" s="756" t="n"/>
       <c r="H325" s="756" t="n"/>
-      <c r="I325" s="897" t="n"/>
-      <c r="J325" s="897" t="n"/>
+      <c r="I325" s="899" t="n"/>
+      <c r="J325" s="899" t="n"/>
       <c r="K325" s="756" t="n"/>
       <c r="L325" s="756" t="n"/>
       <c r="M325" s="756" t="n"/>
       <c r="N325" s="756" t="n"/>
       <c r="O325" s="756" t="n"/>
-      <c r="P325" s="897" t="n"/>
-      <c r="Q325" s="897" t="n"/>
+      <c r="P325" s="899" t="n"/>
+      <c r="Q325" s="899" t="n"/>
       <c r="R325" s="756" t="n"/>
       <c r="S325" s="756" t="n"/>
       <c r="T325" s="756" t="n"/>
       <c r="U325" s="756" t="n"/>
       <c r="V325" s="756" t="n"/>
-      <c r="W325" s="897" t="n"/>
-      <c r="X325" s="897" t="n"/>
+      <c r="W325" s="899" t="n"/>
+      <c r="X325" s="899" t="n"/>
       <c r="Y325" s="756" t="n"/>
       <c r="Z325" s="756" t="n"/>
       <c r="AA325" s="756" t="n"/>
       <c r="AB325" s="756" t="n"/>
       <c r="AC325" s="756" t="n"/>
-      <c r="AD325" s="897" t="n"/>
-      <c r="AE325" s="897" t="n"/>
+      <c r="AD325" s="899" t="n"/>
+      <c r="AE325" s="899" t="n"/>
       <c r="AF325" s="756" t="n"/>
       <c r="AG325" s="756" t="n"/>
       <c r="AH325" s="756" t="n"/>
@@ -31797,34 +31827,34 @@
       </c>
       <c r="B326" s="15" t="n"/>
       <c r="C326" s="15" t="n"/>
-      <c r="D326" s="904" t="n"/>
+      <c r="D326" s="906" t="n"/>
       <c r="E326" s="778" t="n"/>
       <c r="F326" s="778" t="n"/>
       <c r="G326" s="778" t="n"/>
       <c r="H326" s="778" t="n"/>
-      <c r="I326" s="899" t="n"/>
-      <c r="J326" s="899" t="n"/>
+      <c r="I326" s="901" t="n"/>
+      <c r="J326" s="901" t="n"/>
       <c r="K326" s="778" t="n"/>
       <c r="L326" s="778" t="n"/>
       <c r="M326" s="778" t="n"/>
       <c r="N326" s="778" t="n"/>
       <c r="O326" s="778" t="n"/>
-      <c r="P326" s="899" t="n"/>
-      <c r="Q326" s="899" t="n"/>
+      <c r="P326" s="901" t="n"/>
+      <c r="Q326" s="901" t="n"/>
       <c r="R326" s="778" t="n"/>
       <c r="S326" s="778" t="n"/>
       <c r="T326" s="778" t="n"/>
       <c r="U326" s="778" t="n"/>
       <c r="V326" s="778" t="n"/>
-      <c r="W326" s="899" t="n"/>
-      <c r="X326" s="899" t="n"/>
+      <c r="W326" s="901" t="n"/>
+      <c r="X326" s="901" t="n"/>
       <c r="Y326" s="778" t="n"/>
       <c r="Z326" s="778" t="n"/>
       <c r="AA326" s="778" t="n"/>
       <c r="AB326" s="778" t="n"/>
       <c r="AC326" s="778" t="n"/>
-      <c r="AD326" s="899" t="n"/>
-      <c r="AE326" s="899" t="n"/>
+      <c r="AD326" s="901" t="n"/>
+      <c r="AE326" s="901" t="n"/>
       <c r="AF326" s="778" t="n"/>
       <c r="AG326" s="778" t="n"/>
       <c r="AH326" s="778" t="n"/>
@@ -31837,34 +31867,34 @@
       </c>
       <c r="B327" s="11" t="n"/>
       <c r="C327" s="11" t="n"/>
-      <c r="D327" s="902" t="n"/>
+      <c r="D327" s="904" t="n"/>
       <c r="E327" s="755" t="n"/>
       <c r="F327" s="756" t="n"/>
       <c r="G327" s="755" t="n"/>
       <c r="H327" s="756" t="n"/>
-      <c r="I327" s="901" t="n"/>
-      <c r="J327" s="897" t="n"/>
+      <c r="I327" s="903" t="n"/>
+      <c r="J327" s="899" t="n"/>
       <c r="K327" s="755" t="n"/>
       <c r="L327" s="756" t="n"/>
       <c r="M327" s="756" t="n"/>
       <c r="N327" s="755" t="n"/>
       <c r="O327" s="755" t="n"/>
-      <c r="P327" s="897" t="n"/>
-      <c r="Q327" s="897" t="n"/>
+      <c r="P327" s="899" t="n"/>
+      <c r="Q327" s="899" t="n"/>
       <c r="R327" s="755" t="n"/>
       <c r="S327" s="756" t="n"/>
       <c r="T327" s="756" t="n"/>
       <c r="U327" s="755" t="n"/>
       <c r="V327" s="755" t="n"/>
-      <c r="W327" s="897" t="n"/>
-      <c r="X327" s="897" t="n"/>
+      <c r="W327" s="899" t="n"/>
+      <c r="X327" s="899" t="n"/>
       <c r="Y327" s="755" t="n"/>
       <c r="Z327" s="756" t="n"/>
       <c r="AA327" s="756" t="n"/>
       <c r="AB327" s="755" t="n"/>
       <c r="AC327" s="755" t="n"/>
-      <c r="AD327" s="897" t="n"/>
-      <c r="AE327" s="897" t="n"/>
+      <c r="AD327" s="899" t="n"/>
+      <c r="AE327" s="899" t="n"/>
       <c r="AF327" s="755" t="n"/>
       <c r="AG327" s="756" t="n"/>
       <c r="AH327" s="756" t="n"/>
@@ -31877,34 +31907,34 @@
       </c>
       <c r="B328" s="11" t="n"/>
       <c r="C328" s="11" t="n"/>
-      <c r="D328" s="898" t="n"/>
+      <c r="D328" s="900" t="n"/>
       <c r="E328" s="756" t="n"/>
       <c r="F328" s="756" t="n"/>
       <c r="G328" s="756" t="n"/>
       <c r="H328" s="756" t="n"/>
-      <c r="I328" s="897" t="n"/>
-      <c r="J328" s="897" t="n"/>
+      <c r="I328" s="899" t="n"/>
+      <c r="J328" s="899" t="n"/>
       <c r="K328" s="756" t="n"/>
       <c r="L328" s="756" t="n"/>
       <c r="M328" s="756" t="n"/>
       <c r="N328" s="756" t="n"/>
       <c r="O328" s="756" t="n"/>
-      <c r="P328" s="897" t="n"/>
-      <c r="Q328" s="897" t="n"/>
+      <c r="P328" s="899" t="n"/>
+      <c r="Q328" s="899" t="n"/>
       <c r="R328" s="756" t="n"/>
       <c r="S328" s="756" t="n"/>
       <c r="T328" s="756" t="n"/>
       <c r="U328" s="756" t="n"/>
       <c r="V328" s="756" t="n"/>
-      <c r="W328" s="897" t="n"/>
-      <c r="X328" s="897" t="n"/>
+      <c r="W328" s="899" t="n"/>
+      <c r="X328" s="899" t="n"/>
       <c r="Y328" s="756" t="n"/>
       <c r="Z328" s="756" t="n"/>
       <c r="AA328" s="756" t="n"/>
       <c r="AB328" s="756" t="n"/>
       <c r="AC328" s="756" t="n"/>
-      <c r="AD328" s="897" t="n"/>
-      <c r="AE328" s="897" t="n"/>
+      <c r="AD328" s="899" t="n"/>
+      <c r="AE328" s="899" t="n"/>
       <c r="AF328" s="756" t="n"/>
       <c r="AG328" s="756" t="n"/>
       <c r="AH328" s="756" t="n"/>
@@ -31917,34 +31947,34 @@
       </c>
       <c r="B329" s="11" t="n"/>
       <c r="C329" s="11" t="n"/>
-      <c r="D329" s="898" t="n"/>
+      <c r="D329" s="900" t="n"/>
       <c r="E329" s="756" t="n"/>
       <c r="F329" s="756" t="n"/>
       <c r="G329" s="756" t="n"/>
       <c r="H329" s="756" t="n"/>
-      <c r="I329" s="897" t="n"/>
-      <c r="J329" s="897" t="n"/>
+      <c r="I329" s="899" t="n"/>
+      <c r="J329" s="899" t="n"/>
       <c r="K329" s="756" t="n"/>
       <c r="L329" s="756" t="n"/>
       <c r="M329" s="756" t="n"/>
       <c r="N329" s="756" t="n"/>
       <c r="O329" s="756" t="n"/>
-      <c r="P329" s="897" t="n"/>
-      <c r="Q329" s="897" t="n"/>
+      <c r="P329" s="899" t="n"/>
+      <c r="Q329" s="899" t="n"/>
       <c r="R329" s="756" t="n"/>
       <c r="S329" s="756" t="n"/>
       <c r="T329" s="756" t="n"/>
       <c r="U329" s="756" t="n"/>
       <c r="V329" s="756" t="n"/>
-      <c r="W329" s="897" t="n"/>
-      <c r="X329" s="897" t="n"/>
+      <c r="W329" s="899" t="n"/>
+      <c r="X329" s="899" t="n"/>
       <c r="Y329" s="756" t="n"/>
       <c r="Z329" s="756" t="n"/>
       <c r="AA329" s="756" t="n"/>
       <c r="AB329" s="756" t="n"/>
       <c r="AC329" s="756" t="n"/>
-      <c r="AD329" s="897" t="n"/>
-      <c r="AE329" s="897" t="n"/>
+      <c r="AD329" s="899" t="n"/>
+      <c r="AE329" s="899" t="n"/>
       <c r="AF329" s="756" t="n"/>
       <c r="AG329" s="756" t="n"/>
       <c r="AH329" s="756" t="n"/>
@@ -31993,7 +32023,7 @@
       <c r="AI332" s="500" t="n">
         <v>13</v>
       </c>
-      <c r="AK332" s="896" t="inlineStr">
+      <c r="AK332" s="898" t="inlineStr">
         <is>
           <t>Festius: 06/12 Dia de la Constitució (Nacional) · 07/12 Festiu local (canvi pel 15/09) · 08/12 Immaculada Concepció (Nacional) · 25/12 Nadal (Nacional) · Vacances: 23/12–31/12</t>
         </is>
@@ -32121,34 +32151,34 @@
       <c r="D334" s="756" t="n"/>
       <c r="E334" s="756" t="n"/>
       <c r="F334" s="756" t="n"/>
-      <c r="G334" s="897" t="n"/>
-      <c r="H334" s="897" t="n"/>
-      <c r="I334" s="898" t="n"/>
-      <c r="J334" s="898" t="n"/>
-      <c r="K334" s="898" t="n"/>
+      <c r="G334" s="899" t="n"/>
+      <c r="H334" s="899" t="n"/>
+      <c r="I334" s="900" t="n"/>
+      <c r="J334" s="900" t="n"/>
+      <c r="K334" s="900" t="n"/>
       <c r="L334" s="756" t="n"/>
       <c r="M334" s="756" t="n"/>
-      <c r="N334" s="897" t="n"/>
-      <c r="O334" s="897" t="n"/>
+      <c r="N334" s="899" t="n"/>
+      <c r="O334" s="899" t="n"/>
       <c r="P334" s="756" t="n"/>
       <c r="Q334" s="756" t="n"/>
       <c r="R334" s="756" t="n"/>
       <c r="S334" s="756" t="n"/>
       <c r="T334" s="756" t="n"/>
-      <c r="U334" s="897" t="n"/>
-      <c r="V334" s="897" t="n"/>
+      <c r="U334" s="899" t="n"/>
+      <c r="V334" s="899" t="n"/>
       <c r="W334" s="756" t="n"/>
       <c r="X334" s="756" t="n"/>
       <c r="Y334" s="756" t="n"/>
-      <c r="Z334" s="905" t="n"/>
-      <c r="AA334" s="905" t="n"/>
-      <c r="AB334" s="898" t="n"/>
-      <c r="AC334" s="897" t="n"/>
-      <c r="AD334" s="905" t="n"/>
-      <c r="AE334" s="905" t="n"/>
-      <c r="AF334" s="905" t="n"/>
-      <c r="AG334" s="905" t="n"/>
-      <c r="AH334" s="905" t="n"/>
+      <c r="Z334" s="907" t="n"/>
+      <c r="AA334" s="907" t="n"/>
+      <c r="AB334" s="900" t="n"/>
+      <c r="AC334" s="899" t="n"/>
+      <c r="AD334" s="907" t="n"/>
+      <c r="AE334" s="907" t="n"/>
+      <c r="AF334" s="907" t="n"/>
+      <c r="AG334" s="907" t="n"/>
+      <c r="AH334" s="907" t="n"/>
       <c r="AI334" s="4" t="n"/>
     </row>
     <row r="335" ht="15.75" customHeight="1" s="757">
@@ -32162,34 +32192,34 @@
       <c r="D335" s="782" t="n"/>
       <c r="E335" s="756" t="n"/>
       <c r="F335" s="756" t="n"/>
-      <c r="G335" s="897" t="n"/>
-      <c r="H335" s="897" t="n"/>
-      <c r="I335" s="898" t="n"/>
-      <c r="J335" s="898" t="n"/>
-      <c r="K335" s="898" t="n"/>
+      <c r="G335" s="899" t="n"/>
+      <c r="H335" s="899" t="n"/>
+      <c r="I335" s="900" t="n"/>
+      <c r="J335" s="900" t="n"/>
+      <c r="K335" s="900" t="n"/>
       <c r="L335" s="756" t="n"/>
       <c r="M335" s="756" t="n"/>
-      <c r="N335" s="897" t="n"/>
-      <c r="O335" s="897" t="n"/>
+      <c r="N335" s="899" t="n"/>
+      <c r="O335" s="899" t="n"/>
       <c r="P335" s="756" t="n"/>
       <c r="Q335" s="756" t="n"/>
       <c r="R335" s="756" t="n"/>
       <c r="S335" s="756" t="n"/>
       <c r="T335" s="756" t="n"/>
-      <c r="U335" s="897" t="n"/>
-      <c r="V335" s="897" t="n"/>
+      <c r="U335" s="899" t="n"/>
+      <c r="V335" s="899" t="n"/>
       <c r="W335" s="756" t="n"/>
       <c r="X335" s="756" t="n"/>
       <c r="Y335" s="756" t="n"/>
-      <c r="Z335" s="905" t="n"/>
-      <c r="AA335" s="905" t="n"/>
-      <c r="AB335" s="898" t="n"/>
-      <c r="AC335" s="897" t="n"/>
-      <c r="AD335" s="905" t="n"/>
-      <c r="AE335" s="905" t="n"/>
-      <c r="AF335" s="905" t="n"/>
-      <c r="AG335" s="905" t="n"/>
-      <c r="AH335" s="905" t="n"/>
+      <c r="Z335" s="907" t="n"/>
+      <c r="AA335" s="907" t="n"/>
+      <c r="AB335" s="900" t="n"/>
+      <c r="AC335" s="899" t="n"/>
+      <c r="AD335" s="907" t="n"/>
+      <c r="AE335" s="907" t="n"/>
+      <c r="AF335" s="907" t="n"/>
+      <c r="AG335" s="907" t="n"/>
+      <c r="AH335" s="907" t="n"/>
       <c r="AI335" s="4" t="n"/>
     </row>
     <row r="336" ht="19.5" customHeight="1" s="757">
@@ -32203,34 +32233,34 @@
       <c r="D336" s="783" t="n"/>
       <c r="E336" s="778" t="n"/>
       <c r="F336" s="778" t="n"/>
-      <c r="G336" s="899" t="n"/>
-      <c r="H336" s="899" t="n"/>
-      <c r="I336" s="900" t="n"/>
-      <c r="J336" s="900" t="n"/>
-      <c r="K336" s="900" t="n"/>
+      <c r="G336" s="901" t="n"/>
+      <c r="H336" s="901" t="n"/>
+      <c r="I336" s="902" t="n"/>
+      <c r="J336" s="902" t="n"/>
+      <c r="K336" s="902" t="n"/>
       <c r="L336" s="778" t="n"/>
       <c r="M336" s="778" t="n"/>
-      <c r="N336" s="899" t="n"/>
-      <c r="O336" s="899" t="n"/>
+      <c r="N336" s="901" t="n"/>
+      <c r="O336" s="901" t="n"/>
       <c r="P336" s="778" t="n"/>
       <c r="Q336" s="778" t="n"/>
       <c r="R336" s="778" t="n"/>
       <c r="S336" s="778" t="n"/>
       <c r="T336" s="778" t="n"/>
-      <c r="U336" s="899" t="n"/>
-      <c r="V336" s="899" t="n"/>
+      <c r="U336" s="901" t="n"/>
+      <c r="V336" s="901" t="n"/>
       <c r="W336" s="778" t="n"/>
       <c r="X336" s="778" t="n"/>
       <c r="Y336" s="778" t="n"/>
-      <c r="Z336" s="906" t="n"/>
-      <c r="AA336" s="906" t="n"/>
-      <c r="AB336" s="900" t="n"/>
-      <c r="AC336" s="899" t="n"/>
-      <c r="AD336" s="906" t="n"/>
-      <c r="AE336" s="906" t="n"/>
-      <c r="AF336" s="906" t="n"/>
-      <c r="AG336" s="906" t="n"/>
-      <c r="AH336" s="906" t="n"/>
+      <c r="Z336" s="908" t="n"/>
+      <c r="AA336" s="908" t="n"/>
+      <c r="AB336" s="902" t="n"/>
+      <c r="AC336" s="901" t="n"/>
+      <c r="AD336" s="908" t="n"/>
+      <c r="AE336" s="908" t="n"/>
+      <c r="AF336" s="908" t="n"/>
+      <c r="AG336" s="908" t="n"/>
+      <c r="AH336" s="908" t="n"/>
       <c r="AI336" s="4" t="n"/>
     </row>
     <row r="337" ht="16.5" customHeight="1" s="757">
@@ -32244,34 +32274,34 @@
       <c r="D337" s="755" t="n"/>
       <c r="E337" s="756" t="n"/>
       <c r="F337" s="756" t="n"/>
-      <c r="G337" s="897" t="n"/>
-      <c r="H337" s="897" t="n"/>
-      <c r="I337" s="898" t="n"/>
-      <c r="J337" s="898" t="n"/>
-      <c r="K337" s="898" t="n"/>
+      <c r="G337" s="899" t="n"/>
+      <c r="H337" s="899" t="n"/>
+      <c r="I337" s="900" t="n"/>
+      <c r="J337" s="900" t="n"/>
+      <c r="K337" s="900" t="n"/>
       <c r="L337" s="756" t="n"/>
       <c r="M337" s="756" t="n"/>
-      <c r="N337" s="897" t="n"/>
-      <c r="O337" s="897" t="n"/>
+      <c r="N337" s="899" t="n"/>
+      <c r="O337" s="899" t="n"/>
       <c r="P337" s="756" t="n"/>
       <c r="Q337" s="756" t="n"/>
       <c r="R337" s="756" t="n"/>
       <c r="S337" s="756" t="n"/>
       <c r="T337" s="756" t="n"/>
-      <c r="U337" s="897" t="n"/>
-      <c r="V337" s="897" t="n"/>
+      <c r="U337" s="899" t="n"/>
+      <c r="V337" s="899" t="n"/>
       <c r="W337" s="756" t="n"/>
       <c r="X337" s="756" t="n"/>
       <c r="Y337" s="756" t="n"/>
-      <c r="Z337" s="905" t="n"/>
-      <c r="AA337" s="905" t="n"/>
-      <c r="AB337" s="898" t="n"/>
-      <c r="AC337" s="897" t="n"/>
-      <c r="AD337" s="905" t="n"/>
-      <c r="AE337" s="905" t="n"/>
-      <c r="AF337" s="905" t="n"/>
-      <c r="AG337" s="905" t="n"/>
-      <c r="AH337" s="905" t="n"/>
+      <c r="Z337" s="907" t="n"/>
+      <c r="AA337" s="907" t="n"/>
+      <c r="AB337" s="900" t="n"/>
+      <c r="AC337" s="899" t="n"/>
+      <c r="AD337" s="907" t="n"/>
+      <c r="AE337" s="907" t="n"/>
+      <c r="AF337" s="907" t="n"/>
+      <c r="AG337" s="907" t="n"/>
+      <c r="AH337" s="907" t="n"/>
       <c r="AI337" s="4" t="n"/>
     </row>
     <row r="338" ht="15.75" customHeight="1" s="757">
@@ -32285,34 +32315,34 @@
       <c r="D338" s="756" t="n"/>
       <c r="E338" s="756" t="n"/>
       <c r="F338" s="756" t="n"/>
-      <c r="G338" s="897" t="n"/>
-      <c r="H338" s="897" t="n"/>
-      <c r="I338" s="898" t="n"/>
-      <c r="J338" s="898" t="n"/>
-      <c r="K338" s="898" t="n"/>
+      <c r="G338" s="899" t="n"/>
+      <c r="H338" s="899" t="n"/>
+      <c r="I338" s="900" t="n"/>
+      <c r="J338" s="900" t="n"/>
+      <c r="K338" s="900" t="n"/>
       <c r="L338" s="756" t="n"/>
       <c r="M338" s="756" t="n"/>
-      <c r="N338" s="897" t="n"/>
-      <c r="O338" s="897" t="n"/>
+      <c r="N338" s="899" t="n"/>
+      <c r="O338" s="899" t="n"/>
       <c r="P338" s="756" t="n"/>
       <c r="Q338" s="756" t="n"/>
       <c r="R338" s="756" t="n"/>
       <c r="S338" s="756" t="n"/>
       <c r="T338" s="756" t="n"/>
-      <c r="U338" s="897" t="n"/>
-      <c r="V338" s="897" t="n"/>
+      <c r="U338" s="899" t="n"/>
+      <c r="V338" s="899" t="n"/>
       <c r="W338" s="756" t="n"/>
       <c r="X338" s="756" t="n"/>
       <c r="Y338" s="756" t="n"/>
-      <c r="Z338" s="905" t="n"/>
-      <c r="AA338" s="905" t="n"/>
-      <c r="AB338" s="898" t="n"/>
-      <c r="AC338" s="897" t="n"/>
-      <c r="AD338" s="905" t="n"/>
-      <c r="AE338" s="905" t="n"/>
-      <c r="AF338" s="905" t="n"/>
-      <c r="AG338" s="905" t="n"/>
-      <c r="AH338" s="905" t="n"/>
+      <c r="Z338" s="907" t="n"/>
+      <c r="AA338" s="907" t="n"/>
+      <c r="AB338" s="900" t="n"/>
+      <c r="AC338" s="899" t="n"/>
+      <c r="AD338" s="907" t="n"/>
+      <c r="AE338" s="907" t="n"/>
+      <c r="AF338" s="907" t="n"/>
+      <c r="AG338" s="907" t="n"/>
+      <c r="AH338" s="907" t="n"/>
     </row>
     <row r="339" ht="16.5" customHeight="1" s="757">
       <c r="A339" s="14" t="inlineStr">
@@ -32325,34 +32355,34 @@
       <c r="D339" s="783" t="n"/>
       <c r="E339" s="778" t="n"/>
       <c r="F339" s="778" t="n"/>
-      <c r="G339" s="899" t="n"/>
-      <c r="H339" s="899" t="n"/>
-      <c r="I339" s="900" t="n"/>
-      <c r="J339" s="900" t="n"/>
-      <c r="K339" s="900" t="n"/>
+      <c r="G339" s="901" t="n"/>
+      <c r="H339" s="901" t="n"/>
+      <c r="I339" s="902" t="n"/>
+      <c r="J339" s="902" t="n"/>
+      <c r="K339" s="902" t="n"/>
       <c r="L339" s="778" t="n"/>
       <c r="M339" s="778" t="n"/>
-      <c r="N339" s="899" t="n"/>
-      <c r="O339" s="899" t="n"/>
+      <c r="N339" s="901" t="n"/>
+      <c r="O339" s="901" t="n"/>
       <c r="P339" s="778" t="n"/>
       <c r="Q339" s="778" t="n"/>
       <c r="R339" s="778" t="n"/>
       <c r="S339" s="778" t="n"/>
       <c r="T339" s="778" t="n"/>
-      <c r="U339" s="899" t="n"/>
-      <c r="V339" s="899" t="n"/>
+      <c r="U339" s="901" t="n"/>
+      <c r="V339" s="901" t="n"/>
       <c r="W339" s="778" t="n"/>
       <c r="X339" s="778" t="n"/>
       <c r="Y339" s="778" t="n"/>
-      <c r="Z339" s="906" t="n"/>
-      <c r="AA339" s="906" t="n"/>
-      <c r="AB339" s="900" t="n"/>
-      <c r="AC339" s="899" t="n"/>
-      <c r="AD339" s="906" t="n"/>
-      <c r="AE339" s="906" t="n"/>
-      <c r="AF339" s="906" t="n"/>
-      <c r="AG339" s="906" t="n"/>
-      <c r="AH339" s="906" t="n"/>
+      <c r="Z339" s="908" t="n"/>
+      <c r="AA339" s="908" t="n"/>
+      <c r="AB339" s="902" t="n"/>
+      <c r="AC339" s="901" t="n"/>
+      <c r="AD339" s="908" t="n"/>
+      <c r="AE339" s="908" t="n"/>
+      <c r="AF339" s="908" t="n"/>
+      <c r="AG339" s="908" t="n"/>
+      <c r="AH339" s="908" t="n"/>
     </row>
     <row r="340" ht="16.5" customHeight="1" s="757">
       <c r="A340" s="10" t="inlineStr">
@@ -32365,34 +32395,34 @@
       <c r="D340" s="755" t="n"/>
       <c r="E340" s="755" t="n"/>
       <c r="F340" s="756" t="n"/>
-      <c r="G340" s="901" t="n"/>
-      <c r="H340" s="897" t="n"/>
-      <c r="I340" s="902" t="n"/>
-      <c r="J340" s="898" t="n"/>
-      <c r="K340" s="902" t="n"/>
+      <c r="G340" s="903" t="n"/>
+      <c r="H340" s="899" t="n"/>
+      <c r="I340" s="904" t="n"/>
+      <c r="J340" s="900" t="n"/>
+      <c r="K340" s="904" t="n"/>
       <c r="L340" s="756" t="n"/>
       <c r="M340" s="756" t="n"/>
-      <c r="N340" s="901" t="n"/>
-      <c r="O340" s="901" t="n"/>
+      <c r="N340" s="903" t="n"/>
+      <c r="O340" s="903" t="n"/>
       <c r="P340" s="756" t="n"/>
       <c r="Q340" s="756" t="n"/>
       <c r="R340" s="755" t="n"/>
       <c r="S340" s="756" t="n"/>
       <c r="T340" s="756" t="n"/>
-      <c r="U340" s="901" t="n"/>
-      <c r="V340" s="901" t="n"/>
+      <c r="U340" s="903" t="n"/>
+      <c r="V340" s="903" t="n"/>
       <c r="W340" s="756" t="n"/>
       <c r="X340" s="756" t="n"/>
       <c r="Y340" s="755" t="n"/>
-      <c r="Z340" s="905" t="n"/>
-      <c r="AA340" s="905" t="n"/>
-      <c r="AB340" s="902" t="n"/>
-      <c r="AC340" s="901" t="n"/>
-      <c r="AD340" s="905" t="n"/>
-      <c r="AE340" s="905" t="n"/>
-      <c r="AF340" s="907" t="n"/>
-      <c r="AG340" s="905" t="n"/>
-      <c r="AH340" s="905" t="n"/>
+      <c r="Z340" s="907" t="n"/>
+      <c r="AA340" s="907" t="n"/>
+      <c r="AB340" s="904" t="n"/>
+      <c r="AC340" s="903" t="n"/>
+      <c r="AD340" s="907" t="n"/>
+      <c r="AE340" s="907" t="n"/>
+      <c r="AF340" s="909" t="n"/>
+      <c r="AG340" s="907" t="n"/>
+      <c r="AH340" s="907" t="n"/>
     </row>
     <row r="341" ht="15.75" customHeight="1" s="757">
       <c r="A341" s="12" t="inlineStr">
@@ -32405,34 +32435,34 @@
       <c r="D341" s="756" t="n"/>
       <c r="E341" s="756" t="n"/>
       <c r="F341" s="756" t="n"/>
-      <c r="G341" s="897" t="n"/>
-      <c r="H341" s="897" t="n"/>
-      <c r="I341" s="898" t="n"/>
-      <c r="J341" s="898" t="n"/>
-      <c r="K341" s="898" t="n"/>
+      <c r="G341" s="899" t="n"/>
+      <c r="H341" s="899" t="n"/>
+      <c r="I341" s="900" t="n"/>
+      <c r="J341" s="900" t="n"/>
+      <c r="K341" s="900" t="n"/>
       <c r="L341" s="756" t="n"/>
       <c r="M341" s="756" t="n"/>
-      <c r="N341" s="897" t="n"/>
-      <c r="O341" s="897" t="n"/>
+      <c r="N341" s="899" t="n"/>
+      <c r="O341" s="899" t="n"/>
       <c r="P341" s="756" t="n"/>
       <c r="Q341" s="756" t="n"/>
       <c r="R341" s="756" t="n"/>
       <c r="S341" s="756" t="n"/>
       <c r="T341" s="756" t="n"/>
-      <c r="U341" s="897" t="n"/>
-      <c r="V341" s="897" t="n"/>
+      <c r="U341" s="899" t="n"/>
+      <c r="V341" s="899" t="n"/>
       <c r="W341" s="756" t="n"/>
       <c r="X341" s="756" t="n"/>
       <c r="Y341" s="756" t="n"/>
-      <c r="Z341" s="905" t="n"/>
-      <c r="AA341" s="905" t="n"/>
-      <c r="AB341" s="898" t="n"/>
-      <c r="AC341" s="897" t="n"/>
-      <c r="AD341" s="905" t="n"/>
-      <c r="AE341" s="905" t="n"/>
-      <c r="AF341" s="905" t="n"/>
-      <c r="AG341" s="905" t="n"/>
-      <c r="AH341" s="905" t="n"/>
+      <c r="Z341" s="907" t="n"/>
+      <c r="AA341" s="907" t="n"/>
+      <c r="AB341" s="900" t="n"/>
+      <c r="AC341" s="899" t="n"/>
+      <c r="AD341" s="907" t="n"/>
+      <c r="AE341" s="907" t="n"/>
+      <c r="AF341" s="907" t="n"/>
+      <c r="AG341" s="907" t="n"/>
+      <c r="AH341" s="907" t="n"/>
     </row>
     <row r="342" ht="15.75" customHeight="1" s="757">
       <c r="A342" s="12" t="inlineStr">
@@ -32445,34 +32475,34 @@
       <c r="D342" s="756" t="n"/>
       <c r="E342" s="756" t="n"/>
       <c r="F342" s="756" t="n"/>
-      <c r="G342" s="897" t="n"/>
-      <c r="H342" s="897" t="n"/>
-      <c r="I342" s="898" t="n"/>
-      <c r="J342" s="898" t="n"/>
-      <c r="K342" s="898" t="n"/>
+      <c r="G342" s="899" t="n"/>
+      <c r="H342" s="899" t="n"/>
+      <c r="I342" s="900" t="n"/>
+      <c r="J342" s="900" t="n"/>
+      <c r="K342" s="900" t="n"/>
       <c r="L342" s="756" t="n"/>
       <c r="M342" s="756" t="n"/>
-      <c r="N342" s="897" t="n"/>
-      <c r="O342" s="897" t="n"/>
+      <c r="N342" s="899" t="n"/>
+      <c r="O342" s="899" t="n"/>
       <c r="P342" s="756" t="n"/>
       <c r="Q342" s="756" t="n"/>
       <c r="R342" s="756" t="n"/>
       <c r="S342" s="756" t="n"/>
       <c r="T342" s="756" t="n"/>
-      <c r="U342" s="897" t="n"/>
-      <c r="V342" s="897" t="n"/>
+      <c r="U342" s="899" t="n"/>
+      <c r="V342" s="899" t="n"/>
       <c r="W342" s="756" t="n"/>
       <c r="X342" s="756" t="n"/>
       <c r="Y342" s="756" t="n"/>
-      <c r="Z342" s="905" t="n"/>
-      <c r="AA342" s="905" t="n"/>
-      <c r="AB342" s="898" t="n"/>
-      <c r="AC342" s="897" t="n"/>
-      <c r="AD342" s="905" t="n"/>
-      <c r="AE342" s="905" t="n"/>
-      <c r="AF342" s="905" t="n"/>
-      <c r="AG342" s="905" t="n"/>
-      <c r="AH342" s="905" t="n"/>
+      <c r="Z342" s="907" t="n"/>
+      <c r="AA342" s="907" t="n"/>
+      <c r="AB342" s="900" t="n"/>
+      <c r="AC342" s="899" t="n"/>
+      <c r="AD342" s="907" t="n"/>
+      <c r="AE342" s="907" t="n"/>
+      <c r="AF342" s="907" t="n"/>
+      <c r="AG342" s="907" t="n"/>
+      <c r="AH342" s="907" t="n"/>
     </row>
     <row r="343" s="757"/>
     <row r="344" s="757"/>
@@ -32566,7 +32596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="757" min="1" max="1"/>
@@ -32585,1848 +32615,1905 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="908" t="inlineStr">
+      <c r="A1" s="910" t="inlineStr">
         <is>
           <t>CRONOGRAMA 26-27 PROVISIONAL — PLANIFICACIÓ DE FORMACIONS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="909" t="inlineStr">
+      <c r="A2" s="911" t="inlineStr">
         <is>
           <t>Font: FORMACIONS_26-27_PROVISIONAL.xlsx (hores i docents) · Calendari: full 'CRONO 25-26' i CALENDARI_LABORAL_2027.xlsx · Criteri: 5-6 h/dia en dies laborables consecutius.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="910" t="inlineStr">
+      <c r="A4" s="912" t="inlineStr">
         <is>
           <t>CODI</t>
         </is>
       </c>
-      <c r="B4" s="910" t="inlineStr">
+      <c r="B4" s="912" t="inlineStr">
         <is>
           <t>NOM FORMACIÓ</t>
         </is>
       </c>
-      <c r="C4" s="910" t="inlineStr">
+      <c r="C4" s="912" t="inlineStr">
         <is>
           <t>EDICIÓ</t>
         </is>
       </c>
-      <c r="D4" s="910" t="inlineStr">
+      <c r="D4" s="912" t="inlineStr">
         <is>
           <t>DOCENT</t>
         </is>
       </c>
-      <c r="E4" s="910" t="inlineStr">
+      <c r="E4" s="912" t="inlineStr">
         <is>
           <t>AULA</t>
         </is>
       </c>
-      <c r="F4" s="910" t="inlineStr">
+      <c r="F4" s="912" t="inlineStr">
         <is>
           <t>TORN</t>
         </is>
       </c>
-      <c r="G4" s="910" t="inlineStr">
+      <c r="G4" s="912" t="inlineStr">
         <is>
           <t>HORARI</t>
         </is>
       </c>
-      <c r="H4" s="910" t="inlineStr">
+      <c r="H4" s="912" t="inlineStr">
         <is>
           <t>DATA INICI</t>
         </is>
       </c>
-      <c r="I4" s="910" t="inlineStr">
+      <c r="I4" s="912" t="inlineStr">
         <is>
           <t>DATA FINAL</t>
         </is>
       </c>
-      <c r="J4" s="910" t="inlineStr">
+      <c r="J4" s="912" t="inlineStr">
         <is>
           <t>DIES</t>
         </is>
       </c>
-      <c r="K4" s="910" t="inlineStr">
+      <c r="K4" s="912" t="inlineStr">
         <is>
           <t>HORES PREVISTES</t>
         </is>
       </c>
-      <c r="L4" s="910" t="inlineStr">
+      <c r="L4" s="912" t="inlineStr">
         <is>
           <t>HORES PROGRAMADES</t>
         </is>
       </c>
-      <c r="M4" s="910" t="inlineStr">
+      <c r="M4" s="912" t="inlineStr">
         <is>
           <t>DISTRIBUCIÓ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="911" t="inlineStr">
+      <c r="A5" s="913" t="inlineStr">
         <is>
           <t>FCOS02</t>
         </is>
       </c>
-      <c r="B5" s="912" t="inlineStr">
+      <c r="B5" s="914" t="inlineStr">
         <is>
           <t>BASIC PREVENCIO DE RISCOS LABORALS [FORMA I CONTRACTE - ATURATS]</t>
         </is>
       </c>
-      <c r="C5" s="913" t="inlineStr">
+      <c r="C5" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D5" s="913" t="inlineStr">
+      <c r="D5" s="915" t="inlineStr">
         <is>
           <t>PER ASSIGNAR</t>
         </is>
       </c>
-      <c r="E5" s="913" t="inlineStr">
+      <c r="E5" s="915" t="inlineStr">
         <is>
           <t>GOOGLE</t>
         </is>
       </c>
-      <c r="F5" s="913" t="inlineStr">
+      <c r="F5" s="915" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G5" s="912" t="inlineStr">
+      <c r="G5" s="914" t="inlineStr">
         <is>
           <t>9:00-15:00</t>
         </is>
       </c>
-      <c r="H5" s="914" t="n">
+      <c r="H5" s="916" t="n">
         <v>46314</v>
       </c>
-      <c r="I5" s="914" t="n">
+      <c r="I5" s="916" t="n">
         <v>46318</v>
       </c>
-      <c r="J5" s="913" t="n">
+      <c r="J5" s="915" t="n">
         <v>5</v>
       </c>
-      <c r="K5" s="913" t="n">
+      <c r="K5" s="915" t="n">
         <v>30</v>
       </c>
-      <c r="L5" s="913" t="n">
+      <c r="L5" s="915" t="n">
         <v>30</v>
       </c>
-      <c r="M5" s="912" t="inlineStr">
+      <c r="M5" s="914" t="inlineStr">
         <is>
           <t>5 dies × 6 h</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="915" t="inlineStr">
+      <c r="A6" s="917" t="inlineStr">
         <is>
           <t>FC01_CTRP0005_202370</t>
         </is>
       </c>
-      <c r="B6" s="912" t="inlineStr">
+      <c r="B6" s="914" t="inlineStr">
         <is>
           <t>Coaching de fortaleses</t>
         </is>
       </c>
-      <c r="C6" s="913" t="inlineStr">
+      <c r="C6" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D6" s="913" t="inlineStr">
+      <c r="D6" s="915" t="inlineStr">
         <is>
           <t>RAMON</t>
         </is>
       </c>
-      <c r="E6" s="913" t="inlineStr">
+      <c r="E6" s="915" t="inlineStr">
         <is>
           <t>FIREFOX</t>
         </is>
       </c>
-      <c r="F6" s="913" t="inlineStr">
+      <c r="F6" s="915" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G6" s="912" t="inlineStr">
+      <c r="G6" s="914" t="inlineStr">
         <is>
           <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
         </is>
       </c>
-      <c r="H6" s="914" t="n">
+      <c r="H6" s="916" t="n">
         <v>46314</v>
       </c>
-      <c r="I6" s="914" t="n">
+      <c r="I6" s="916" t="n">
         <v>46322</v>
       </c>
-      <c r="J6" s="913" t="n">
+      <c r="J6" s="915" t="n">
         <v>7</v>
       </c>
-      <c r="K6" s="913" t="n">
+      <c r="K6" s="915" t="n">
         <v>40</v>
       </c>
-      <c r="L6" s="913" t="n">
+      <c r="L6" s="915" t="n">
         <v>40</v>
       </c>
-      <c r="M6" s="912" t="inlineStr">
+      <c r="M6" s="914" t="inlineStr">
         <is>
           <t>5 dies × 6 h + 2 dies × 5 h</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="916" t="inlineStr">
+      <c r="A7" s="918" t="inlineStr">
         <is>
           <t>FC01_CTRL0040_202470</t>
         </is>
       </c>
-      <c r="B7" s="912" t="inlineStr">
+      <c r="B7" s="914" t="inlineStr">
         <is>
           <t>CTRL0040_2024_Català A1 (Català nivell inicial A1)</t>
         </is>
       </c>
-      <c r="C7" s="913" t="inlineStr">
+      <c r="C7" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D7" s="913" t="inlineStr">
+      <c r="D7" s="915" t="inlineStr">
         <is>
           <t>PER ASSIGNAR</t>
         </is>
       </c>
-      <c r="E7" s="913" t="inlineStr">
+      <c r="E7" s="915" t="inlineStr">
         <is>
           <t>COPILOT</t>
         </is>
       </c>
-      <c r="F7" s="913" t="inlineStr">
+      <c r="F7" s="915" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G7" s="912" t="inlineStr">
+      <c r="G7" s="914" t="inlineStr">
         <is>
           <t>9:00-15:00</t>
         </is>
       </c>
-      <c r="H7" s="914" t="n">
+      <c r="H7" s="916" t="n">
         <v>46314</v>
       </c>
-      <c r="I7" s="914" t="n">
+      <c r="I7" s="916" t="n">
         <v>46332</v>
       </c>
-      <c r="J7" s="913" t="n">
+      <c r="J7" s="915" t="n">
         <v>15</v>
       </c>
-      <c r="K7" s="913" t="n">
+      <c r="K7" s="915" t="n">
         <v>90</v>
       </c>
-      <c r="L7" s="913" t="n">
+      <c r="L7" s="915" t="n">
         <v>90</v>
       </c>
-      <c r="M7" s="912" t="inlineStr">
+      <c r="M7" s="914" t="inlineStr">
         <is>
           <t>15 dies × 6 h</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="917" t="inlineStr">
+      <c r="A8" s="919" t="inlineStr">
         <is>
           <t>FCOS02</t>
         </is>
       </c>
-      <c r="B8" s="912" t="inlineStr">
+      <c r="B8" s="914" t="inlineStr">
         <is>
           <t>BASIC PREVENCIO DE RISCOS LABORALS [CFCC - TREBALLADORS]</t>
         </is>
       </c>
-      <c r="C8" s="913" t="inlineStr">
+      <c r="C8" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D8" s="913" t="inlineStr">
+      <c r="D8" s="915" t="inlineStr">
         <is>
           <t>PER ASSIGNAR</t>
         </is>
       </c>
-      <c r="E8" s="913" t="inlineStr">
+      <c r="E8" s="915" t="inlineStr">
         <is>
           <t>FIREFOX</t>
         </is>
       </c>
-      <c r="F8" s="913" t="inlineStr">
+      <c r="F8" s="915" t="inlineStr">
         <is>
           <t>TARDA</t>
         </is>
       </c>
-      <c r="G8" s="912" t="inlineStr">
+      <c r="G8" s="914" t="inlineStr">
         <is>
           <t>15:00-21:00</t>
         </is>
       </c>
-      <c r="H8" s="914" t="n">
+      <c r="H8" s="916" t="n">
         <v>46314</v>
       </c>
-      <c r="I8" s="914" t="n">
+      <c r="I8" s="916" t="n">
         <v>46318</v>
       </c>
-      <c r="J8" s="913" t="n">
+      <c r="J8" s="915" t="n">
         <v>5</v>
       </c>
-      <c r="K8" s="913" t="n">
+      <c r="K8" s="915" t="n">
         <v>30</v>
       </c>
-      <c r="L8" s="913" t="n">
+      <c r="L8" s="915" t="n">
         <v>30</v>
       </c>
-      <c r="M8" s="912" t="inlineStr">
+      <c r="M8" s="914" t="inlineStr">
         <is>
           <t>5 dies × 6 h</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="918" t="inlineStr">
+      <c r="A9" s="920" t="inlineStr">
         <is>
           <t>FC01_IMPE0006_202449</t>
         </is>
       </c>
-      <c r="B9" s="912" t="inlineStr">
+      <c r="B9" s="914" t="inlineStr">
         <is>
           <t>Biomagnetisme aplicat a l'estètica</t>
         </is>
       </c>
-      <c r="C9" s="913" t="inlineStr">
+      <c r="C9" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D9" s="913" t="inlineStr">
+      <c r="D9" s="915" t="inlineStr">
         <is>
           <t>ESTHER</t>
         </is>
       </c>
-      <c r="E9" s="913" t="inlineStr">
+      <c r="E9" s="915" t="inlineStr">
         <is>
           <t>COPILOT</t>
         </is>
       </c>
-      <c r="F9" s="913" t="inlineStr">
+      <c r="F9" s="915" t="inlineStr">
         <is>
           <t>TARDA</t>
         </is>
       </c>
-      <c r="G9" s="912" t="inlineStr">
+      <c r="G9" s="914" t="inlineStr">
         <is>
           <t>15:00-21:00 (15:00-20:00 els dies de 5 h)</t>
         </is>
       </c>
-      <c r="H9" s="914" t="n">
+      <c r="H9" s="916" t="n">
         <v>46314</v>
       </c>
-      <c r="I9" s="914" t="n">
+      <c r="I9" s="916" t="n">
         <v>46316</v>
       </c>
-      <c r="J9" s="913" t="n">
+      <c r="J9" s="915" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="913" t="n">
+      <c r="K9" s="915" t="n">
         <v>16</v>
       </c>
-      <c r="L9" s="913" t="n">
+      <c r="L9" s="915" t="n">
         <v>16</v>
       </c>
-      <c r="M9" s="912" t="inlineStr">
+      <c r="M9" s="914" t="inlineStr">
         <is>
           <t>1 dies × 6 h + 2 dies × 5 h</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="919" t="inlineStr">
+      <c r="A10" s="921" t="inlineStr">
         <is>
           <t>CTRH0011</t>
         </is>
       </c>
-      <c r="B10" s="912" t="inlineStr">
+      <c r="B10" s="914" t="inlineStr">
         <is>
           <t>DRETS I DEURES LABORALS [FORMA I CONTRACTE - ATURATS]</t>
         </is>
       </c>
-      <c r="C10" s="913" t="inlineStr">
+      <c r="C10" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D10" s="913" t="inlineStr">
+      <c r="D10" s="915" t="inlineStr">
         <is>
           <t>PER ASSIGNAR</t>
         </is>
       </c>
-      <c r="E10" s="913" t="inlineStr">
+      <c r="E10" s="915" t="inlineStr">
         <is>
           <t>GOOGLE</t>
         </is>
       </c>
-      <c r="F10" s="913" t="inlineStr">
+      <c r="F10" s="915" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G10" s="912" t="inlineStr">
+      <c r="G10" s="914" t="inlineStr">
         <is>
           <t>9:00-14:00</t>
         </is>
       </c>
-      <c r="H10" s="914" t="n">
+      <c r="H10" s="916" t="n">
         <v>46321</v>
       </c>
-      <c r="I10" s="914" t="n">
+      <c r="I10" s="916" t="n">
         <v>46322</v>
       </c>
-      <c r="J10" s="913" t="n">
+      <c r="J10" s="915" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="913" t="n">
+      <c r="K10" s="915" t="n">
         <v>10</v>
       </c>
-      <c r="L10" s="913" t="n">
+      <c r="L10" s="915" t="n">
         <v>10</v>
       </c>
-      <c r="M10" s="912" t="inlineStr">
+      <c r="M10" s="914" t="inlineStr">
         <is>
           <t>2 dies × 5 h</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="920" t="inlineStr">
+      <c r="A11" s="922" t="inlineStr">
         <is>
           <t>ADGG0208</t>
         </is>
       </c>
-      <c r="B11" s="912" t="inlineStr">
+      <c r="B11" s="914" t="inlineStr">
         <is>
           <t>ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [CFCC - TREBALLADORS]</t>
         </is>
       </c>
-      <c r="C11" s="913" t="inlineStr">
+      <c r="C11" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D11" s="913" t="inlineStr">
+      <c r="D11" s="915" t="inlineStr">
         <is>
           <t>PER ASSIGNAR</t>
         </is>
       </c>
-      <c r="E11" s="913" t="inlineStr">
+      <c r="E11" s="915" t="inlineStr">
         <is>
           <t>FIREFOX</t>
         </is>
       </c>
-      <c r="F11" s="913" t="inlineStr">
+      <c r="F11" s="915" t="inlineStr">
         <is>
           <t>TARDA</t>
         </is>
       </c>
-      <c r="G11" s="912" t="inlineStr">
+      <c r="G11" s="914" t="inlineStr">
         <is>
           <t>15:00-21:00</t>
         </is>
       </c>
-      <c r="H11" s="914" t="n">
+      <c r="H11" s="916" t="n">
         <v>46321</v>
       </c>
-      <c r="I11" s="914" t="n">
+      <c r="I11" s="916" t="n">
         <v>46493</v>
       </c>
-      <c r="J11" s="913" t="n">
+      <c r="J11" s="915" t="n">
         <v>113</v>
       </c>
-      <c r="K11" s="913" t="n">
+      <c r="K11" s="915" t="n">
         <v>678</v>
       </c>
-      <c r="L11" s="913" t="n">
+      <c r="L11" s="915" t="n">
         <v>678</v>
       </c>
-      <c r="M11" s="912" t="inlineStr">
+      <c r="M11" s="914" t="inlineStr">
         <is>
           <t>113 dies × 6 h</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="921" t="inlineStr">
+      <c r="A12" s="923" t="inlineStr">
         <is>
           <t>CTRHI0015</t>
         </is>
       </c>
-      <c r="B12" s="912" t="inlineStr">
+      <c r="B12" s="914" t="inlineStr">
         <is>
           <t>IGUALTAT DE GÈNERE EN L'AMBIT LABORAL [FORMA I CONTRACTE - ATURATS]</t>
         </is>
       </c>
-      <c r="C12" s="913" t="inlineStr">
+      <c r="C12" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D12" s="913" t="inlineStr">
+      <c r="D12" s="915" t="inlineStr">
         <is>
           <t>PER ASSIGNAR</t>
         </is>
       </c>
-      <c r="E12" s="913" t="inlineStr">
+      <c r="E12" s="915" t="inlineStr">
         <is>
           <t>GOOGLE</t>
         </is>
       </c>
-      <c r="F12" s="913" t="inlineStr">
+      <c r="F12" s="915" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G12" s="912" t="inlineStr">
+      <c r="G12" s="914" t="inlineStr">
         <is>
           <t>9:00-14:00</t>
         </is>
       </c>
-      <c r="H12" s="914" t="n">
+      <c r="H12" s="916" t="n">
         <v>46323</v>
       </c>
-      <c r="I12" s="914" t="n">
+      <c r="I12" s="916" t="n">
         <v>46324</v>
       </c>
-      <c r="J12" s="913" t="n">
+      <c r="J12" s="915" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="913" t="n">
+      <c r="K12" s="915" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="913" t="n">
+      <c r="L12" s="915" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="912" t="inlineStr">
+      <c r="M12" s="914" t="inlineStr">
         <is>
           <t>2 dies × 5 h</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="922" t="inlineStr">
+      <c r="A13" s="924" t="inlineStr">
+        <is>
+          <t>FCOI25</t>
+        </is>
+      </c>
+      <c r="B13" s="914" t="inlineStr">
+        <is>
+          <t>ACTIC. Seguretat i civisme en l'entorn digital – nivell intermedi [FORMA I CONTRACTE - ATURATS]</t>
+        </is>
+      </c>
+      <c r="C13" s="915" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D13" s="915" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E13" s="915" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F13" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G13" s="914" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H13" s="916" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I13" s="916" t="n">
+        <v>46335</v>
+      </c>
+      <c r="J13" s="915" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="L13" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="M13" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="925" t="inlineStr">
+        <is>
+          <t>FC01_FCOI18_202271</t>
+        </is>
+      </c>
+      <c r="B14" s="914" t="inlineStr">
+        <is>
+          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell bàsic)</t>
+        </is>
+      </c>
+      <c r="C14" s="915" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D14" s="915" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E14" s="915" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F14" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G14" s="914" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H14" s="916" t="n">
+        <v>46328</v>
+      </c>
+      <c r="I14" s="916" t="n">
+        <v>46336</v>
+      </c>
+      <c r="J14" s="915" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="L14" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="M14" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="926" t="inlineStr">
+        <is>
+          <t>FC01_COMM0009_202370</t>
+        </is>
+      </c>
+      <c r="B15" s="914" t="inlineStr">
+        <is>
+          <t>Atenció al client</t>
+        </is>
+      </c>
+      <c r="C15" s="915" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D15" s="915" t="inlineStr">
+        <is>
+          <t>TANIA/?</t>
+        </is>
+      </c>
+      <c r="E15" s="915" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F15" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G15" s="914" t="inlineStr">
+        <is>
+          <t>9:00-15:00</t>
+        </is>
+      </c>
+      <c r="H15" s="916" t="n">
+        <v>46335</v>
+      </c>
+      <c r="I15" s="916" t="n">
+        <v>46339</v>
+      </c>
+      <c r="J15" s="915" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="915" t="n">
+        <v>30</v>
+      </c>
+      <c r="L15" s="915" t="n">
+        <v>30</v>
+      </c>
+      <c r="M15" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="927" t="inlineStr">
         <is>
           <t>ADGG0208</t>
         </is>
       </c>
-      <c r="B13" s="912" t="inlineStr">
+      <c r="B16" s="914" t="inlineStr">
         <is>
           <t>ACTIVITATS ADMINISTRATIVES EN LA RELACIO AMB EL CLIENT [FORMA I CONTRACTE - ATURATS]</t>
         </is>
       </c>
-      <c r="C13" s="913" t="inlineStr">
+      <c r="C16" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D13" s="913" t="inlineStr">
+      <c r="D16" s="915" t="inlineStr">
         <is>
           <t>PER ASSIGNAR</t>
         </is>
       </c>
-      <c r="E13" s="913" t="inlineStr">
+      <c r="E16" s="915" t="inlineStr">
         <is>
           <t>GOOGLE</t>
         </is>
       </c>
-      <c r="F13" s="913" t="inlineStr">
+      <c r="F16" s="915" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G13" s="912" t="inlineStr">
+      <c r="G16" s="914" t="inlineStr">
         <is>
           <t>9:00-15:00</t>
         </is>
       </c>
-      <c r="H13" s="914" t="n">
-        <v>46325</v>
-      </c>
-      <c r="I13" s="914" t="n">
-        <v>46499</v>
-      </c>
-      <c r="J13" s="913" t="n">
+      <c r="H16" s="916" t="n">
+        <v>46336</v>
+      </c>
+      <c r="I16" s="916" t="n">
+        <v>46510</v>
+      </c>
+      <c r="J16" s="915" t="n">
         <v>113</v>
       </c>
-      <c r="K13" s="913" t="n">
+      <c r="K16" s="915" t="n">
         <v>678</v>
       </c>
-      <c r="L13" s="913" t="n">
+      <c r="L16" s="915" t="n">
         <v>678</v>
       </c>
-      <c r="M13" s="912" t="inlineStr">
+      <c r="M16" s="914" t="inlineStr">
         <is>
           <t>113 dies × 6 h</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="923" t="inlineStr">
-        <is>
-          <t>FC01_FCOI18_202271</t>
-        </is>
-      </c>
-      <c r="B14" s="912" t="inlineStr">
-        <is>
-          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell bàsic)</t>
-        </is>
-      </c>
-      <c r="C14" s="913" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="928" t="inlineStr">
+        <is>
+          <t>FC01_SANP0011_202349</t>
+        </is>
+      </c>
+      <c r="B17" s="914" t="inlineStr">
+        <is>
+          <t>Tècniques de massatge</t>
+        </is>
+      </c>
+      <c r="C17" s="915" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="D17" s="915" t="inlineStr">
+        <is>
+          <t>ESTHER</t>
+        </is>
+      </c>
+      <c r="E17" s="915" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F17" s="915" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G17" s="914" t="inlineStr">
+        <is>
+          <t>15:00-20:00</t>
+        </is>
+      </c>
+      <c r="H17" s="916" t="n">
+        <v>46342</v>
+      </c>
+      <c r="I17" s="916" t="n">
+        <v>46345</v>
+      </c>
+      <c r="J17" s="915" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="915" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" s="915" t="n">
+        <v>20</v>
+      </c>
+      <c r="M17" s="914" t="inlineStr">
+        <is>
+          <t>4 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="929" t="inlineStr">
+        <is>
+          <t>FC01_FCOI15_202271</t>
+        </is>
+      </c>
+      <c r="B18" s="914" t="inlineStr">
+        <is>
+          <t>Creació de continguts digitals (ACTIC Nivell bàsic)</t>
+        </is>
+      </c>
+      <c r="C18" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D14" s="913" t="inlineStr">
+      <c r="D18" s="915" t="inlineStr">
         <is>
           <t>MARIA</t>
         </is>
       </c>
-      <c r="E14" s="913" t="inlineStr">
+      <c r="E18" s="915" t="inlineStr">
         <is>
           <t>FIREFOX</t>
         </is>
       </c>
-      <c r="F14" s="913" t="inlineStr">
+      <c r="F18" s="915" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G14" s="912" t="inlineStr">
+      <c r="G18" s="914" t="inlineStr">
         <is>
           <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
         </is>
       </c>
-      <c r="H14" s="914" t="n">
-        <v>46328</v>
-      </c>
-      <c r="I14" s="914" t="n">
-        <v>46336</v>
-      </c>
-      <c r="J14" s="913" t="n">
+      <c r="H18" s="916" t="n">
+        <v>46349</v>
+      </c>
+      <c r="I18" s="916" t="n">
+        <v>46357</v>
+      </c>
+      <c r="J18" s="915" t="n">
         <v>7</v>
       </c>
-      <c r="K14" s="913" t="n">
+      <c r="K18" s="915" t="n">
         <v>40</v>
       </c>
-      <c r="L14" s="913" t="n">
+      <c r="L18" s="915" t="n">
         <v>40</v>
       </c>
-      <c r="M14" s="912" t="inlineStr">
+      <c r="M18" s="914" t="inlineStr">
         <is>
           <t>5 dies × 6 h + 2 dies × 5 h</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="924" t="inlineStr">
-        <is>
-          <t>FC01_COMM0009_202370</t>
-        </is>
-      </c>
-      <c r="B15" s="912" t="inlineStr">
-        <is>
-          <t>Atenció al client</t>
-        </is>
-      </c>
-      <c r="C15" s="913" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="930" t="inlineStr">
+        <is>
+          <t>FC01_IFCT117_202470</t>
+        </is>
+      </c>
+      <c r="B19" s="914" t="inlineStr">
+        <is>
+          <t>Introducció a la intel·ligència artificial</t>
+        </is>
+      </c>
+      <c r="C19" s="915" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="D19" s="915" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E19" s="915" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F19" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G19" s="914" t="inlineStr">
+        <is>
+          <t>9:00-14:00</t>
+        </is>
+      </c>
+      <c r="H19" s="916" t="n">
+        <v>46398</v>
+      </c>
+      <c r="I19" s="916" t="n">
+        <v>46402</v>
+      </c>
+      <c r="J19" s="915" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="915" t="n">
+        <v>25</v>
+      </c>
+      <c r="L19" s="915" t="n">
+        <v>25</v>
+      </c>
+      <c r="M19" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="931" t="inlineStr">
+        <is>
+          <t>FC01_IFCD64_202164</t>
+        </is>
+      </c>
+      <c r="B20" s="914" t="inlineStr">
+        <is>
+          <t>Gestió de Projectes d'implementació del CRM</t>
+        </is>
+      </c>
+      <c r="C20" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D15" s="913" t="inlineStr">
-        <is>
-          <t>TANIA/?</t>
-        </is>
-      </c>
-      <c r="E15" s="913" t="inlineStr">
+      <c r="D20" s="915" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E20" s="915" t="inlineStr">
         <is>
           <t>COPILOT</t>
         </is>
       </c>
-      <c r="F15" s="913" t="inlineStr">
+      <c r="F20" s="915" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G15" s="912" t="inlineStr">
+      <c r="G20" s="914" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H20" s="916" t="n">
+        <v>46398</v>
+      </c>
+      <c r="I20" s="916" t="n">
+        <v>46430</v>
+      </c>
+      <c r="J20" s="915" t="n">
+        <v>25</v>
+      </c>
+      <c r="K20" s="915" t="n">
+        <v>145</v>
+      </c>
+      <c r="L20" s="915" t="n">
+        <v>145</v>
+      </c>
+      <c r="M20" s="914" t="inlineStr">
+        <is>
+          <t>20 dies × 6 h + 5 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="932" t="inlineStr">
+        <is>
+          <t>FC01_CTRP0006_202370</t>
+        </is>
+      </c>
+      <c r="B21" s="914" t="inlineStr">
+        <is>
+          <t>Mindfulness</t>
+        </is>
+      </c>
+      <c r="C21" s="915" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D21" s="915" t="inlineStr">
+        <is>
+          <t>RAMON</t>
+        </is>
+      </c>
+      <c r="E21" s="915" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F21" s="915" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G21" s="914" t="inlineStr">
+        <is>
+          <t>15:00-21:00</t>
+        </is>
+      </c>
+      <c r="H21" s="916" t="n">
+        <v>46398</v>
+      </c>
+      <c r="I21" s="916" t="n">
+        <v>46402</v>
+      </c>
+      <c r="J21" s="915" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="915" t="n">
+        <v>30</v>
+      </c>
+      <c r="L21" s="915" t="n">
+        <v>30</v>
+      </c>
+      <c r="M21" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="933" t="inlineStr">
+        <is>
+          <t>FC01_SEAD0227_202370</t>
+        </is>
+      </c>
+      <c r="B22" s="914" t="inlineStr">
+        <is>
+          <t>Tècniques de relaxació</t>
+        </is>
+      </c>
+      <c r="C22" s="915" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D22" s="915" t="inlineStr">
+        <is>
+          <t>ESTHER</t>
+        </is>
+      </c>
+      <c r="E22" s="915" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F22" s="915" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G22" s="914" t="inlineStr">
+        <is>
+          <t>15:00-20:00</t>
+        </is>
+      </c>
+      <c r="H22" s="916" t="n">
+        <v>46405</v>
+      </c>
+      <c r="I22" s="916" t="n">
+        <v>46408</v>
+      </c>
+      <c r="J22" s="915" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" s="915" t="n">
+        <v>20</v>
+      </c>
+      <c r="L22" s="915" t="n">
+        <v>20</v>
+      </c>
+      <c r="M22" s="914" t="inlineStr">
+        <is>
+          <t>4 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="934" t="inlineStr">
+        <is>
+          <t>FC01_CTRL0041_202470</t>
+        </is>
+      </c>
+      <c r="B23" s="914" t="inlineStr">
+        <is>
+          <t>CTRL0041_2024_Català A2.1 (Català bàsic 1 )</t>
+        </is>
+      </c>
+      <c r="C23" s="915" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D23" s="915" t="inlineStr">
+        <is>
+          <t>PER ASSIGNAR</t>
+        </is>
+      </c>
+      <c r="E23" s="915" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F23" s="915" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G23" s="914" t="inlineStr">
+        <is>
+          <t>15:00-21:00 (15:00-20:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H23" s="916" t="n">
+        <v>46405</v>
+      </c>
+      <c r="I23" s="916" t="n">
+        <v>46414</v>
+      </c>
+      <c r="J23" s="915" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" s="915" t="n">
+        <v>45</v>
+      </c>
+      <c r="L23" s="915" t="n">
+        <v>45</v>
+      </c>
+      <c r="M23" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 3 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="935" t="inlineStr">
+        <is>
+          <t>FC01_FCOI19_202271</t>
+        </is>
+      </c>
+      <c r="B24" s="914" t="inlineStr">
+        <is>
+          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi)</t>
+        </is>
+      </c>
+      <c r="C24" s="915" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="D24" s="915" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E24" s="915" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F24" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G24" s="914" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H24" s="916" t="n">
+        <v>46419</v>
+      </c>
+      <c r="I24" s="916" t="n">
+        <v>46427</v>
+      </c>
+      <c r="J24" s="915" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="L24" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="M24" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="936" t="inlineStr">
+        <is>
+          <t>B_IMPE0110_MF0063</t>
+        </is>
+      </c>
+      <c r="B25" s="914" t="inlineStr">
+        <is>
+          <t>MASSATGES ESTÈTIC MANUAL I MECÀNIC</t>
+        </is>
+      </c>
+      <c r="C25" s="915" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D25" s="915" t="inlineStr">
+        <is>
+          <t>LEIRE</t>
+        </is>
+      </c>
+      <c r="E25" s="915" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F25" s="915" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G25" s="914" t="inlineStr">
+        <is>
+          <t>15:00-21:00 (15:00-20:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H25" s="916" t="n">
+        <v>46419</v>
+      </c>
+      <c r="I25" s="916" t="n">
+        <v>46454</v>
+      </c>
+      <c r="J25" s="915" t="n">
+        <v>26</v>
+      </c>
+      <c r="K25" s="915" t="n">
+        <v>152</v>
+      </c>
+      <c r="L25" s="915" t="n">
+        <v>152</v>
+      </c>
+      <c r="M25" s="914" t="inlineStr">
+        <is>
+          <t>22 dies × 6 h + 4 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="937" t="inlineStr">
+        <is>
+          <t>FC01_CTRP0037_202670</t>
+        </is>
+      </c>
+      <c r="B26" s="914" t="inlineStr">
+        <is>
+          <t>Coaching de fortaleses. Nivell II</t>
+        </is>
+      </c>
+      <c r="C26" s="915" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D26" s="915" t="inlineStr">
+        <is>
+          <t>RAMON</t>
+        </is>
+      </c>
+      <c r="E26" s="915" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F26" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G26" s="914" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H26" s="916" t="n">
+        <v>46433</v>
+      </c>
+      <c r="I26" s="916" t="n">
+        <v>46441</v>
+      </c>
+      <c r="J26" s="915" t="n">
+        <v>7</v>
+      </c>
+      <c r="K26" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="L26" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="M26" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="938" t="inlineStr">
+        <is>
+          <t>FC01_FCOI16_202271</t>
+        </is>
+      </c>
+      <c r="B27" s="914" t="inlineStr">
+        <is>
+          <t>Creació de continguts digitals i programació (ACTIC Nivell intermedi)</t>
+        </is>
+      </c>
+      <c r="C27" s="915" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="D27" s="915" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E27" s="915" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F27" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G27" s="914" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H27" s="916" t="n">
+        <v>46440</v>
+      </c>
+      <c r="I27" s="916" t="n">
+        <v>46448</v>
+      </c>
+      <c r="J27" s="915" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="L27" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="M27" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="928" t="inlineStr">
+        <is>
+          <t>FC01_SANP0011_202349</t>
+        </is>
+      </c>
+      <c r="B28" s="914" t="inlineStr">
+        <is>
+          <t>Tècniques de massatge</t>
+        </is>
+      </c>
+      <c r="C28" s="915" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D28" s="915" t="inlineStr">
+        <is>
+          <t>ESTHER</t>
+        </is>
+      </c>
+      <c r="E28" s="915" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F28" s="915" t="inlineStr">
+        <is>
+          <t>TARDA</t>
+        </is>
+      </c>
+      <c r="G28" s="914" t="inlineStr">
+        <is>
+          <t>15:00-20:00</t>
+        </is>
+      </c>
+      <c r="H28" s="916" t="n">
+        <v>46447</v>
+      </c>
+      <c r="I28" s="916" t="n">
+        <v>46450</v>
+      </c>
+      <c r="J28" s="915" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="915" t="n">
+        <v>20</v>
+      </c>
+      <c r="L28" s="915" t="n">
+        <v>20</v>
+      </c>
+      <c r="M28" s="914" t="inlineStr">
+        <is>
+          <t>4 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="919" t="inlineStr">
+        <is>
+          <t>B_IMPE0110_MF0790</t>
+        </is>
+      </c>
+      <c r="B29" s="914" t="inlineStr">
+        <is>
+          <t>DRENATGE LIMFÀTIC ESTÈTIC MANUAL I MECÀNIC</t>
+        </is>
+      </c>
+      <c r="C29" s="915" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D29" s="915" t="inlineStr">
+        <is>
+          <t>LEIRE</t>
+        </is>
+      </c>
+      <c r="E29" s="915" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F29" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G29" s="914" t="inlineStr">
         <is>
           <t>9:00-15:00</t>
         </is>
       </c>
-      <c r="H15" s="914" t="n">
-        <v>46335</v>
-      </c>
-      <c r="I15" s="914" t="n">
-        <v>46339</v>
-      </c>
-      <c r="J15" s="913" t="n">
+      <c r="H29" s="916" t="n">
+        <v>46455</v>
+      </c>
+      <c r="I29" s="916" t="n">
+        <v>46483</v>
+      </c>
+      <c r="J29" s="915" t="n">
+        <v>19</v>
+      </c>
+      <c r="K29" s="915" t="n">
+        <v>114</v>
+      </c>
+      <c r="L29" s="915" t="n">
+        <v>114</v>
+      </c>
+      <c r="M29" s="914" t="inlineStr">
+        <is>
+          <t>19 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="935" t="inlineStr">
+        <is>
+          <t>FC01_FCOI19_202271</t>
+        </is>
+      </c>
+      <c r="B30" s="914" t="inlineStr">
+        <is>
+          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi)</t>
+        </is>
+      </c>
+      <c r="C30" s="915" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D30" s="915" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E30" s="915" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F30" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G30" s="914" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H30" s="916" t="n">
+        <v>46461</v>
+      </c>
+      <c r="I30" s="916" t="n">
+        <v>46469</v>
+      </c>
+      <c r="J30" s="915" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="L30" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="M30" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="922" t="inlineStr">
+        <is>
+          <t>B_IMPE110_MF0791</t>
+        </is>
+      </c>
+      <c r="B31" s="914" t="inlineStr">
+        <is>
+          <t>MASSATGES ESTÈTICS AMB TÈCNIQUES PER PRESSIÓ</t>
+        </is>
+      </c>
+      <c r="C31" s="915" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D31" s="915" t="inlineStr">
+        <is>
+          <t>LEIRE</t>
+        </is>
+      </c>
+      <c r="E31" s="915" t="inlineStr">
+        <is>
+          <t>COPILOT</t>
+        </is>
+      </c>
+      <c r="F31" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G31" s="914" t="inlineStr">
+        <is>
+          <t>9:00-15:00</t>
+        </is>
+      </c>
+      <c r="H31" s="916" t="n">
+        <v>46484</v>
+      </c>
+      <c r="I31" s="916" t="n">
+        <v>46510</v>
+      </c>
+      <c r="J31" s="915" t="n">
+        <v>19</v>
+      </c>
+      <c r="K31" s="915" t="n">
+        <v>114</v>
+      </c>
+      <c r="L31" s="915" t="n">
+        <v>114</v>
+      </c>
+      <c r="M31" s="914" t="inlineStr">
+        <is>
+          <t>19 dies × 6 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="938" t="inlineStr">
+        <is>
+          <t>FC01_FCOI16_202271</t>
+        </is>
+      </c>
+      <c r="B32" s="914" t="inlineStr">
+        <is>
+          <t>Creació de continguts digitals i programació (ACTIC Nivell intermedi)</t>
+        </is>
+      </c>
+      <c r="C32" s="915" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D32" s="915" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E32" s="915" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F32" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G32" s="914" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H32" s="916" t="n">
+        <v>46489</v>
+      </c>
+      <c r="I32" s="916" t="n">
+        <v>46497</v>
+      </c>
+      <c r="J32" s="915" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="L32" s="915" t="n">
+        <v>40</v>
+      </c>
+      <c r="M32" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="930" t="inlineStr">
+        <is>
+          <t>FC01_IFCT117_202470</t>
+        </is>
+      </c>
+      <c r="B33" s="914" t="inlineStr">
+        <is>
+          <t>Introducció a la intel·ligència artificial</t>
+        </is>
+      </c>
+      <c r="C33" s="915" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D33" s="915" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="E33" s="915" t="inlineStr">
+        <is>
+          <t>FIREFOX</t>
+        </is>
+      </c>
+      <c r="F33" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G33" s="914" t="inlineStr">
+        <is>
+          <t>9:00-14:00</t>
+        </is>
+      </c>
+      <c r="H33" s="916" t="n">
+        <v>46510</v>
+      </c>
+      <c r="I33" s="916" t="n">
+        <v>46514</v>
+      </c>
+      <c r="J33" s="915" t="n">
         <v>5</v>
       </c>
-      <c r="K15" s="913" t="n">
-        <v>30</v>
-      </c>
-      <c r="L15" s="913" t="n">
-        <v>30</v>
-      </c>
-      <c r="M15" s="912" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="925" t="inlineStr">
-        <is>
-          <t>FC01_SANP0011_202349</t>
-        </is>
-      </c>
-      <c r="B16" s="912" t="inlineStr">
-        <is>
-          <t>Tècniques de massatge</t>
-        </is>
-      </c>
-      <c r="C16" s="913" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="D16" s="913" t="inlineStr">
-        <is>
-          <t>ESTHER</t>
-        </is>
-      </c>
-      <c r="E16" s="913" t="inlineStr">
-        <is>
-          <t>COPILOT</t>
-        </is>
-      </c>
-      <c r="F16" s="913" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G16" s="912" t="inlineStr">
-        <is>
-          <t>15:00-20:00</t>
-        </is>
-      </c>
-      <c r="H16" s="914" t="n">
-        <v>46342</v>
-      </c>
-      <c r="I16" s="914" t="n">
-        <v>46345</v>
-      </c>
-      <c r="J16" s="913" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" s="913" t="n">
-        <v>20</v>
-      </c>
-      <c r="L16" s="913" t="n">
-        <v>20</v>
-      </c>
-      <c r="M16" s="912" t="inlineStr">
-        <is>
-          <t>4 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="926" t="inlineStr">
-        <is>
-          <t>FC01_FCOI15_202271</t>
-        </is>
-      </c>
-      <c r="B17" s="912" t="inlineStr">
-        <is>
-          <t>Creació de continguts digitals (ACTIC Nivell bàsic)</t>
-        </is>
-      </c>
-      <c r="C17" s="913" t="inlineStr">
+      <c r="K33" s="915" t="n">
+        <v>25</v>
+      </c>
+      <c r="L33" s="915" t="n">
+        <v>25</v>
+      </c>
+      <c r="M33" s="914" t="inlineStr">
+        <is>
+          <t>5 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="913" t="inlineStr">
+        <is>
+          <t>B_IMPE0110_MF0792</t>
+        </is>
+      </c>
+      <c r="B34" s="914" t="inlineStr">
+        <is>
+          <t>TÈCNIQUES SENSORIALS ESTÈTIQUES</t>
+        </is>
+      </c>
+      <c r="C34" s="915" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="D17" s="913" t="inlineStr">
+      <c r="D34" s="915" t="inlineStr">
+        <is>
+          <t>LEIRE</t>
+        </is>
+      </c>
+      <c r="E34" s="915" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F34" s="915" t="inlineStr">
+        <is>
+          <t>MATÍ</t>
+        </is>
+      </c>
+      <c r="G34" s="914" t="inlineStr">
+        <is>
+          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
+        </is>
+      </c>
+      <c r="H34" s="916" t="n">
+        <v>46511</v>
+      </c>
+      <c r="I34" s="916" t="n">
+        <v>46527</v>
+      </c>
+      <c r="J34" s="915" t="n">
+        <v>13</v>
+      </c>
+      <c r="K34" s="915" t="n">
+        <v>76</v>
+      </c>
+      <c r="L34" s="915" t="n">
+        <v>76</v>
+      </c>
+      <c r="M34" s="914" t="inlineStr">
+        <is>
+          <t>11 dies × 6 h + 2 dies × 5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="939" t="inlineStr">
+        <is>
+          <t>FC01_FCOI20_202271</t>
+        </is>
+      </c>
+      <c r="B35" s="914" t="inlineStr">
+        <is>
+          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell avançat)</t>
+        </is>
+      </c>
+      <c r="C35" s="915" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D35" s="915" t="inlineStr">
         <is>
           <t>MARIA</t>
         </is>
       </c>
-      <c r="E17" s="913" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F17" s="913" t="inlineStr">
+      <c r="E35" s="915" t="inlineStr">
+        <is>
+          <t>GOOGLE</t>
+        </is>
+      </c>
+      <c r="F35" s="915" t="inlineStr">
         <is>
           <t>MATÍ</t>
         </is>
       </c>
-      <c r="G17" s="912" t="inlineStr">
+      <c r="G35" s="914" t="inlineStr">
         <is>
           <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
         </is>
       </c>
-      <c r="H17" s="914" t="n">
-        <v>46349</v>
-      </c>
-      <c r="I17" s="914" t="n">
-        <v>46357</v>
-      </c>
-      <c r="J17" s="913" t="n">
+      <c r="H35" s="916" t="n">
+        <v>46531</v>
+      </c>
+      <c r="I35" s="916" t="n">
+        <v>46539</v>
+      </c>
+      <c r="J35" s="915" t="n">
         <v>7</v>
       </c>
-      <c r="K17" s="913" t="n">
+      <c r="K35" s="915" t="n">
         <v>40</v>
       </c>
-      <c r="L17" s="913" t="n">
+      <c r="L35" s="915" t="n">
         <v>40</v>
       </c>
-      <c r="M17" s="912" t="inlineStr">
+      <c r="M35" s="914" t="inlineStr">
         <is>
           <t>5 dies × 6 h + 2 dies × 5 h</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="927" t="inlineStr">
-        <is>
-          <t>FC01_IFCT117_202470</t>
-        </is>
-      </c>
-      <c r="B18" s="912" t="inlineStr">
-        <is>
-          <t>Introducció a la intel·ligència artificial</t>
-        </is>
-      </c>
-      <c r="C18" s="913" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="D18" s="913" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E18" s="913" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F18" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G18" s="912" t="inlineStr">
-        <is>
-          <t>9:00-14:00</t>
-        </is>
-      </c>
-      <c r="H18" s="914" t="n">
-        <v>46398</v>
-      </c>
-      <c r="I18" s="914" t="n">
-        <v>46402</v>
-      </c>
-      <c r="J18" s="913" t="n">
-        <v>5</v>
-      </c>
-      <c r="K18" s="913" t="n">
-        <v>25</v>
-      </c>
-      <c r="L18" s="913" t="n">
-        <v>25</v>
-      </c>
-      <c r="M18" s="912" t="inlineStr">
-        <is>
-          <t>5 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="928" t="inlineStr">
-        <is>
-          <t>FC01_IFCD64_202164</t>
-        </is>
-      </c>
-      <c r="B19" s="912" t="inlineStr">
-        <is>
-          <t>Gestió de Projectes d'implementació del CRM</t>
-        </is>
-      </c>
-      <c r="C19" s="913" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D19" s="913" t="inlineStr">
-        <is>
-          <t>PER ASSIGNAR</t>
-        </is>
-      </c>
-      <c r="E19" s="913" t="inlineStr">
-        <is>
-          <t>COPILOT</t>
-        </is>
-      </c>
-      <c r="F19" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G19" s="912" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H19" s="914" t="n">
-        <v>46398</v>
-      </c>
-      <c r="I19" s="914" t="n">
-        <v>46430</v>
-      </c>
-      <c r="J19" s="913" t="n">
-        <v>25</v>
-      </c>
-      <c r="K19" s="913" t="n">
-        <v>145</v>
-      </c>
-      <c r="L19" s="913" t="n">
-        <v>145</v>
-      </c>
-      <c r="M19" s="912" t="inlineStr">
-        <is>
-          <t>20 dies × 6 h + 5 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="929" t="inlineStr">
-        <is>
-          <t>FC01_CTRP0006_202370</t>
-        </is>
-      </c>
-      <c r="B20" s="912" t="inlineStr">
-        <is>
-          <t>Mindfulness</t>
-        </is>
-      </c>
-      <c r="C20" s="913" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D20" s="913" t="inlineStr">
-        <is>
-          <t>RAMON</t>
-        </is>
-      </c>
-      <c r="E20" s="913" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F20" s="913" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G20" s="912" t="inlineStr">
-        <is>
-          <t>15:00-21:00</t>
-        </is>
-      </c>
-      <c r="H20" s="914" t="n">
-        <v>46398</v>
-      </c>
-      <c r="I20" s="914" t="n">
-        <v>46402</v>
-      </c>
-      <c r="J20" s="913" t="n">
-        <v>5</v>
-      </c>
-      <c r="K20" s="913" t="n">
-        <v>30</v>
-      </c>
-      <c r="L20" s="913" t="n">
-        <v>30</v>
-      </c>
-      <c r="M20" s="912" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="930" t="inlineStr">
-        <is>
-          <t>FC01_SEAD0227_202370</t>
-        </is>
-      </c>
-      <c r="B21" s="912" t="inlineStr">
-        <is>
-          <t>Tècniques de relaxació</t>
-        </is>
-      </c>
-      <c r="C21" s="913" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D21" s="913" t="inlineStr">
-        <is>
-          <t>ESTHER</t>
-        </is>
-      </c>
-      <c r="E21" s="913" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F21" s="913" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G21" s="912" t="inlineStr">
-        <is>
-          <t>15:00-20:00</t>
-        </is>
-      </c>
-      <c r="H21" s="914" t="n">
-        <v>46405</v>
-      </c>
-      <c r="I21" s="914" t="n">
-        <v>46408</v>
-      </c>
-      <c r="J21" s="913" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" s="913" t="n">
-        <v>20</v>
-      </c>
-      <c r="L21" s="913" t="n">
-        <v>20</v>
-      </c>
-      <c r="M21" s="912" t="inlineStr">
-        <is>
-          <t>4 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="931" t="inlineStr">
-        <is>
-          <t>FC01_CTRL0041_202470</t>
-        </is>
-      </c>
-      <c r="B22" s="912" t="inlineStr">
-        <is>
-          <t>CTRL0041_2024_Català A2.1 (Català bàsic 1 )</t>
-        </is>
-      </c>
-      <c r="C22" s="913" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D22" s="913" t="inlineStr">
-        <is>
-          <t>PER ASSIGNAR</t>
-        </is>
-      </c>
-      <c r="E22" s="913" t="inlineStr">
-        <is>
-          <t>COPILOT</t>
-        </is>
-      </c>
-      <c r="F22" s="913" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G22" s="912" t="inlineStr">
-        <is>
-          <t>15:00-21:00 (15:00-20:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H22" s="914" t="n">
-        <v>46405</v>
-      </c>
-      <c r="I22" s="914" t="n">
-        <v>46414</v>
-      </c>
-      <c r="J22" s="913" t="n">
-        <v>8</v>
-      </c>
-      <c r="K22" s="913" t="n">
-        <v>45</v>
-      </c>
-      <c r="L22" s="913" t="n">
-        <v>45</v>
-      </c>
-      <c r="M22" s="912" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 3 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="932" t="inlineStr">
-        <is>
-          <t>FC01_FCOI19_202271</t>
-        </is>
-      </c>
-      <c r="B23" s="912" t="inlineStr">
-        <is>
-          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi)</t>
-        </is>
-      </c>
-      <c r="C23" s="913" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="D23" s="913" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E23" s="913" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F23" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G23" s="912" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H23" s="914" t="n">
-        <v>46419</v>
-      </c>
-      <c r="I23" s="914" t="n">
-        <v>46427</v>
-      </c>
-      <c r="J23" s="913" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="L23" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="M23" s="912" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="933" t="inlineStr">
-        <is>
-          <t>B_IMPE0110_MF0063</t>
-        </is>
-      </c>
-      <c r="B24" s="912" t="inlineStr">
-        <is>
-          <t>MASSATGES ESTÈTIC MANUAL I MECÀNIC</t>
-        </is>
-      </c>
-      <c r="C24" s="913" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D24" s="913" t="inlineStr">
-        <is>
-          <t>LEIRE</t>
-        </is>
-      </c>
-      <c r="E24" s="913" t="inlineStr">
-        <is>
-          <t>COPILOT</t>
-        </is>
-      </c>
-      <c r="F24" s="913" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G24" s="912" t="inlineStr">
-        <is>
-          <t>15:00-21:00 (15:00-20:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H24" s="914" t="n">
-        <v>46419</v>
-      </c>
-      <c r="I24" s="914" t="n">
-        <v>46454</v>
-      </c>
-      <c r="J24" s="913" t="n">
-        <v>26</v>
-      </c>
-      <c r="K24" s="913" t="n">
-        <v>152</v>
-      </c>
-      <c r="L24" s="913" t="n">
-        <v>152</v>
-      </c>
-      <c r="M24" s="912" t="inlineStr">
-        <is>
-          <t>22 dies × 6 h + 4 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="934" t="inlineStr">
-        <is>
-          <t>FC01_CTRP0037_202670</t>
-        </is>
-      </c>
-      <c r="B25" s="912" t="inlineStr">
-        <is>
-          <t>Coaching de fortaleses. Nivell II</t>
-        </is>
-      </c>
-      <c r="C25" s="913" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D25" s="913" t="inlineStr">
-        <is>
-          <t>RAMON</t>
-        </is>
-      </c>
-      <c r="E25" s="913" t="inlineStr">
-        <is>
-          <t>COPILOT</t>
-        </is>
-      </c>
-      <c r="F25" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G25" s="912" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H25" s="914" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I25" s="914" t="n">
-        <v>46441</v>
-      </c>
-      <c r="J25" s="913" t="n">
-        <v>7</v>
-      </c>
-      <c r="K25" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="L25" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="M25" s="912" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="935" t="inlineStr">
-        <is>
-          <t>FC01_FCOI16_202271</t>
-        </is>
-      </c>
-      <c r="B26" s="912" t="inlineStr">
-        <is>
-          <t>Creació de continguts digitals i programació (ACTIC Nivell intermedi)</t>
-        </is>
-      </c>
-      <c r="C26" s="913" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="D26" s="913" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E26" s="913" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F26" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G26" s="912" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H26" s="914" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I26" s="914" t="n">
-        <v>46448</v>
-      </c>
-      <c r="J26" s="913" t="n">
-        <v>7</v>
-      </c>
-      <c r="K26" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="L26" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="M26" s="912" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="925" t="inlineStr">
-        <is>
-          <t>FC01_SANP0011_202349</t>
-        </is>
-      </c>
-      <c r="B27" s="912" t="inlineStr">
-        <is>
-          <t>Tècniques de massatge</t>
-        </is>
-      </c>
-      <c r="C27" s="913" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="D27" s="913" t="inlineStr">
-        <is>
-          <t>ESTHER</t>
-        </is>
-      </c>
-      <c r="E27" s="913" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F27" s="913" t="inlineStr">
-        <is>
-          <t>TARDA</t>
-        </is>
-      </c>
-      <c r="G27" s="912" t="inlineStr">
-        <is>
-          <t>15:00-20:00</t>
-        </is>
-      </c>
-      <c r="H27" s="914" t="n">
-        <v>46447</v>
-      </c>
-      <c r="I27" s="914" t="n">
-        <v>46450</v>
-      </c>
-      <c r="J27" s="913" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" s="913" t="n">
-        <v>20</v>
-      </c>
-      <c r="L27" s="913" t="n">
-        <v>20</v>
-      </c>
-      <c r="M27" s="912" t="inlineStr">
-        <is>
-          <t>4 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="936" t="inlineStr">
-        <is>
-          <t>B_IMPE0110_MF0790</t>
-        </is>
-      </c>
-      <c r="B28" s="912" t="inlineStr">
-        <is>
-          <t>DRENATGE LIMFÀTIC ESTÈTIC MANUAL I MECÀNIC</t>
-        </is>
-      </c>
-      <c r="C28" s="913" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D28" s="913" t="inlineStr">
-        <is>
-          <t>LEIRE</t>
-        </is>
-      </c>
-      <c r="E28" s="913" t="inlineStr">
-        <is>
-          <t>COPILOT</t>
-        </is>
-      </c>
-      <c r="F28" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G28" s="912" t="inlineStr">
-        <is>
-          <t>9:00-15:00</t>
-        </is>
-      </c>
-      <c r="H28" s="914" t="n">
-        <v>46455</v>
-      </c>
-      <c r="I28" s="914" t="n">
-        <v>46483</v>
-      </c>
-      <c r="J28" s="913" t="n">
-        <v>19</v>
-      </c>
-      <c r="K28" s="913" t="n">
-        <v>114</v>
-      </c>
-      <c r="L28" s="913" t="n">
-        <v>114</v>
-      </c>
-      <c r="M28" s="912" t="inlineStr">
-        <is>
-          <t>19 dies × 6 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="932" t="inlineStr">
-        <is>
-          <t>FC01_FCOI19_202271</t>
-        </is>
-      </c>
-      <c r="B29" s="912" t="inlineStr">
-        <is>
-          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell intermedi)</t>
-        </is>
-      </c>
-      <c r="C29" s="913" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="D29" s="913" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E29" s="913" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F29" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G29" s="912" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H29" s="914" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I29" s="914" t="n">
-        <v>46469</v>
-      </c>
-      <c r="J29" s="913" t="n">
-        <v>7</v>
-      </c>
-      <c r="K29" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="L29" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="M29" s="912" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="917" t="inlineStr">
-        <is>
-          <t>B_IMPE110_MF0791</t>
-        </is>
-      </c>
-      <c r="B30" s="912" t="inlineStr">
-        <is>
-          <t>MASSATGES ESTÈTICS AMB TÈCNIQUES PER PRESSIÓ</t>
-        </is>
-      </c>
-      <c r="C30" s="913" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D30" s="913" t="inlineStr">
-        <is>
-          <t>LEIRE</t>
-        </is>
-      </c>
-      <c r="E30" s="913" t="inlineStr">
-        <is>
-          <t>COPILOT</t>
-        </is>
-      </c>
-      <c r="F30" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G30" s="912" t="inlineStr">
-        <is>
-          <t>9:00-15:00</t>
-        </is>
-      </c>
-      <c r="H30" s="914" t="n">
-        <v>46484</v>
-      </c>
-      <c r="I30" s="914" t="n">
-        <v>46510</v>
-      </c>
-      <c r="J30" s="913" t="n">
-        <v>19</v>
-      </c>
-      <c r="K30" s="913" t="n">
-        <v>114</v>
-      </c>
-      <c r="L30" s="913" t="n">
-        <v>114</v>
-      </c>
-      <c r="M30" s="912" t="inlineStr">
-        <is>
-          <t>19 dies × 6 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="935" t="inlineStr">
-        <is>
-          <t>FC01_FCOI16_202271</t>
-        </is>
-      </c>
-      <c r="B31" s="912" t="inlineStr">
-        <is>
-          <t>Creació de continguts digitals i programació (ACTIC Nivell intermedi)</t>
-        </is>
-      </c>
-      <c r="C31" s="913" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="D31" s="913" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E31" s="913" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F31" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G31" s="912" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H31" s="914" t="n">
-        <v>46489</v>
-      </c>
-      <c r="I31" s="914" t="n">
-        <v>46497</v>
-      </c>
-      <c r="J31" s="913" t="n">
-        <v>7</v>
-      </c>
-      <c r="K31" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="L31" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="M31" s="912" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="927" t="inlineStr">
-        <is>
-          <t>FC01_IFCT117_202470</t>
-        </is>
-      </c>
-      <c r="B32" s="912" t="inlineStr">
-        <is>
-          <t>Introducció a la intel·ligència artificial</t>
-        </is>
-      </c>
-      <c r="C32" s="913" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="D32" s="913" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E32" s="913" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F32" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G32" s="912" t="inlineStr">
-        <is>
-          <t>9:00-14:00</t>
-        </is>
-      </c>
-      <c r="H32" s="914" t="n">
-        <v>46510</v>
-      </c>
-      <c r="I32" s="914" t="n">
-        <v>46514</v>
-      </c>
-      <c r="J32" s="913" t="n">
-        <v>5</v>
-      </c>
-      <c r="K32" s="913" t="n">
-        <v>25</v>
-      </c>
-      <c r="L32" s="913" t="n">
-        <v>25</v>
-      </c>
-      <c r="M32" s="912" t="inlineStr">
-        <is>
-          <t>5 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="920" t="inlineStr">
-        <is>
-          <t>B_IMPE0110_MF0792</t>
-        </is>
-      </c>
-      <c r="B33" s="912" t="inlineStr">
-        <is>
-          <t>TÈCNIQUES SENSORIALS ESTÈTIQUES</t>
-        </is>
-      </c>
-      <c r="C33" s="913" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D33" s="913" t="inlineStr">
-        <is>
-          <t>LEIRE</t>
-        </is>
-      </c>
-      <c r="E33" s="913" t="inlineStr">
-        <is>
-          <t>FIREFOX</t>
-        </is>
-      </c>
-      <c r="F33" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G33" s="912" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H33" s="914" t="n">
-        <v>46511</v>
-      </c>
-      <c r="I33" s="914" t="n">
-        <v>46527</v>
-      </c>
-      <c r="J33" s="913" t="n">
-        <v>13</v>
-      </c>
-      <c r="K33" s="913" t="n">
-        <v>76</v>
-      </c>
-      <c r="L33" s="913" t="n">
-        <v>76</v>
-      </c>
-      <c r="M33" s="912" t="inlineStr">
-        <is>
-          <t>11 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="937" t="inlineStr">
-        <is>
-          <t>FC01_FCOI20_202271</t>
-        </is>
-      </c>
-      <c r="B34" s="912" t="inlineStr">
-        <is>
-          <t>Comunicació i col·laboració amb eines digitals (ACTIC Nivell avançat)</t>
-        </is>
-      </c>
-      <c r="C34" s="913" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D34" s="913" t="inlineStr">
-        <is>
-          <t>MARIA</t>
-        </is>
-      </c>
-      <c r="E34" s="913" t="inlineStr">
-        <is>
-          <t>GOOGLE</t>
-        </is>
-      </c>
-      <c r="F34" s="913" t="inlineStr">
-        <is>
-          <t>MATÍ</t>
-        </is>
-      </c>
-      <c r="G34" s="912" t="inlineStr">
-        <is>
-          <t>9:00-15:00 (9:00-14:00 els dies de 5 h)</t>
-        </is>
-      </c>
-      <c r="H34" s="914" t="n">
-        <v>46531</v>
-      </c>
-      <c r="I34" s="914" t="n">
-        <v>46539</v>
-      </c>
-      <c r="J34" s="913" t="n">
-        <v>7</v>
-      </c>
-      <c r="K34" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="L34" s="913" t="n">
-        <v>40</v>
-      </c>
-      <c r="M34" s="912" t="inlineStr">
-        <is>
-          <t>5 dies × 6 h + 2 dies × 5 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="J35" s="938" t="inlineStr">
+    <row r="36">
+      <c r="J36" s="940" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="K35" s="938">
-        <f>SUM(K5:K34)</f>
+      <c r="K36" s="940">
+        <f>SUM(K5:K35)</f>
         <v/>
       </c>
-      <c r="L35" s="938">
-        <f>SUM(L5:L34)</f>
+      <c r="L36" s="940">
+        <f>SUM(L5:L35)</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="939" t="inlineStr">
-        <is>
-          <t>• Hores d'ADGG0208 (678), FCOS02 (30), CTRH0011 (10) i CTRHI0015 (10) facilitades per l'usuari. FCOI25 i els codis de les files 31-43 no tenen hores i no s'han programat.</t>
-        </is>
-      </c>
-    </row>
     <row r="39">
-      <c r="A39" s="939" t="inlineStr">
+      <c r="A39" s="941" t="inlineStr">
+        <is>
+          <t>• Hores d'ADGG0208 (678), FCOS02 (30), CTRH0011 (10) i CTRHI0015 (10) facilitades per l'usuari. FCOI25 (40 h) es programa dins de Forma i Contracte. Els codis de les files 31-43 no tenen hores i no s'han programat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="941" t="inlineStr">
         <is>
           <t>• MARIA: només matins (disponibilitat 'Matins lliure // Tardes: 1 formació per mes'). S'han evitat els dies en què ja fa 'IA MARIA' a GOOGLE MATINS (set.-oct. 2026).</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="939" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="941" t="inlineStr">
         <is>
           <t>• Un docent no té mai dues formacions el mateix dia. Els nivells (bàsic → intermedi → avançat, Coaching I → II, Català A1 → A2.1 i mòduls IMPE0110) es programen en ordre.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="939" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="941" t="inlineStr">
         <is>
           <t>• No s'ha tocat cap cel·la ja ocupada del cronograma ni les aules de TARRAGONA / ON LINE.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="939" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="941" t="inlineStr">
         <is>
           <t>• Setembre-desembre 2027: festius i vacances del CALENDARI_LABORAL_2027 (els festius locals 04/09 i 15/09 hi consten com 'a omplir'). S'hi afegeix el 12/10 com a festiu.</t>
         </is>
@@ -35946,13 +36033,13 @@
           <t>004-FCOV05 1A ED (5H)</t>
         </is>
       </c>
-      <c r="AP22" s="940" t="inlineStr">
+      <c r="AP22" s="942" t="inlineStr">
         <is>
           <t>019+020 FCO</t>
         </is>
       </c>
-      <c r="AQ22" s="940" t="n"/>
-      <c r="AR22" s="941" t="n"/>
+      <c r="AQ22" s="942" t="n"/>
+      <c r="AR22" s="943" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="757">
       <c r="A23" s="10" t="inlineStr">
@@ -41937,13 +42024,13 @@
           <t>004-FCOV05 1A ED (5H)</t>
         </is>
       </c>
-      <c r="AP22" s="940" t="inlineStr">
+      <c r="AP22" s="942" t="inlineStr">
         <is>
           <t>019+020 FCO</t>
         </is>
       </c>
-      <c r="AQ22" s="940" t="n"/>
-      <c r="AR22" s="941" t="n"/>
+      <c r="AQ22" s="942" t="n"/>
+      <c r="AR22" s="943" t="n"/>
       <c r="AS22" s="745" t="inlineStr">
         <is>
           <t>015- FCOI11ACTIC MITJ- FOAP(5 H)</t>

--- a/cronograma/CRONOGRAMA_26-27_PROVISIONAL.xlsx
+++ b/cronograma/CRONOGRAMA_26-27_PROVISIONAL.xlsx
@@ -29398,7 +29398,7 @@
       <c r="AG265" s="156" t="n"/>
       <c r="AH265" s="142" t="n"/>
       <c r="AI265" s="500" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="266" ht="51" customHeight="1" s="757">
@@ -32021,11 +32021,11 @@
       <c r="AG332" s="156" t="n"/>
       <c r="AH332" s="142" t="n"/>
       <c r="AI332" s="500" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK332" s="898" t="inlineStr">
         <is>
-          <t>Festius: 06/12 Dia de la Constitució (Nacional) · 07/12 Festiu local (canvi pel 15/09) · 08/12 Immaculada Concepció (Nacional) · 25/12 Nadal (Nacional) · Vacances: 23/12–31/12</t>
+          <t>Festius: 06/12 Dia de la Constitució (Nacional) · 07/12 Festiu Multimèdia · 08/12 Immaculada Concepció (Nacional) · 25/12 Nadal (Nacional) · Vacances: 24/12–31/12</t>
         </is>
       </c>
     </row>
@@ -32170,7 +32170,7 @@
       <c r="W334" s="756" t="n"/>
       <c r="X334" s="756" t="n"/>
       <c r="Y334" s="756" t="n"/>
-      <c r="Z334" s="907" t="n"/>
+      <c r="Z334" s="756" t="n"/>
       <c r="AA334" s="907" t="n"/>
       <c r="AB334" s="900" t="n"/>
       <c r="AC334" s="899" t="n"/>
@@ -32211,7 +32211,7 @@
       <c r="W335" s="756" t="n"/>
       <c r="X335" s="756" t="n"/>
       <c r="Y335" s="756" t="n"/>
-      <c r="Z335" s="907" t="n"/>
+      <c r="Z335" s="756" t="n"/>
       <c r="AA335" s="907" t="n"/>
       <c r="AB335" s="900" t="n"/>
       <c r="AC335" s="899" t="n"/>
@@ -32252,7 +32252,7 @@
       <c r="W336" s="778" t="n"/>
       <c r="X336" s="778" t="n"/>
       <c r="Y336" s="778" t="n"/>
-      <c r="Z336" s="908" t="n"/>
+      <c r="Z336" s="778" t="n"/>
       <c r="AA336" s="908" t="n"/>
       <c r="AB336" s="902" t="n"/>
       <c r="AC336" s="901" t="n"/>
@@ -32293,7 +32293,7 @@
       <c r="W337" s="756" t="n"/>
       <c r="X337" s="756" t="n"/>
       <c r="Y337" s="756" t="n"/>
-      <c r="Z337" s="907" t="n"/>
+      <c r="Z337" s="756" t="n"/>
       <c r="AA337" s="907" t="n"/>
       <c r="AB337" s="900" t="n"/>
       <c r="AC337" s="899" t="n"/>
@@ -32334,7 +32334,7 @@
       <c r="W338" s="756" t="n"/>
       <c r="X338" s="756" t="n"/>
       <c r="Y338" s="756" t="n"/>
-      <c r="Z338" s="907" t="n"/>
+      <c r="Z338" s="756" t="n"/>
       <c r="AA338" s="907" t="n"/>
       <c r="AB338" s="900" t="n"/>
       <c r="AC338" s="899" t="n"/>
@@ -32374,7 +32374,7 @@
       <c r="W339" s="778" t="n"/>
       <c r="X339" s="778" t="n"/>
       <c r="Y339" s="778" t="n"/>
-      <c r="Z339" s="908" t="n"/>
+      <c r="Z339" s="778" t="n"/>
       <c r="AA339" s="908" t="n"/>
       <c r="AB339" s="902" t="n"/>
       <c r="AC339" s="901" t="n"/>
@@ -32414,7 +32414,7 @@
       <c r="W340" s="756" t="n"/>
       <c r="X340" s="756" t="n"/>
       <c r="Y340" s="755" t="n"/>
-      <c r="Z340" s="907" t="n"/>
+      <c r="Z340" s="756" t="n"/>
       <c r="AA340" s="907" t="n"/>
       <c r="AB340" s="904" t="n"/>
       <c r="AC340" s="903" t="n"/>
@@ -32454,7 +32454,7 @@
       <c r="W341" s="756" t="n"/>
       <c r="X341" s="756" t="n"/>
       <c r="Y341" s="756" t="n"/>
-      <c r="Z341" s="907" t="n"/>
+      <c r="Z341" s="756" t="n"/>
       <c r="AA341" s="907" t="n"/>
       <c r="AB341" s="900" t="n"/>
       <c r="AC341" s="899" t="n"/>
@@ -32494,7 +32494,7 @@
       <c r="W342" s="756" t="n"/>
       <c r="X342" s="756" t="n"/>
       <c r="Y342" s="756" t="n"/>
-      <c r="Z342" s="907" t="n"/>
+      <c r="Z342" s="756" t="n"/>
       <c r="AA342" s="907" t="n"/>
       <c r="AB342" s="900" t="n"/>
       <c r="AC342" s="899" t="n"/>
@@ -34515,7 +34515,7 @@
     <row r="43">
       <c r="A43" s="941" t="inlineStr">
         <is>
-          <t>• Setembre-desembre 2027: festius i vacances del CALENDARI_LABORAL_2027 (els festius locals 04/09 i 15/09 hi consten com 'a omplir'). S'hi afegeix el 12/10 com a festiu.</t>
+          <t>• 2027: festius, vacances i dies laborables segons la graella 'Calendari 2027' del CALENDARI_LABORAL_2027 corregit (12/10 festiu; 04/09 i 15/09 laborables a canvi del 25/06 i 07/12, festius Multimèdia; vacances de Nadal 24-31/12).</t>
         </is>
       </c>
     </row>
